--- a/data/raw/Compiled Data.xlsx
+++ b/data/raw/Compiled Data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>TEM</t>
   </si>
@@ -26,6 +26,42 @@
   </si>
   <si>
     <t>NGDE</t>
+  </si>
+  <si>
+    <t>1h_avg_pct_retention</t>
+  </si>
+  <si>
+    <t>1h_se</t>
+  </si>
+  <si>
+    <t>2h_avg_pct_retention</t>
+  </si>
+  <si>
+    <t>2h_se</t>
+  </si>
+  <si>
+    <t>4h_avg_pct_retention</t>
+  </si>
+  <si>
+    <t>4h_se</t>
+  </si>
+  <si>
+    <t>8h_avg_pct_retention</t>
+  </si>
+  <si>
+    <t>8h_se</t>
+  </si>
+  <si>
+    <t>24h_avg_pct_retention</t>
+  </si>
+  <si>
+    <t>24h_se</t>
+  </si>
+  <si>
+    <t>48h_avg_pct_retention</t>
+  </si>
+  <si>
+    <t>48h_se</t>
   </si>
   <si>
     <t>Dry Strength Mean</t>
@@ -82,13 +118,7 @@
     <t>24h_avg_pct absorption</t>
   </si>
   <si>
-    <t>24h_se</t>
-  </si>
-  <si>
     <t>48h_avg_pct absorption</t>
-  </si>
-  <si>
-    <t>48h_se</t>
   </si>
   <si>
     <t>72h_avg_pct absorption</t>
@@ -107,12 +137,6 @@
   </si>
   <si>
     <t>144h_sat_se</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Duplicates, should I average the data?</t>
   </si>
 </sst>
 </file>
@@ -163,29 +187,26 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="165" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -404,11 +425,19 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="5" width="7.13"/>
-    <col customWidth="1" min="6" max="6" width="15.75"/>
-    <col customWidth="1" min="7" max="7" width="14.25"/>
-    <col customWidth="1" min="8" max="8" width="17.38"/>
-    <col customWidth="1" min="9" max="13" width="15.75"/>
-    <col customWidth="1" min="14" max="16" width="5.88"/>
+    <col customWidth="1" min="6" max="6" width="9.25"/>
+    <col customWidth="1" min="7" max="9" width="7.13"/>
+    <col customWidth="1" min="10" max="10" width="8.38"/>
+    <col customWidth="1" min="11" max="17" width="7.13"/>
+    <col customWidth="1" min="18" max="18" width="15.75"/>
+    <col customWidth="1" min="19" max="19" width="14.25"/>
+    <col customWidth="1" min="20" max="20" width="17.38"/>
+    <col customWidth="1" min="21" max="25" width="15.75"/>
+    <col customWidth="1" min="26" max="26" width="7.75"/>
+    <col customWidth="1" min="27" max="27" width="7.38"/>
+    <col customWidth="1" min="28" max="28" width="8.38"/>
+    <col customWidth="1" min="29" max="29" width="16.13"/>
+    <col customWidth="1" min="30" max="30" width="15.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -427,178 +456,245 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="AH1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AS1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="6">
         <v>8.0</v>
       </c>
       <c r="F2" s="7">
+        <v>88.55</v>
+      </c>
+      <c r="G2" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>81.3</v>
+      </c>
+      <c r="I2" s="7">
+        <v>2.38</v>
+      </c>
+      <c r="J2" s="7">
+        <v>65.85</v>
+      </c>
+      <c r="K2" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="L2" s="7">
+        <v>52.66</v>
+      </c>
+      <c r="M2" s="7">
+        <v>3.85</v>
+      </c>
+      <c r="N2" s="7">
+        <v>31.77</v>
+      </c>
+      <c r="O2" s="7">
+        <v>2.81</v>
+      </c>
+      <c r="P2" s="7">
+        <v>18.58</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>2.16</v>
+      </c>
+      <c r="R2" s="7">
         <v>53.67473304196518</v>
       </c>
-      <c r="G2" s="7">
+      <c r="S2" s="7">
         <v>1.008133169659043</v>
       </c>
-      <c r="H2" s="7">
+      <c r="T2" s="7">
         <v>53.47914177731975</v>
       </c>
-      <c r="I2" s="7">
+      <c r="U2" s="7">
         <v>0.4095397619889469</v>
       </c>
-      <c r="J2" s="7">
+      <c r="V2" s="7">
         <v>23.68</v>
       </c>
-      <c r="K2" s="7">
+      <c r="W2" s="7">
         <v>0.2</v>
       </c>
-      <c r="L2" s="7">
+      <c r="X2" s="7">
         <v>67.03</v>
       </c>
-      <c r="M2" s="7">
+      <c r="Y2" s="7">
         <v>0.57</v>
       </c>
-      <c r="N2" s="6">
+      <c r="Z2" s="6">
         <v>0.195</v>
       </c>
-      <c r="O2" s="6">
+      <c r="AA2" s="6">
         <v>0.187</v>
       </c>
-      <c r="P2" s="6">
+      <c r="AB2" s="6">
         <v>0.195</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="AC2" s="6">
         <v>0.192</v>
       </c>
-      <c r="R2" s="9">
+      <c r="AD2" s="8">
         <v>0.00266666666666667</v>
       </c>
-      <c r="S2" s="10">
+      <c r="AE2" s="9">
         <v>77.11239131971443</v>
       </c>
-      <c r="T2" s="11">
+      <c r="AF2" s="9">
         <v>0.1672602340438917</v>
       </c>
-      <c r="U2" s="11">
+      <c r="AG2" s="9">
         <v>89.4</v>
       </c>
-      <c r="V2" s="11">
+      <c r="AH2" s="9">
         <v>5.8</v>
       </c>
-      <c r="W2" s="11">
+      <c r="AI2" s="9">
         <v>113.6169427361906</v>
       </c>
-      <c r="X2" s="11">
+      <c r="AJ2" s="9">
         <v>5.271375039388817</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="AK2" s="9">
         <v>133.962308459587</v>
       </c>
-      <c r="Z2" s="11">
+      <c r="AL2" s="9">
         <v>7.105138914912204</v>
       </c>
-      <c r="AA2" s="11">
+      <c r="AM2" s="9">
         <v>168.3410695632368</v>
       </c>
-      <c r="AB2" s="11">
+      <c r="AN2" s="9">
         <v>6.502075473541932</v>
       </c>
-      <c r="AC2" s="11">
+      <c r="AO2" s="9">
         <v>185.8592084697973</v>
       </c>
-      <c r="AD2" s="11">
+      <c r="AP2" s="9">
         <v>5.312056385702611</v>
       </c>
-      <c r="AE2" s="11">
+      <c r="AQ2" s="9">
         <v>187.6648366752275</v>
       </c>
-      <c r="AF2" s="11">
+      <c r="AR2" s="9">
         <v>2.601339795350884</v>
-      </c>
-      <c r="AG2" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -606,84 +702,120 @@
         <v>0.7</v>
       </c>
       <c r="F3" s="7">
+        <v>88.15</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1.48</v>
+      </c>
+      <c r="H3" s="7">
+        <v>80.4</v>
+      </c>
+      <c r="I3" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="J3" s="7">
+        <v>63.71</v>
+      </c>
+      <c r="K3" s="7">
+        <v>2.84</v>
+      </c>
+      <c r="L3" s="7">
+        <v>51.88</v>
+      </c>
+      <c r="M3" s="7">
+        <v>2.73</v>
+      </c>
+      <c r="N3" s="7">
+        <v>33.12</v>
+      </c>
+      <c r="O3" s="7">
+        <v>2.57</v>
+      </c>
+      <c r="P3" s="7">
+        <v>21.29</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>2.46</v>
+      </c>
+      <c r="R3" s="7">
         <v>68.86371691293316</v>
       </c>
-      <c r="G3" s="7">
+      <c r="S3" s="7">
         <v>4.24316525996537</v>
       </c>
-      <c r="H3" s="7">
+      <c r="T3" s="7">
         <v>52.41070235112232</v>
       </c>
-      <c r="I3" s="7">
+      <c r="U3" s="7">
         <v>0.2585107517579094</v>
       </c>
-      <c r="J3" s="7">
+      <c r="V3" s="7">
         <v>24.25848056121774</v>
       </c>
-      <c r="K3" s="7">
+      <c r="W3" s="7">
         <v>1.187076167521593</v>
       </c>
-      <c r="L3" s="7">
+      <c r="X3" s="7">
         <v>68.07868554032801</v>
       </c>
-      <c r="M3" s="7">
+      <c r="Y3" s="7">
         <v>1.505665685169286</v>
       </c>
-      <c r="N3" s="6">
+      <c r="Z3" s="6">
         <v>0.181</v>
       </c>
-      <c r="O3" s="6">
+      <c r="AA3" s="6">
         <v>0.215</v>
       </c>
-      <c r="P3" s="6">
+      <c r="AB3" s="6">
         <v>0.189</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="AC3" s="6">
         <v>0.195</v>
       </c>
-      <c r="R3" s="9">
+      <c r="AD3" s="8">
         <v>0.0072632028788938</v>
       </c>
-      <c r="S3" s="10">
+      <c r="AE3" s="9">
         <v>63.84821587957725</v>
       </c>
-      <c r="T3" s="11">
+      <c r="AF3" s="9">
         <v>1.0150745133266</v>
       </c>
-      <c r="U3" s="11">
+      <c r="AG3" s="9">
         <v>77.1</v>
       </c>
-      <c r="V3" s="11">
+      <c r="AH3" s="9">
         <v>8.1</v>
       </c>
-      <c r="W3" s="11">
+      <c r="AI3" s="9">
         <v>103.8173093768247</v>
       </c>
-      <c r="X3" s="11">
+      <c r="AJ3" s="9">
         <v>3.496765993217292</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="AK3" s="9">
         <v>125.299677883427</v>
       </c>
-      <c r="Z3" s="11">
+      <c r="AL3" s="9">
         <v>2.287077732159186</v>
       </c>
-      <c r="AA3" s="11">
+      <c r="AM3" s="9">
         <v>159.1451689990535</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="AN3" s="9">
         <v>4.563409598934756</v>
       </c>
-      <c r="AC3" s="11">
+      <c r="AO3" s="9">
         <v>183.2846207935303</v>
       </c>
-      <c r="AD3" s="11">
+      <c r="AP3" s="9">
         <v>4.78591250206897</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AQ3" s="9">
         <v>173.1976544877471</v>
       </c>
-      <c r="AF3" s="11">
+      <c r="AR3" s="9">
         <v>2.147753250227566</v>
       </c>
     </row>
@@ -692,84 +824,120 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="7">
+        <v>88.19</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="H4" s="7">
+        <v>79.34</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="J4" s="7">
+        <v>68.96</v>
+      </c>
+      <c r="K4" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="L4" s="7">
+        <v>56.31</v>
+      </c>
+      <c r="M4" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="N4" s="7">
+        <v>36.25</v>
+      </c>
+      <c r="O4" s="7">
+        <v>1.77</v>
+      </c>
+      <c r="P4" s="7">
+        <v>23.6</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1.97</v>
+      </c>
+      <c r="R4" s="7">
         <v>50.40584469123189</v>
       </c>
-      <c r="G4" s="7">
+      <c r="S4" s="7">
         <v>2.550662320452894</v>
       </c>
-      <c r="H4" s="7">
+      <c r="T4" s="7">
         <v>53.95112663564925</v>
       </c>
-      <c r="I4" s="7">
+      <c r="U4" s="7">
         <v>0.6497154151302418</v>
       </c>
-      <c r="J4" s="7">
+      <c r="V4" s="7">
         <v>21.32945005703285</v>
       </c>
-      <c r="K4" s="7">
+      <c r="W4" s="7">
         <v>1.916880719941594</v>
       </c>
-      <c r="L4" s="7">
+      <c r="X4" s="7">
         <v>68.59995168768056</v>
       </c>
-      <c r="M4" s="7">
+      <c r="Y4" s="7">
         <v>0.309893258251236</v>
       </c>
-      <c r="N4" s="6">
+      <c r="Z4" s="6">
         <v>0.149</v>
       </c>
-      <c r="O4" s="6">
+      <c r="AA4" s="6">
         <v>0.163</v>
       </c>
-      <c r="P4" s="6">
+      <c r="AB4" s="6">
         <v>0.165</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="AC4" s="8">
         <v>0.159</v>
       </c>
-      <c r="R4" s="9">
+      <c r="AD4" s="8">
         <v>0.005033222956847171</v>
       </c>
-      <c r="S4" s="10">
+      <c r="AE4" s="9">
         <v>81.38603373361754</v>
       </c>
-      <c r="T4" s="11">
+      <c r="AF4" s="9">
         <v>6.246054693774116</v>
       </c>
-      <c r="U4" s="11">
+      <c r="AG4" s="9">
         <v>97.0</v>
       </c>
-      <c r="V4" s="11">
+      <c r="AH4" s="9">
         <v>10.4</v>
       </c>
-      <c r="W4" s="11">
+      <c r="AI4" s="9">
         <v>129.4642920454502</v>
       </c>
-      <c r="X4" s="11">
+      <c r="AJ4" s="9">
         <v>5.490085506971515</v>
       </c>
-      <c r="Y4" s="11">
+      <c r="AK4" s="9">
         <v>154.9908250096513</v>
       </c>
-      <c r="Z4" s="11">
+      <c r="AL4" s="9">
         <v>1.245419156401135</v>
       </c>
-      <c r="AA4" s="11">
+      <c r="AM4" s="9">
         <v>193.4677643493112</v>
       </c>
-      <c r="AB4" s="11">
+      <c r="AN4" s="9">
         <v>1.372421621550906</v>
       </c>
-      <c r="AC4" s="11">
+      <c r="AO4" s="9">
         <v>208.4567723813864</v>
       </c>
-      <c r="AD4" s="11">
+      <c r="AP4" s="9">
         <v>2.247584070210912</v>
       </c>
-      <c r="AE4" s="11">
+      <c r="AQ4" s="9">
         <v>208.8696149580333</v>
       </c>
-      <c r="AF4" s="11">
+      <c r="AR4" s="9">
         <v>5.170234840470934</v>
       </c>
     </row>
@@ -778,84 +946,120 @@
         <v>1.5</v>
       </c>
       <c r="F5" s="7">
+        <v>83.18</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1.13</v>
+      </c>
+      <c r="H5" s="7">
+        <v>71.05</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.86</v>
+      </c>
+      <c r="J5" s="7">
+        <v>57.81</v>
+      </c>
+      <c r="K5" s="7">
+        <v>1.27</v>
+      </c>
+      <c r="L5" s="7">
+        <v>45.25</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="N5" s="7">
+        <v>25.33</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="P5" s="7">
+        <v>12.77</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="R5" s="7">
         <v>54.71760549373374</v>
       </c>
-      <c r="G5" s="7">
+      <c r="S5" s="7">
         <v>0.566775683441974</v>
       </c>
-      <c r="H5" s="7">
+      <c r="T5" s="7">
         <v>53.24232843169546</v>
       </c>
-      <c r="I5" s="7">
+      <c r="U5" s="7">
         <v>0.04295266825046352</v>
       </c>
-      <c r="J5" s="7">
+      <c r="V5" s="7">
         <v>20.18359207053008</v>
       </c>
-      <c r="K5" s="7">
+      <c r="W5" s="7">
         <v>0.2766394974507091</v>
       </c>
-      <c r="L5" s="7">
+      <c r="X5" s="7">
         <v>72.05727703336318</v>
       </c>
-      <c r="M5" s="7">
+      <c r="Y5" s="7">
         <v>0.6025536261200348</v>
       </c>
-      <c r="N5" s="6">
+      <c r="Z5" s="6">
         <v>0.166</v>
       </c>
-      <c r="O5" s="6">
+      <c r="AA5" s="6">
         <v>0.161</v>
       </c>
-      <c r="P5" s="6">
+      <c r="AB5" s="6">
         <v>0.151</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="AC5" s="8">
         <v>0.159933333333333</v>
       </c>
-      <c r="R5" s="9">
+      <c r="AD5" s="8">
         <v>0.004409585518440987</v>
       </c>
-      <c r="S5" s="10">
+      <c r="AE5" s="9">
         <v>86.0543802531359</v>
       </c>
-      <c r="T5" s="11">
+      <c r="AF5" s="9">
         <v>3.053212916361236</v>
       </c>
-      <c r="U5" s="11">
+      <c r="AG5" s="9">
         <v>97.6</v>
       </c>
-      <c r="V5" s="11">
+      <c r="AH5" s="9">
         <v>6.8</v>
       </c>
-      <c r="W5" s="11">
+      <c r="AI5" s="9">
         <v>120.749404657604</v>
       </c>
-      <c r="X5" s="11">
+      <c r="AJ5" s="9">
         <v>2.66051884559691</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="AK5" s="9">
         <v>131.6254664314278</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="AL5" s="9">
         <v>4.017147664245909</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AM5" s="9">
         <v>162.6624122145846</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AN5" s="9">
         <v>6.67390082545365</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AO5" s="9">
         <v>175.5839505231567</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AP5" s="9">
         <v>1.939059926402317</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AQ5" s="9">
         <v>186.1278366543653</v>
       </c>
-      <c r="AF5" s="11">
+      <c r="AR5" s="9">
         <v>8.819628832502602</v>
       </c>
     </row>
@@ -864,84 +1068,120 @@
         <v>2.0</v>
       </c>
       <c r="F6" s="7">
+        <v>83.82</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1.08</v>
+      </c>
+      <c r="H6" s="7">
+        <v>70.85</v>
+      </c>
+      <c r="I6" s="7">
+        <v>2.57</v>
+      </c>
+      <c r="J6" s="7">
+        <v>56.25</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.23</v>
+      </c>
+      <c r="L6" s="7">
+        <v>44.77</v>
+      </c>
+      <c r="M6" s="7">
+        <v>1.14</v>
+      </c>
+      <c r="N6" s="7">
+        <v>26.58</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="P6" s="7">
+        <v>15.1</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="R6" s="7">
         <v>85.78778524722911</v>
       </c>
-      <c r="G6" s="7">
+      <c r="S6" s="7">
         <v>6.78165313289879</v>
       </c>
-      <c r="H6" s="7">
+      <c r="T6" s="7">
         <v>53.41750528241602</v>
       </c>
-      <c r="I6" s="7">
+      <c r="U6" s="7">
         <v>0.6411332212682744</v>
       </c>
-      <c r="J6" s="7">
+      <c r="V6" s="7">
         <v>27.58535713922851</v>
       </c>
-      <c r="K6" s="7">
+      <c r="W6" s="7">
         <v>2.27488127363537</v>
       </c>
-      <c r="L6" s="7">
+      <c r="X6" s="7">
         <v>65.86145746497489</v>
       </c>
-      <c r="M6" s="7">
+      <c r="Y6" s="7">
         <v>1.255336800972233</v>
       </c>
-      <c r="N6" s="6">
+      <c r="Z6" s="6">
         <v>0.222</v>
       </c>
-      <c r="O6" s="6">
+      <c r="AA6" s="6">
         <v>0.195</v>
       </c>
-      <c r="P6" s="6">
+      <c r="AB6" s="6">
         <v>0.186</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="AC6" s="8">
         <v>0.201</v>
       </c>
-      <c r="R6" s="9">
+      <c r="AD6" s="8">
         <v>0.008816653826392</v>
       </c>
-      <c r="S6" s="10">
+      <c r="AE6" s="9">
         <v>79.66526777216477</v>
       </c>
-      <c r="T6" s="11">
+      <c r="AF6" s="9">
         <v>7.107852435311745</v>
       </c>
-      <c r="U6" s="11">
+      <c r="AG6" s="9">
         <v>90.9</v>
       </c>
-      <c r="V6" s="11">
+      <c r="AH6" s="9">
         <v>5.5</v>
       </c>
-      <c r="W6" s="11">
+      <c r="AI6" s="9">
         <v>113.8715809178626</v>
       </c>
-      <c r="X6" s="11">
+      <c r="AJ6" s="9">
         <v>2.071998082951354</v>
       </c>
-      <c r="Y6" s="11">
+      <c r="AK6" s="9">
         <v>122.9807159357212</v>
       </c>
-      <c r="Z6" s="11">
+      <c r="AL6" s="9">
         <v>2.986950694346786</v>
       </c>
-      <c r="AA6" s="11">
+      <c r="AM6" s="9">
         <v>154.8825750569884</v>
       </c>
-      <c r="AB6" s="11">
+      <c r="AN6" s="9">
         <v>4.036757601394203</v>
       </c>
-      <c r="AC6" s="11">
+      <c r="AO6" s="9">
         <v>182.0622355575698</v>
       </c>
-      <c r="AD6" s="11">
+      <c r="AP6" s="9">
         <v>9.591855721777439</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AQ6" s="9">
         <v>179.6522842632562</v>
       </c>
-      <c r="AF6" s="11">
+      <c r="AR6" s="9">
         <v>5.289481735913742</v>
       </c>
     </row>
@@ -950,84 +1190,120 @@
         <v>3.0</v>
       </c>
       <c r="F7" s="7">
+        <v>82.87</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2.09</v>
+      </c>
+      <c r="H7" s="7">
+        <v>68.6</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="J7" s="7">
+        <v>54.71</v>
+      </c>
+      <c r="K7" s="7">
+        <v>2.45</v>
+      </c>
+      <c r="L7" s="7">
+        <v>44.14</v>
+      </c>
+      <c r="M7" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N7" s="7">
+        <v>27.4</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="P7" s="7">
+        <v>16.83</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="R7" s="7">
         <v>80.53544312730453</v>
       </c>
-      <c r="G7" s="7">
+      <c r="S7" s="7">
         <v>3.474368073685636</v>
       </c>
-      <c r="H7" s="7">
+      <c r="T7" s="7">
         <v>52.51462444014873</v>
       </c>
-      <c r="I7" s="7">
+      <c r="U7" s="7">
         <v>0.5533632158856152</v>
       </c>
-      <c r="J7" s="7">
+      <c r="V7" s="7">
         <v>27.92190131259633</v>
       </c>
-      <c r="K7" s="7">
+      <c r="W7" s="7">
         <v>1.26623486113035</v>
       </c>
-      <c r="L7" s="7">
+      <c r="X7" s="7">
         <v>67.53771965261954</v>
       </c>
-      <c r="M7" s="7">
+      <c r="Y7" s="7">
         <v>0.6652049418372559</v>
       </c>
-      <c r="N7" s="6">
+      <c r="Z7" s="6">
         <v>0.212</v>
       </c>
-      <c r="O7" s="6">
+      <c r="AA7" s="6">
         <v>0.205</v>
       </c>
-      <c r="P7" s="6">
+      <c r="AB7" s="6">
         <v>0.189</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="AC7" s="8">
         <v>0.202</v>
       </c>
-      <c r="R7" s="9">
+      <c r="AD7" s="8">
         <v>0.006806859285554042</v>
       </c>
-      <c r="S7" s="10">
+      <c r="AE7" s="9">
         <v>78.81598482349061</v>
       </c>
-      <c r="T7" s="11">
+      <c r="AF7" s="9">
         <v>4.478124835785626</v>
       </c>
-      <c r="U7" s="11">
+      <c r="AG7" s="9">
         <v>89.5</v>
       </c>
-      <c r="V7" s="11">
+      <c r="AH7" s="9">
         <v>4.9</v>
       </c>
-      <c r="W7" s="11">
+      <c r="AI7" s="9">
         <v>111.044347300121</v>
       </c>
-      <c r="X7" s="11">
+      <c r="AJ7" s="9">
         <v>1.803141863978357</v>
       </c>
-      <c r="Y7" s="11">
+      <c r="AK7" s="9">
         <v>118.1734513561881</v>
       </c>
-      <c r="Z7" s="11">
+      <c r="AL7" s="9">
         <v>3.542331767536524</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AM7" s="9">
         <v>144.6203435709787</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AN7" s="9">
         <v>6.475909322536161</v>
       </c>
-      <c r="AC7" s="11">
+      <c r="AO7" s="9">
         <v>134.7496950701339</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AP7" s="9">
         <v>3.755955745370885</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AQ7" s="9">
         <v>148.7509091658919</v>
       </c>
-      <c r="AF7" s="11">
+      <c r="AR7" s="9">
         <v>3.848106434267764</v>
       </c>
     </row>
@@ -1035,73 +1311,121 @@
       <c r="A8" s="6">
         <v>5.0</v>
       </c>
-      <c r="J8" s="13">
+      <c r="F8" s="10">
+        <v>73.99355924452814</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.2019169515889416</v>
+      </c>
+      <c r="H8" s="10">
+        <v>63.84502903896671</v>
+      </c>
+      <c r="I8" s="10">
+        <v>1.534789151100213</v>
+      </c>
+      <c r="J8" s="10">
+        <v>58.88002598277671</v>
+      </c>
+      <c r="K8" s="10">
+        <v>1.458721097509793</v>
+      </c>
+      <c r="L8" s="10">
+        <v>54.42699117129592</v>
+      </c>
+      <c r="M8" s="10">
+        <v>1.40209177267346</v>
+      </c>
+      <c r="N8" s="10">
+        <v>36.61485192537276</v>
+      </c>
+      <c r="O8" s="10">
+        <v>1.185059863175494</v>
+      </c>
+      <c r="P8" s="10">
+        <v>22.69466458079118</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0.9093739693106002</v>
+      </c>
+      <c r="R8" s="7">
+        <v>157.6598757405977</v>
+      </c>
+      <c r="S8" s="7">
+        <v>2.948773766866778</v>
+      </c>
+      <c r="T8" s="7">
+        <v>58.15264770051918</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0.1492823005907599</v>
+      </c>
+      <c r="V8" s="10">
         <v>51.13370272005709</v>
       </c>
-      <c r="K8" s="13">
+      <c r="W8" s="10">
         <v>1.236392889802275</v>
       </c>
-      <c r="L8" s="13">
+      <c r="X8" s="10">
         <v>67.30582937252298</v>
       </c>
-      <c r="M8" s="13">
+      <c r="Y8" s="10">
         <v>0.1622273702403538</v>
       </c>
-      <c r="N8" s="7">
+      <c r="Z8" s="7">
         <v>0.2996286622517219</v>
       </c>
-      <c r="O8" s="7">
+      <c r="AA8" s="7">
         <v>0.2996286622517219</v>
       </c>
-      <c r="P8" s="7">
+      <c r="AB8" s="7">
         <v>0.3013076211363221</v>
       </c>
-      <c r="Q8" s="12">
+      <c r="AC8" s="8">
         <v>0.2989295604295896</v>
       </c>
-      <c r="R8" s="9">
+      <c r="AD8" s="8">
         <v>0.00161311527340026</v>
       </c>
-      <c r="S8" s="10">
+      <c r="AE8" s="9">
         <v>30.07219661484343</v>
       </c>
-      <c r="T8" s="11">
+      <c r="AF8" s="9">
         <v>0.4</v>
       </c>
-      <c r="U8" s="11">
+      <c r="AG8" s="9">
         <v>39.03</v>
       </c>
-      <c r="V8" s="11">
+      <c r="AH8" s="9">
         <v>0.61</v>
       </c>
-      <c r="W8" s="11">
+      <c r="AI8" s="9">
         <v>56.958537908634334</v>
       </c>
-      <c r="X8" s="11">
+      <c r="AJ8" s="9">
         <v>2.6</v>
       </c>
-      <c r="Y8" s="11">
+      <c r="AK8" s="9">
         <v>65.74721689548407</v>
       </c>
-      <c r="Z8" s="11">
+      <c r="AL8" s="9">
         <v>2.0</v>
       </c>
-      <c r="AA8" s="11">
+      <c r="AM8" s="9">
         <v>80.4732005571861</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AN8" s="9">
         <v>2.6</v>
       </c>
-      <c r="AC8" s="11">
+      <c r="AO8" s="9">
         <v>99.53222717388411</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AP8" s="9">
         <v>4.8</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AQ8" s="9">
         <v>105.74031782547944</v>
       </c>
-      <c r="AF8" s="11">
+      <c r="AR8" s="9">
         <v>2.7</v>
       </c>
     </row>
@@ -1109,73 +1433,121 @@
       <c r="C9" s="6">
         <v>0.7</v>
       </c>
-      <c r="J9" s="13">
+      <c r="F9" s="10">
+        <v>79.92421293722248</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1.060739414862349</v>
+      </c>
+      <c r="H9" s="10">
+        <v>71.16695716510256</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0.637433488948495</v>
+      </c>
+      <c r="J9" s="10">
+        <v>66.1113443070845</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.6931062667198676</v>
+      </c>
+      <c r="L9" s="10">
+        <v>61.80656739110039</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0.6555559788753325</v>
+      </c>
+      <c r="N9" s="10">
+        <v>44.58745972716397</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0.5390411507977482</v>
+      </c>
+      <c r="P9" s="10">
+        <v>31.08458782866331</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0.5817211875057109</v>
+      </c>
+      <c r="R9" s="7">
+        <v>215.9893245733189</v>
+      </c>
+      <c r="S9" s="7">
+        <v>6.77977108139273</v>
+      </c>
+      <c r="T9" s="7">
+        <v>58.18992997855728</v>
+      </c>
+      <c r="U9" s="7">
+        <v>0.3699396952701384</v>
+      </c>
+      <c r="V9" s="10">
         <v>82.81246062063757</v>
       </c>
-      <c r="K9" s="13">
+      <c r="W9" s="10">
         <v>4.037828309503719</v>
       </c>
-      <c r="L9" s="13">
+      <c r="X9" s="10">
         <v>62.21860357942923</v>
       </c>
-      <c r="M9" s="13">
+      <c r="Y9" s="10">
         <v>1.567317736857665</v>
       </c>
-      <c r="N9" s="7">
+      <c r="Z9" s="7">
         <v>0.3607137068965667</v>
       </c>
-      <c r="O9" s="7">
+      <c r="AA9" s="7">
         <v>0.3626670405616667</v>
       </c>
-      <c r="P9" s="7">
+      <c r="AB9" s="7">
         <v>0.3567255508143103</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="AC9" s="8">
         <v>0.3600354327575146</v>
       </c>
-      <c r="R9" s="9">
+      <c r="AD9" s="8">
         <v>0.001748367520504539</v>
       </c>
-      <c r="S9" s="10">
+      <c r="AE9" s="9">
         <v>29.188752979334033</v>
       </c>
-      <c r="T9" s="11">
+      <c r="AF9" s="9">
         <v>0.4</v>
       </c>
-      <c r="U9" s="11">
+      <c r="AG9" s="9">
         <v>38.5</v>
       </c>
-      <c r="V9" s="11">
+      <c r="AH9" s="9">
         <v>1.03</v>
       </c>
-      <c r="W9" s="11">
+      <c r="AI9" s="9">
         <v>57.11516010261215</v>
       </c>
-      <c r="X9" s="11">
+      <c r="AJ9" s="9">
         <v>3.0</v>
       </c>
-      <c r="Y9" s="11">
+      <c r="AK9" s="9">
         <v>67.11581114721132</v>
       </c>
-      <c r="Z9" s="11">
+      <c r="AL9" s="9">
         <v>3.2</v>
       </c>
-      <c r="AA9" s="11">
+      <c r="AM9" s="9">
         <v>78.54939073242085</v>
       </c>
-      <c r="AB9" s="11">
+      <c r="AN9" s="9">
         <v>2.5</v>
       </c>
-      <c r="AC9" s="11">
+      <c r="AO9" s="9">
         <v>99.77213140551049</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AP9" s="9">
         <v>3.0</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AQ9" s="9">
         <v>95.65988059852906</v>
       </c>
-      <c r="AF9" s="11">
+      <c r="AR9" s="9">
         <v>1.5</v>
       </c>
     </row>
@@ -1183,73 +1555,121 @@
       <c r="C10" s="6">
         <v>1.0</v>
       </c>
-      <c r="J10" s="13">
+      <c r="F10" s="10">
+        <v>76.90387499485618</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1.187870053705751</v>
+      </c>
+      <c r="H10" s="10">
+        <v>69.4709174227594</v>
+      </c>
+      <c r="I10" s="10">
+        <v>1.789894463929565</v>
+      </c>
+      <c r="J10" s="10">
+        <v>64.67219529003106</v>
+      </c>
+      <c r="K10" s="10">
+        <v>1.614203341015746</v>
+      </c>
+      <c r="L10" s="10">
+        <v>60.49107167180846</v>
+      </c>
+      <c r="M10" s="10">
+        <v>1.526449247778018</v>
+      </c>
+      <c r="N10" s="10">
+        <v>43.76657719891806</v>
+      </c>
+      <c r="O10" s="10">
+        <v>1.175434272963217</v>
+      </c>
+      <c r="P10" s="10">
+        <v>30.35502059653167</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>1.198847225582804</v>
+      </c>
+      <c r="R10" s="7">
+        <v>218.5437785891325</v>
+      </c>
+      <c r="S10" s="7">
+        <v>5.777922915635362</v>
+      </c>
+      <c r="T10" s="7">
+        <v>58.7000968475319</v>
+      </c>
+      <c r="U10" s="7">
+        <v>0.261805359978352</v>
+      </c>
+      <c r="V10" s="10">
         <v>77.13435359656211</v>
       </c>
-      <c r="K10" s="13">
+      <c r="W10" s="10">
         <v>1.777061441073681</v>
       </c>
-      <c r="L10" s="13">
+      <c r="X10" s="10">
         <v>66.76975615838113</v>
       </c>
-      <c r="M10" s="13">
+      <c r="Y10" s="10">
         <v>0.5165008525294192</v>
       </c>
-      <c r="N10" s="7">
+      <c r="Z10" s="7">
         <v>0.3583353747631828</v>
       </c>
-      <c r="O10" s="7">
+      <c r="AA10" s="7">
         <v>0.3571795507362534</v>
       </c>
-      <c r="P10" s="7">
+      <c r="AB10" s="7">
         <v>0.3511556881680956</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="AC10" s="8">
         <v>0.3555568712225106</v>
       </c>
-      <c r="R10" s="9">
+      <c r="AD10" s="8">
         <v>0.002225742685349396</v>
       </c>
-      <c r="S10" s="10">
+      <c r="AE10" s="9">
         <v>27.225458071349035</v>
       </c>
-      <c r="T10" s="11">
+      <c r="AF10" s="9">
         <v>1.7999999999999998</v>
       </c>
-      <c r="U10" s="11">
+      <c r="AG10" s="9">
         <v>32.92</v>
       </c>
-      <c r="V10" s="11">
+      <c r="AH10" s="9">
         <v>1.19</v>
       </c>
-      <c r="W10" s="11">
+      <c r="AI10" s="9">
         <v>44.308894750685845</v>
       </c>
-      <c r="X10" s="11">
+      <c r="AJ10" s="9">
         <v>0.0</v>
       </c>
-      <c r="Y10" s="11">
+      <c r="AK10" s="9">
         <v>58.26806764311343</v>
       </c>
-      <c r="Z10" s="11">
+      <c r="AL10" s="9">
         <v>1.5</v>
       </c>
-      <c r="AA10" s="11">
+      <c r="AM10" s="9">
         <v>75.50498621937007</v>
       </c>
-      <c r="AB10" s="11">
+      <c r="AN10" s="9">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AC10" s="11">
+      <c r="AO10" s="9">
         <v>93.20985797032287</v>
       </c>
-      <c r="AD10" s="11">
+      <c r="AP10" s="9">
         <v>2.3</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AQ10" s="9">
         <v>94.78889696470317</v>
       </c>
-      <c r="AF10" s="11">
+      <c r="AR10" s="9">
         <v>0.8999999999999999</v>
       </c>
     </row>
@@ -1257,73 +1677,121 @@
       <c r="C11" s="6">
         <v>2.0</v>
       </c>
-      <c r="J11" s="13">
+      <c r="F11" s="10">
+        <v>77.79637766080326</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.8747470232756213</v>
+      </c>
+      <c r="H11" s="10">
+        <v>71.27647448658456</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0.9834641427533747</v>
+      </c>
+      <c r="J11" s="10">
+        <v>66.99628823200119</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.9099873534908839</v>
+      </c>
+      <c r="L11" s="10">
+        <v>62.43433783532269</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0.9879723396750385</v>
+      </c>
+      <c r="N11" s="10">
+        <v>44.18653624860868</v>
+      </c>
+      <c r="O11" s="10">
+        <v>1.472876730519528</v>
+      </c>
+      <c r="P11" s="10">
+        <v>30.00491915322759</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>1.264635353404087</v>
+      </c>
+      <c r="R11" s="7">
+        <v>196.3411935102102</v>
+      </c>
+      <c r="S11" s="7">
+        <v>4.896257192047281</v>
+      </c>
+      <c r="T11" s="7">
+        <v>58.39793455827721</v>
+      </c>
+      <c r="U11" s="7">
+        <v>0.2336208538258209</v>
+      </c>
+      <c r="V11" s="10">
         <v>76.40645992317215</v>
       </c>
-      <c r="K11" s="13">
+      <c r="W11" s="10">
         <v>2.33576366017232</v>
       </c>
-      <c r="L11" s="13">
+      <c r="X11" s="10">
         <v>68.83493440642118</v>
       </c>
-      <c r="M11" s="13">
+      <c r="Y11" s="10">
         <v>0.3312629767268597</v>
       </c>
-      <c r="N11" s="7">
+      <c r="Z11" s="7">
         <v>0.365949160207593</v>
       </c>
-      <c r="O11" s="7">
+      <c r="AA11" s="7">
         <v>0.3475864218942114</v>
       </c>
-      <c r="P11" s="7">
+      <c r="AB11" s="7">
         <v>0.360628742714065</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="AC11" s="8">
         <v>0.3580547749386231</v>
       </c>
-      <c r="R11" s="9">
+      <c r="AD11" s="8">
         <v>0.005454860895665853</v>
       </c>
-      <c r="S11" s="10">
+      <c r="AE11" s="9">
         <v>26.298348823506316</v>
       </c>
-      <c r="T11" s="11">
+      <c r="AF11" s="9">
         <v>0.7000000000000001</v>
       </c>
-      <c r="U11" s="11">
+      <c r="AG11" s="9">
         <v>31.97</v>
       </c>
-      <c r="V11" s="11">
+      <c r="AH11" s="9">
         <v>0.66</v>
       </c>
-      <c r="W11" s="11">
+      <c r="AI11" s="9">
         <v>43.3263006892421</v>
       </c>
-      <c r="X11" s="11">
+      <c r="AJ11" s="9">
         <v>1.3</v>
       </c>
-      <c r="Y11" s="11">
+      <c r="AK11" s="9">
         <v>52.977134725650046</v>
       </c>
-      <c r="Z11" s="11">
+      <c r="AL11" s="9">
         <v>1.7999999999999998</v>
       </c>
-      <c r="AA11" s="11">
+      <c r="AM11" s="9">
         <v>68.68092379263973</v>
       </c>
-      <c r="AB11" s="11">
+      <c r="AN11" s="9">
         <v>1.2</v>
       </c>
-      <c r="AC11" s="11">
+      <c r="AO11" s="9">
         <v>80.32051752560548</v>
       </c>
-      <c r="AD11" s="11">
+      <c r="AP11" s="9">
         <v>2.1999999999999997</v>
       </c>
-      <c r="AE11" s="11">
+      <c r="AQ11" s="9">
         <v>85.87628964258877</v>
       </c>
-      <c r="AF11" s="11">
+      <c r="AR11" s="9">
         <v>1.7000000000000002</v>
       </c>
     </row>
@@ -1331,73 +1799,121 @@
       <c r="C12" s="6">
         <v>3.0</v>
       </c>
-      <c r="J12" s="13">
+      <c r="F12" s="10">
+        <v>74.14754443574773</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.6913763566767633</v>
+      </c>
+      <c r="H12" s="10">
+        <v>61.45754875090975</v>
+      </c>
+      <c r="I12" s="10">
+        <v>1.461714730517133</v>
+      </c>
+      <c r="J12" s="10">
+        <v>56.21463438750984</v>
+      </c>
+      <c r="K12" s="10">
+        <v>1.260675235678731</v>
+      </c>
+      <c r="L12" s="10">
+        <v>51.46090793541097</v>
+      </c>
+      <c r="M12" s="10">
+        <v>1.193208375102689</v>
+      </c>
+      <c r="N12" s="10">
+        <v>32.44600212701546</v>
+      </c>
+      <c r="O12" s="10">
+        <v>0.9503504455416049</v>
+      </c>
+      <c r="P12" s="10">
+        <v>17.47684828697292</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0.6574157761751536</v>
+      </c>
+      <c r="R12" s="7">
+        <v>92.40012085636496</v>
+      </c>
+      <c r="S12" s="7">
+        <v>1.131912214722878</v>
+      </c>
+      <c r="T12" s="7">
+        <v>57.69806352620724</v>
+      </c>
+      <c r="U12" s="7">
+        <v>0.07073680256538416</v>
+      </c>
+      <c r="V12" s="10">
         <v>35.34997661060815</v>
       </c>
-      <c r="K12" s="13">
+      <c r="W12" s="10">
         <v>0.4679941073813578</v>
       </c>
-      <c r="L12" s="13">
+      <c r="X12" s="10">
         <v>73.18199863839158</v>
       </c>
-      <c r="M12" s="13">
+      <c r="Y12" s="10">
         <v>2.079040093759844</v>
       </c>
-      <c r="N12" s="7">
+      <c r="Z12" s="7">
         <v>0.2571843873247172</v>
       </c>
-      <c r="O12" s="7">
+      <c r="AA12" s="7">
         <v>0.2638158032569805</v>
       </c>
-      <c r="P12" s="7">
+      <c r="AB12" s="7">
         <v>0.2578889750611289</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="AC12" s="8">
         <v>0.2596297218809422</v>
       </c>
-      <c r="R12" s="9">
+      <c r="AD12" s="8">
         <v>0.002102900293617236</v>
       </c>
-      <c r="S12" s="10">
+      <c r="AE12" s="9">
         <v>39.85367343244271</v>
       </c>
-      <c r="T12" s="11">
+      <c r="AF12" s="9">
         <v>0.4</v>
       </c>
-      <c r="U12" s="11">
+      <c r="AG12" s="9">
         <v>45.81</v>
       </c>
-      <c r="V12" s="11">
+      <c r="AH12" s="9">
         <v>0.79</v>
       </c>
-      <c r="W12" s="11">
+      <c r="AI12" s="9">
         <v>57.722205312755506</v>
       </c>
-      <c r="X12" s="11">
+      <c r="AJ12" s="9">
         <v>2.8000000000000003</v>
       </c>
-      <c r="Y12" s="11">
+      <c r="AK12" s="9">
         <v>63.962665318456416</v>
       </c>
-      <c r="Z12" s="11">
+      <c r="AL12" s="9">
         <v>1.3</v>
       </c>
-      <c r="AA12" s="11">
+      <c r="AM12" s="9">
         <v>83.28273992472873</v>
       </c>
-      <c r="AB12" s="11">
+      <c r="AN12" s="9">
         <v>1.6</v>
       </c>
-      <c r="AC12" s="11">
+      <c r="AO12" s="9">
         <v>93.49580915208546</v>
       </c>
-      <c r="AD12" s="11">
+      <c r="AP12" s="9">
         <v>1.2</v>
       </c>
-      <c r="AE12" s="11">
+      <c r="AQ12" s="9">
         <v>104.87348592777128</v>
       </c>
-      <c r="AF12" s="11">
+      <c r="AR12" s="9">
         <v>2.4</v>
       </c>
     </row>
@@ -1409,84 +1925,120 @@
         <v>1.0</v>
       </c>
       <c r="F13" s="7">
-        <v>50.99</v>
+        <v>85.47</v>
       </c>
       <c r="G13" s="7">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="7">
-        <v>51.64</v>
+        <v>78.86</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17</v>
+        <v>0.77</v>
       </c>
       <c r="J13" s="7">
-        <v>19.56</v>
+        <v>72.85</v>
       </c>
       <c r="K13" s="7">
-        <v>0.38</v>
+        <v>1.07</v>
       </c>
       <c r="L13" s="7">
         <v>65.59</v>
       </c>
       <c r="M13" s="7">
+        <v>1.18</v>
+      </c>
+      <c r="N13" s="7">
+        <v>43.57</v>
+      </c>
+      <c r="O13" s="7">
+        <v>1.44</v>
+      </c>
+      <c r="P13" s="7">
+        <v>9.75</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="R13" s="7">
+        <v>50.99</v>
+      </c>
+      <c r="S13" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="T13" s="7">
+        <v>51.64</v>
+      </c>
+      <c r="U13" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="V13" s="7">
+        <v>19.56</v>
+      </c>
+      <c r="W13" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="X13" s="7">
+        <v>65.59</v>
+      </c>
+      <c r="Y13" s="7">
         <v>0.97</v>
       </c>
-      <c r="N13" s="7">
+      <c r="Z13" s="7">
         <v>0.1648</v>
       </c>
-      <c r="O13" s="7">
+      <c r="AA13" s="7">
         <v>0.1627</v>
       </c>
-      <c r="P13" s="7">
+      <c r="AB13" s="7">
         <v>0.1661</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="AC13" s="8">
         <v>0.1645333333333333</v>
       </c>
-      <c r="R13" s="9">
+      <c r="AD13" s="8">
         <v>9.905105305402378E-4</v>
       </c>
-      <c r="S13" s="14">
+      <c r="AE13" s="7">
         <v>134.16</v>
       </c>
-      <c r="T13" s="7">
+      <c r="AF13" s="7">
         <v>2.38</v>
       </c>
-      <c r="U13" s="7">
+      <c r="AG13" s="7">
         <v>156.35</v>
       </c>
-      <c r="V13" s="7">
+      <c r="AH13" s="7">
         <v>2.99</v>
       </c>
-      <c r="W13" s="7">
+      <c r="AI13" s="7">
         <v>200.74</v>
       </c>
-      <c r="X13" s="7">
+      <c r="AJ13" s="7">
         <v>4.36</v>
       </c>
-      <c r="Y13" s="7">
+      <c r="AK13" s="7">
         <v>234.37</v>
       </c>
-      <c r="Z13" s="7">
+      <c r="AL13" s="7">
         <v>3.0</v>
       </c>
-      <c r="AA13" s="7">
+      <c r="AM13" s="7">
         <v>245.99</v>
       </c>
-      <c r="AB13" s="7">
+      <c r="AN13" s="7">
         <v>0.37</v>
       </c>
-      <c r="AC13" s="7">
+      <c r="AO13" s="7">
         <v>267.98</v>
       </c>
-      <c r="AD13" s="7">
+      <c r="AP13" s="7">
         <v>2.08</v>
       </c>
-      <c r="AE13" s="7">
+      <c r="AQ13" s="7">
         <v>276.71000000000004</v>
       </c>
-      <c r="AF13" s="7">
+      <c r="AR13" s="7">
         <v>1.36</v>
       </c>
     </row>
@@ -1498,84 +2050,120 @@
         <v>1.0</v>
       </c>
       <c r="F14" s="7">
+        <v>89.68</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="H14" s="7">
+        <v>84.09</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="J14" s="7">
+        <v>78.41</v>
+      </c>
+      <c r="K14" s="7">
+        <v>1.13</v>
+      </c>
+      <c r="L14" s="7">
+        <v>71.86</v>
+      </c>
+      <c r="M14" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="N14" s="7">
+        <v>30.12</v>
+      </c>
+      <c r="O14" s="7">
+        <v>2.41</v>
+      </c>
+      <c r="P14" s="7">
+        <v>4.94</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>1.38</v>
+      </c>
+      <c r="R14" s="7">
         <v>40.1</v>
       </c>
-      <c r="G14" s="7">
+      <c r="S14" s="7">
         <v>2.92</v>
       </c>
-      <c r="H14" s="7">
+      <c r="T14" s="7">
         <v>52.19</v>
       </c>
-      <c r="I14" s="7">
+      <c r="U14" s="7">
         <v>0.33</v>
       </c>
-      <c r="J14" s="7">
+      <c r="V14" s="7">
         <v>19.61</v>
       </c>
-      <c r="K14" s="7">
+      <c r="W14" s="7">
         <v>1.17</v>
       </c>
-      <c r="L14" s="7">
+      <c r="X14" s="7">
         <v>58.88</v>
       </c>
-      <c r="M14" s="7">
+      <c r="Y14" s="7">
         <v>1.23</v>
       </c>
-      <c r="N14" s="7">
+      <c r="Z14" s="7">
         <v>0.1612</v>
       </c>
-      <c r="O14" s="7">
+      <c r="AA14" s="7">
         <v>0.1518</v>
       </c>
-      <c r="P14" s="7">
+      <c r="AB14" s="7">
         <v>0.1537</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="AC14" s="8">
         <v>0.1555666666666667</v>
       </c>
-      <c r="R14" s="9">
+      <c r="AD14" s="8">
         <v>0.002869572170976795</v>
       </c>
-      <c r="S14" s="14">
+      <c r="AE14" s="7">
         <v>144.68</v>
       </c>
-      <c r="T14" s="7">
+      <c r="AF14" s="7">
         <v>13.83</v>
       </c>
-      <c r="U14" s="7">
+      <c r="AG14" s="7">
         <v>168.81</v>
       </c>
-      <c r="V14" s="7">
+      <c r="AH14" s="7">
         <v>16.23</v>
       </c>
-      <c r="W14" s="7">
+      <c r="AI14" s="7">
         <v>217.06</v>
       </c>
-      <c r="X14" s="7">
+      <c r="AJ14" s="7">
         <v>21.17</v>
       </c>
-      <c r="Y14" s="7">
+      <c r="AK14" s="7">
         <v>268.81</v>
       </c>
-      <c r="Z14" s="7">
+      <c r="AL14" s="7">
         <v>24.49</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AM14" s="7">
         <v>295.65999999999997</v>
       </c>
-      <c r="AB14" s="7">
+      <c r="AN14" s="7">
         <v>19.08</v>
       </c>
-      <c r="AC14" s="7">
+      <c r="AO14" s="7">
         <v>304.31</v>
       </c>
-      <c r="AD14" s="7">
+      <c r="AP14" s="7">
         <v>22.42</v>
       </c>
-      <c r="AE14" s="7">
+      <c r="AQ14" s="7">
         <v>294.72</v>
       </c>
-      <c r="AF14" s="7">
+      <c r="AR14" s="7">
         <v>21.46</v>
       </c>
     </row>
@@ -1587,84 +2175,120 @@
         <v>2.0</v>
       </c>
       <c r="F15" s="7">
+        <v>89.06</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1.86</v>
+      </c>
+      <c r="H15" s="7">
+        <v>82.82</v>
+      </c>
+      <c r="I15" s="7">
+        <v>2.75</v>
+      </c>
+      <c r="J15" s="7">
+        <v>74.91</v>
+      </c>
+      <c r="K15" s="7">
+        <v>2.58</v>
+      </c>
+      <c r="L15" s="7">
+        <v>67.01</v>
+      </c>
+      <c r="M15" s="7">
+        <v>2.27</v>
+      </c>
+      <c r="N15" s="7">
+        <v>45.6</v>
+      </c>
+      <c r="O15" s="7">
+        <v>0.98</v>
+      </c>
+      <c r="P15" s="7">
+        <v>10.55</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>1.02</v>
+      </c>
+      <c r="R15" s="7">
         <v>39.06</v>
       </c>
-      <c r="G15" s="7">
+      <c r="S15" s="7">
         <v>1.13</v>
       </c>
-      <c r="H15" s="7">
+      <c r="T15" s="7">
         <v>52.01</v>
       </c>
-      <c r="I15" s="7">
+      <c r="U15" s="7">
         <v>0.33</v>
       </c>
-      <c r="J15" s="7">
+      <c r="V15" s="7">
         <v>16.73</v>
       </c>
-      <c r="K15" s="7">
+      <c r="W15" s="7">
         <v>0.82</v>
       </c>
-      <c r="L15" s="7">
+      <c r="X15" s="7">
         <v>63.88</v>
       </c>
-      <c r="M15" s="7">
+      <c r="Y15" s="7">
         <v>0.32</v>
       </c>
-      <c r="N15" s="7">
+      <c r="Z15" s="7">
         <v>0.1504</v>
       </c>
-      <c r="O15" s="7">
+      <c r="AA15" s="7">
         <v>0.1391</v>
       </c>
-      <c r="P15" s="7">
+      <c r="AB15" s="7">
         <v>0.1403</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="AC15" s="8">
         <v>0.1432666666666667</v>
       </c>
-      <c r="R15" s="9">
+      <c r="AD15" s="8">
         <v>0.003583449610516536</v>
       </c>
-      <c r="S15" s="14">
+      <c r="AE15" s="7">
         <v>154.67000000000002</v>
       </c>
-      <c r="T15" s="7">
+      <c r="AF15" s="7">
         <v>3.47</v>
       </c>
-      <c r="U15" s="7">
+      <c r="AG15" s="7">
         <v>173.0</v>
       </c>
-      <c r="V15" s="7">
+      <c r="AH15" s="7">
         <v>2.01</v>
       </c>
-      <c r="W15" s="7">
+      <c r="AI15" s="7">
         <v>209.67</v>
       </c>
-      <c r="X15" s="7">
+      <c r="AJ15" s="7">
         <v>5.48</v>
       </c>
-      <c r="Y15" s="7">
+      <c r="AK15" s="7">
         <v>249.31</v>
       </c>
-      <c r="Z15" s="7">
+      <c r="AL15" s="7">
         <v>5.17</v>
       </c>
-      <c r="AA15" s="7">
+      <c r="AM15" s="7">
         <v>270.74</v>
       </c>
-      <c r="AB15" s="7">
+      <c r="AN15" s="7">
         <v>6.94</v>
       </c>
-      <c r="AC15" s="7">
+      <c r="AO15" s="7">
         <v>270.85</v>
       </c>
-      <c r="AD15" s="7">
+      <c r="AP15" s="7">
         <v>10.78</v>
       </c>
-      <c r="AE15" s="7">
+      <c r="AQ15" s="7">
         <v>294.18</v>
       </c>
-      <c r="AF15" s="7">
+      <c r="AR15" s="7">
         <v>5.5</v>
       </c>
     </row>
@@ -1676,84 +2300,120 @@
         <v>2.0</v>
       </c>
       <c r="F16" s="7">
+        <v>87.76</v>
+      </c>
+      <c r="G16" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="H16" s="7">
+        <v>81.67</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="J16" s="7">
+        <v>75.33</v>
+      </c>
+      <c r="K16" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="L16" s="7">
+        <v>69.2</v>
+      </c>
+      <c r="M16" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="N16" s="7">
+        <v>44.87</v>
+      </c>
+      <c r="O16" s="7">
+        <v>1.44</v>
+      </c>
+      <c r="P16" s="7">
+        <v>9.93</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="R16" s="7">
         <v>44.45</v>
       </c>
-      <c r="G16" s="7">
+      <c r="S16" s="7">
         <v>1.08</v>
       </c>
-      <c r="H16" s="7">
+      <c r="T16" s="7">
         <v>52.39</v>
       </c>
-      <c r="I16" s="7">
+      <c r="U16" s="7">
         <v>0.14</v>
       </c>
-      <c r="J16" s="7">
+      <c r="V16" s="7">
         <v>16.97</v>
       </c>
-      <c r="K16" s="7">
+      <c r="W16" s="7">
         <v>0.36</v>
       </c>
-      <c r="L16" s="7">
+      <c r="X16" s="7">
         <v>63.96</v>
       </c>
-      <c r="M16" s="7">
+      <c r="Y16" s="7">
         <v>0.96</v>
       </c>
-      <c r="N16" s="7">
+      <c r="Z16" s="7">
         <v>0.1607</v>
       </c>
-      <c r="O16" s="7">
+      <c r="AA16" s="7">
         <v>0.1612</v>
       </c>
-      <c r="P16" s="7">
+      <c r="AB16" s="7">
         <v>0.1618</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="AC16" s="8">
         <v>0.1612333333333333</v>
       </c>
-      <c r="R16" s="15">
+      <c r="AD16" s="11">
         <v>3.179797338056456E-4</v>
       </c>
-      <c r="S16" s="14">
+      <c r="AE16" s="7">
         <v>169.89</v>
       </c>
-      <c r="T16" s="7">
+      <c r="AF16" s="7">
         <v>3.49</v>
       </c>
-      <c r="U16" s="7">
+      <c r="AG16" s="7">
         <v>199.73</v>
       </c>
-      <c r="V16" s="7">
+      <c r="AH16" s="7">
         <v>6.37</v>
       </c>
-      <c r="W16" s="7">
+      <c r="AI16" s="7">
         <v>259.4</v>
       </c>
-      <c r="X16" s="7">
+      <c r="AJ16" s="7">
         <v>12.68</v>
       </c>
-      <c r="Y16" s="7">
+      <c r="AK16" s="7">
         <v>289.48</v>
       </c>
-      <c r="Z16" s="7">
+      <c r="AL16" s="7">
         <v>20.81</v>
       </c>
-      <c r="AA16" s="7">
+      <c r="AM16" s="7">
         <v>320.89</v>
       </c>
-      <c r="AB16" s="7">
+      <c r="AN16" s="7">
         <v>13.76</v>
       </c>
-      <c r="AC16" s="7">
+      <c r="AO16" s="7">
         <v>322.28</v>
       </c>
-      <c r="AD16" s="7">
+      <c r="AP16" s="7">
         <v>10.85</v>
       </c>
-      <c r="AE16" s="7">
+      <c r="AQ16" s="7">
         <v>336.29</v>
       </c>
-      <c r="AF16" s="7">
+      <c r="AR16" s="7">
         <v>1.6</v>
       </c>
     </row>
@@ -1768,84 +2428,120 @@
         <v>1.0</v>
       </c>
       <c r="F17" s="7">
+        <v>90.83</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.96</v>
+      </c>
+      <c r="H17" s="7">
+        <v>84.44</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="J17" s="7">
+        <v>75.82</v>
+      </c>
+      <c r="K17" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="L17" s="7">
+        <v>66.84</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0.52</v>
+      </c>
+      <c r="N17" s="7">
+        <v>36.69</v>
+      </c>
+      <c r="O17" s="7">
+        <v>1.52</v>
+      </c>
+      <c r="P17" s="7">
+        <v>4.27</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="7">
         <v>36.15</v>
       </c>
-      <c r="G17" s="7">
+      <c r="S17" s="7">
         <v>0.44</v>
       </c>
-      <c r="H17" s="7">
+      <c r="T17" s="7">
         <v>51.16</v>
       </c>
-      <c r="I17" s="7">
+      <c r="U17" s="7">
         <v>0.28</v>
       </c>
-      <c r="J17" s="7">
+      <c r="V17" s="7">
         <v>17.04</v>
       </c>
-      <c r="K17" s="7">
+      <c r="W17" s="7">
         <v>0.32</v>
       </c>
-      <c r="L17" s="7">
+      <c r="X17" s="7">
         <v>59.19</v>
       </c>
-      <c r="M17" s="7">
+      <c r="Y17" s="7">
         <v>0.61</v>
       </c>
-      <c r="N17" s="7">
+      <c r="Z17" s="7">
         <v>0.141</v>
       </c>
-      <c r="O17" s="7">
+      <c r="AA17" s="7">
         <v>0.1443</v>
       </c>
-      <c r="P17" s="7">
+      <c r="AB17" s="7">
         <v>0.146</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="AC17" s="8">
         <v>0.1437666666666667</v>
       </c>
-      <c r="R17" s="9">
+      <c r="AD17" s="8">
         <v>0.001467802590420269</v>
       </c>
-      <c r="S17" s="14">
+      <c r="AE17" s="7">
         <v>154.84</v>
       </c>
-      <c r="T17" s="7">
+      <c r="AF17" s="7">
         <v>5.27</v>
       </c>
-      <c r="U17" s="7">
+      <c r="AG17" s="7">
         <v>181.99</v>
       </c>
-      <c r="V17" s="7">
+      <c r="AH17" s="7">
         <v>3.76</v>
       </c>
-      <c r="W17" s="7">
+      <c r="AI17" s="7">
         <v>236.27</v>
       </c>
-      <c r="X17" s="7">
+      <c r="AJ17" s="7">
         <v>4.18</v>
       </c>
-      <c r="Y17" s="7">
+      <c r="AK17" s="7">
         <v>299.1</v>
       </c>
-      <c r="Z17" s="7">
+      <c r="AL17" s="7">
         <v>8.88</v>
       </c>
-      <c r="AA17" s="7">
+      <c r="AM17" s="7">
         <v>321.41</v>
       </c>
-      <c r="AB17" s="7">
+      <c r="AN17" s="7">
         <v>7.24</v>
       </c>
-      <c r="AC17" s="7">
+      <c r="AO17" s="7">
         <v>323.8</v>
       </c>
-      <c r="AD17" s="7">
+      <c r="AP17" s="7">
         <v>5.77</v>
       </c>
-      <c r="AE17" s="7">
+      <c r="AQ17" s="7">
         <v>313.21</v>
       </c>
-      <c r="AF17" s="7">
+      <c r="AR17" s="7">
         <v>9.56</v>
       </c>
     </row>
@@ -1860,84 +2556,120 @@
         <v>2.0</v>
       </c>
       <c r="F18" s="7">
+        <v>87.65</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="H18" s="7">
+        <v>80.59</v>
+      </c>
+      <c r="I18" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="J18" s="7">
+        <v>74.72</v>
+      </c>
+      <c r="K18" s="7">
+        <v>1.59</v>
+      </c>
+      <c r="L18" s="7">
+        <v>67.36</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="N18" s="7">
+        <v>33.97</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="7">
+        <v>5.79</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="R18" s="7">
         <v>46.35</v>
       </c>
-      <c r="G18" s="7">
+      <c r="S18" s="7">
         <v>3.5</v>
       </c>
-      <c r="H18" s="7">
+      <c r="T18" s="7">
         <v>50.81</v>
       </c>
-      <c r="I18" s="7">
+      <c r="U18" s="7">
         <v>0.43</v>
       </c>
-      <c r="J18" s="7">
+      <c r="V18" s="7">
         <v>19.62</v>
       </c>
-      <c r="K18" s="7">
+      <c r="W18" s="7">
         <v>0.48</v>
       </c>
-      <c r="L18" s="7">
+      <c r="X18" s="7">
         <v>61.23</v>
       </c>
-      <c r="M18" s="7">
+      <c r="Y18" s="7">
         <v>0.54</v>
       </c>
-      <c r="N18" s="7">
+      <c r="Z18" s="7">
         <v>0.1635</v>
       </c>
-      <c r="O18" s="7">
+      <c r="AA18" s="7">
         <v>0.1673</v>
       </c>
-      <c r="P18" s="7">
+      <c r="AB18" s="7">
         <v>0.154</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="AC18" s="8">
         <v>0.1616</v>
       </c>
-      <c r="R18" s="9">
+      <c r="AD18" s="8">
         <v>0.003955165398985654</v>
       </c>
-      <c r="S18" s="14">
+      <c r="AE18" s="7">
         <v>134.93</v>
       </c>
-      <c r="T18" s="7">
+      <c r="AF18" s="7">
         <v>5.31</v>
       </c>
-      <c r="U18" s="7">
+      <c r="AG18" s="7">
         <v>164.18</v>
       </c>
-      <c r="V18" s="7">
+      <c r="AH18" s="7">
         <v>9.44</v>
       </c>
-      <c r="W18" s="7">
+      <c r="AI18" s="7">
         <v>222.68</v>
       </c>
-      <c r="X18" s="7">
+      <c r="AJ18" s="7">
         <v>19.18</v>
       </c>
-      <c r="Y18" s="7">
+      <c r="AK18" s="7">
         <v>276.13</v>
       </c>
-      <c r="Z18" s="7">
+      <c r="AL18" s="7">
         <v>15.68</v>
       </c>
-      <c r="AA18" s="7">
+      <c r="AM18" s="7">
         <v>273.96</v>
       </c>
-      <c r="AB18" s="7">
+      <c r="AN18" s="7">
         <v>22.9</v>
       </c>
-      <c r="AC18" s="7">
+      <c r="AO18" s="7">
         <v>271.96</v>
       </c>
-      <c r="AD18" s="7">
+      <c r="AP18" s="7">
         <v>15.94</v>
       </c>
-      <c r="AE18" s="7">
+      <c r="AQ18" s="7">
         <v>288.53</v>
       </c>
-      <c r="AF18" s="7">
+      <c r="AR18" s="7">
         <v>18.94</v>
       </c>
     </row>
@@ -1945,85 +2677,121 @@
       <c r="D19" s="6">
         <v>0.7</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="10">
+        <v>84.18601536311839</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0.9091840279411826</v>
+      </c>
+      <c r="H19" s="10">
+        <v>68.45509097589972</v>
+      </c>
+      <c r="I19" s="10">
+        <v>0.3598969647516739</v>
+      </c>
+      <c r="J19" s="10">
+        <v>52.14960489232937</v>
+      </c>
+      <c r="K19" s="10">
+        <v>1.185313900570214</v>
+      </c>
+      <c r="L19" s="10">
+        <v>45.01676355204248</v>
+      </c>
+      <c r="M19" s="10">
+        <v>1.330500135072292</v>
+      </c>
+      <c r="N19" s="10">
+        <v>16.48539819089498</v>
+      </c>
+      <c r="O19" s="10">
+        <v>1.9240272456203</v>
+      </c>
+      <c r="P19" s="10">
+        <v>-1.464601584160882</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>1.305516197334365</v>
+      </c>
+      <c r="R19" s="7">
         <v>89.0481433832673</v>
       </c>
-      <c r="G19" s="7">
+      <c r="S19" s="7">
         <v>1.18647372096663</v>
       </c>
-      <c r="H19" s="7">
+      <c r="T19" s="7">
         <v>49.10348294734803</v>
       </c>
-      <c r="I19" s="7">
+      <c r="U19" s="7">
         <v>0.2886175748144108</v>
       </c>
-      <c r="J19" s="13">
+      <c r="V19" s="10">
         <v>29.00836015821067</v>
       </c>
-      <c r="K19" s="13">
+      <c r="W19" s="10">
         <v>0.3694448583843284</v>
       </c>
-      <c r="L19" s="13">
+      <c r="X19" s="10">
         <v>64.31160131613926</v>
       </c>
-      <c r="M19" s="13">
+      <c r="Y19" s="10">
         <v>0.6415226993872251</v>
       </c>
-      <c r="N19" s="7">
+      <c r="Z19" s="7">
         <v>0.2092008279381022</v>
       </c>
-      <c r="O19" s="7">
+      <c r="AA19" s="7">
         <v>0.2119277039286546</v>
       </c>
-      <c r="P19" s="7">
+      <c r="AB19" s="7">
         <v>0.2151163213759757</v>
       </c>
-      <c r="Q19" s="12">
+      <c r="AC19" s="8">
         <v>0.2120816177475775</v>
       </c>
-      <c r="R19" s="9">
+      <c r="AD19" s="8">
         <v>0.0017093890478884193</v>
       </c>
-      <c r="S19" s="10">
+      <c r="AE19" s="9">
         <v>118.79560716723606</v>
       </c>
-      <c r="T19" s="11">
+      <c r="AF19" s="9">
         <v>3.5000000000000004</v>
       </c>
-      <c r="U19" s="11">
+      <c r="AG19" s="9">
         <v>162.5</v>
       </c>
-      <c r="V19" s="11">
+      <c r="AH19" s="9">
         <v>3.71</v>
       </c>
-      <c r="W19" s="11">
+      <c r="AI19" s="9">
         <v>249.90658645684127</v>
       </c>
-      <c r="X19" s="11">
+      <c r="AJ19" s="9">
         <v>8.4</v>
       </c>
-      <c r="Y19" s="11">
+      <c r="AK19" s="9">
         <v>239.93913407353057</v>
       </c>
-      <c r="Z19" s="11">
+      <c r="AL19" s="9">
         <v>4.3999999999999995</v>
       </c>
-      <c r="AA19" s="11">
+      <c r="AM19" s="9">
         <v>237.36302169990267</v>
       </c>
-      <c r="AB19" s="11">
+      <c r="AN19" s="9">
         <v>3.8</v>
       </c>
-      <c r="AC19" s="11">
+      <c r="AO19" s="9">
         <v>243.73038508421251</v>
       </c>
-      <c r="AD19" s="11">
+      <c r="AP19" s="9">
         <v>3.9</v>
       </c>
-      <c r="AE19" s="11">
+      <c r="AQ19" s="9">
         <v>230.20642844706484</v>
       </c>
-      <c r="AF19" s="11">
+      <c r="AR19" s="9">
         <v>5.7</v>
       </c>
     </row>
@@ -2031,85 +2799,121 @@
       <c r="D20" s="6">
         <v>1.0</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="10">
+        <v>81.2426020220643</v>
+      </c>
+      <c r="G20" s="10">
+        <v>1.292547431931647</v>
+      </c>
+      <c r="H20" s="10">
+        <v>64.06396712380118</v>
+      </c>
+      <c r="I20" s="10">
+        <v>1.073899233258391</v>
+      </c>
+      <c r="J20" s="10">
+        <v>46.65428644688735</v>
+      </c>
+      <c r="K20" s="10">
+        <v>1.173277863282734</v>
+      </c>
+      <c r="L20" s="10">
+        <v>38.83791036948328</v>
+      </c>
+      <c r="M20" s="10">
+        <v>1.6619042723634</v>
+      </c>
+      <c r="N20" s="10">
+        <v>7.572406059866998</v>
+      </c>
+      <c r="O20" s="10">
+        <v>3.625971252381777</v>
+      </c>
+      <c r="P20" s="10">
+        <v>-5.827536358239263</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>1.025210659646665</v>
+      </c>
+      <c r="R20" s="7">
         <v>78.38053241938218</v>
       </c>
-      <c r="G20" s="7">
+      <c r="S20" s="7">
         <v>3.91627937022548</v>
       </c>
-      <c r="H20" s="7">
+      <c r="T20" s="7">
         <v>49.20273354407312</v>
       </c>
-      <c r="I20" s="7">
+      <c r="U20" s="7">
         <v>0.2538071006812823</v>
       </c>
-      <c r="J20" s="13">
+      <c r="V20" s="10">
         <v>27.35995235026642</v>
       </c>
-      <c r="K20" s="13">
+      <c r="W20" s="10">
         <v>0.2903977663608577</v>
       </c>
-      <c r="L20" s="13">
+      <c r="X20" s="10">
         <v>63.35090212594795</v>
       </c>
-      <c r="M20" s="13">
+      <c r="Y20" s="10">
         <v>0.3736357215980802</v>
       </c>
-      <c r="N20" s="7">
+      <c r="Z20" s="7">
         <v>0.1972999767318492</v>
       </c>
-      <c r="O20" s="7">
+      <c r="AA20" s="7">
         <v>0.1954871269910046</v>
       </c>
-      <c r="P20" s="7">
+      <c r="AB20" s="7">
         <v>0.2009341581326582</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="AC20" s="8">
         <v>0.1979070872851707</v>
       </c>
-      <c r="R20" s="9">
+      <c r="AD20" s="8">
         <v>0.0016014550136778467</v>
       </c>
-      <c r="S20" s="10">
+      <c r="AE20" s="9">
         <v>141.83519345970382</v>
       </c>
-      <c r="T20" s="11">
+      <c r="AF20" s="9">
         <v>1.0</v>
       </c>
-      <c r="U20" s="11">
+      <c r="AG20" s="9">
         <v>186.45</v>
       </c>
-      <c r="V20" s="11">
+      <c r="AH20" s="9">
         <v>2.56</v>
       </c>
-      <c r="W20" s="11">
+      <c r="AI20" s="9">
         <v>275.68332578784714</v>
       </c>
-      <c r="X20" s="11">
+      <c r="AJ20" s="9">
         <v>6.800000000000001</v>
       </c>
-      <c r="Y20" s="11">
+      <c r="AK20" s="9">
         <v>262.7928796855829</v>
       </c>
-      <c r="Z20" s="11">
+      <c r="AL20" s="9">
         <v>4.1000000000000005</v>
       </c>
-      <c r="AA20" s="11">
+      <c r="AM20" s="9">
         <v>261.1442893792361</v>
       </c>
-      <c r="AB20" s="11">
+      <c r="AN20" s="9">
         <v>5.3</v>
       </c>
-      <c r="AC20" s="11">
+      <c r="AO20" s="9">
         <v>253.0857101614734</v>
       </c>
-      <c r="AD20" s="11">
+      <c r="AP20" s="9">
         <v>5.0</v>
       </c>
-      <c r="AE20" s="11">
+      <c r="AQ20" s="9">
         <v>243.4196143272379</v>
       </c>
-      <c r="AF20" s="11">
+      <c r="AR20" s="9">
         <v>2.1</v>
       </c>
     </row>
@@ -2117,85 +2921,121 @@
       <c r="D21" s="6">
         <v>2.0</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="10">
+        <v>86.6940144786473</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0.7114936580565371</v>
+      </c>
+      <c r="H21" s="10">
+        <v>64.9105623379963</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0.7718934035498882</v>
+      </c>
+      <c r="J21" s="10">
+        <v>38.00580449625971</v>
+      </c>
+      <c r="K21" s="10">
+        <v>1.319861812881732</v>
+      </c>
+      <c r="L21" s="10">
+        <v>28.60627320686058</v>
+      </c>
+      <c r="M21" s="10">
+        <v>1.073964193309294</v>
+      </c>
+      <c r="N21" s="10">
+        <v>-0.99185195073595</v>
+      </c>
+      <c r="O21" s="10">
+        <v>0.09076982424857508</v>
+      </c>
+      <c r="P21" s="10">
+        <v>-10.13385366047071</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>0.2784644868687212</v>
+      </c>
+      <c r="R21" s="7">
         <v>65.35706344934643</v>
       </c>
-      <c r="G21" s="7">
+      <c r="S21" s="7">
         <v>2.482883743031702</v>
       </c>
-      <c r="H21" s="7">
+      <c r="T21" s="7">
         <v>50.52225618415896</v>
       </c>
-      <c r="I21" s="7">
+      <c r="U21" s="7">
         <v>1.269214306624886</v>
       </c>
-      <c r="J21" s="13">
+      <c r="V21" s="10">
         <v>20.68191732117495</v>
       </c>
-      <c r="K21" s="13">
+      <c r="W21" s="10">
         <v>0.04663818994114876</v>
       </c>
-      <c r="L21" s="13">
+      <c r="X21" s="10">
         <v>66.32566586185372</v>
       </c>
-      <c r="M21" s="13">
+      <c r="Y21" s="10">
         <v>3.327097647494963</v>
       </c>
-      <c r="N21" s="7">
+      <c r="Z21" s="7">
         <v>0.1999504778438347</v>
       </c>
-      <c r="O21" s="7">
+      <c r="AA21" s="7">
         <v>0.197023081122061</v>
       </c>
-      <c r="P21" s="7">
+      <c r="AB21" s="7">
         <v>0.1885801357962559</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="AC21" s="8">
         <v>0.1951845649207172</v>
       </c>
-      <c r="R21" s="9">
+      <c r="AD21" s="8">
         <v>0.003408630024740504</v>
       </c>
-      <c r="S21" s="10">
+      <c r="AE21" s="9">
         <v>257.23724108415917</v>
       </c>
-      <c r="T21" s="11">
+      <c r="AF21" s="9">
         <v>4.2</v>
       </c>
-      <c r="U21" s="11">
+      <c r="AG21" s="9">
         <v>262.27</v>
       </c>
-      <c r="V21" s="11">
+      <c r="AH21" s="9">
         <v>4.22</v>
       </c>
-      <c r="W21" s="11">
+      <c r="AI21" s="9">
         <v>272.34655321910924</v>
       </c>
-      <c r="X21" s="11">
+      <c r="AJ21" s="9">
         <v>4.3999999999999995</v>
       </c>
-      <c r="Y21" s="11">
+      <c r="AK21" s="9">
         <v>267.442043712898</v>
       </c>
-      <c r="Z21" s="11">
+      <c r="AL21" s="9">
         <v>8.7</v>
       </c>
-      <c r="AA21" s="11">
+      <c r="AM21" s="9">
         <v>261.17994912167387</v>
       </c>
-      <c r="AB21" s="11">
+      <c r="AN21" s="9">
         <v>9.8</v>
       </c>
-      <c r="AC21" s="11">
+      <c r="AO21" s="9">
         <v>255.9129215265774</v>
       </c>
-      <c r="AD21" s="11">
+      <c r="AP21" s="9">
         <v>7.000000000000001</v>
       </c>
-      <c r="AE21" s="11">
+      <c r="AQ21" s="9">
         <v>235.408294280136</v>
       </c>
-      <c r="AF21" s="11">
+      <c r="AR21" s="9">
         <v>8.0</v>
       </c>
     </row>
@@ -2203,85 +3043,121 @@
       <c r="D22" s="6">
         <v>3.0</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="10">
+        <v>86.57815055361479</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0.7989513576844337</v>
+      </c>
+      <c r="H22" s="10">
+        <v>64.15458644690212</v>
+      </c>
+      <c r="I22" s="10">
+        <v>0.71808930421684</v>
+      </c>
+      <c r="J22" s="10">
+        <v>35.78785292872072</v>
+      </c>
+      <c r="K22" s="10">
+        <v>2.012024404631783</v>
+      </c>
+      <c r="L22" s="10">
+        <v>26.79474108383413</v>
+      </c>
+      <c r="M22" s="10">
+        <v>1.643657644782541</v>
+      </c>
+      <c r="N22" s="10">
+        <v>-1.17770629571225</v>
+      </c>
+      <c r="O22" s="10">
+        <v>0.2509473820695613</v>
+      </c>
+      <c r="P22" s="10">
+        <v>-11.78482783718485</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>0.1444021369679515</v>
+      </c>
+      <c r="R22" s="7">
         <v>71.69835746230225</v>
       </c>
-      <c r="G22" s="7">
+      <c r="S22" s="7">
         <v>1.744662889343355</v>
       </c>
-      <c r="H22" s="7">
+      <c r="T22" s="7">
         <v>50.57422063689638</v>
       </c>
-      <c r="I22" s="7">
+      <c r="U22" s="7">
         <v>0.1278441837045718</v>
       </c>
-      <c r="J22" s="13">
+      <c r="V22" s="10">
         <v>25.88702503377038</v>
       </c>
-      <c r="K22" s="13">
+      <c r="W22" s="10">
         <v>0.6750472904119466</v>
       </c>
-      <c r="L22" s="13">
+      <c r="X22" s="10">
         <v>66.37588979908838</v>
       </c>
-      <c r="M22" s="13">
+      <c r="Y22" s="10">
         <v>0.7460293320340622</v>
       </c>
-      <c r="N22" s="7">
+      <c r="Z22" s="7">
         <v>0.2177557502118987</v>
       </c>
-      <c r="O22" s="7">
+      <c r="AA22" s="7">
         <v>0.2151644077647281</v>
       </c>
-      <c r="P22" s="7">
+      <c r="AB22" s="7">
         <v>0.2145954997463901</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="AC22" s="8">
         <v>0.215838552574339</v>
       </c>
-      <c r="R22" s="9">
+      <c r="AD22" s="8">
         <v>9.725651939468739E-4</v>
       </c>
-      <c r="S22" s="10">
+      <c r="AE22" s="9">
         <v>205.29349393528</v>
       </c>
-      <c r="T22" s="11">
+      <c r="AF22" s="9">
         <v>7.8</v>
       </c>
-      <c r="U22" s="11">
+      <c r="AG22" s="9">
         <v>216.76</v>
       </c>
-      <c r="V22" s="11">
+      <c r="AH22" s="9">
         <v>5.29</v>
       </c>
-      <c r="W22" s="11">
+      <c r="AI22" s="9">
         <v>239.68541823775467</v>
       </c>
-      <c r="X22" s="11">
+      <c r="AJ22" s="9">
         <v>1.4000000000000001</v>
       </c>
-      <c r="Y22" s="11">
+      <c r="AK22" s="9">
         <v>231.99150168640784</v>
       </c>
-      <c r="Z22" s="11">
+      <c r="AL22" s="9">
         <v>2.9000000000000004</v>
       </c>
-      <c r="AA22" s="11">
+      <c r="AM22" s="9">
         <v>230.54378229165394</v>
       </c>
-      <c r="AB22" s="11">
+      <c r="AN22" s="9">
         <v>0.2</v>
       </c>
-      <c r="AC22" s="11">
+      <c r="AO22" s="9">
         <v>221.193914515624</v>
       </c>
-      <c r="AD22" s="11">
+      <c r="AP22" s="9">
         <v>1.2</v>
       </c>
-      <c r="AE22" s="11">
+      <c r="AQ22" s="9">
         <v>201.890598443713</v>
       </c>
-      <c r="AF22" s="11">
+      <c r="AR22" s="9">
         <v>2.3</v>
       </c>
     </row>
@@ -2289,85 +3165,121 @@
       <c r="E23" s="6">
         <v>0.7</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="10">
+        <v>81.77790114931372</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0.3691331159436907</v>
+      </c>
+      <c r="H23" s="10">
+        <v>65.43236709011298</v>
+      </c>
+      <c r="I23" s="10">
+        <v>0.3955130409555167</v>
+      </c>
+      <c r="J23" s="10">
+        <v>57.59146145032134</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0.4985572271949375</v>
+      </c>
+      <c r="L23" s="10">
+        <v>52.98138102135169</v>
+      </c>
+      <c r="M23" s="10">
+        <v>0.5283540464278488</v>
+      </c>
+      <c r="N23" s="10">
+        <v>34.54105930547313</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0.6677593534746807</v>
+      </c>
+      <c r="P23" s="10">
+        <v>21.76236995963651</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>0.4820305041701456</v>
+      </c>
+      <c r="R23" s="6">
         <v>82.86703293255823</v>
       </c>
-      <c r="G23" s="6">
+      <c r="S23" s="6">
         <v>2.565762402027691</v>
       </c>
-      <c r="H23" s="6">
+      <c r="T23" s="6">
         <v>49.44605984969515</v>
       </c>
-      <c r="I23" s="6">
+      <c r="U23" s="6">
         <v>0.1815763206872865</v>
       </c>
-      <c r="J23" s="13">
+      <c r="V23" s="10">
         <v>28.97870735652493</v>
       </c>
-      <c r="K23" s="13">
+      <c r="W23" s="10">
         <v>1.016937112532046</v>
       </c>
-      <c r="L23" s="13">
+      <c r="X23" s="10">
         <v>67.95761378035826</v>
       </c>
-      <c r="M23" s="13">
+      <c r="Y23" s="10">
         <v>1.048582259919522</v>
       </c>
-      <c r="N23" s="7">
+      <c r="Z23" s="7">
         <v>0.2065312987831774</v>
       </c>
-      <c r="O23" s="7">
+      <c r="AA23" s="7">
         <v>0.2034094888227279</v>
       </c>
-      <c r="P23" s="7">
+      <c r="AB23" s="7">
         <v>0.1972628984293499</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="AC23" s="8">
         <v>0.2024012286784184</v>
       </c>
-      <c r="R23" s="9">
+      <c r="AD23" s="8">
         <v>0.0027226367531408297</v>
       </c>
-      <c r="S23" s="10">
+      <c r="AE23" s="9">
         <v>74.73931289322557</v>
       </c>
-      <c r="T23" s="11">
+      <c r="AF23" s="9">
         <v>4.9</v>
       </c>
-      <c r="U23" s="11">
+      <c r="AG23" s="9">
         <v>89.14</v>
       </c>
-      <c r="V23" s="11">
+      <c r="AH23" s="9">
         <v>3.38</v>
       </c>
-      <c r="W23" s="11">
+      <c r="AI23" s="9">
         <v>117.93915715725419</v>
       </c>
-      <c r="X23" s="11">
+      <c r="AJ23" s="9">
         <v>1.2</v>
       </c>
-      <c r="Y23" s="11">
+      <c r="AK23" s="9">
         <v>149.33480197505727</v>
       </c>
-      <c r="Z23" s="11">
+      <c r="AL23" s="9">
         <v>2.6</v>
       </c>
-      <c r="AA23" s="11">
+      <c r="AM23" s="9">
         <v>165.62585502308067</v>
       </c>
-      <c r="AB23" s="11">
+      <c r="AN23" s="9">
         <v>1.3</v>
       </c>
-      <c r="AC23" s="11">
+      <c r="AO23" s="9">
         <v>187.73450290455395</v>
       </c>
-      <c r="AD23" s="11">
+      <c r="AP23" s="9">
         <v>4.7</v>
       </c>
-      <c r="AE23" s="11">
+      <c r="AQ23" s="9">
         <v>190.7379520486293</v>
       </c>
-      <c r="AF23" s="11">
+      <c r="AR23" s="9">
         <v>2.9000000000000004</v>
       </c>
     </row>
@@ -2375,85 +3287,121 @@
       <c r="E24" s="6">
         <v>1.0</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="10">
+        <v>79.28518883688204</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0.4342792604025347</v>
+      </c>
+      <c r="H24" s="10">
+        <v>62.88819200284733</v>
+      </c>
+      <c r="I24" s="10">
+        <v>0.2472251768427733</v>
+      </c>
+      <c r="J24" s="10">
+        <v>53.8168715161362</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.3650401921196924</v>
+      </c>
+      <c r="L24" s="10">
+        <v>49.16109123093711</v>
+      </c>
+      <c r="M24" s="10">
+        <v>0.3538628427661411</v>
+      </c>
+      <c r="N24" s="10">
+        <v>30.53797009014078</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0.3334940408981691</v>
+      </c>
+      <c r="P24" s="10">
+        <v>18.03367078727906</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>0.2150558749298457</v>
+      </c>
+      <c r="R24" s="6">
         <v>75.00201936637428</v>
       </c>
-      <c r="G24" s="6">
+      <c r="S24" s="6">
         <v>2.983380937693707</v>
       </c>
-      <c r="H24" s="6">
+      <c r="T24" s="6">
         <v>49.33450488256515</v>
       </c>
-      <c r="I24" s="6">
+      <c r="U24" s="6">
         <v>0.3128919174986041</v>
       </c>
-      <c r="J24" s="13">
+      <c r="V24" s="10">
         <v>25.60440652380082</v>
       </c>
-      <c r="K24" s="13">
+      <c r="W24" s="10">
         <v>0.633579669032225</v>
       </c>
-      <c r="L24" s="13">
+      <c r="X24" s="10">
         <v>66.85940228952235</v>
       </c>
-      <c r="M24" s="13">
+      <c r="Y24" s="10">
         <v>0.4474666968200189</v>
       </c>
-      <c r="N24" s="7">
+      <c r="Z24" s="7">
         <v>0.1943147706918784</v>
       </c>
-      <c r="O24" s="7">
+      <c r="AA24" s="7">
         <v>0.1936770907615779</v>
       </c>
-      <c r="P24" s="7">
+      <c r="AB24" s="7">
         <v>0.1924486319501935</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="AC24" s="8">
         <v>0.1934801644678833</v>
       </c>
-      <c r="R24" s="9">
+      <c r="AD24" s="8">
         <v>5.476323050690061E-4</v>
       </c>
-      <c r="S24" s="10">
+      <c r="AE24" s="9">
         <v>77.96651649203147</v>
       </c>
-      <c r="T24" s="11">
+      <c r="AF24" s="9">
         <v>4.3</v>
       </c>
-      <c r="U24" s="11">
+      <c r="AG24" s="9">
         <v>94.31</v>
       </c>
-      <c r="V24" s="11">
+      <c r="AH24" s="9">
         <v>2.73</v>
       </c>
-      <c r="W24" s="11">
+      <c r="AI24" s="9">
         <v>127.00274842372134</v>
       </c>
-      <c r="X24" s="11">
+      <c r="AJ24" s="9">
         <v>3.4000000000000004</v>
       </c>
-      <c r="Y24" s="11">
+      <c r="AK24" s="9">
         <v>149.18364608574467</v>
       </c>
-      <c r="Z24" s="11">
+      <c r="AL24" s="9">
         <v>3.9</v>
       </c>
-      <c r="AA24" s="11">
+      <c r="AM24" s="9">
         <v>171.8301810908432</v>
       </c>
-      <c r="AB24" s="11">
+      <c r="AN24" s="9">
         <v>3.4000000000000004</v>
       </c>
-      <c r="AC24" s="11">
+      <c r="AO24" s="9">
         <v>208.32032633715366</v>
       </c>
-      <c r="AD24" s="11">
+      <c r="AP24" s="9">
         <v>6.3</v>
       </c>
-      <c r="AE24" s="11">
+      <c r="AQ24" s="9">
         <v>205.56669653732936</v>
       </c>
-      <c r="AF24" s="11">
+      <c r="AR24" s="9">
         <v>0.8</v>
       </c>
     </row>
@@ -2462,75 +3410,111 @@
         <v>2.0</v>
       </c>
       <c r="F25" s="6">
+        <v>89.01</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1.04</v>
+      </c>
+      <c r="H25" s="6">
+        <v>73.79</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="J25" s="6">
+        <v>65.53</v>
+      </c>
+      <c r="K25" s="6">
+        <v>0.74</v>
+      </c>
+      <c r="L25" s="6">
+        <v>55.47</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="N25" s="6">
+        <v>39.54</v>
+      </c>
+      <c r="O25" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="P25" s="6">
+        <v>29.48</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0.54</v>
+      </c>
+      <c r="R25" s="6">
         <v>85.74892</v>
       </c>
-      <c r="G25" s="6">
+      <c r="S25" s="6">
         <v>4.343431994580431</v>
       </c>
-      <c r="H25" s="6">
+      <c r="T25" s="6">
         <v>48.72223400707693</v>
       </c>
-      <c r="I25" s="6">
+      <c r="U25" s="6">
         <v>1.54167771885102</v>
       </c>
-      <c r="J25" s="13">
+      <c r="V25" s="10">
         <v>49.37446984808432</v>
       </c>
-      <c r="K25" s="13">
+      <c r="W25" s="10">
         <v>3.756724844909057</v>
       </c>
-      <c r="L25" s="13">
+      <c r="X25" s="10">
         <v>63.2545941277447</v>
       </c>
-      <c r="M25" s="13">
+      <c r="Y25" s="10">
         <v>0.9731452218857441</v>
       </c>
-      <c r="Q25" s="12">
+      <c r="AC25" s="8">
         <v>0.228</v>
       </c>
-      <c r="R25" s="9">
+      <c r="AD25" s="8">
         <v>0.006244997998398403</v>
       </c>
-      <c r="S25" s="14">
+      <c r="AE25" s="7">
         <v>42.71484159166465</v>
       </c>
-      <c r="T25" s="11">
+      <c r="AF25" s="9">
         <v>2.026291190884083</v>
       </c>
-      <c r="U25" s="11">
+      <c r="AG25" s="9">
         <v>54.7</v>
       </c>
-      <c r="V25" s="11">
+      <c r="AH25" s="9">
         <v>1.7</v>
       </c>
-      <c r="W25" s="11">
+      <c r="AI25" s="9">
         <v>78.47970527286436</v>
       </c>
-      <c r="X25" s="11">
+      <c r="AJ25" s="9">
         <v>1.987869150904027</v>
       </c>
-      <c r="Y25" s="11">
+      <c r="AK25" s="9">
         <v>88.81213182315925</v>
       </c>
-      <c r="Z25" s="11">
+      <c r="AL25" s="9">
         <v>2.199119433131225</v>
       </c>
-      <c r="AA25" s="11">
+      <c r="AM25" s="9">
         <v>101.4549364494276</v>
       </c>
-      <c r="AB25" s="11">
+      <c r="AN25" s="9">
         <v>1.961670576355626</v>
       </c>
-      <c r="AC25" s="11">
+      <c r="AO25" s="9">
         <v>112.0039560638274</v>
       </c>
-      <c r="AD25" s="11">
+      <c r="AP25" s="9">
         <v>3.442678156322653</v>
       </c>
-      <c r="AE25" s="11">
+      <c r="AQ25" s="9">
         <v>115.382405481801</v>
       </c>
-      <c r="AF25" s="11">
+      <c r="AR25" s="9">
         <v>4.326348150175688</v>
       </c>
     </row>
@@ -2539,3981 +3523,3891 @@
         <v>3.0</v>
       </c>
       <c r="F26" s="6">
+        <v>87.98</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="H26" s="6">
+        <v>77.72</v>
+      </c>
+      <c r="I26" s="6">
+        <v>1.38</v>
+      </c>
+      <c r="J26" s="6">
+        <v>66.67</v>
+      </c>
+      <c r="K26" s="6">
+        <v>1.46</v>
+      </c>
+      <c r="L26" s="6">
+        <v>55.51</v>
+      </c>
+      <c r="M26" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="N26" s="6">
+        <v>37.83</v>
+      </c>
+      <c r="O26" s="6">
+        <v>1.01</v>
+      </c>
+      <c r="P26" s="6">
+        <v>26.67</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>0.84</v>
+      </c>
+      <c r="R26" s="6">
         <v>110.38968</v>
       </c>
-      <c r="G26" s="6">
+      <c r="S26" s="6">
         <v>4.646917716861571</v>
       </c>
-      <c r="H26" s="6">
+      <c r="T26" s="6">
         <v>51.72393828630471</v>
       </c>
-      <c r="I26" s="6">
+      <c r="U26" s="6">
         <v>0.1030087882187284</v>
       </c>
-      <c r="J26" s="13">
+      <c r="V26" s="10">
         <v>60.73168100916474</v>
       </c>
-      <c r="K26" s="13">
+      <c r="W26" s="10">
         <v>4.669153324683568</v>
       </c>
-      <c r="L26" s="13">
+      <c r="X26" s="10">
         <v>60.16621966134054</v>
       </c>
-      <c r="M26" s="13">
+      <c r="Y26" s="10">
         <v>1.319433183635669</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="AC26" s="8">
         <v>0.248</v>
       </c>
-      <c r="R26" s="9">
+      <c r="AD26" s="8">
         <v>0.005033222956847129</v>
       </c>
-      <c r="S26" s="14">
+      <c r="AE26" s="7">
         <v>49.47531920166992</v>
       </c>
-      <c r="T26" s="11">
+      <c r="AF26" s="9">
         <v>3.527062802376458</v>
       </c>
-      <c r="U26" s="11">
+      <c r="AG26" s="9">
         <v>61.9</v>
       </c>
-      <c r="V26" s="11">
+      <c r="AH26" s="9">
         <v>4.3</v>
       </c>
-      <c r="W26" s="11">
+      <c r="AI26" s="9">
         <v>87.22199839760599</v>
       </c>
-      <c r="X26" s="11">
+      <c r="AJ26" s="9">
         <v>1.260375235822281</v>
       </c>
-      <c r="Y26" s="11">
+      <c r="AK26" s="9">
         <v>96.64986862154689</v>
       </c>
-      <c r="Z26" s="11">
+      <c r="AL26" s="9">
         <v>2.334668932419874</v>
       </c>
-      <c r="AA26" s="11">
+      <c r="AM26" s="9">
         <v>113.8445849615078</v>
       </c>
-      <c r="AB26" s="11">
+      <c r="AN26" s="9">
         <v>1.135970856435371</v>
       </c>
-      <c r="AC26" s="11">
+      <c r="AO26" s="9">
         <v>118.03760701509</v>
       </c>
-      <c r="AD26" s="11">
+      <c r="AP26" s="9">
         <v>3.171384684367847</v>
       </c>
-      <c r="AE26" s="11">
+      <c r="AQ26" s="9">
         <v>129.8586855134664</v>
       </c>
-      <c r="AF26" s="11">
+      <c r="AR26" s="9">
         <v>1.942780602199172</v>
       </c>
     </row>
     <row r="27">
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="Q27" s="14"/>
-      <c r="S27" s="14"/>
-    </row>
-    <row r="28">
-      <c r="Q28" s="14"/>
-      <c r="S28" s="14"/>
-    </row>
-    <row r="29">
-      <c r="Q29" s="14"/>
-      <c r="S29" s="14"/>
-    </row>
-    <row r="30">
-      <c r="Q30" s="14"/>
-      <c r="S30" s="14"/>
-    </row>
-    <row r="31">
-      <c r="Q31" s="14"/>
-      <c r="S31" s="14"/>
-    </row>
-    <row r="32">
-      <c r="Q32" s="14"/>
-      <c r="S32" s="14"/>
-    </row>
-    <row r="33">
-      <c r="Q33" s="14"/>
-      <c r="S33" s="14"/>
-    </row>
-    <row r="34">
-      <c r="Q34" s="14"/>
-      <c r="S34" s="14"/>
-    </row>
-    <row r="35">
-      <c r="Q35" s="14"/>
-      <c r="S35" s="14"/>
-    </row>
-    <row r="36">
-      <c r="Q36" s="14"/>
-      <c r="S36" s="14"/>
-    </row>
-    <row r="37">
-      <c r="Q37" s="14"/>
-      <c r="S37" s="14"/>
-    </row>
-    <row r="38">
-      <c r="Q38" s="14"/>
-      <c r="S38" s="14"/>
-    </row>
-    <row r="39">
-      <c r="Q39" s="14"/>
-      <c r="S39" s="14"/>
-    </row>
-    <row r="40">
-      <c r="Q40" s="14"/>
-      <c r="S40" s="14"/>
-    </row>
-    <row r="41">
-      <c r="Q41" s="14"/>
-      <c r="S41" s="14"/>
-    </row>
-    <row r="42">
-      <c r="Q42" s="14"/>
-      <c r="S42" s="14"/>
-    </row>
-    <row r="43">
-      <c r="Q43" s="14"/>
-      <c r="S43" s="14"/>
-    </row>
-    <row r="44">
-      <c r="Q44" s="14"/>
-      <c r="S44" s="14"/>
-    </row>
-    <row r="45">
-      <c r="Q45" s="14"/>
-      <c r="S45" s="14"/>
-    </row>
-    <row r="46">
-      <c r="Q46" s="14"/>
-      <c r="S46" s="14"/>
-    </row>
-    <row r="47">
-      <c r="Q47" s="14"/>
-      <c r="S47" s="14"/>
-    </row>
-    <row r="48">
-      <c r="Q48" s="14"/>
-      <c r="S48" s="14"/>
-    </row>
-    <row r="49">
-      <c r="Q49" s="14"/>
-      <c r="S49" s="14"/>
-    </row>
-    <row r="50">
-      <c r="Q50" s="14"/>
-      <c r="S50" s="14"/>
-    </row>
-    <row r="51">
-      <c r="Q51" s="14"/>
-      <c r="S51" s="14"/>
-    </row>
-    <row r="52">
-      <c r="Q52" s="14"/>
-      <c r="S52" s="14"/>
-    </row>
-    <row r="53">
-      <c r="Q53" s="14"/>
-      <c r="S53" s="14"/>
-    </row>
-    <row r="54">
-      <c r="Q54" s="14"/>
-      <c r="S54" s="14"/>
-    </row>
-    <row r="55">
-      <c r="Q55" s="14"/>
-      <c r="S55" s="14"/>
-    </row>
-    <row r="56">
-      <c r="Q56" s="14"/>
-      <c r="S56" s="14"/>
-    </row>
-    <row r="57">
-      <c r="Q57" s="14"/>
-      <c r="S57" s="14"/>
-    </row>
-    <row r="58">
-      <c r="Q58" s="14"/>
-      <c r="S58" s="14"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
+      <c r="U27" s="6"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
     </row>
     <row r="59">
-      <c r="Q59" s="14"/>
-      <c r="S59" s="14"/>
+      <c r="AC59" s="12"/>
+      <c r="AE59" s="12"/>
     </row>
     <row r="60">
-      <c r="Q60" s="14"/>
-      <c r="S60" s="14"/>
+      <c r="AC60" s="12"/>
+      <c r="AE60" s="12"/>
     </row>
     <row r="61">
-      <c r="Q61" s="14"/>
-      <c r="S61" s="14"/>
+      <c r="AC61" s="12"/>
+      <c r="AE61" s="12"/>
     </row>
     <row r="62">
-      <c r="Q62" s="14"/>
-      <c r="S62" s="14"/>
+      <c r="AC62" s="12"/>
+      <c r="AE62" s="12"/>
     </row>
     <row r="63">
-      <c r="Q63" s="14"/>
-      <c r="S63" s="14"/>
+      <c r="AC63" s="12"/>
+      <c r="AE63" s="12"/>
     </row>
     <row r="64">
-      <c r="Q64" s="14"/>
-      <c r="S64" s="14"/>
+      <c r="AC64" s="12"/>
+      <c r="AE64" s="12"/>
     </row>
     <row r="65">
-      <c r="Q65" s="14"/>
-      <c r="S65" s="14"/>
+      <c r="AC65" s="12"/>
+      <c r="AE65" s="12"/>
     </row>
     <row r="66">
-      <c r="Q66" s="14"/>
-      <c r="S66" s="14"/>
+      <c r="AC66" s="12"/>
+      <c r="AE66" s="12"/>
     </row>
     <row r="67">
-      <c r="Q67" s="14"/>
-      <c r="S67" s="14"/>
+      <c r="AC67" s="12"/>
+      <c r="AE67" s="12"/>
     </row>
     <row r="68">
-      <c r="Q68" s="14"/>
-      <c r="S68" s="14"/>
+      <c r="AC68" s="12"/>
+      <c r="AE68" s="12"/>
     </row>
     <row r="69">
-      <c r="Q69" s="14"/>
-      <c r="S69" s="14"/>
+      <c r="AC69" s="12"/>
+      <c r="AE69" s="12"/>
     </row>
     <row r="70">
-      <c r="Q70" s="14"/>
-      <c r="S70" s="14"/>
+      <c r="AC70" s="12"/>
+      <c r="AE70" s="12"/>
     </row>
     <row r="71">
-      <c r="Q71" s="14"/>
-      <c r="S71" s="14"/>
+      <c r="AC71" s="12"/>
+      <c r="AE71" s="12"/>
     </row>
     <row r="72">
-      <c r="Q72" s="14"/>
-      <c r="S72" s="14"/>
+      <c r="AC72" s="12"/>
+      <c r="AE72" s="12"/>
     </row>
     <row r="73">
-      <c r="Q73" s="14"/>
-      <c r="S73" s="14"/>
+      <c r="AC73" s="12"/>
+      <c r="AE73" s="12"/>
     </row>
     <row r="74">
-      <c r="Q74" s="14"/>
-      <c r="S74" s="14"/>
+      <c r="AC74" s="12"/>
+      <c r="AE74" s="12"/>
     </row>
     <row r="75">
-      <c r="Q75" s="14"/>
-      <c r="S75" s="14"/>
+      <c r="AC75" s="12"/>
+      <c r="AE75" s="12"/>
     </row>
     <row r="76">
-      <c r="Q76" s="14"/>
-      <c r="S76" s="14"/>
+      <c r="AC76" s="12"/>
+      <c r="AE76" s="12"/>
     </row>
     <row r="77">
-      <c r="Q77" s="14"/>
-      <c r="S77" s="14"/>
+      <c r="AC77" s="12"/>
+      <c r="AE77" s="12"/>
     </row>
     <row r="78">
-      <c r="Q78" s="14"/>
-      <c r="S78" s="14"/>
+      <c r="AC78" s="12"/>
+      <c r="AE78" s="12"/>
     </row>
     <row r="79">
-      <c r="Q79" s="14"/>
-      <c r="S79" s="14"/>
+      <c r="AC79" s="12"/>
+      <c r="AE79" s="12"/>
     </row>
     <row r="80">
-      <c r="Q80" s="14"/>
-      <c r="S80" s="14"/>
+      <c r="AC80" s="12"/>
+      <c r="AE80" s="12"/>
     </row>
     <row r="81">
-      <c r="Q81" s="14"/>
-      <c r="S81" s="14"/>
+      <c r="AC81" s="12"/>
+      <c r="AE81" s="12"/>
     </row>
     <row r="82">
-      <c r="Q82" s="14"/>
-      <c r="S82" s="14"/>
+      <c r="AC82" s="12"/>
+      <c r="AE82" s="12"/>
     </row>
     <row r="83">
-      <c r="Q83" s="14"/>
-      <c r="S83" s="14"/>
+      <c r="AC83" s="12"/>
+      <c r="AE83" s="12"/>
     </row>
     <row r="84">
-      <c r="Q84" s="14"/>
-      <c r="S84" s="14"/>
+      <c r="AC84" s="12"/>
+      <c r="AE84" s="12"/>
     </row>
     <row r="85">
-      <c r="Q85" s="14"/>
-      <c r="S85" s="14"/>
+      <c r="AC85" s="12"/>
+      <c r="AE85" s="12"/>
     </row>
     <row r="86">
-      <c r="Q86" s="14"/>
-      <c r="S86" s="14"/>
+      <c r="AC86" s="12"/>
+      <c r="AE86" s="12"/>
     </row>
     <row r="87">
-      <c r="Q87" s="14"/>
-      <c r="S87" s="14"/>
+      <c r="AC87" s="12"/>
+      <c r="AE87" s="12"/>
     </row>
     <row r="88">
-      <c r="Q88" s="14"/>
-      <c r="S88" s="14"/>
+      <c r="AC88" s="12"/>
+      <c r="AE88" s="12"/>
     </row>
     <row r="89">
-      <c r="Q89" s="14"/>
-      <c r="S89" s="14"/>
+      <c r="AC89" s="12"/>
+      <c r="AE89" s="12"/>
     </row>
     <row r="90">
-      <c r="Q90" s="14"/>
-      <c r="S90" s="14"/>
+      <c r="AC90" s="12"/>
+      <c r="AE90" s="12"/>
     </row>
     <row r="91">
-      <c r="Q91" s="14"/>
-      <c r="S91" s="14"/>
+      <c r="AC91" s="12"/>
+      <c r="AE91" s="12"/>
     </row>
     <row r="92">
-      <c r="Q92" s="14"/>
-      <c r="S92" s="14"/>
+      <c r="AC92" s="12"/>
+      <c r="AE92" s="12"/>
     </row>
     <row r="93">
-      <c r="Q93" s="14"/>
-      <c r="S93" s="14"/>
+      <c r="AC93" s="12"/>
+      <c r="AE93" s="12"/>
     </row>
     <row r="94">
-      <c r="Q94" s="14"/>
-      <c r="S94" s="14"/>
+      <c r="AC94" s="12"/>
+      <c r="AE94" s="12"/>
     </row>
     <row r="95">
-      <c r="Q95" s="14"/>
-      <c r="S95" s="14"/>
+      <c r="AC95" s="12"/>
+      <c r="AE95" s="12"/>
     </row>
     <row r="96">
-      <c r="Q96" s="14"/>
-      <c r="S96" s="14"/>
+      <c r="AC96" s="12"/>
+      <c r="AE96" s="12"/>
     </row>
     <row r="97">
-      <c r="Q97" s="14"/>
-      <c r="S97" s="14"/>
+      <c r="AC97" s="12"/>
+      <c r="AE97" s="12"/>
     </row>
     <row r="98">
-      <c r="Q98" s="14"/>
-      <c r="S98" s="14"/>
+      <c r="AC98" s="12"/>
+      <c r="AE98" s="12"/>
     </row>
     <row r="99">
-      <c r="Q99" s="14"/>
-      <c r="S99" s="14"/>
+      <c r="AC99" s="12"/>
+      <c r="AE99" s="12"/>
     </row>
     <row r="100">
-      <c r="Q100" s="14"/>
-      <c r="S100" s="14"/>
+      <c r="AC100" s="12"/>
+      <c r="AE100" s="12"/>
     </row>
     <row r="101">
-      <c r="Q101" s="14"/>
-      <c r="S101" s="14"/>
+      <c r="AC101" s="12"/>
+      <c r="AE101" s="12"/>
     </row>
     <row r="102">
-      <c r="Q102" s="14"/>
-      <c r="S102" s="14"/>
+      <c r="AC102" s="12"/>
+      <c r="AE102" s="12"/>
     </row>
     <row r="103">
-      <c r="Q103" s="14"/>
-      <c r="S103" s="14"/>
+      <c r="AC103" s="12"/>
+      <c r="AE103" s="12"/>
     </row>
     <row r="104">
-      <c r="Q104" s="14"/>
-      <c r="S104" s="14"/>
+      <c r="AC104" s="12"/>
+      <c r="AE104" s="12"/>
     </row>
     <row r="105">
-      <c r="Q105" s="14"/>
-      <c r="S105" s="14"/>
+      <c r="AC105" s="12"/>
+      <c r="AE105" s="12"/>
     </row>
     <row r="106">
-      <c r="Q106" s="14"/>
-      <c r="S106" s="14"/>
+      <c r="AC106" s="12"/>
+      <c r="AE106" s="12"/>
     </row>
     <row r="107">
-      <c r="Q107" s="14"/>
-      <c r="S107" s="14"/>
+      <c r="AC107" s="12"/>
+      <c r="AE107" s="12"/>
     </row>
     <row r="108">
-      <c r="Q108" s="14"/>
-      <c r="S108" s="14"/>
+      <c r="AC108" s="12"/>
+      <c r="AE108" s="12"/>
     </row>
     <row r="109">
-      <c r="Q109" s="14"/>
-      <c r="S109" s="14"/>
+      <c r="AC109" s="12"/>
+      <c r="AE109" s="12"/>
     </row>
     <row r="110">
-      <c r="Q110" s="14"/>
-      <c r="S110" s="14"/>
+      <c r="AC110" s="12"/>
+      <c r="AE110" s="12"/>
     </row>
     <row r="111">
-      <c r="Q111" s="14"/>
-      <c r="S111" s="14"/>
+      <c r="AC111" s="12"/>
+      <c r="AE111" s="12"/>
     </row>
     <row r="112">
-      <c r="Q112" s="14"/>
-      <c r="S112" s="14"/>
+      <c r="AC112" s="12"/>
+      <c r="AE112" s="12"/>
     </row>
     <row r="113">
-      <c r="Q113" s="14"/>
-      <c r="S113" s="14"/>
+      <c r="AC113" s="12"/>
+      <c r="AE113" s="12"/>
     </row>
     <row r="114">
-      <c r="Q114" s="14"/>
-      <c r="S114" s="14"/>
+      <c r="AC114" s="12"/>
+      <c r="AE114" s="12"/>
     </row>
     <row r="115">
-      <c r="Q115" s="14"/>
-      <c r="S115" s="14"/>
+      <c r="AC115" s="12"/>
+      <c r="AE115" s="12"/>
     </row>
     <row r="116">
-      <c r="Q116" s="14"/>
-      <c r="S116" s="14"/>
+      <c r="AC116" s="12"/>
+      <c r="AE116" s="12"/>
     </row>
     <row r="117">
-      <c r="Q117" s="14"/>
-      <c r="S117" s="14"/>
+      <c r="AC117" s="12"/>
+      <c r="AE117" s="12"/>
     </row>
     <row r="118">
-      <c r="Q118" s="14"/>
-      <c r="S118" s="14"/>
+      <c r="AC118" s="12"/>
+      <c r="AE118" s="12"/>
     </row>
     <row r="119">
-      <c r="Q119" s="14"/>
-      <c r="S119" s="14"/>
+      <c r="AC119" s="12"/>
+      <c r="AE119" s="12"/>
     </row>
     <row r="120">
-      <c r="Q120" s="14"/>
-      <c r="S120" s="14"/>
+      <c r="AC120" s="12"/>
+      <c r="AE120" s="12"/>
     </row>
     <row r="121">
-      <c r="Q121" s="14"/>
-      <c r="S121" s="14"/>
+      <c r="AC121" s="12"/>
+      <c r="AE121" s="12"/>
     </row>
     <row r="122">
-      <c r="Q122" s="14"/>
-      <c r="S122" s="14"/>
+      <c r="AC122" s="12"/>
+      <c r="AE122" s="12"/>
     </row>
     <row r="123">
-      <c r="Q123" s="14"/>
-      <c r="S123" s="14"/>
+      <c r="AC123" s="12"/>
+      <c r="AE123" s="12"/>
     </row>
     <row r="124">
-      <c r="Q124" s="14"/>
-      <c r="S124" s="14"/>
+      <c r="AC124" s="12"/>
+      <c r="AE124" s="12"/>
     </row>
     <row r="125">
-      <c r="Q125" s="14"/>
-      <c r="S125" s="14"/>
+      <c r="AC125" s="12"/>
+      <c r="AE125" s="12"/>
     </row>
     <row r="126">
-      <c r="Q126" s="14"/>
-      <c r="S126" s="14"/>
+      <c r="AC126" s="12"/>
+      <c r="AE126" s="12"/>
     </row>
     <row r="127">
-      <c r="Q127" s="14"/>
-      <c r="S127" s="14"/>
+      <c r="AC127" s="12"/>
+      <c r="AE127" s="12"/>
     </row>
     <row r="128">
-      <c r="Q128" s="14"/>
-      <c r="S128" s="14"/>
+      <c r="AC128" s="12"/>
+      <c r="AE128" s="12"/>
     </row>
     <row r="129">
-      <c r="Q129" s="14"/>
-      <c r="S129" s="14"/>
+      <c r="AC129" s="12"/>
+      <c r="AE129" s="12"/>
     </row>
     <row r="130">
-      <c r="Q130" s="14"/>
-      <c r="S130" s="14"/>
+      <c r="AC130" s="12"/>
+      <c r="AE130" s="12"/>
     </row>
     <row r="131">
-      <c r="Q131" s="14"/>
-      <c r="S131" s="14"/>
+      <c r="AC131" s="12"/>
+      <c r="AE131" s="12"/>
     </row>
     <row r="132">
-      <c r="Q132" s="14"/>
-      <c r="S132" s="14"/>
+      <c r="AC132" s="12"/>
+      <c r="AE132" s="12"/>
     </row>
     <row r="133">
-      <c r="Q133" s="14"/>
-      <c r="S133" s="14"/>
+      <c r="AC133" s="12"/>
+      <c r="AE133" s="12"/>
     </row>
     <row r="134">
-      <c r="Q134" s="14"/>
-      <c r="S134" s="14"/>
+      <c r="AC134" s="12"/>
+      <c r="AE134" s="12"/>
     </row>
     <row r="135">
-      <c r="Q135" s="14"/>
-      <c r="S135" s="14"/>
+      <c r="AC135" s="12"/>
+      <c r="AE135" s="12"/>
     </row>
     <row r="136">
-      <c r="Q136" s="14"/>
-      <c r="S136" s="14"/>
+      <c r="AC136" s="12"/>
+      <c r="AE136" s="12"/>
     </row>
     <row r="137">
-      <c r="Q137" s="14"/>
-      <c r="S137" s="14"/>
+      <c r="AC137" s="12"/>
+      <c r="AE137" s="12"/>
     </row>
     <row r="138">
-      <c r="Q138" s="14"/>
-      <c r="S138" s="14"/>
+      <c r="AC138" s="12"/>
+      <c r="AE138" s="12"/>
     </row>
     <row r="139">
-      <c r="Q139" s="14"/>
-      <c r="S139" s="14"/>
+      <c r="AC139" s="12"/>
+      <c r="AE139" s="12"/>
     </row>
     <row r="140">
-      <c r="Q140" s="14"/>
-      <c r="S140" s="14"/>
+      <c r="AC140" s="12"/>
+      <c r="AE140" s="12"/>
     </row>
     <row r="141">
-      <c r="Q141" s="14"/>
-      <c r="S141" s="14"/>
+      <c r="AC141" s="12"/>
+      <c r="AE141" s="12"/>
     </row>
     <row r="142">
-      <c r="Q142" s="14"/>
-      <c r="S142" s="14"/>
+      <c r="AC142" s="12"/>
+      <c r="AE142" s="12"/>
     </row>
     <row r="143">
-      <c r="Q143" s="14"/>
-      <c r="S143" s="14"/>
+      <c r="AC143" s="12"/>
+      <c r="AE143" s="12"/>
     </row>
     <row r="144">
-      <c r="Q144" s="14"/>
-      <c r="S144" s="14"/>
+      <c r="AC144" s="12"/>
+      <c r="AE144" s="12"/>
     </row>
     <row r="145">
-      <c r="Q145" s="14"/>
-      <c r="S145" s="14"/>
+      <c r="AC145" s="12"/>
+      <c r="AE145" s="12"/>
     </row>
     <row r="146">
-      <c r="Q146" s="14"/>
-      <c r="S146" s="14"/>
+      <c r="AC146" s="12"/>
+      <c r="AE146" s="12"/>
     </row>
     <row r="147">
-      <c r="Q147" s="14"/>
-      <c r="S147" s="14"/>
+      <c r="AC147" s="12"/>
+      <c r="AE147" s="12"/>
     </row>
     <row r="148">
-      <c r="Q148" s="14"/>
-      <c r="S148" s="14"/>
+      <c r="AC148" s="12"/>
+      <c r="AE148" s="12"/>
     </row>
     <row r="149">
-      <c r="Q149" s="14"/>
-      <c r="S149" s="14"/>
+      <c r="AC149" s="12"/>
+      <c r="AE149" s="12"/>
     </row>
     <row r="150">
-      <c r="Q150" s="14"/>
-      <c r="S150" s="14"/>
+      <c r="AC150" s="12"/>
+      <c r="AE150" s="12"/>
     </row>
     <row r="151">
-      <c r="Q151" s="14"/>
-      <c r="S151" s="14"/>
+      <c r="AC151" s="12"/>
+      <c r="AE151" s="12"/>
     </row>
     <row r="152">
-      <c r="Q152" s="14"/>
-      <c r="S152" s="14"/>
+      <c r="AC152" s="12"/>
+      <c r="AE152" s="12"/>
     </row>
     <row r="153">
-      <c r="Q153" s="14"/>
-      <c r="S153" s="14"/>
+      <c r="AC153" s="12"/>
+      <c r="AE153" s="12"/>
     </row>
     <row r="154">
-      <c r="Q154" s="14"/>
-      <c r="S154" s="14"/>
+      <c r="AC154" s="12"/>
+      <c r="AE154" s="12"/>
     </row>
     <row r="155">
-      <c r="Q155" s="14"/>
-      <c r="S155" s="14"/>
+      <c r="AC155" s="12"/>
+      <c r="AE155" s="12"/>
     </row>
     <row r="156">
-      <c r="Q156" s="14"/>
-      <c r="S156" s="14"/>
+      <c r="AC156" s="12"/>
+      <c r="AE156" s="12"/>
     </row>
     <row r="157">
-      <c r="Q157" s="14"/>
-      <c r="S157" s="14"/>
+      <c r="AC157" s="12"/>
+      <c r="AE157" s="12"/>
     </row>
     <row r="158">
-      <c r="Q158" s="14"/>
-      <c r="S158" s="14"/>
+      <c r="AC158" s="12"/>
+      <c r="AE158" s="12"/>
     </row>
     <row r="159">
-      <c r="Q159" s="14"/>
-      <c r="S159" s="14"/>
+      <c r="AC159" s="12"/>
+      <c r="AE159" s="12"/>
     </row>
     <row r="160">
-      <c r="Q160" s="14"/>
-      <c r="S160" s="14"/>
+      <c r="AC160" s="12"/>
+      <c r="AE160" s="12"/>
     </row>
     <row r="161">
-      <c r="Q161" s="14"/>
-      <c r="S161" s="14"/>
+      <c r="AC161" s="12"/>
+      <c r="AE161" s="12"/>
     </row>
     <row r="162">
-      <c r="Q162" s="14"/>
-      <c r="S162" s="14"/>
+      <c r="AC162" s="12"/>
+      <c r="AE162" s="12"/>
     </row>
     <row r="163">
-      <c r="Q163" s="14"/>
-      <c r="S163" s="14"/>
+      <c r="AC163" s="12"/>
+      <c r="AE163" s="12"/>
     </row>
     <row r="164">
-      <c r="Q164" s="14"/>
-      <c r="S164" s="14"/>
+      <c r="AC164" s="12"/>
+      <c r="AE164" s="12"/>
     </row>
     <row r="165">
-      <c r="Q165" s="14"/>
-      <c r="S165" s="14"/>
+      <c r="AC165" s="12"/>
+      <c r="AE165" s="12"/>
     </row>
     <row r="166">
-      <c r="Q166" s="14"/>
-      <c r="S166" s="14"/>
+      <c r="AC166" s="12"/>
+      <c r="AE166" s="12"/>
     </row>
     <row r="167">
-      <c r="Q167" s="14"/>
-      <c r="S167" s="14"/>
+      <c r="AC167" s="12"/>
+      <c r="AE167" s="12"/>
     </row>
     <row r="168">
-      <c r="Q168" s="14"/>
-      <c r="S168" s="14"/>
+      <c r="AC168" s="12"/>
+      <c r="AE168" s="12"/>
     </row>
     <row r="169">
-      <c r="Q169" s="14"/>
-      <c r="S169" s="14"/>
+      <c r="AC169" s="12"/>
+      <c r="AE169" s="12"/>
     </row>
     <row r="170">
-      <c r="Q170" s="14"/>
-      <c r="S170" s="14"/>
+      <c r="AC170" s="12"/>
+      <c r="AE170" s="12"/>
     </row>
     <row r="171">
-      <c r="Q171" s="14"/>
-      <c r="S171" s="14"/>
+      <c r="AC171" s="12"/>
+      <c r="AE171" s="12"/>
     </row>
     <row r="172">
-      <c r="Q172" s="14"/>
-      <c r="S172" s="14"/>
+      <c r="AC172" s="12"/>
+      <c r="AE172" s="12"/>
     </row>
     <row r="173">
-      <c r="Q173" s="14"/>
-      <c r="S173" s="14"/>
+      <c r="AC173" s="12"/>
+      <c r="AE173" s="12"/>
     </row>
     <row r="174">
-      <c r="Q174" s="14"/>
-      <c r="S174" s="14"/>
+      <c r="AC174" s="12"/>
+      <c r="AE174" s="12"/>
     </row>
     <row r="175">
-      <c r="Q175" s="14"/>
-      <c r="S175" s="14"/>
+      <c r="AC175" s="12"/>
+      <c r="AE175" s="12"/>
     </row>
     <row r="176">
-      <c r="Q176" s="14"/>
-      <c r="S176" s="14"/>
+      <c r="AC176" s="12"/>
+      <c r="AE176" s="12"/>
     </row>
     <row r="177">
-      <c r="Q177" s="14"/>
-      <c r="S177" s="14"/>
+      <c r="AC177" s="12"/>
+      <c r="AE177" s="12"/>
     </row>
     <row r="178">
-      <c r="Q178" s="14"/>
-      <c r="S178" s="14"/>
+      <c r="AC178" s="12"/>
+      <c r="AE178" s="12"/>
     </row>
     <row r="179">
-      <c r="Q179" s="14"/>
-      <c r="S179" s="14"/>
+      <c r="AC179" s="12"/>
+      <c r="AE179" s="12"/>
     </row>
     <row r="180">
-      <c r="Q180" s="14"/>
-      <c r="S180" s="14"/>
+      <c r="AC180" s="12"/>
+      <c r="AE180" s="12"/>
     </row>
     <row r="181">
-      <c r="Q181" s="14"/>
-      <c r="S181" s="14"/>
+      <c r="AC181" s="12"/>
+      <c r="AE181" s="12"/>
     </row>
     <row r="182">
-      <c r="Q182" s="14"/>
-      <c r="S182" s="14"/>
+      <c r="AC182" s="12"/>
+      <c r="AE182" s="12"/>
     </row>
     <row r="183">
-      <c r="Q183" s="14"/>
-      <c r="S183" s="14"/>
+      <c r="AC183" s="12"/>
+      <c r="AE183" s="12"/>
     </row>
     <row r="184">
-      <c r="Q184" s="14"/>
-      <c r="S184" s="14"/>
+      <c r="AC184" s="12"/>
+      <c r="AE184" s="12"/>
     </row>
     <row r="185">
-      <c r="Q185" s="14"/>
-      <c r="S185" s="14"/>
+      <c r="AC185" s="12"/>
+      <c r="AE185" s="12"/>
     </row>
     <row r="186">
-      <c r="Q186" s="14"/>
-      <c r="S186" s="14"/>
+      <c r="AC186" s="12"/>
+      <c r="AE186" s="12"/>
     </row>
     <row r="187">
-      <c r="Q187" s="14"/>
-      <c r="S187" s="14"/>
+      <c r="AC187" s="12"/>
+      <c r="AE187" s="12"/>
     </row>
     <row r="188">
-      <c r="Q188" s="14"/>
-      <c r="S188" s="14"/>
+      <c r="AC188" s="12"/>
+      <c r="AE188" s="12"/>
     </row>
     <row r="189">
-      <c r="Q189" s="14"/>
-      <c r="S189" s="14"/>
+      <c r="AC189" s="12"/>
+      <c r="AE189" s="12"/>
     </row>
     <row r="190">
-      <c r="Q190" s="14"/>
-      <c r="S190" s="14"/>
+      <c r="AC190" s="12"/>
+      <c r="AE190" s="12"/>
     </row>
     <row r="191">
-      <c r="Q191" s="14"/>
-      <c r="S191" s="14"/>
+      <c r="AC191" s="12"/>
+      <c r="AE191" s="12"/>
     </row>
     <row r="192">
-      <c r="Q192" s="14"/>
-      <c r="S192" s="14"/>
+      <c r="AC192" s="12"/>
+      <c r="AE192" s="12"/>
     </row>
     <row r="193">
-      <c r="Q193" s="14"/>
-      <c r="S193" s="14"/>
+      <c r="AC193" s="12"/>
+      <c r="AE193" s="12"/>
     </row>
     <row r="194">
-      <c r="Q194" s="14"/>
-      <c r="S194" s="14"/>
+      <c r="AC194" s="12"/>
+      <c r="AE194" s="12"/>
     </row>
     <row r="195">
-      <c r="Q195" s="14"/>
-      <c r="S195" s="14"/>
+      <c r="AC195" s="12"/>
+      <c r="AE195" s="12"/>
     </row>
     <row r="196">
-      <c r="Q196" s="14"/>
-      <c r="S196" s="14"/>
+      <c r="AC196" s="12"/>
+      <c r="AE196" s="12"/>
     </row>
     <row r="197">
-      <c r="Q197" s="14"/>
-      <c r="S197" s="14"/>
+      <c r="AC197" s="12"/>
+      <c r="AE197" s="12"/>
     </row>
     <row r="198">
-      <c r="Q198" s="14"/>
-      <c r="S198" s="14"/>
+      <c r="AC198" s="12"/>
+      <c r="AE198" s="12"/>
     </row>
     <row r="199">
-      <c r="Q199" s="14"/>
-      <c r="S199" s="14"/>
+      <c r="AC199" s="12"/>
+      <c r="AE199" s="12"/>
     </row>
     <row r="200">
-      <c r="Q200" s="14"/>
-      <c r="S200" s="14"/>
+      <c r="AC200" s="12"/>
+      <c r="AE200" s="12"/>
     </row>
     <row r="201">
-      <c r="Q201" s="14"/>
-      <c r="S201" s="14"/>
+      <c r="AC201" s="12"/>
+      <c r="AE201" s="12"/>
     </row>
     <row r="202">
-      <c r="Q202" s="14"/>
-      <c r="S202" s="14"/>
+      <c r="AC202" s="12"/>
+      <c r="AE202" s="12"/>
     </row>
     <row r="203">
-      <c r="Q203" s="14"/>
-      <c r="S203" s="14"/>
+      <c r="AC203" s="12"/>
+      <c r="AE203" s="12"/>
     </row>
     <row r="204">
-      <c r="Q204" s="14"/>
-      <c r="S204" s="14"/>
+      <c r="AC204" s="12"/>
+      <c r="AE204" s="12"/>
     </row>
     <row r="205">
-      <c r="Q205" s="14"/>
-      <c r="S205" s="14"/>
+      <c r="AC205" s="12"/>
+      <c r="AE205" s="12"/>
     </row>
     <row r="206">
-      <c r="Q206" s="14"/>
-      <c r="S206" s="14"/>
+      <c r="AC206" s="12"/>
+      <c r="AE206" s="12"/>
     </row>
     <row r="207">
-      <c r="Q207" s="14"/>
-      <c r="S207" s="14"/>
+      <c r="AC207" s="12"/>
+      <c r="AE207" s="12"/>
     </row>
     <row r="208">
-      <c r="Q208" s="14"/>
-      <c r="S208" s="14"/>
+      <c r="AC208" s="12"/>
+      <c r="AE208" s="12"/>
     </row>
     <row r="209">
-      <c r="Q209" s="14"/>
-      <c r="S209" s="14"/>
+      <c r="AC209" s="12"/>
+      <c r="AE209" s="12"/>
     </row>
     <row r="210">
-      <c r="Q210" s="14"/>
-      <c r="S210" s="14"/>
+      <c r="AC210" s="12"/>
+      <c r="AE210" s="12"/>
     </row>
     <row r="211">
-      <c r="Q211" s="14"/>
-      <c r="S211" s="14"/>
+      <c r="AC211" s="12"/>
+      <c r="AE211" s="12"/>
     </row>
     <row r="212">
-      <c r="Q212" s="14"/>
-      <c r="S212" s="14"/>
+      <c r="AC212" s="12"/>
+      <c r="AE212" s="12"/>
     </row>
     <row r="213">
-      <c r="Q213" s="14"/>
-      <c r="S213" s="14"/>
+      <c r="AC213" s="12"/>
+      <c r="AE213" s="12"/>
     </row>
     <row r="214">
-      <c r="Q214" s="14"/>
-      <c r="S214" s="14"/>
+      <c r="AC214" s="12"/>
+      <c r="AE214" s="12"/>
     </row>
     <row r="215">
-      <c r="Q215" s="14"/>
-      <c r="S215" s="14"/>
+      <c r="AC215" s="12"/>
+      <c r="AE215" s="12"/>
     </row>
     <row r="216">
-      <c r="Q216" s="14"/>
-      <c r="S216" s="14"/>
+      <c r="AC216" s="12"/>
+      <c r="AE216" s="12"/>
     </row>
     <row r="217">
-      <c r="Q217" s="14"/>
-      <c r="S217" s="14"/>
+      <c r="AC217" s="12"/>
+      <c r="AE217" s="12"/>
     </row>
     <row r="218">
-      <c r="Q218" s="14"/>
-      <c r="S218" s="14"/>
+      <c r="AC218" s="12"/>
+      <c r="AE218" s="12"/>
     </row>
     <row r="219">
-      <c r="Q219" s="14"/>
-      <c r="S219" s="14"/>
+      <c r="AC219" s="12"/>
+      <c r="AE219" s="12"/>
     </row>
     <row r="220">
-      <c r="Q220" s="14"/>
-      <c r="S220" s="14"/>
+      <c r="AC220" s="12"/>
+      <c r="AE220" s="12"/>
     </row>
     <row r="221">
-      <c r="Q221" s="14"/>
-      <c r="S221" s="14"/>
+      <c r="AC221" s="12"/>
+      <c r="AE221" s="12"/>
     </row>
     <row r="222">
-      <c r="Q222" s="14"/>
-      <c r="S222" s="14"/>
+      <c r="AC222" s="12"/>
+      <c r="AE222" s="12"/>
     </row>
     <row r="223">
-      <c r="Q223" s="14"/>
-      <c r="S223" s="14"/>
+      <c r="AC223" s="12"/>
+      <c r="AE223" s="12"/>
     </row>
     <row r="224">
-      <c r="Q224" s="14"/>
-      <c r="S224" s="14"/>
+      <c r="AC224" s="12"/>
+      <c r="AE224" s="12"/>
     </row>
     <row r="225">
-      <c r="Q225" s="14"/>
-      <c r="S225" s="14"/>
+      <c r="AC225" s="12"/>
+      <c r="AE225" s="12"/>
     </row>
     <row r="226">
-      <c r="Q226" s="14"/>
-      <c r="S226" s="14"/>
+      <c r="AC226" s="12"/>
+      <c r="AE226" s="12"/>
     </row>
     <row r="227">
-      <c r="Q227" s="14"/>
-      <c r="S227" s="14"/>
+      <c r="AC227" s="12"/>
+      <c r="AE227" s="12"/>
     </row>
     <row r="228">
-      <c r="Q228" s="14"/>
-      <c r="S228" s="14"/>
+      <c r="AC228" s="12"/>
+      <c r="AE228" s="12"/>
     </row>
     <row r="229">
-      <c r="Q229" s="14"/>
-      <c r="S229" s="14"/>
+      <c r="AC229" s="12"/>
+      <c r="AE229" s="12"/>
     </row>
     <row r="230">
-      <c r="Q230" s="14"/>
-      <c r="S230" s="14"/>
+      <c r="AC230" s="12"/>
+      <c r="AE230" s="12"/>
     </row>
     <row r="231">
-      <c r="Q231" s="14"/>
-      <c r="S231" s="14"/>
+      <c r="AC231" s="12"/>
+      <c r="AE231" s="12"/>
     </row>
     <row r="232">
-      <c r="Q232" s="14"/>
-      <c r="S232" s="14"/>
+      <c r="AC232" s="12"/>
+      <c r="AE232" s="12"/>
     </row>
     <row r="233">
-      <c r="Q233" s="14"/>
-      <c r="S233" s="14"/>
+      <c r="AC233" s="12"/>
+      <c r="AE233" s="12"/>
     </row>
     <row r="234">
-      <c r="Q234" s="14"/>
-      <c r="S234" s="14"/>
+      <c r="AC234" s="12"/>
+      <c r="AE234" s="12"/>
     </row>
     <row r="235">
-      <c r="Q235" s="14"/>
-      <c r="S235" s="14"/>
+      <c r="AC235" s="12"/>
+      <c r="AE235" s="12"/>
     </row>
     <row r="236">
-      <c r="Q236" s="14"/>
-      <c r="S236" s="14"/>
+      <c r="AC236" s="12"/>
+      <c r="AE236" s="12"/>
     </row>
     <row r="237">
-      <c r="Q237" s="14"/>
-      <c r="S237" s="14"/>
+      <c r="AC237" s="12"/>
+      <c r="AE237" s="12"/>
     </row>
     <row r="238">
-      <c r="Q238" s="14"/>
-      <c r="S238" s="14"/>
+      <c r="AC238" s="12"/>
+      <c r="AE238" s="12"/>
     </row>
     <row r="239">
-      <c r="Q239" s="14"/>
-      <c r="S239" s="14"/>
+      <c r="AC239" s="12"/>
+      <c r="AE239" s="12"/>
     </row>
     <row r="240">
-      <c r="Q240" s="14"/>
-      <c r="S240" s="14"/>
+      <c r="AC240" s="12"/>
+      <c r="AE240" s="12"/>
     </row>
     <row r="241">
-      <c r="Q241" s="14"/>
-      <c r="S241" s="14"/>
+      <c r="AC241" s="12"/>
+      <c r="AE241" s="12"/>
     </row>
     <row r="242">
-      <c r="Q242" s="14"/>
-      <c r="S242" s="14"/>
+      <c r="AC242" s="12"/>
+      <c r="AE242" s="12"/>
     </row>
     <row r="243">
-      <c r="Q243" s="14"/>
-      <c r="S243" s="14"/>
+      <c r="AC243" s="12"/>
+      <c r="AE243" s="12"/>
     </row>
     <row r="244">
-      <c r="Q244" s="14"/>
-      <c r="S244" s="14"/>
+      <c r="AC244" s="12"/>
+      <c r="AE244" s="12"/>
     </row>
     <row r="245">
-      <c r="Q245" s="14"/>
-      <c r="S245" s="14"/>
+      <c r="AC245" s="12"/>
+      <c r="AE245" s="12"/>
     </row>
     <row r="246">
-      <c r="Q246" s="14"/>
-      <c r="S246" s="14"/>
+      <c r="AC246" s="12"/>
+      <c r="AE246" s="12"/>
     </row>
     <row r="247">
-      <c r="Q247" s="14"/>
-      <c r="S247" s="14"/>
+      <c r="AC247" s="12"/>
+      <c r="AE247" s="12"/>
     </row>
     <row r="248">
-      <c r="Q248" s="14"/>
-      <c r="S248" s="14"/>
+      <c r="AC248" s="12"/>
+      <c r="AE248" s="12"/>
     </row>
     <row r="249">
-      <c r="Q249" s="14"/>
-      <c r="S249" s="14"/>
+      <c r="AC249" s="12"/>
+      <c r="AE249" s="12"/>
     </row>
     <row r="250">
-      <c r="Q250" s="14"/>
-      <c r="S250" s="14"/>
+      <c r="AC250" s="12"/>
+      <c r="AE250" s="12"/>
     </row>
     <row r="251">
-      <c r="Q251" s="14"/>
-      <c r="S251" s="14"/>
+      <c r="AC251" s="12"/>
+      <c r="AE251" s="12"/>
     </row>
     <row r="252">
-      <c r="Q252" s="14"/>
-      <c r="S252" s="14"/>
+      <c r="AC252" s="12"/>
+      <c r="AE252" s="12"/>
     </row>
     <row r="253">
-      <c r="Q253" s="14"/>
-      <c r="S253" s="14"/>
+      <c r="AC253" s="12"/>
+      <c r="AE253" s="12"/>
     </row>
     <row r="254">
-      <c r="Q254" s="14"/>
-      <c r="S254" s="14"/>
+      <c r="AC254" s="12"/>
+      <c r="AE254" s="12"/>
     </row>
     <row r="255">
-      <c r="Q255" s="14"/>
-      <c r="S255" s="14"/>
+      <c r="AC255" s="12"/>
+      <c r="AE255" s="12"/>
     </row>
     <row r="256">
-      <c r="Q256" s="14"/>
-      <c r="S256" s="14"/>
+      <c r="AC256" s="12"/>
+      <c r="AE256" s="12"/>
     </row>
     <row r="257">
-      <c r="Q257" s="14"/>
-      <c r="S257" s="14"/>
+      <c r="AC257" s="12"/>
+      <c r="AE257" s="12"/>
     </row>
     <row r="258">
-      <c r="Q258" s="14"/>
-      <c r="S258" s="14"/>
+      <c r="AC258" s="12"/>
+      <c r="AE258" s="12"/>
     </row>
     <row r="259">
-      <c r="Q259" s="14"/>
-      <c r="S259" s="14"/>
+      <c r="AC259" s="12"/>
+      <c r="AE259" s="12"/>
     </row>
     <row r="260">
-      <c r="Q260" s="14"/>
-      <c r="S260" s="14"/>
+      <c r="AC260" s="12"/>
+      <c r="AE260" s="12"/>
     </row>
     <row r="261">
-      <c r="Q261" s="14"/>
-      <c r="S261" s="14"/>
+      <c r="AC261" s="12"/>
+      <c r="AE261" s="12"/>
     </row>
     <row r="262">
-      <c r="Q262" s="14"/>
-      <c r="S262" s="14"/>
+      <c r="AC262" s="12"/>
+      <c r="AE262" s="12"/>
     </row>
     <row r="263">
-      <c r="Q263" s="14"/>
-      <c r="S263" s="14"/>
+      <c r="AC263" s="12"/>
+      <c r="AE263" s="12"/>
     </row>
     <row r="264">
-      <c r="Q264" s="14"/>
-      <c r="S264" s="14"/>
+      <c r="AC264" s="12"/>
+      <c r="AE264" s="12"/>
     </row>
     <row r="265">
-      <c r="Q265" s="14"/>
-      <c r="S265" s="14"/>
+      <c r="AC265" s="12"/>
+      <c r="AE265" s="12"/>
     </row>
     <row r="266">
-      <c r="Q266" s="14"/>
-      <c r="S266" s="14"/>
+      <c r="AC266" s="12"/>
+      <c r="AE266" s="12"/>
     </row>
     <row r="267">
-      <c r="Q267" s="14"/>
-      <c r="S267" s="14"/>
+      <c r="AC267" s="12"/>
+      <c r="AE267" s="12"/>
     </row>
     <row r="268">
-      <c r="Q268" s="14"/>
-      <c r="S268" s="14"/>
+      <c r="AC268" s="12"/>
+      <c r="AE268" s="12"/>
     </row>
     <row r="269">
-      <c r="Q269" s="14"/>
-      <c r="S269" s="14"/>
+      <c r="AC269" s="12"/>
+      <c r="AE269" s="12"/>
     </row>
     <row r="270">
-      <c r="Q270" s="14"/>
-      <c r="S270" s="14"/>
+      <c r="AC270" s="12"/>
+      <c r="AE270" s="12"/>
     </row>
     <row r="271">
-      <c r="Q271" s="14"/>
-      <c r="S271" s="14"/>
+      <c r="AC271" s="12"/>
+      <c r="AE271" s="12"/>
     </row>
     <row r="272">
-      <c r="Q272" s="14"/>
-      <c r="S272" s="14"/>
+      <c r="AC272" s="12"/>
+      <c r="AE272" s="12"/>
     </row>
     <row r="273">
-      <c r="Q273" s="14"/>
-      <c r="S273" s="14"/>
+      <c r="AC273" s="12"/>
+      <c r="AE273" s="12"/>
     </row>
     <row r="274">
-      <c r="Q274" s="14"/>
-      <c r="S274" s="14"/>
+      <c r="AC274" s="12"/>
+      <c r="AE274" s="12"/>
     </row>
     <row r="275">
-      <c r="Q275" s="14"/>
-      <c r="S275" s="14"/>
+      <c r="AC275" s="12"/>
+      <c r="AE275" s="12"/>
     </row>
     <row r="276">
-      <c r="Q276" s="14"/>
-      <c r="S276" s="14"/>
+      <c r="AC276" s="12"/>
+      <c r="AE276" s="12"/>
     </row>
     <row r="277">
-      <c r="Q277" s="14"/>
-      <c r="S277" s="14"/>
+      <c r="AC277" s="12"/>
+      <c r="AE277" s="12"/>
     </row>
     <row r="278">
-      <c r="Q278" s="14"/>
-      <c r="S278" s="14"/>
+      <c r="AC278" s="12"/>
+      <c r="AE278" s="12"/>
     </row>
     <row r="279">
-      <c r="Q279" s="14"/>
-      <c r="S279" s="14"/>
+      <c r="AC279" s="12"/>
+      <c r="AE279" s="12"/>
     </row>
     <row r="280">
-      <c r="Q280" s="14"/>
-      <c r="S280" s="14"/>
+      <c r="AC280" s="12"/>
+      <c r="AE280" s="12"/>
     </row>
     <row r="281">
-      <c r="Q281" s="14"/>
-      <c r="S281" s="14"/>
+      <c r="AC281" s="12"/>
+      <c r="AE281" s="12"/>
     </row>
     <row r="282">
-      <c r="Q282" s="14"/>
-      <c r="S282" s="14"/>
+      <c r="AC282" s="12"/>
+      <c r="AE282" s="12"/>
     </row>
     <row r="283">
-      <c r="Q283" s="14"/>
-      <c r="S283" s="14"/>
+      <c r="AC283" s="12"/>
+      <c r="AE283" s="12"/>
     </row>
     <row r="284">
-      <c r="Q284" s="14"/>
-      <c r="S284" s="14"/>
+      <c r="AC284" s="12"/>
+      <c r="AE284" s="12"/>
     </row>
     <row r="285">
-      <c r="Q285" s="14"/>
-      <c r="S285" s="14"/>
+      <c r="AC285" s="12"/>
+      <c r="AE285" s="12"/>
     </row>
     <row r="286">
-      <c r="Q286" s="14"/>
-      <c r="S286" s="14"/>
+      <c r="AC286" s="12"/>
+      <c r="AE286" s="12"/>
     </row>
     <row r="287">
-      <c r="Q287" s="14"/>
-      <c r="S287" s="14"/>
+      <c r="AC287" s="12"/>
+      <c r="AE287" s="12"/>
     </row>
     <row r="288">
-      <c r="Q288" s="14"/>
-      <c r="S288" s="14"/>
+      <c r="AC288" s="12"/>
+      <c r="AE288" s="12"/>
     </row>
     <row r="289">
-      <c r="Q289" s="14"/>
-      <c r="S289" s="14"/>
+      <c r="AC289" s="12"/>
+      <c r="AE289" s="12"/>
     </row>
     <row r="290">
-      <c r="Q290" s="14"/>
-      <c r="S290" s="14"/>
+      <c r="AC290" s="12"/>
+      <c r="AE290" s="12"/>
     </row>
     <row r="291">
-      <c r="Q291" s="14"/>
-      <c r="S291" s="14"/>
+      <c r="AC291" s="12"/>
+      <c r="AE291" s="12"/>
     </row>
     <row r="292">
-      <c r="Q292" s="14"/>
-      <c r="S292" s="14"/>
+      <c r="AC292" s="12"/>
+      <c r="AE292" s="12"/>
     </row>
     <row r="293">
-      <c r="Q293" s="14"/>
-      <c r="S293" s="14"/>
+      <c r="AC293" s="12"/>
+      <c r="AE293" s="12"/>
     </row>
     <row r="294">
-      <c r="Q294" s="14"/>
-      <c r="S294" s="14"/>
+      <c r="AC294" s="12"/>
+      <c r="AE294" s="12"/>
     </row>
     <row r="295">
-      <c r="Q295" s="14"/>
-      <c r="S295" s="14"/>
+      <c r="AC295" s="12"/>
+      <c r="AE295" s="12"/>
     </row>
     <row r="296">
-      <c r="Q296" s="14"/>
-      <c r="S296" s="14"/>
+      <c r="AC296" s="12"/>
+      <c r="AE296" s="12"/>
     </row>
     <row r="297">
-      <c r="Q297" s="14"/>
-      <c r="S297" s="14"/>
+      <c r="AC297" s="12"/>
+      <c r="AE297" s="12"/>
     </row>
     <row r="298">
-      <c r="Q298" s="14"/>
-      <c r="S298" s="14"/>
+      <c r="AC298" s="12"/>
+      <c r="AE298" s="12"/>
     </row>
     <row r="299">
-      <c r="Q299" s="14"/>
-      <c r="S299" s="14"/>
+      <c r="AC299" s="12"/>
+      <c r="AE299" s="12"/>
     </row>
     <row r="300">
-      <c r="Q300" s="14"/>
-      <c r="S300" s="14"/>
+      <c r="AC300" s="12"/>
+      <c r="AE300" s="12"/>
     </row>
     <row r="301">
-      <c r="Q301" s="14"/>
-      <c r="S301" s="14"/>
+      <c r="AC301" s="12"/>
+      <c r="AE301" s="12"/>
     </row>
     <row r="302">
-      <c r="Q302" s="14"/>
-      <c r="S302" s="14"/>
+      <c r="AC302" s="12"/>
+      <c r="AE302" s="12"/>
     </row>
     <row r="303">
-      <c r="Q303" s="14"/>
-      <c r="S303" s="14"/>
+      <c r="AC303" s="12"/>
+      <c r="AE303" s="12"/>
     </row>
     <row r="304">
-      <c r="Q304" s="14"/>
-      <c r="S304" s="14"/>
+      <c r="AC304" s="12"/>
+      <c r="AE304" s="12"/>
     </row>
     <row r="305">
-      <c r="Q305" s="14"/>
-      <c r="S305" s="14"/>
+      <c r="AC305" s="12"/>
+      <c r="AE305" s="12"/>
     </row>
     <row r="306">
-      <c r="Q306" s="14"/>
-      <c r="S306" s="14"/>
+      <c r="AC306" s="12"/>
+      <c r="AE306" s="12"/>
     </row>
     <row r="307">
-      <c r="Q307" s="14"/>
-      <c r="S307" s="14"/>
+      <c r="AC307" s="12"/>
+      <c r="AE307" s="12"/>
     </row>
     <row r="308">
-      <c r="Q308" s="14"/>
-      <c r="S308" s="14"/>
+      <c r="AC308" s="12"/>
+      <c r="AE308" s="12"/>
     </row>
     <row r="309">
-      <c r="Q309" s="14"/>
-      <c r="S309" s="14"/>
+      <c r="AC309" s="12"/>
+      <c r="AE309" s="12"/>
     </row>
     <row r="310">
-      <c r="Q310" s="14"/>
-      <c r="S310" s="14"/>
+      <c r="AC310" s="12"/>
+      <c r="AE310" s="12"/>
     </row>
     <row r="311">
-      <c r="Q311" s="14"/>
-      <c r="S311" s="14"/>
+      <c r="AC311" s="12"/>
+      <c r="AE311" s="12"/>
     </row>
     <row r="312">
-      <c r="Q312" s="14"/>
-      <c r="S312" s="14"/>
+      <c r="AC312" s="12"/>
+      <c r="AE312" s="12"/>
     </row>
     <row r="313">
-      <c r="Q313" s="14"/>
-      <c r="S313" s="14"/>
+      <c r="AC313" s="12"/>
+      <c r="AE313" s="12"/>
     </row>
     <row r="314">
-      <c r="Q314" s="14"/>
-      <c r="S314" s="14"/>
+      <c r="AC314" s="12"/>
+      <c r="AE314" s="12"/>
     </row>
     <row r="315">
-      <c r="Q315" s="14"/>
-      <c r="S315" s="14"/>
+      <c r="AC315" s="12"/>
+      <c r="AE315" s="12"/>
     </row>
     <row r="316">
-      <c r="Q316" s="14"/>
-      <c r="S316" s="14"/>
+      <c r="AC316" s="12"/>
+      <c r="AE316" s="12"/>
     </row>
     <row r="317">
-      <c r="Q317" s="14"/>
-      <c r="S317" s="14"/>
+      <c r="AC317" s="12"/>
+      <c r="AE317" s="12"/>
     </row>
     <row r="318">
-      <c r="Q318" s="14"/>
-      <c r="S318" s="14"/>
+      <c r="AC318" s="12"/>
+      <c r="AE318" s="12"/>
     </row>
     <row r="319">
-      <c r="Q319" s="14"/>
-      <c r="S319" s="14"/>
+      <c r="AC319" s="12"/>
+      <c r="AE319" s="12"/>
     </row>
     <row r="320">
-      <c r="Q320" s="14"/>
-      <c r="S320" s="14"/>
+      <c r="AC320" s="12"/>
+      <c r="AE320" s="12"/>
     </row>
     <row r="321">
-      <c r="Q321" s="14"/>
-      <c r="S321" s="14"/>
+      <c r="AC321" s="12"/>
+      <c r="AE321" s="12"/>
     </row>
     <row r="322">
-      <c r="Q322" s="14"/>
-      <c r="S322" s="14"/>
+      <c r="AC322" s="12"/>
+      <c r="AE322" s="12"/>
     </row>
     <row r="323">
-      <c r="Q323" s="14"/>
-      <c r="S323" s="14"/>
+      <c r="AC323" s="12"/>
+      <c r="AE323" s="12"/>
     </row>
     <row r="324">
-      <c r="Q324" s="14"/>
-      <c r="S324" s="14"/>
+      <c r="AC324" s="12"/>
+      <c r="AE324" s="12"/>
     </row>
     <row r="325">
-      <c r="Q325" s="14"/>
-      <c r="S325" s="14"/>
+      <c r="AC325" s="12"/>
+      <c r="AE325" s="12"/>
     </row>
     <row r="326">
-      <c r="Q326" s="14"/>
-      <c r="S326" s="14"/>
+      <c r="AC326" s="12"/>
+      <c r="AE326" s="12"/>
     </row>
     <row r="327">
-      <c r="Q327" s="14"/>
-      <c r="S327" s="14"/>
+      <c r="AC327" s="12"/>
+      <c r="AE327" s="12"/>
     </row>
     <row r="328">
-      <c r="Q328" s="14"/>
-      <c r="S328" s="14"/>
+      <c r="AC328" s="12"/>
+      <c r="AE328" s="12"/>
     </row>
     <row r="329">
-      <c r="Q329" s="14"/>
-      <c r="S329" s="14"/>
+      <c r="AC329" s="12"/>
+      <c r="AE329" s="12"/>
     </row>
     <row r="330">
-      <c r="Q330" s="14"/>
-      <c r="S330" s="14"/>
+      <c r="AC330" s="12"/>
+      <c r="AE330" s="12"/>
     </row>
     <row r="331">
-      <c r="Q331" s="14"/>
-      <c r="S331" s="14"/>
+      <c r="AC331" s="12"/>
+      <c r="AE331" s="12"/>
     </row>
     <row r="332">
-      <c r="Q332" s="14"/>
-      <c r="S332" s="14"/>
+      <c r="AC332" s="12"/>
+      <c r="AE332" s="12"/>
     </row>
     <row r="333">
-      <c r="Q333" s="14"/>
-      <c r="S333" s="14"/>
+      <c r="AC333" s="12"/>
+      <c r="AE333" s="12"/>
     </row>
     <row r="334">
-      <c r="Q334" s="14"/>
-      <c r="S334" s="14"/>
+      <c r="AC334" s="12"/>
+      <c r="AE334" s="12"/>
     </row>
     <row r="335">
-      <c r="Q335" s="14"/>
-      <c r="S335" s="14"/>
+      <c r="AC335" s="12"/>
+      <c r="AE335" s="12"/>
     </row>
     <row r="336">
-      <c r="Q336" s="14"/>
-      <c r="S336" s="14"/>
+      <c r="AC336" s="12"/>
+      <c r="AE336" s="12"/>
     </row>
     <row r="337">
-      <c r="Q337" s="14"/>
-      <c r="S337" s="14"/>
+      <c r="AC337" s="12"/>
+      <c r="AE337" s="12"/>
     </row>
     <row r="338">
-      <c r="Q338" s="14"/>
-      <c r="S338" s="14"/>
+      <c r="AC338" s="12"/>
+      <c r="AE338" s="12"/>
     </row>
     <row r="339">
-      <c r="Q339" s="14"/>
-      <c r="S339" s="14"/>
+      <c r="AC339" s="12"/>
+      <c r="AE339" s="12"/>
     </row>
     <row r="340">
-      <c r="Q340" s="14"/>
-      <c r="S340" s="14"/>
+      <c r="AC340" s="12"/>
+      <c r="AE340" s="12"/>
     </row>
     <row r="341">
-      <c r="Q341" s="14"/>
-      <c r="S341" s="14"/>
+      <c r="AC341" s="12"/>
+      <c r="AE341" s="12"/>
     </row>
     <row r="342">
-      <c r="Q342" s="14"/>
-      <c r="S342" s="14"/>
+      <c r="AC342" s="12"/>
+      <c r="AE342" s="12"/>
     </row>
     <row r="343">
-      <c r="Q343" s="14"/>
-      <c r="S343" s="14"/>
+      <c r="AC343" s="12"/>
+      <c r="AE343" s="12"/>
     </row>
     <row r="344">
-      <c r="Q344" s="14"/>
-      <c r="S344" s="14"/>
+      <c r="AC344" s="12"/>
+      <c r="AE344" s="12"/>
     </row>
     <row r="345">
-      <c r="Q345" s="14"/>
-      <c r="S345" s="14"/>
+      <c r="AC345" s="12"/>
+      <c r="AE345" s="12"/>
     </row>
     <row r="346">
-      <c r="Q346" s="14"/>
-      <c r="S346" s="14"/>
+      <c r="AC346" s="12"/>
+      <c r="AE346" s="12"/>
     </row>
     <row r="347">
-      <c r="Q347" s="14"/>
-      <c r="S347" s="14"/>
+      <c r="AC347" s="12"/>
+      <c r="AE347" s="12"/>
     </row>
     <row r="348">
-      <c r="Q348" s="14"/>
-      <c r="S348" s="14"/>
+      <c r="AC348" s="12"/>
+      <c r="AE348" s="12"/>
     </row>
     <row r="349">
-      <c r="Q349" s="14"/>
-      <c r="S349" s="14"/>
+      <c r="AC349" s="12"/>
+      <c r="AE349" s="12"/>
     </row>
     <row r="350">
-      <c r="Q350" s="14"/>
-      <c r="S350" s="14"/>
+      <c r="AC350" s="12"/>
+      <c r="AE350" s="12"/>
     </row>
     <row r="351">
-      <c r="Q351" s="14"/>
-      <c r="S351" s="14"/>
+      <c r="AC351" s="12"/>
+      <c r="AE351" s="12"/>
     </row>
     <row r="352">
-      <c r="Q352" s="14"/>
-      <c r="S352" s="14"/>
+      <c r="AC352" s="12"/>
+      <c r="AE352" s="12"/>
     </row>
     <row r="353">
-      <c r="Q353" s="14"/>
-      <c r="S353" s="14"/>
+      <c r="AC353" s="12"/>
+      <c r="AE353" s="12"/>
     </row>
     <row r="354">
-      <c r="Q354" s="14"/>
-      <c r="S354" s="14"/>
+      <c r="AC354" s="12"/>
+      <c r="AE354" s="12"/>
     </row>
     <row r="355">
-      <c r="Q355" s="14"/>
-      <c r="S355" s="14"/>
+      <c r="AC355" s="12"/>
+      <c r="AE355" s="12"/>
     </row>
     <row r="356">
-      <c r="Q356" s="14"/>
-      <c r="S356" s="14"/>
+      <c r="AC356" s="12"/>
+      <c r="AE356" s="12"/>
     </row>
     <row r="357">
-      <c r="Q357" s="14"/>
-      <c r="S357" s="14"/>
+      <c r="AC357" s="12"/>
+      <c r="AE357" s="12"/>
     </row>
     <row r="358">
-      <c r="Q358" s="14"/>
-      <c r="S358" s="14"/>
+      <c r="AC358" s="12"/>
+      <c r="AE358" s="12"/>
     </row>
     <row r="359">
-      <c r="Q359" s="14"/>
-      <c r="S359" s="14"/>
+      <c r="AC359" s="12"/>
+      <c r="AE359" s="12"/>
     </row>
     <row r="360">
-      <c r="Q360" s="14"/>
-      <c r="S360" s="14"/>
+      <c r="AC360" s="12"/>
+      <c r="AE360" s="12"/>
     </row>
     <row r="361">
-      <c r="Q361" s="14"/>
-      <c r="S361" s="14"/>
+      <c r="AC361" s="12"/>
+      <c r="AE361" s="12"/>
     </row>
     <row r="362">
-      <c r="Q362" s="14"/>
-      <c r="S362" s="14"/>
+      <c r="AC362" s="12"/>
+      <c r="AE362" s="12"/>
     </row>
     <row r="363">
-      <c r="Q363" s="14"/>
-      <c r="S363" s="14"/>
+      <c r="AC363" s="12"/>
+      <c r="AE363" s="12"/>
     </row>
     <row r="364">
-      <c r="Q364" s="14"/>
-      <c r="S364" s="14"/>
+      <c r="AC364" s="12"/>
+      <c r="AE364" s="12"/>
     </row>
     <row r="365">
-      <c r="Q365" s="14"/>
-      <c r="S365" s="14"/>
+      <c r="AC365" s="12"/>
+      <c r="AE365" s="12"/>
     </row>
     <row r="366">
-      <c r="Q366" s="14"/>
-      <c r="S366" s="14"/>
+      <c r="AC366" s="12"/>
+      <c r="AE366" s="12"/>
     </row>
     <row r="367">
-      <c r="Q367" s="14"/>
-      <c r="S367" s="14"/>
+      <c r="AC367" s="12"/>
+      <c r="AE367" s="12"/>
     </row>
     <row r="368">
-      <c r="Q368" s="14"/>
-      <c r="S368" s="14"/>
+      <c r="AC368" s="12"/>
+      <c r="AE368" s="12"/>
     </row>
     <row r="369">
-      <c r="Q369" s="14"/>
-      <c r="S369" s="14"/>
+      <c r="AC369" s="12"/>
+      <c r="AE369" s="12"/>
     </row>
     <row r="370">
-      <c r="Q370" s="14"/>
-      <c r="S370" s="14"/>
+      <c r="AC370" s="12"/>
+      <c r="AE370" s="12"/>
     </row>
     <row r="371">
-      <c r="Q371" s="14"/>
-      <c r="S371" s="14"/>
+      <c r="AC371" s="12"/>
+      <c r="AE371" s="12"/>
     </row>
     <row r="372">
-      <c r="Q372" s="14"/>
-      <c r="S372" s="14"/>
+      <c r="AC372" s="12"/>
+      <c r="AE372" s="12"/>
     </row>
     <row r="373">
-      <c r="Q373" s="14"/>
-      <c r="S373" s="14"/>
+      <c r="AC373" s="12"/>
+      <c r="AE373" s="12"/>
     </row>
     <row r="374">
-      <c r="Q374" s="14"/>
-      <c r="S374" s="14"/>
+      <c r="AC374" s="12"/>
+      <c r="AE374" s="12"/>
     </row>
     <row r="375">
-      <c r="Q375" s="14"/>
-      <c r="S375" s="14"/>
+      <c r="AC375" s="12"/>
+      <c r="AE375" s="12"/>
     </row>
     <row r="376">
-      <c r="Q376" s="14"/>
-      <c r="S376" s="14"/>
+      <c r="AC376" s="12"/>
+      <c r="AE376" s="12"/>
     </row>
     <row r="377">
-      <c r="Q377" s="14"/>
-      <c r="S377" s="14"/>
+      <c r="AC377" s="12"/>
+      <c r="AE377" s="12"/>
     </row>
     <row r="378">
-      <c r="Q378" s="14"/>
-      <c r="S378" s="14"/>
+      <c r="AC378" s="12"/>
+      <c r="AE378" s="12"/>
     </row>
     <row r="379">
-      <c r="Q379" s="14"/>
-      <c r="S379" s="14"/>
+      <c r="AC379" s="12"/>
+      <c r="AE379" s="12"/>
     </row>
     <row r="380">
-      <c r="Q380" s="14"/>
-      <c r="S380" s="14"/>
+      <c r="AC380" s="12"/>
+      <c r="AE380" s="12"/>
     </row>
     <row r="381">
-      <c r="Q381" s="14"/>
-      <c r="S381" s="14"/>
+      <c r="AC381" s="12"/>
+      <c r="AE381" s="12"/>
     </row>
     <row r="382">
-      <c r="Q382" s="14"/>
-      <c r="S382" s="14"/>
+      <c r="AC382" s="12"/>
+      <c r="AE382" s="12"/>
     </row>
     <row r="383">
-      <c r="Q383" s="14"/>
-      <c r="S383" s="14"/>
+      <c r="AC383" s="12"/>
+      <c r="AE383" s="12"/>
     </row>
     <row r="384">
-      <c r="Q384" s="14"/>
-      <c r="S384" s="14"/>
+      <c r="AC384" s="12"/>
+      <c r="AE384" s="12"/>
     </row>
     <row r="385">
-      <c r="Q385" s="14"/>
-      <c r="S385" s="14"/>
+      <c r="AC385" s="12"/>
+      <c r="AE385" s="12"/>
     </row>
     <row r="386">
-      <c r="Q386" s="14"/>
-      <c r="S386" s="14"/>
+      <c r="AC386" s="12"/>
+      <c r="AE386" s="12"/>
     </row>
     <row r="387">
-      <c r="Q387" s="14"/>
-      <c r="S387" s="14"/>
+      <c r="AC387" s="12"/>
+      <c r="AE387" s="12"/>
     </row>
     <row r="388">
-      <c r="Q388" s="14"/>
-      <c r="S388" s="14"/>
+      <c r="AC388" s="12"/>
+      <c r="AE388" s="12"/>
     </row>
     <row r="389">
-      <c r="Q389" s="14"/>
-      <c r="S389" s="14"/>
+      <c r="AC389" s="12"/>
+      <c r="AE389" s="12"/>
     </row>
     <row r="390">
-      <c r="Q390" s="14"/>
-      <c r="S390" s="14"/>
+      <c r="AC390" s="12"/>
+      <c r="AE390" s="12"/>
     </row>
     <row r="391">
-      <c r="Q391" s="14"/>
-      <c r="S391" s="14"/>
+      <c r="AC391" s="12"/>
+      <c r="AE391" s="12"/>
     </row>
     <row r="392">
-      <c r="Q392" s="14"/>
-      <c r="S392" s="14"/>
+      <c r="AC392" s="12"/>
+      <c r="AE392" s="12"/>
     </row>
     <row r="393">
-      <c r="Q393" s="14"/>
-      <c r="S393" s="14"/>
+      <c r="AC393" s="12"/>
+      <c r="AE393" s="12"/>
     </row>
     <row r="394">
-      <c r="Q394" s="14"/>
-      <c r="S394" s="14"/>
+      <c r="AC394" s="12"/>
+      <c r="AE394" s="12"/>
     </row>
     <row r="395">
-      <c r="Q395" s="14"/>
-      <c r="S395" s="14"/>
+      <c r="AC395" s="12"/>
+      <c r="AE395" s="12"/>
     </row>
     <row r="396">
-      <c r="Q396" s="14"/>
-      <c r="S396" s="14"/>
+      <c r="AC396" s="12"/>
+      <c r="AE396" s="12"/>
     </row>
     <row r="397">
-      <c r="Q397" s="14"/>
-      <c r="S397" s="14"/>
+      <c r="AC397" s="12"/>
+      <c r="AE397" s="12"/>
     </row>
     <row r="398">
-      <c r="Q398" s="14"/>
-      <c r="S398" s="14"/>
+      <c r="AC398" s="12"/>
+      <c r="AE398" s="12"/>
     </row>
     <row r="399">
-      <c r="Q399" s="14"/>
-      <c r="S399" s="14"/>
+      <c r="AC399" s="12"/>
+      <c r="AE399" s="12"/>
     </row>
     <row r="400">
-      <c r="Q400" s="14"/>
-      <c r="S400" s="14"/>
+      <c r="AC400" s="12"/>
+      <c r="AE400" s="12"/>
     </row>
     <row r="401">
-      <c r="Q401" s="14"/>
-      <c r="S401" s="14"/>
+      <c r="AC401" s="12"/>
+      <c r="AE401" s="12"/>
     </row>
     <row r="402">
-      <c r="Q402" s="14"/>
-      <c r="S402" s="14"/>
+      <c r="AC402" s="12"/>
+      <c r="AE402" s="12"/>
     </row>
     <row r="403">
-      <c r="Q403" s="14"/>
-      <c r="S403" s="14"/>
+      <c r="AC403" s="12"/>
+      <c r="AE403" s="12"/>
     </row>
     <row r="404">
-      <c r="Q404" s="14"/>
-      <c r="S404" s="14"/>
+      <c r="AC404" s="12"/>
+      <c r="AE404" s="12"/>
     </row>
     <row r="405">
-      <c r="Q405" s="14"/>
-      <c r="S405" s="14"/>
+      <c r="AC405" s="12"/>
+      <c r="AE405" s="12"/>
     </row>
     <row r="406">
-      <c r="Q406" s="14"/>
-      <c r="S406" s="14"/>
+      <c r="AC406" s="12"/>
+      <c r="AE406" s="12"/>
     </row>
     <row r="407">
-      <c r="Q407" s="14"/>
-      <c r="S407" s="14"/>
+      <c r="AC407" s="12"/>
+      <c r="AE407" s="12"/>
     </row>
     <row r="408">
-      <c r="Q408" s="14"/>
-      <c r="S408" s="14"/>
+      <c r="AC408" s="12"/>
+      <c r="AE408" s="12"/>
     </row>
     <row r="409">
-      <c r="Q409" s="14"/>
-      <c r="S409" s="14"/>
+      <c r="AC409" s="12"/>
+      <c r="AE409" s="12"/>
     </row>
     <row r="410">
-      <c r="Q410" s="14"/>
-      <c r="S410" s="14"/>
+      <c r="AC410" s="12"/>
+      <c r="AE410" s="12"/>
     </row>
     <row r="411">
-      <c r="Q411" s="14"/>
-      <c r="S411" s="14"/>
+      <c r="AC411" s="12"/>
+      <c r="AE411" s="12"/>
     </row>
     <row r="412">
-      <c r="Q412" s="14"/>
-      <c r="S412" s="14"/>
+      <c r="AC412" s="12"/>
+      <c r="AE412" s="12"/>
     </row>
     <row r="413">
-      <c r="Q413" s="14"/>
-      <c r="S413" s="14"/>
+      <c r="AC413" s="12"/>
+      <c r="AE413" s="12"/>
     </row>
     <row r="414">
-      <c r="Q414" s="14"/>
-      <c r="S414" s="14"/>
+      <c r="AC414" s="12"/>
+      <c r="AE414" s="12"/>
     </row>
     <row r="415">
-      <c r="Q415" s="14"/>
-      <c r="S415" s="14"/>
+      <c r="AC415" s="12"/>
+      <c r="AE415" s="12"/>
     </row>
     <row r="416">
-      <c r="Q416" s="14"/>
-      <c r="S416" s="14"/>
+      <c r="AC416" s="12"/>
+      <c r="AE416" s="12"/>
     </row>
     <row r="417">
-      <c r="Q417" s="14"/>
-      <c r="S417" s="14"/>
+      <c r="AC417" s="12"/>
+      <c r="AE417" s="12"/>
     </row>
     <row r="418">
-      <c r="Q418" s="14"/>
-      <c r="S418" s="14"/>
+      <c r="AC418" s="12"/>
+      <c r="AE418" s="12"/>
     </row>
     <row r="419">
-      <c r="Q419" s="14"/>
-      <c r="S419" s="14"/>
+      <c r="AC419" s="12"/>
+      <c r="AE419" s="12"/>
     </row>
     <row r="420">
-      <c r="Q420" s="14"/>
-      <c r="S420" s="14"/>
+      <c r="AC420" s="12"/>
+      <c r="AE420" s="12"/>
     </row>
     <row r="421">
-      <c r="Q421" s="14"/>
-      <c r="S421" s="14"/>
+      <c r="AC421" s="12"/>
+      <c r="AE421" s="12"/>
     </row>
     <row r="422">
-      <c r="Q422" s="14"/>
-      <c r="S422" s="14"/>
+      <c r="AC422" s="12"/>
+      <c r="AE422" s="12"/>
     </row>
     <row r="423">
-      <c r="Q423" s="14"/>
-      <c r="S423" s="14"/>
+      <c r="AC423" s="12"/>
+      <c r="AE423" s="12"/>
     </row>
     <row r="424">
-      <c r="Q424" s="14"/>
-      <c r="S424" s="14"/>
+      <c r="AC424" s="12"/>
+      <c r="AE424" s="12"/>
     </row>
     <row r="425">
-      <c r="Q425" s="14"/>
-      <c r="S425" s="14"/>
+      <c r="AC425" s="12"/>
+      <c r="AE425" s="12"/>
     </row>
     <row r="426">
-      <c r="Q426" s="14"/>
-      <c r="S426" s="14"/>
+      <c r="AC426" s="12"/>
+      <c r="AE426" s="12"/>
     </row>
     <row r="427">
-      <c r="Q427" s="14"/>
-      <c r="S427" s="14"/>
+      <c r="AC427" s="12"/>
+      <c r="AE427" s="12"/>
     </row>
     <row r="428">
-      <c r="Q428" s="14"/>
-      <c r="S428" s="14"/>
+      <c r="AC428" s="12"/>
+      <c r="AE428" s="12"/>
     </row>
     <row r="429">
-      <c r="Q429" s="14"/>
-      <c r="S429" s="14"/>
+      <c r="AC429" s="12"/>
+      <c r="AE429" s="12"/>
     </row>
     <row r="430">
-      <c r="Q430" s="14"/>
-      <c r="S430" s="14"/>
+      <c r="AC430" s="12"/>
+      <c r="AE430" s="12"/>
     </row>
     <row r="431">
-      <c r="Q431" s="14"/>
-      <c r="S431" s="14"/>
+      <c r="AC431" s="12"/>
+      <c r="AE431" s="12"/>
     </row>
     <row r="432">
-      <c r="Q432" s="14"/>
-      <c r="S432" s="14"/>
+      <c r="AC432" s="12"/>
+      <c r="AE432" s="12"/>
     </row>
     <row r="433">
-      <c r="Q433" s="14"/>
-      <c r="S433" s="14"/>
+      <c r="AC433" s="12"/>
+      <c r="AE433" s="12"/>
     </row>
     <row r="434">
-      <c r="Q434" s="14"/>
-      <c r="S434" s="14"/>
+      <c r="AC434" s="12"/>
+      <c r="AE434" s="12"/>
     </row>
     <row r="435">
-      <c r="Q435" s="14"/>
-      <c r="S435" s="14"/>
+      <c r="AC435" s="12"/>
+      <c r="AE435" s="12"/>
     </row>
     <row r="436">
-      <c r="Q436" s="14"/>
-      <c r="S436" s="14"/>
+      <c r="AC436" s="12"/>
+      <c r="AE436" s="12"/>
     </row>
     <row r="437">
-      <c r="Q437" s="14"/>
-      <c r="S437" s="14"/>
+      <c r="AC437" s="12"/>
+      <c r="AE437" s="12"/>
     </row>
     <row r="438">
-      <c r="Q438" s="14"/>
-      <c r="S438" s="14"/>
+      <c r="AC438" s="12"/>
+      <c r="AE438" s="12"/>
     </row>
     <row r="439">
-      <c r="Q439" s="14"/>
-      <c r="S439" s="14"/>
+      <c r="AC439" s="12"/>
+      <c r="AE439" s="12"/>
     </row>
     <row r="440">
-      <c r="Q440" s="14"/>
-      <c r="S440" s="14"/>
+      <c r="AC440" s="12"/>
+      <c r="AE440" s="12"/>
     </row>
     <row r="441">
-      <c r="Q441" s="14"/>
-      <c r="S441" s="14"/>
+      <c r="AC441" s="12"/>
+      <c r="AE441" s="12"/>
     </row>
     <row r="442">
-      <c r="Q442" s="14"/>
-      <c r="S442" s="14"/>
+      <c r="AC442" s="12"/>
+      <c r="AE442" s="12"/>
     </row>
     <row r="443">
-      <c r="Q443" s="14"/>
-      <c r="S443" s="14"/>
+      <c r="AC443" s="12"/>
+      <c r="AE443" s="12"/>
     </row>
     <row r="444">
-      <c r="Q444" s="14"/>
-      <c r="S444" s="14"/>
+      <c r="AC444" s="12"/>
+      <c r="AE444" s="12"/>
     </row>
     <row r="445">
-      <c r="Q445" s="14"/>
-      <c r="S445" s="14"/>
+      <c r="AC445" s="12"/>
+      <c r="AE445" s="12"/>
     </row>
     <row r="446">
-      <c r="Q446" s="14"/>
-      <c r="S446" s="14"/>
+      <c r="AC446" s="12"/>
+      <c r="AE446" s="12"/>
     </row>
     <row r="447">
-      <c r="Q447" s="14"/>
-      <c r="S447" s="14"/>
+      <c r="AC447" s="12"/>
+      <c r="AE447" s="12"/>
     </row>
     <row r="448">
-      <c r="Q448" s="14"/>
-      <c r="S448" s="14"/>
+      <c r="AC448" s="12"/>
+      <c r="AE448" s="12"/>
     </row>
     <row r="449">
-      <c r="Q449" s="14"/>
-      <c r="S449" s="14"/>
+      <c r="AC449" s="12"/>
+      <c r="AE449" s="12"/>
     </row>
     <row r="450">
-      <c r="Q450" s="14"/>
-      <c r="S450" s="14"/>
+      <c r="AC450" s="12"/>
+      <c r="AE450" s="12"/>
     </row>
     <row r="451">
-      <c r="Q451" s="14"/>
-      <c r="S451" s="14"/>
+      <c r="AC451" s="12"/>
+      <c r="AE451" s="12"/>
     </row>
     <row r="452">
-      <c r="Q452" s="14"/>
-      <c r="S452" s="14"/>
+      <c r="AC452" s="12"/>
+      <c r="AE452" s="12"/>
     </row>
     <row r="453">
-      <c r="Q453" s="14"/>
-      <c r="S453" s="14"/>
+      <c r="AC453" s="12"/>
+      <c r="AE453" s="12"/>
     </row>
     <row r="454">
-      <c r="Q454" s="14"/>
-      <c r="S454" s="14"/>
+      <c r="AC454" s="12"/>
+      <c r="AE454" s="12"/>
     </row>
     <row r="455">
-      <c r="Q455" s="14"/>
-      <c r="S455" s="14"/>
+      <c r="AC455" s="12"/>
+      <c r="AE455" s="12"/>
     </row>
     <row r="456">
-      <c r="Q456" s="14"/>
-      <c r="S456" s="14"/>
+      <c r="AC456" s="12"/>
+      <c r="AE456" s="12"/>
     </row>
     <row r="457">
-      <c r="Q457" s="14"/>
-      <c r="S457" s="14"/>
+      <c r="AC457" s="12"/>
+      <c r="AE457" s="12"/>
     </row>
     <row r="458">
-      <c r="Q458" s="14"/>
-      <c r="S458" s="14"/>
+      <c r="AC458" s="12"/>
+      <c r="AE458" s="12"/>
     </row>
     <row r="459">
-      <c r="Q459" s="14"/>
-      <c r="S459" s="14"/>
+      <c r="AC459" s="12"/>
+      <c r="AE459" s="12"/>
     </row>
     <row r="460">
-      <c r="Q460" s="14"/>
-      <c r="S460" s="14"/>
+      <c r="AC460" s="12"/>
+      <c r="AE460" s="12"/>
     </row>
     <row r="461">
-      <c r="Q461" s="14"/>
-      <c r="S461" s="14"/>
+      <c r="AC461" s="12"/>
+      <c r="AE461" s="12"/>
     </row>
     <row r="462">
-      <c r="Q462" s="14"/>
-      <c r="S462" s="14"/>
+      <c r="AC462" s="12"/>
+      <c r="AE462" s="12"/>
     </row>
     <row r="463">
-      <c r="Q463" s="14"/>
-      <c r="S463" s="14"/>
+      <c r="AC463" s="12"/>
+      <c r="AE463" s="12"/>
     </row>
     <row r="464">
-      <c r="Q464" s="14"/>
-      <c r="S464" s="14"/>
+      <c r="AC464" s="12"/>
+      <c r="AE464" s="12"/>
     </row>
     <row r="465">
-      <c r="Q465" s="14"/>
-      <c r="S465" s="14"/>
+      <c r="AC465" s="12"/>
+      <c r="AE465" s="12"/>
     </row>
     <row r="466">
-      <c r="Q466" s="14"/>
-      <c r="S466" s="14"/>
+      <c r="AC466" s="12"/>
+      <c r="AE466" s="12"/>
     </row>
     <row r="467">
-      <c r="Q467" s="14"/>
-      <c r="S467" s="14"/>
+      <c r="AC467" s="12"/>
+      <c r="AE467" s="12"/>
     </row>
     <row r="468">
-      <c r="Q468" s="14"/>
-      <c r="S468" s="14"/>
+      <c r="AC468" s="12"/>
+      <c r="AE468" s="12"/>
     </row>
     <row r="469">
-      <c r="Q469" s="14"/>
-      <c r="S469" s="14"/>
+      <c r="AC469" s="12"/>
+      <c r="AE469" s="12"/>
     </row>
     <row r="470">
-      <c r="Q470" s="14"/>
-      <c r="S470" s="14"/>
+      <c r="AC470" s="12"/>
+      <c r="AE470" s="12"/>
     </row>
     <row r="471">
-      <c r="Q471" s="14"/>
-      <c r="S471" s="14"/>
+      <c r="AC471" s="12"/>
+      <c r="AE471" s="12"/>
     </row>
     <row r="472">
-      <c r="Q472" s="14"/>
-      <c r="S472" s="14"/>
+      <c r="AC472" s="12"/>
+      <c r="AE472" s="12"/>
     </row>
     <row r="473">
-      <c r="Q473" s="14"/>
-      <c r="S473" s="14"/>
+      <c r="AC473" s="12"/>
+      <c r="AE473" s="12"/>
     </row>
     <row r="474">
-      <c r="Q474" s="14"/>
-      <c r="S474" s="14"/>
+      <c r="AC474" s="12"/>
+      <c r="AE474" s="12"/>
     </row>
     <row r="475">
-      <c r="Q475" s="14"/>
-      <c r="S475" s="14"/>
+      <c r="AC475" s="12"/>
+      <c r="AE475" s="12"/>
     </row>
     <row r="476">
-      <c r="Q476" s="14"/>
-      <c r="S476" s="14"/>
+      <c r="AC476" s="12"/>
+      <c r="AE476" s="12"/>
     </row>
     <row r="477">
-      <c r="Q477" s="14"/>
-      <c r="S477" s="14"/>
+      <c r="AC477" s="12"/>
+      <c r="AE477" s="12"/>
     </row>
     <row r="478">
-      <c r="Q478" s="14"/>
-      <c r="S478" s="14"/>
+      <c r="AC478" s="12"/>
+      <c r="AE478" s="12"/>
     </row>
     <row r="479">
-      <c r="Q479" s="14"/>
-      <c r="S479" s="14"/>
+      <c r="AC479" s="12"/>
+      <c r="AE479" s="12"/>
     </row>
     <row r="480">
-      <c r="Q480" s="14"/>
-      <c r="S480" s="14"/>
+      <c r="AC480" s="12"/>
+      <c r="AE480" s="12"/>
     </row>
     <row r="481">
-      <c r="Q481" s="14"/>
-      <c r="S481" s="14"/>
+      <c r="AC481" s="12"/>
+      <c r="AE481" s="12"/>
     </row>
     <row r="482">
-      <c r="Q482" s="14"/>
-      <c r="S482" s="14"/>
+      <c r="AC482" s="12"/>
+      <c r="AE482" s="12"/>
     </row>
     <row r="483">
-      <c r="Q483" s="14"/>
-      <c r="S483" s="14"/>
+      <c r="AC483" s="12"/>
+      <c r="AE483" s="12"/>
     </row>
     <row r="484">
-      <c r="Q484" s="14"/>
-      <c r="S484" s="14"/>
+      <c r="AC484" s="12"/>
+      <c r="AE484" s="12"/>
     </row>
     <row r="485">
-      <c r="Q485" s="14"/>
-      <c r="S485" s="14"/>
+      <c r="AC485" s="12"/>
+      <c r="AE485" s="12"/>
     </row>
     <row r="486">
-      <c r="Q486" s="14"/>
-      <c r="S486" s="14"/>
+      <c r="AC486" s="12"/>
+      <c r="AE486" s="12"/>
     </row>
     <row r="487">
-      <c r="Q487" s="14"/>
-      <c r="S487" s="14"/>
+      <c r="AC487" s="12"/>
+      <c r="AE487" s="12"/>
     </row>
     <row r="488">
-      <c r="Q488" s="14"/>
-      <c r="S488" s="14"/>
+      <c r="AC488" s="12"/>
+      <c r="AE488" s="12"/>
     </row>
     <row r="489">
-      <c r="Q489" s="14"/>
-      <c r="S489" s="14"/>
+      <c r="AC489" s="12"/>
+      <c r="AE489" s="12"/>
     </row>
     <row r="490">
-      <c r="Q490" s="14"/>
-      <c r="S490" s="14"/>
+      <c r="AC490" s="12"/>
+      <c r="AE490" s="12"/>
     </row>
     <row r="491">
-      <c r="Q491" s="14"/>
-      <c r="S491" s="14"/>
+      <c r="AC491" s="12"/>
+      <c r="AE491" s="12"/>
     </row>
     <row r="492">
-      <c r="Q492" s="14"/>
-      <c r="S492" s="14"/>
+      <c r="AC492" s="12"/>
+      <c r="AE492" s="12"/>
     </row>
     <row r="493">
-      <c r="Q493" s="14"/>
-      <c r="S493" s="14"/>
+      <c r="AC493" s="12"/>
+      <c r="AE493" s="12"/>
     </row>
     <row r="494">
-      <c r="Q494" s="14"/>
-      <c r="S494" s="14"/>
+      <c r="AC494" s="12"/>
+      <c r="AE494" s="12"/>
     </row>
     <row r="495">
-      <c r="Q495" s="14"/>
-      <c r="S495" s="14"/>
+      <c r="AC495" s="12"/>
+      <c r="AE495" s="12"/>
     </row>
     <row r="496">
-      <c r="Q496" s="14"/>
-      <c r="S496" s="14"/>
+      <c r="AC496" s="12"/>
+      <c r="AE496" s="12"/>
     </row>
     <row r="497">
-      <c r="Q497" s="14"/>
-      <c r="S497" s="14"/>
+      <c r="AC497" s="12"/>
+      <c r="AE497" s="12"/>
     </row>
     <row r="498">
-      <c r="Q498" s="14"/>
-      <c r="S498" s="14"/>
+      <c r="AC498" s="12"/>
+      <c r="AE498" s="12"/>
     </row>
     <row r="499">
-      <c r="Q499" s="14"/>
-      <c r="S499" s="14"/>
+      <c r="AC499" s="12"/>
+      <c r="AE499" s="12"/>
     </row>
     <row r="500">
-      <c r="Q500" s="14"/>
-      <c r="S500" s="14"/>
+      <c r="AC500" s="12"/>
+      <c r="AE500" s="12"/>
     </row>
     <row r="501">
-      <c r="Q501" s="14"/>
-      <c r="S501" s="14"/>
+      <c r="AC501" s="12"/>
+      <c r="AE501" s="12"/>
     </row>
     <row r="502">
-      <c r="Q502" s="14"/>
-      <c r="S502" s="14"/>
+      <c r="AC502" s="12"/>
+      <c r="AE502" s="12"/>
     </row>
     <row r="503">
-      <c r="Q503" s="14"/>
-      <c r="S503" s="14"/>
+      <c r="AC503" s="12"/>
+      <c r="AE503" s="12"/>
     </row>
     <row r="504">
-      <c r="Q504" s="14"/>
-      <c r="S504" s="14"/>
+      <c r="AC504" s="12"/>
+      <c r="AE504" s="12"/>
     </row>
     <row r="505">
-      <c r="Q505" s="14"/>
-      <c r="S505" s="14"/>
+      <c r="AC505" s="12"/>
+      <c r="AE505" s="12"/>
     </row>
     <row r="506">
-      <c r="Q506" s="14"/>
-      <c r="S506" s="14"/>
+      <c r="AC506" s="12"/>
+      <c r="AE506" s="12"/>
     </row>
     <row r="507">
-      <c r="Q507" s="14"/>
-      <c r="S507" s="14"/>
+      <c r="AC507" s="12"/>
+      <c r="AE507" s="12"/>
     </row>
     <row r="508">
-      <c r="Q508" s="14"/>
-      <c r="S508" s="14"/>
+      <c r="AC508" s="12"/>
+      <c r="AE508" s="12"/>
     </row>
     <row r="509">
-      <c r="Q509" s="14"/>
-      <c r="S509" s="14"/>
+      <c r="AC509" s="12"/>
+      <c r="AE509" s="12"/>
     </row>
     <row r="510">
-      <c r="Q510" s="14"/>
-      <c r="S510" s="14"/>
+      <c r="AC510" s="12"/>
+      <c r="AE510" s="12"/>
     </row>
     <row r="511">
-      <c r="Q511" s="14"/>
-      <c r="S511" s="14"/>
+      <c r="AC511" s="12"/>
+      <c r="AE511" s="12"/>
     </row>
     <row r="512">
-      <c r="Q512" s="14"/>
-      <c r="S512" s="14"/>
+      <c r="AC512" s="12"/>
+      <c r="AE512" s="12"/>
     </row>
     <row r="513">
-      <c r="Q513" s="14"/>
-      <c r="S513" s="14"/>
+      <c r="AC513" s="12"/>
+      <c r="AE513" s="12"/>
     </row>
     <row r="514">
-      <c r="Q514" s="14"/>
-      <c r="S514" s="14"/>
+      <c r="AC514" s="12"/>
+      <c r="AE514" s="12"/>
     </row>
     <row r="515">
-      <c r="Q515" s="14"/>
-      <c r="S515" s="14"/>
+      <c r="AC515" s="12"/>
+      <c r="AE515" s="12"/>
     </row>
     <row r="516">
-      <c r="Q516" s="14"/>
-      <c r="S516" s="14"/>
+      <c r="AC516" s="12"/>
+      <c r="AE516" s="12"/>
     </row>
     <row r="517">
-      <c r="Q517" s="14"/>
-      <c r="S517" s="14"/>
+      <c r="AC517" s="12"/>
+      <c r="AE517" s="12"/>
     </row>
     <row r="518">
-      <c r="Q518" s="14"/>
-      <c r="S518" s="14"/>
+      <c r="AC518" s="12"/>
+      <c r="AE518" s="12"/>
     </row>
     <row r="519">
-      <c r="Q519" s="14"/>
-      <c r="S519" s="14"/>
+      <c r="AC519" s="12"/>
+      <c r="AE519" s="12"/>
     </row>
     <row r="520">
-      <c r="Q520" s="14"/>
-      <c r="S520" s="14"/>
+      <c r="AC520" s="12"/>
+      <c r="AE520" s="12"/>
     </row>
     <row r="521">
-      <c r="Q521" s="14"/>
-      <c r="S521" s="14"/>
+      <c r="AC521" s="12"/>
+      <c r="AE521" s="12"/>
     </row>
     <row r="522">
-      <c r="Q522" s="14"/>
-      <c r="S522" s="14"/>
+      <c r="AC522" s="12"/>
+      <c r="AE522" s="12"/>
     </row>
     <row r="523">
-      <c r="Q523" s="14"/>
-      <c r="S523" s="14"/>
+      <c r="AC523" s="12"/>
+      <c r="AE523" s="12"/>
     </row>
     <row r="524">
-      <c r="Q524" s="14"/>
-      <c r="S524" s="14"/>
+      <c r="AC524" s="12"/>
+      <c r="AE524" s="12"/>
     </row>
     <row r="525">
-      <c r="Q525" s="14"/>
-      <c r="S525" s="14"/>
+      <c r="AC525" s="12"/>
+      <c r="AE525" s="12"/>
     </row>
     <row r="526">
-      <c r="Q526" s="14"/>
-      <c r="S526" s="14"/>
+      <c r="AC526" s="12"/>
+      <c r="AE526" s="12"/>
     </row>
     <row r="527">
-      <c r="Q527" s="14"/>
-      <c r="S527" s="14"/>
+      <c r="AC527" s="12"/>
+      <c r="AE527" s="12"/>
     </row>
     <row r="528">
-      <c r="Q528" s="14"/>
-      <c r="S528" s="14"/>
+      <c r="AC528" s="12"/>
+      <c r="AE528" s="12"/>
     </row>
     <row r="529">
-      <c r="Q529" s="14"/>
-      <c r="S529" s="14"/>
+      <c r="AC529" s="12"/>
+      <c r="AE529" s="12"/>
     </row>
     <row r="530">
-      <c r="Q530" s="14"/>
-      <c r="S530" s="14"/>
+      <c r="AC530" s="12"/>
+      <c r="AE530" s="12"/>
     </row>
     <row r="531">
-      <c r="Q531" s="14"/>
-      <c r="S531" s="14"/>
+      <c r="AC531" s="12"/>
+      <c r="AE531" s="12"/>
     </row>
     <row r="532">
-      <c r="Q532" s="14"/>
-      <c r="S532" s="14"/>
+      <c r="AC532" s="12"/>
+      <c r="AE532" s="12"/>
     </row>
     <row r="533">
-      <c r="Q533" s="14"/>
-      <c r="S533" s="14"/>
+      <c r="AC533" s="12"/>
+      <c r="AE533" s="12"/>
     </row>
     <row r="534">
-      <c r="Q534" s="14"/>
-      <c r="S534" s="14"/>
+      <c r="AC534" s="12"/>
+      <c r="AE534" s="12"/>
     </row>
     <row r="535">
-      <c r="Q535" s="14"/>
-      <c r="S535" s="14"/>
+      <c r="AC535" s="12"/>
+      <c r="AE535" s="12"/>
     </row>
     <row r="536">
-      <c r="Q536" s="14"/>
-      <c r="S536" s="14"/>
+      <c r="AC536" s="12"/>
+      <c r="AE536" s="12"/>
     </row>
     <row r="537">
-      <c r="Q537" s="14"/>
-      <c r="S537" s="14"/>
+      <c r="AC537" s="12"/>
+      <c r="AE537" s="12"/>
     </row>
     <row r="538">
-      <c r="Q538" s="14"/>
-      <c r="S538" s="14"/>
+      <c r="AC538" s="12"/>
+      <c r="AE538" s="12"/>
     </row>
     <row r="539">
-      <c r="Q539" s="14"/>
-      <c r="S539" s="14"/>
+      <c r="AC539" s="12"/>
+      <c r="AE539" s="12"/>
     </row>
     <row r="540">
-      <c r="Q540" s="14"/>
-      <c r="S540" s="14"/>
+      <c r="AC540" s="12"/>
+      <c r="AE540" s="12"/>
     </row>
     <row r="541">
-      <c r="Q541" s="14"/>
-      <c r="S541" s="14"/>
+      <c r="AC541" s="12"/>
+      <c r="AE541" s="12"/>
     </row>
     <row r="542">
-      <c r="Q542" s="14"/>
-      <c r="S542" s="14"/>
+      <c r="AC542" s="12"/>
+      <c r="AE542" s="12"/>
     </row>
     <row r="543">
-      <c r="Q543" s="14"/>
-      <c r="S543" s="14"/>
+      <c r="AC543" s="12"/>
+      <c r="AE543" s="12"/>
     </row>
     <row r="544">
-      <c r="Q544" s="14"/>
-      <c r="S544" s="14"/>
+      <c r="AC544" s="12"/>
+      <c r="AE544" s="12"/>
     </row>
     <row r="545">
-      <c r="Q545" s="14"/>
-      <c r="S545" s="14"/>
+      <c r="AC545" s="12"/>
+      <c r="AE545" s="12"/>
     </row>
     <row r="546">
-      <c r="Q546" s="14"/>
-      <c r="S546" s="14"/>
+      <c r="AC546" s="12"/>
+      <c r="AE546" s="12"/>
     </row>
     <row r="547">
-      <c r="Q547" s="14"/>
-      <c r="S547" s="14"/>
+      <c r="AC547" s="12"/>
+      <c r="AE547" s="12"/>
     </row>
     <row r="548">
-      <c r="Q548" s="14"/>
-      <c r="S548" s="14"/>
+      <c r="AC548" s="12"/>
+      <c r="AE548" s="12"/>
     </row>
     <row r="549">
-      <c r="Q549" s="14"/>
-      <c r="S549" s="14"/>
+      <c r="AC549" s="12"/>
+      <c r="AE549" s="12"/>
     </row>
     <row r="550">
-      <c r="Q550" s="14"/>
-      <c r="S550" s="14"/>
+      <c r="AC550" s="12"/>
+      <c r="AE550" s="12"/>
     </row>
     <row r="551">
-      <c r="Q551" s="14"/>
-      <c r="S551" s="14"/>
+      <c r="AC551" s="12"/>
+      <c r="AE551" s="12"/>
     </row>
     <row r="552">
-      <c r="Q552" s="14"/>
-      <c r="S552" s="14"/>
+      <c r="AC552" s="12"/>
+      <c r="AE552" s="12"/>
     </row>
     <row r="553">
-      <c r="Q553" s="14"/>
-      <c r="S553" s="14"/>
+      <c r="AC553" s="12"/>
+      <c r="AE553" s="12"/>
     </row>
     <row r="554">
-      <c r="Q554" s="14"/>
-      <c r="S554" s="14"/>
+      <c r="AC554" s="12"/>
+      <c r="AE554" s="12"/>
     </row>
     <row r="555">
-      <c r="Q555" s="14"/>
-      <c r="S555" s="14"/>
+      <c r="AC555" s="12"/>
+      <c r="AE555" s="12"/>
     </row>
     <row r="556">
-      <c r="Q556" s="14"/>
-      <c r="S556" s="14"/>
+      <c r="AC556" s="12"/>
+      <c r="AE556" s="12"/>
     </row>
     <row r="557">
-      <c r="Q557" s="14"/>
-      <c r="S557" s="14"/>
+      <c r="AC557" s="12"/>
+      <c r="AE557" s="12"/>
     </row>
     <row r="558">
-      <c r="Q558" s="14"/>
-      <c r="S558" s="14"/>
+      <c r="AC558" s="12"/>
+      <c r="AE558" s="12"/>
     </row>
     <row r="559">
-      <c r="Q559" s="14"/>
-      <c r="S559" s="14"/>
+      <c r="AC559" s="12"/>
+      <c r="AE559" s="12"/>
     </row>
     <row r="560">
-      <c r="Q560" s="14"/>
-      <c r="S560" s="14"/>
+      <c r="AC560" s="12"/>
+      <c r="AE560" s="12"/>
     </row>
     <row r="561">
-      <c r="Q561" s="14"/>
-      <c r="S561" s="14"/>
+      <c r="AC561" s="12"/>
+      <c r="AE561" s="12"/>
     </row>
     <row r="562">
-      <c r="Q562" s="14"/>
-      <c r="S562" s="14"/>
+      <c r="AC562" s="12"/>
+      <c r="AE562" s="12"/>
     </row>
     <row r="563">
-      <c r="Q563" s="14"/>
-      <c r="S563" s="14"/>
+      <c r="AC563" s="12"/>
+      <c r="AE563" s="12"/>
     </row>
     <row r="564">
-      <c r="Q564" s="14"/>
-      <c r="S564" s="14"/>
+      <c r="AC564" s="12"/>
+      <c r="AE564" s="12"/>
     </row>
     <row r="565">
-      <c r="Q565" s="14"/>
-      <c r="S565" s="14"/>
+      <c r="AC565" s="12"/>
+      <c r="AE565" s="12"/>
     </row>
     <row r="566">
-      <c r="Q566" s="14"/>
-      <c r="S566" s="14"/>
+      <c r="AC566" s="12"/>
+      <c r="AE566" s="12"/>
     </row>
     <row r="567">
-      <c r="Q567" s="14"/>
-      <c r="S567" s="14"/>
+      <c r="AC567" s="12"/>
+      <c r="AE567" s="12"/>
     </row>
     <row r="568">
-      <c r="Q568" s="14"/>
-      <c r="S568" s="14"/>
+      <c r="AC568" s="12"/>
+      <c r="AE568" s="12"/>
     </row>
     <row r="569">
-      <c r="Q569" s="14"/>
-      <c r="S569" s="14"/>
+      <c r="AC569" s="12"/>
+      <c r="AE569" s="12"/>
     </row>
     <row r="570">
-      <c r="Q570" s="14"/>
-      <c r="S570" s="14"/>
+      <c r="AC570" s="12"/>
+      <c r="AE570" s="12"/>
     </row>
     <row r="571">
-      <c r="Q571" s="14"/>
-      <c r="S571" s="14"/>
+      <c r="AC571" s="12"/>
+      <c r="AE571" s="12"/>
     </row>
     <row r="572">
-      <c r="Q572" s="14"/>
-      <c r="S572" s="14"/>
+      <c r="AC572" s="12"/>
+      <c r="AE572" s="12"/>
     </row>
     <row r="573">
-      <c r="Q573" s="14"/>
-      <c r="S573" s="14"/>
+      <c r="AC573" s="12"/>
+      <c r="AE573" s="12"/>
     </row>
     <row r="574">
-      <c r="Q574" s="14"/>
-      <c r="S574" s="14"/>
+      <c r="AC574" s="12"/>
+      <c r="AE574" s="12"/>
     </row>
     <row r="575">
-      <c r="Q575" s="14"/>
-      <c r="S575" s="14"/>
+      <c r="AC575" s="12"/>
+      <c r="AE575" s="12"/>
     </row>
     <row r="576">
-      <c r="Q576" s="14"/>
-      <c r="S576" s="14"/>
+      <c r="AC576" s="12"/>
+      <c r="AE576" s="12"/>
     </row>
     <row r="577">
-      <c r="Q577" s="14"/>
-      <c r="S577" s="14"/>
+      <c r="AC577" s="12"/>
+      <c r="AE577" s="12"/>
     </row>
     <row r="578">
-      <c r="Q578" s="14"/>
-      <c r="S578" s="14"/>
+      <c r="AC578" s="12"/>
+      <c r="AE578" s="12"/>
     </row>
     <row r="579">
-      <c r="Q579" s="14"/>
-      <c r="S579" s="14"/>
+      <c r="AC579" s="12"/>
+      <c r="AE579" s="12"/>
     </row>
     <row r="580">
-      <c r="Q580" s="14"/>
-      <c r="S580" s="14"/>
+      <c r="AC580" s="12"/>
+      <c r="AE580" s="12"/>
     </row>
     <row r="581">
-      <c r="Q581" s="14"/>
-      <c r="S581" s="14"/>
+      <c r="AC581" s="12"/>
+      <c r="AE581" s="12"/>
     </row>
     <row r="582">
-      <c r="Q582" s="14"/>
-      <c r="S582" s="14"/>
+      <c r="AC582" s="12"/>
+      <c r="AE582" s="12"/>
     </row>
     <row r="583">
-      <c r="Q583" s="14"/>
-      <c r="S583" s="14"/>
+      <c r="AC583" s="12"/>
+      <c r="AE583" s="12"/>
     </row>
     <row r="584">
-      <c r="Q584" s="14"/>
-      <c r="S584" s="14"/>
+      <c r="AC584" s="12"/>
+      <c r="AE584" s="12"/>
     </row>
     <row r="585">
-      <c r="Q585" s="14"/>
-      <c r="S585" s="14"/>
+      <c r="AC585" s="12"/>
+      <c r="AE585" s="12"/>
     </row>
     <row r="586">
-      <c r="Q586" s="14"/>
-      <c r="S586" s="14"/>
+      <c r="AC586" s="12"/>
+      <c r="AE586" s="12"/>
     </row>
     <row r="587">
-      <c r="Q587" s="14"/>
-      <c r="S587" s="14"/>
+      <c r="AC587" s="12"/>
+      <c r="AE587" s="12"/>
     </row>
     <row r="588">
-      <c r="Q588" s="14"/>
-      <c r="S588" s="14"/>
+      <c r="AC588" s="12"/>
+      <c r="AE588" s="12"/>
     </row>
     <row r="589">
-      <c r="Q589" s="14"/>
-      <c r="S589" s="14"/>
+      <c r="AC589" s="12"/>
+      <c r="AE589" s="12"/>
     </row>
     <row r="590">
-      <c r="Q590" s="14"/>
-      <c r="S590" s="14"/>
+      <c r="AC590" s="12"/>
+      <c r="AE590" s="12"/>
     </row>
     <row r="591">
-      <c r="Q591" s="14"/>
-      <c r="S591" s="14"/>
+      <c r="AC591" s="12"/>
+      <c r="AE591" s="12"/>
     </row>
     <row r="592">
-      <c r="Q592" s="14"/>
-      <c r="S592" s="14"/>
+      <c r="AC592" s="12"/>
+      <c r="AE592" s="12"/>
     </row>
     <row r="593">
-      <c r="Q593" s="14"/>
-      <c r="S593" s="14"/>
+      <c r="AC593" s="12"/>
+      <c r="AE593" s="12"/>
     </row>
     <row r="594">
-      <c r="Q594" s="14"/>
-      <c r="S594" s="14"/>
+      <c r="AC594" s="12"/>
+      <c r="AE594" s="12"/>
     </row>
     <row r="595">
-      <c r="Q595" s="14"/>
-      <c r="S595" s="14"/>
+      <c r="AC595" s="12"/>
+      <c r="AE595" s="12"/>
     </row>
     <row r="596">
-      <c r="Q596" s="14"/>
-      <c r="S596" s="14"/>
+      <c r="AC596" s="12"/>
+      <c r="AE596" s="12"/>
     </row>
     <row r="597">
-      <c r="Q597" s="14"/>
-      <c r="S597" s="14"/>
+      <c r="AC597" s="12"/>
+      <c r="AE597" s="12"/>
     </row>
     <row r="598">
-      <c r="Q598" s="14"/>
-      <c r="S598" s="14"/>
+      <c r="AC598" s="12"/>
+      <c r="AE598" s="12"/>
     </row>
     <row r="599">
-      <c r="Q599" s="14"/>
-      <c r="S599" s="14"/>
+      <c r="AC599" s="12"/>
+      <c r="AE599" s="12"/>
     </row>
     <row r="600">
-      <c r="Q600" s="14"/>
-      <c r="S600" s="14"/>
+      <c r="AC600" s="12"/>
+      <c r="AE600" s="12"/>
     </row>
     <row r="601">
-      <c r="Q601" s="14"/>
-      <c r="S601" s="14"/>
+      <c r="AC601" s="12"/>
+      <c r="AE601" s="12"/>
     </row>
     <row r="602">
-      <c r="Q602" s="14"/>
-      <c r="S602" s="14"/>
+      <c r="AC602" s="12"/>
+      <c r="AE602" s="12"/>
     </row>
     <row r="603">
-      <c r="Q603" s="14"/>
-      <c r="S603" s="14"/>
+      <c r="AC603" s="12"/>
+      <c r="AE603" s="12"/>
     </row>
     <row r="604">
-      <c r="Q604" s="14"/>
-      <c r="S604" s="14"/>
+      <c r="AC604" s="12"/>
+      <c r="AE604" s="12"/>
     </row>
     <row r="605">
-      <c r="Q605" s="14"/>
-      <c r="S605" s="14"/>
+      <c r="AC605" s="12"/>
+      <c r="AE605" s="12"/>
     </row>
     <row r="606">
-      <c r="Q606" s="14"/>
-      <c r="S606" s="14"/>
+      <c r="AC606" s="12"/>
+      <c r="AE606" s="12"/>
     </row>
     <row r="607">
-      <c r="Q607" s="14"/>
-      <c r="S607" s="14"/>
+      <c r="AC607" s="12"/>
+      <c r="AE607" s="12"/>
     </row>
     <row r="608">
-      <c r="Q608" s="14"/>
-      <c r="S608" s="14"/>
+      <c r="AC608" s="12"/>
+      <c r="AE608" s="12"/>
     </row>
     <row r="609">
-      <c r="Q609" s="14"/>
-      <c r="S609" s="14"/>
+      <c r="AC609" s="12"/>
+      <c r="AE609" s="12"/>
     </row>
     <row r="610">
-      <c r="Q610" s="14"/>
-      <c r="S610" s="14"/>
+      <c r="AC610" s="12"/>
+      <c r="AE610" s="12"/>
     </row>
     <row r="611">
-      <c r="Q611" s="14"/>
-      <c r="S611" s="14"/>
+      <c r="AC611" s="12"/>
+      <c r="AE611" s="12"/>
     </row>
     <row r="612">
-      <c r="Q612" s="14"/>
-      <c r="S612" s="14"/>
+      <c r="AC612" s="12"/>
+      <c r="AE612" s="12"/>
     </row>
     <row r="613">
-      <c r="Q613" s="14"/>
-      <c r="S613" s="14"/>
+      <c r="AC613" s="12"/>
+      <c r="AE613" s="12"/>
     </row>
     <row r="614">
-      <c r="Q614" s="14"/>
-      <c r="S614" s="14"/>
+      <c r="AC614" s="12"/>
+      <c r="AE614" s="12"/>
     </row>
     <row r="615">
-      <c r="Q615" s="14"/>
-      <c r="S615" s="14"/>
+      <c r="AC615" s="12"/>
+      <c r="AE615" s="12"/>
     </row>
     <row r="616">
-      <c r="Q616" s="14"/>
-      <c r="S616" s="14"/>
+      <c r="AC616" s="12"/>
+      <c r="AE616" s="12"/>
     </row>
     <row r="617">
-      <c r="Q617" s="14"/>
-      <c r="S617" s="14"/>
+      <c r="AC617" s="12"/>
+      <c r="AE617" s="12"/>
     </row>
     <row r="618">
-      <c r="Q618" s="14"/>
-      <c r="S618" s="14"/>
+      <c r="AC618" s="12"/>
+      <c r="AE618" s="12"/>
     </row>
     <row r="619">
-      <c r="Q619" s="14"/>
-      <c r="S619" s="14"/>
+      <c r="AC619" s="12"/>
+      <c r="AE619" s="12"/>
     </row>
     <row r="620">
-      <c r="Q620" s="14"/>
-      <c r="S620" s="14"/>
+      <c r="AC620" s="12"/>
+      <c r="AE620" s="12"/>
     </row>
     <row r="621">
-      <c r="Q621" s="14"/>
-      <c r="S621" s="14"/>
+      <c r="AC621" s="12"/>
+      <c r="AE621" s="12"/>
     </row>
     <row r="622">
-      <c r="Q622" s="14"/>
-      <c r="S622" s="14"/>
+      <c r="AC622" s="12"/>
+      <c r="AE622" s="12"/>
     </row>
     <row r="623">
-      <c r="Q623" s="14"/>
-      <c r="S623" s="14"/>
+      <c r="AC623" s="12"/>
+      <c r="AE623" s="12"/>
     </row>
     <row r="624">
-      <c r="Q624" s="14"/>
-      <c r="S624" s="14"/>
+      <c r="AC624" s="12"/>
+      <c r="AE624" s="12"/>
     </row>
     <row r="625">
-      <c r="Q625" s="14"/>
-      <c r="S625" s="14"/>
+      <c r="AC625" s="12"/>
+      <c r="AE625" s="12"/>
     </row>
     <row r="626">
-      <c r="Q626" s="14"/>
-      <c r="S626" s="14"/>
+      <c r="AC626" s="12"/>
+      <c r="AE626" s="12"/>
     </row>
     <row r="627">
-      <c r="Q627" s="14"/>
-      <c r="S627" s="14"/>
+      <c r="AC627" s="12"/>
+      <c r="AE627" s="12"/>
     </row>
     <row r="628">
-      <c r="Q628" s="14"/>
-      <c r="S628" s="14"/>
+      <c r="AC628" s="12"/>
+      <c r="AE628" s="12"/>
     </row>
     <row r="629">
-      <c r="Q629" s="14"/>
-      <c r="S629" s="14"/>
+      <c r="AC629" s="12"/>
+      <c r="AE629" s="12"/>
     </row>
     <row r="630">
-      <c r="Q630" s="14"/>
-      <c r="S630" s="14"/>
+      <c r="AC630" s="12"/>
+      <c r="AE630" s="12"/>
     </row>
     <row r="631">
-      <c r="Q631" s="14"/>
-      <c r="S631" s="14"/>
+      <c r="AC631" s="12"/>
+      <c r="AE631" s="12"/>
     </row>
     <row r="632">
-      <c r="Q632" s="14"/>
-      <c r="S632" s="14"/>
+      <c r="AC632" s="12"/>
+      <c r="AE632" s="12"/>
     </row>
     <row r="633">
-      <c r="Q633" s="14"/>
-      <c r="S633" s="14"/>
+      <c r="AC633" s="12"/>
+      <c r="AE633" s="12"/>
     </row>
     <row r="634">
-      <c r="Q634" s="14"/>
-      <c r="S634" s="14"/>
+      <c r="AC634" s="12"/>
+      <c r="AE634" s="12"/>
     </row>
     <row r="635">
-      <c r="Q635" s="14"/>
-      <c r="S635" s="14"/>
+      <c r="AC635" s="12"/>
+      <c r="AE635" s="12"/>
     </row>
     <row r="636">
-      <c r="Q636" s="14"/>
-      <c r="S636" s="14"/>
+      <c r="AC636" s="12"/>
+      <c r="AE636" s="12"/>
     </row>
     <row r="637">
-      <c r="Q637" s="14"/>
-      <c r="S637" s="14"/>
+      <c r="AC637" s="12"/>
+      <c r="AE637" s="12"/>
     </row>
     <row r="638">
-      <c r="Q638" s="14"/>
-      <c r="S638" s="14"/>
+      <c r="AC638" s="12"/>
+      <c r="AE638" s="12"/>
     </row>
     <row r="639">
-      <c r="Q639" s="14"/>
-      <c r="S639" s="14"/>
+      <c r="AC639" s="12"/>
+      <c r="AE639" s="12"/>
     </row>
     <row r="640">
-      <c r="Q640" s="14"/>
-      <c r="S640" s="14"/>
+      <c r="AC640" s="12"/>
+      <c r="AE640" s="12"/>
     </row>
     <row r="641">
-      <c r="Q641" s="14"/>
-      <c r="S641" s="14"/>
+      <c r="AC641" s="12"/>
+      <c r="AE641" s="12"/>
     </row>
     <row r="642">
-      <c r="Q642" s="14"/>
-      <c r="S642" s="14"/>
+      <c r="AC642" s="12"/>
+      <c r="AE642" s="12"/>
     </row>
     <row r="643">
-      <c r="Q643" s="14"/>
-      <c r="S643" s="14"/>
+      <c r="AC643" s="12"/>
+      <c r="AE643" s="12"/>
     </row>
     <row r="644">
-      <c r="Q644" s="14"/>
-      <c r="S644" s="14"/>
+      <c r="AC644" s="12"/>
+      <c r="AE644" s="12"/>
     </row>
     <row r="645">
-      <c r="Q645" s="14"/>
-      <c r="S645" s="14"/>
+      <c r="AC645" s="12"/>
+      <c r="AE645" s="12"/>
     </row>
     <row r="646">
-      <c r="Q646" s="14"/>
-      <c r="S646" s="14"/>
+      <c r="AC646" s="12"/>
+      <c r="AE646" s="12"/>
     </row>
     <row r="647">
-      <c r="Q647" s="14"/>
-      <c r="S647" s="14"/>
+      <c r="AC647" s="12"/>
+      <c r="AE647" s="12"/>
     </row>
     <row r="648">
-      <c r="Q648" s="14"/>
-      <c r="S648" s="14"/>
+      <c r="AC648" s="12"/>
+      <c r="AE648" s="12"/>
     </row>
     <row r="649">
-      <c r="Q649" s="14"/>
-      <c r="S649" s="14"/>
+      <c r="AC649" s="12"/>
+      <c r="AE649" s="12"/>
     </row>
     <row r="650">
-      <c r="Q650" s="14"/>
-      <c r="S650" s="14"/>
+      <c r="AC650" s="12"/>
+      <c r="AE650" s="12"/>
     </row>
     <row r="651">
-      <c r="Q651" s="14"/>
-      <c r="S651" s="14"/>
+      <c r="AC651" s="12"/>
+      <c r="AE651" s="12"/>
     </row>
     <row r="652">
-      <c r="Q652" s="14"/>
-      <c r="S652" s="14"/>
+      <c r="AC652" s="12"/>
+      <c r="AE652" s="12"/>
     </row>
     <row r="653">
-      <c r="Q653" s="14"/>
-      <c r="S653" s="14"/>
+      <c r="AC653" s="12"/>
+      <c r="AE653" s="12"/>
     </row>
     <row r="654">
-      <c r="Q654" s="14"/>
-      <c r="S654" s="14"/>
+      <c r="AC654" s="12"/>
+      <c r="AE654" s="12"/>
     </row>
     <row r="655">
-      <c r="Q655" s="14"/>
-      <c r="S655" s="14"/>
+      <c r="AC655" s="12"/>
+      <c r="AE655" s="12"/>
     </row>
     <row r="656">
-      <c r="Q656" s="14"/>
-      <c r="S656" s="14"/>
+      <c r="AC656" s="12"/>
+      <c r="AE656" s="12"/>
     </row>
     <row r="657">
-      <c r="Q657" s="14"/>
-      <c r="S657" s="14"/>
+      <c r="AC657" s="12"/>
+      <c r="AE657" s="12"/>
     </row>
     <row r="658">
-      <c r="Q658" s="14"/>
-      <c r="S658" s="14"/>
+      <c r="AC658" s="12"/>
+      <c r="AE658" s="12"/>
     </row>
     <row r="659">
-      <c r="Q659" s="14"/>
-      <c r="S659" s="14"/>
+      <c r="AC659" s="12"/>
+      <c r="AE659" s="12"/>
     </row>
     <row r="660">
-      <c r="Q660" s="14"/>
-      <c r="S660" s="14"/>
+      <c r="AC660" s="12"/>
+      <c r="AE660" s="12"/>
     </row>
     <row r="661">
-      <c r="Q661" s="14"/>
-      <c r="S661" s="14"/>
+      <c r="AC661" s="12"/>
+      <c r="AE661" s="12"/>
     </row>
     <row r="662">
-      <c r="Q662" s="14"/>
-      <c r="S662" s="14"/>
+      <c r="AC662" s="12"/>
+      <c r="AE662" s="12"/>
     </row>
     <row r="663">
-      <c r="Q663" s="14"/>
-      <c r="S663" s="14"/>
+      <c r="AC663" s="12"/>
+      <c r="AE663" s="12"/>
     </row>
     <row r="664">
-      <c r="Q664" s="14"/>
-      <c r="S664" s="14"/>
+      <c r="AC664" s="12"/>
+      <c r="AE664" s="12"/>
     </row>
     <row r="665">
-      <c r="Q665" s="14"/>
-      <c r="S665" s="14"/>
+      <c r="AC665" s="12"/>
+      <c r="AE665" s="12"/>
     </row>
     <row r="666">
-      <c r="Q666" s="14"/>
-      <c r="S666" s="14"/>
+      <c r="AC666" s="12"/>
+      <c r="AE666" s="12"/>
     </row>
     <row r="667">
-      <c r="Q667" s="14"/>
-      <c r="S667" s="14"/>
+      <c r="AC667" s="12"/>
+      <c r="AE667" s="12"/>
     </row>
     <row r="668">
-      <c r="Q668" s="14"/>
-      <c r="S668" s="14"/>
+      <c r="AC668" s="12"/>
+      <c r="AE668" s="12"/>
     </row>
     <row r="669">
-      <c r="Q669" s="14"/>
-      <c r="S669" s="14"/>
+      <c r="AC669" s="12"/>
+      <c r="AE669" s="12"/>
     </row>
     <row r="670">
-      <c r="Q670" s="14"/>
-      <c r="S670" s="14"/>
+      <c r="AC670" s="12"/>
+      <c r="AE670" s="12"/>
     </row>
     <row r="671">
-      <c r="Q671" s="14"/>
-      <c r="S671" s="14"/>
+      <c r="AC671" s="12"/>
+      <c r="AE671" s="12"/>
     </row>
     <row r="672">
-      <c r="Q672" s="14"/>
-      <c r="S672" s="14"/>
+      <c r="AC672" s="12"/>
+      <c r="AE672" s="12"/>
     </row>
     <row r="673">
-      <c r="Q673" s="14"/>
-      <c r="S673" s="14"/>
+      <c r="AC673" s="12"/>
+      <c r="AE673" s="12"/>
     </row>
     <row r="674">
-      <c r="Q674" s="14"/>
-      <c r="S674" s="14"/>
+      <c r="AC674" s="12"/>
+      <c r="AE674" s="12"/>
     </row>
     <row r="675">
-      <c r="Q675" s="14"/>
-      <c r="S675" s="14"/>
+      <c r="AC675" s="12"/>
+      <c r="AE675" s="12"/>
     </row>
     <row r="676">
-      <c r="Q676" s="14"/>
-      <c r="S676" s="14"/>
+      <c r="AC676" s="12"/>
+      <c r="AE676" s="12"/>
     </row>
     <row r="677">
-      <c r="Q677" s="14"/>
-      <c r="S677" s="14"/>
+      <c r="AC677" s="12"/>
+      <c r="AE677" s="12"/>
     </row>
     <row r="678">
-      <c r="Q678" s="14"/>
-      <c r="S678" s="14"/>
+      <c r="AC678" s="12"/>
+      <c r="AE678" s="12"/>
     </row>
     <row r="679">
-      <c r="Q679" s="14"/>
-      <c r="S679" s="14"/>
+      <c r="AC679" s="12"/>
+      <c r="AE679" s="12"/>
     </row>
     <row r="680">
-      <c r="Q680" s="14"/>
-      <c r="S680" s="14"/>
+      <c r="AC680" s="12"/>
+      <c r="AE680" s="12"/>
     </row>
     <row r="681">
-      <c r="Q681" s="14"/>
-      <c r="S681" s="14"/>
+      <c r="AC681" s="12"/>
+      <c r="AE681" s="12"/>
     </row>
     <row r="682">
-      <c r="Q682" s="14"/>
-      <c r="S682" s="14"/>
+      <c r="AC682" s="12"/>
+      <c r="AE682" s="12"/>
     </row>
     <row r="683">
-      <c r="Q683" s="14"/>
-      <c r="S683" s="14"/>
+      <c r="AC683" s="12"/>
+      <c r="AE683" s="12"/>
     </row>
     <row r="684">
-      <c r="Q684" s="14"/>
-      <c r="S684" s="14"/>
+      <c r="AC684" s="12"/>
+      <c r="AE684" s="12"/>
     </row>
     <row r="685">
-      <c r="Q685" s="14"/>
-      <c r="S685" s="14"/>
+      <c r="AC685" s="12"/>
+      <c r="AE685" s="12"/>
     </row>
     <row r="686">
-      <c r="Q686" s="14"/>
-      <c r="S686" s="14"/>
+      <c r="AC686" s="12"/>
+      <c r="AE686" s="12"/>
     </row>
     <row r="687">
-      <c r="Q687" s="14"/>
-      <c r="S687" s="14"/>
+      <c r="AC687" s="12"/>
+      <c r="AE687" s="12"/>
     </row>
     <row r="688">
-      <c r="Q688" s="14"/>
-      <c r="S688" s="14"/>
+      <c r="AC688" s="12"/>
+      <c r="AE688" s="12"/>
     </row>
     <row r="689">
-      <c r="Q689" s="14"/>
-      <c r="S689" s="14"/>
+      <c r="AC689" s="12"/>
+      <c r="AE689" s="12"/>
     </row>
     <row r="690">
-      <c r="Q690" s="14"/>
-      <c r="S690" s="14"/>
+      <c r="AC690" s="12"/>
+      <c r="AE690" s="12"/>
     </row>
     <row r="691">
-      <c r="Q691" s="14"/>
-      <c r="S691" s="14"/>
+      <c r="AC691" s="12"/>
+      <c r="AE691" s="12"/>
     </row>
     <row r="692">
-      <c r="Q692" s="14"/>
-      <c r="S692" s="14"/>
+      <c r="AC692" s="12"/>
+      <c r="AE692" s="12"/>
     </row>
     <row r="693">
-      <c r="Q693" s="14"/>
-      <c r="S693" s="14"/>
+      <c r="AC693" s="12"/>
+      <c r="AE693" s="12"/>
     </row>
     <row r="694">
-      <c r="Q694" s="14"/>
-      <c r="S694" s="14"/>
+      <c r="AC694" s="12"/>
+      <c r="AE694" s="12"/>
     </row>
     <row r="695">
-      <c r="Q695" s="14"/>
-      <c r="S695" s="14"/>
+      <c r="AC695" s="12"/>
+      <c r="AE695" s="12"/>
     </row>
     <row r="696">
-      <c r="Q696" s="14"/>
-      <c r="S696" s="14"/>
+      <c r="AC696" s="12"/>
+      <c r="AE696" s="12"/>
     </row>
     <row r="697">
-      <c r="Q697" s="14"/>
-      <c r="S697" s="14"/>
+      <c r="AC697" s="12"/>
+      <c r="AE697" s="12"/>
     </row>
     <row r="698">
-      <c r="Q698" s="14"/>
-      <c r="S698" s="14"/>
+      <c r="AC698" s="12"/>
+      <c r="AE698" s="12"/>
     </row>
     <row r="699">
-      <c r="Q699" s="14"/>
-      <c r="S699" s="14"/>
+      <c r="AC699" s="12"/>
+      <c r="AE699" s="12"/>
     </row>
     <row r="700">
-      <c r="Q700" s="14"/>
-      <c r="S700" s="14"/>
+      <c r="AC700" s="12"/>
+      <c r="AE700" s="12"/>
     </row>
     <row r="701">
-      <c r="Q701" s="14"/>
-      <c r="S701" s="14"/>
+      <c r="AC701" s="12"/>
+      <c r="AE701" s="12"/>
     </row>
     <row r="702">
-      <c r="Q702" s="14"/>
-      <c r="S702" s="14"/>
+      <c r="AC702" s="12"/>
+      <c r="AE702" s="12"/>
     </row>
     <row r="703">
-      <c r="Q703" s="14"/>
-      <c r="S703" s="14"/>
+      <c r="AC703" s="12"/>
+      <c r="AE703" s="12"/>
     </row>
     <row r="704">
-      <c r="Q704" s="14"/>
-      <c r="S704" s="14"/>
+      <c r="AC704" s="12"/>
+      <c r="AE704" s="12"/>
     </row>
     <row r="705">
-      <c r="Q705" s="14"/>
-      <c r="S705" s="14"/>
+      <c r="AC705" s="12"/>
+      <c r="AE705" s="12"/>
     </row>
     <row r="706">
-      <c r="Q706" s="14"/>
-      <c r="S706" s="14"/>
+      <c r="AC706" s="12"/>
+      <c r="AE706" s="12"/>
     </row>
     <row r="707">
-      <c r="Q707" s="14"/>
-      <c r="S707" s="14"/>
+      <c r="AC707" s="12"/>
+      <c r="AE707" s="12"/>
     </row>
     <row r="708">
-      <c r="Q708" s="14"/>
-      <c r="S708" s="14"/>
+      <c r="AC708" s="12"/>
+      <c r="AE708" s="12"/>
     </row>
     <row r="709">
-      <c r="Q709" s="14"/>
-      <c r="S709" s="14"/>
+      <c r="AC709" s="12"/>
+      <c r="AE709" s="12"/>
     </row>
     <row r="710">
-      <c r="Q710" s="14"/>
-      <c r="S710" s="14"/>
+      <c r="AC710" s="12"/>
+      <c r="AE710" s="12"/>
     </row>
     <row r="711">
-      <c r="Q711" s="14"/>
-      <c r="S711" s="14"/>
+      <c r="AC711" s="12"/>
+      <c r="AE711" s="12"/>
     </row>
     <row r="712">
-      <c r="Q712" s="14"/>
-      <c r="S712" s="14"/>
+      <c r="AC712" s="12"/>
+      <c r="AE712" s="12"/>
     </row>
     <row r="713">
-      <c r="Q713" s="14"/>
-      <c r="S713" s="14"/>
+      <c r="AC713" s="12"/>
+      <c r="AE713" s="12"/>
     </row>
     <row r="714">
-      <c r="Q714" s="14"/>
-      <c r="S714" s="14"/>
+      <c r="AC714" s="12"/>
+      <c r="AE714" s="12"/>
     </row>
     <row r="715">
-      <c r="Q715" s="14"/>
-      <c r="S715" s="14"/>
+      <c r="AC715" s="12"/>
+      <c r="AE715" s="12"/>
     </row>
     <row r="716">
-      <c r="Q716" s="14"/>
-      <c r="S716" s="14"/>
+      <c r="AC716" s="12"/>
+      <c r="AE716" s="12"/>
     </row>
     <row r="717">
-      <c r="Q717" s="14"/>
-      <c r="S717" s="14"/>
+      <c r="AC717" s="12"/>
+      <c r="AE717" s="12"/>
     </row>
     <row r="718">
-      <c r="Q718" s="14"/>
-      <c r="S718" s="14"/>
+      <c r="AC718" s="12"/>
+      <c r="AE718" s="12"/>
     </row>
     <row r="719">
-      <c r="Q719" s="14"/>
-      <c r="S719" s="14"/>
+      <c r="AC719" s="12"/>
+      <c r="AE719" s="12"/>
     </row>
     <row r="720">
-      <c r="Q720" s="14"/>
-      <c r="S720" s="14"/>
+      <c r="AC720" s="12"/>
+      <c r="AE720" s="12"/>
     </row>
     <row r="721">
-      <c r="Q721" s="14"/>
-      <c r="S721" s="14"/>
+      <c r="AC721" s="12"/>
+      <c r="AE721" s="12"/>
     </row>
     <row r="722">
-      <c r="Q722" s="14"/>
-      <c r="S722" s="14"/>
+      <c r="AC722" s="12"/>
+      <c r="AE722" s="12"/>
     </row>
     <row r="723">
-      <c r="Q723" s="14"/>
-      <c r="S723" s="14"/>
+      <c r="AC723" s="12"/>
+      <c r="AE723" s="12"/>
     </row>
     <row r="724">
-      <c r="Q724" s="14"/>
-      <c r="S724" s="14"/>
+      <c r="AC724" s="12"/>
+      <c r="AE724" s="12"/>
     </row>
     <row r="725">
-      <c r="Q725" s="14"/>
-      <c r="S725" s="14"/>
+      <c r="AC725" s="12"/>
+      <c r="AE725" s="12"/>
     </row>
     <row r="726">
-      <c r="Q726" s="14"/>
-      <c r="S726" s="14"/>
+      <c r="AC726" s="12"/>
+      <c r="AE726" s="12"/>
     </row>
     <row r="727">
-      <c r="Q727" s="14"/>
-      <c r="S727" s="14"/>
+      <c r="AC727" s="12"/>
+      <c r="AE727" s="12"/>
     </row>
     <row r="728">
-      <c r="Q728" s="14"/>
-      <c r="S728" s="14"/>
+      <c r="AC728" s="12"/>
+      <c r="AE728" s="12"/>
     </row>
     <row r="729">
-      <c r="Q729" s="14"/>
-      <c r="S729" s="14"/>
+      <c r="AC729" s="12"/>
+      <c r="AE729" s="12"/>
     </row>
     <row r="730">
-      <c r="Q730" s="14"/>
-      <c r="S730" s="14"/>
+      <c r="AC730" s="12"/>
+      <c r="AE730" s="12"/>
     </row>
     <row r="731">
-      <c r="Q731" s="14"/>
-      <c r="S731" s="14"/>
+      <c r="AC731" s="12"/>
+      <c r="AE731" s="12"/>
     </row>
     <row r="732">
-      <c r="Q732" s="14"/>
-      <c r="S732" s="14"/>
+      <c r="AC732" s="12"/>
+      <c r="AE732" s="12"/>
     </row>
     <row r="733">
-      <c r="Q733" s="14"/>
-      <c r="S733" s="14"/>
+      <c r="AC733" s="12"/>
+      <c r="AE733" s="12"/>
     </row>
     <row r="734">
-      <c r="Q734" s="14"/>
-      <c r="S734" s="14"/>
+      <c r="AC734" s="12"/>
+      <c r="AE734" s="12"/>
     </row>
     <row r="735">
-      <c r="Q735" s="14"/>
-      <c r="S735" s="14"/>
+      <c r="AC735" s="12"/>
+      <c r="AE735" s="12"/>
     </row>
     <row r="736">
-      <c r="Q736" s="14"/>
-      <c r="S736" s="14"/>
+      <c r="AC736" s="12"/>
+      <c r="AE736" s="12"/>
     </row>
     <row r="737">
-      <c r="Q737" s="14"/>
-      <c r="S737" s="14"/>
+      <c r="AC737" s="12"/>
+      <c r="AE737" s="12"/>
     </row>
     <row r="738">
-      <c r="Q738" s="14"/>
-      <c r="S738" s="14"/>
+      <c r="AC738" s="12"/>
+      <c r="AE738" s="12"/>
     </row>
     <row r="739">
-      <c r="Q739" s="14"/>
-      <c r="S739" s="14"/>
+      <c r="AC739" s="12"/>
+      <c r="AE739" s="12"/>
     </row>
     <row r="740">
-      <c r="Q740" s="14"/>
-      <c r="S740" s="14"/>
+      <c r="AC740" s="12"/>
+      <c r="AE740" s="12"/>
     </row>
     <row r="741">
-      <c r="Q741" s="14"/>
-      <c r="S741" s="14"/>
+      <c r="AC741" s="12"/>
+      <c r="AE741" s="12"/>
     </row>
     <row r="742">
-      <c r="Q742" s="14"/>
-      <c r="S742" s="14"/>
+      <c r="AC742" s="12"/>
+      <c r="AE742" s="12"/>
     </row>
     <row r="743">
-      <c r="Q743" s="14"/>
-      <c r="S743" s="14"/>
+      <c r="AC743" s="12"/>
+      <c r="AE743" s="12"/>
     </row>
     <row r="744">
-      <c r="Q744" s="14"/>
-      <c r="S744" s="14"/>
+      <c r="AC744" s="12"/>
+      <c r="AE744" s="12"/>
     </row>
     <row r="745">
-      <c r="Q745" s="14"/>
-      <c r="S745" s="14"/>
+      <c r="AC745" s="12"/>
+      <c r="AE745" s="12"/>
     </row>
     <row r="746">
-      <c r="Q746" s="14"/>
-      <c r="S746" s="14"/>
+      <c r="AC746" s="12"/>
+      <c r="AE746" s="12"/>
     </row>
     <row r="747">
-      <c r="Q747" s="14"/>
-      <c r="S747" s="14"/>
+      <c r="AC747" s="12"/>
+      <c r="AE747" s="12"/>
     </row>
     <row r="748">
-      <c r="Q748" s="14"/>
-      <c r="S748" s="14"/>
+      <c r="AC748" s="12"/>
+      <c r="AE748" s="12"/>
     </row>
     <row r="749">
-      <c r="Q749" s="14"/>
-      <c r="S749" s="14"/>
+      <c r="AC749" s="12"/>
+      <c r="AE749" s="12"/>
     </row>
     <row r="750">
-      <c r="Q750" s="14"/>
-      <c r="S750" s="14"/>
+      <c r="AC750" s="12"/>
+      <c r="AE750" s="12"/>
     </row>
     <row r="751">
-      <c r="Q751" s="14"/>
-      <c r="S751" s="14"/>
+      <c r="AC751" s="12"/>
+      <c r="AE751" s="12"/>
     </row>
     <row r="752">
-      <c r="Q752" s="14"/>
-      <c r="S752" s="14"/>
+      <c r="AC752" s="12"/>
+      <c r="AE752" s="12"/>
     </row>
     <row r="753">
-      <c r="Q753" s="14"/>
-      <c r="S753" s="14"/>
+      <c r="AC753" s="12"/>
+      <c r="AE753" s="12"/>
     </row>
     <row r="754">
-      <c r="Q754" s="14"/>
-      <c r="S754" s="14"/>
+      <c r="AC754" s="12"/>
+      <c r="AE754" s="12"/>
     </row>
     <row r="755">
-      <c r="Q755" s="14"/>
-      <c r="S755" s="14"/>
+      <c r="AC755" s="12"/>
+      <c r="AE755" s="12"/>
     </row>
     <row r="756">
-      <c r="Q756" s="14"/>
-      <c r="S756" s="14"/>
+      <c r="AC756" s="12"/>
+      <c r="AE756" s="12"/>
     </row>
     <row r="757">
-      <c r="Q757" s="14"/>
-      <c r="S757" s="14"/>
+      <c r="AC757" s="12"/>
+      <c r="AE757" s="12"/>
     </row>
     <row r="758">
-      <c r="Q758" s="14"/>
-      <c r="S758" s="14"/>
+      <c r="AC758" s="12"/>
+      <c r="AE758" s="12"/>
     </row>
     <row r="759">
-      <c r="Q759" s="14"/>
-      <c r="S759" s="14"/>
+      <c r="AC759" s="12"/>
+      <c r="AE759" s="12"/>
     </row>
     <row r="760">
-      <c r="Q760" s="14"/>
-      <c r="S760" s="14"/>
+      <c r="AC760" s="12"/>
+      <c r="AE760" s="12"/>
     </row>
     <row r="761">
-      <c r="Q761" s="14"/>
-      <c r="S761" s="14"/>
+      <c r="AC761" s="12"/>
+      <c r="AE761" s="12"/>
     </row>
     <row r="762">
-      <c r="Q762" s="14"/>
-      <c r="S762" s="14"/>
+      <c r="AC762" s="12"/>
+      <c r="AE762" s="12"/>
     </row>
     <row r="763">
-      <c r="Q763" s="14"/>
-      <c r="S763" s="14"/>
+      <c r="AC763" s="12"/>
+      <c r="AE763" s="12"/>
     </row>
     <row r="764">
-      <c r="Q764" s="14"/>
-      <c r="S764" s="14"/>
+      <c r="AC764" s="12"/>
+      <c r="AE764" s="12"/>
     </row>
     <row r="765">
-      <c r="Q765" s="14"/>
-      <c r="S765" s="14"/>
+      <c r="AC765" s="12"/>
+      <c r="AE765" s="12"/>
     </row>
     <row r="766">
-      <c r="Q766" s="14"/>
-      <c r="S766" s="14"/>
+      <c r="AC766" s="12"/>
+      <c r="AE766" s="12"/>
     </row>
     <row r="767">
-      <c r="Q767" s="14"/>
-      <c r="S767" s="14"/>
+      <c r="AC767" s="12"/>
+      <c r="AE767" s="12"/>
     </row>
     <row r="768">
-      <c r="Q768" s="14"/>
-      <c r="S768" s="14"/>
+      <c r="AC768" s="12"/>
+      <c r="AE768" s="12"/>
     </row>
     <row r="769">
-      <c r="Q769" s="14"/>
-      <c r="S769" s="14"/>
+      <c r="AC769" s="12"/>
+      <c r="AE769" s="12"/>
     </row>
     <row r="770">
-      <c r="Q770" s="14"/>
-      <c r="S770" s="14"/>
+      <c r="AC770" s="12"/>
+      <c r="AE770" s="12"/>
     </row>
     <row r="771">
-      <c r="Q771" s="14"/>
-      <c r="S771" s="14"/>
+      <c r="AC771" s="12"/>
+      <c r="AE771" s="12"/>
     </row>
     <row r="772">
-      <c r="Q772" s="14"/>
-      <c r="S772" s="14"/>
+      <c r="AC772" s="12"/>
+      <c r="AE772" s="12"/>
     </row>
     <row r="773">
-      <c r="Q773" s="14"/>
-      <c r="S773" s="14"/>
+      <c r="AC773" s="12"/>
+      <c r="AE773" s="12"/>
     </row>
     <row r="774">
-      <c r="Q774" s="14"/>
-      <c r="S774" s="14"/>
+      <c r="AC774" s="12"/>
+      <c r="AE774" s="12"/>
     </row>
     <row r="775">
-      <c r="Q775" s="14"/>
-      <c r="S775" s="14"/>
+      <c r="AC775" s="12"/>
+      <c r="AE775" s="12"/>
     </row>
     <row r="776">
-      <c r="Q776" s="14"/>
-      <c r="S776" s="14"/>
+      <c r="AC776" s="12"/>
+      <c r="AE776" s="12"/>
     </row>
     <row r="777">
-      <c r="Q777" s="14"/>
-      <c r="S777" s="14"/>
+      <c r="AC777" s="12"/>
+      <c r="AE777" s="12"/>
     </row>
     <row r="778">
-      <c r="Q778" s="14"/>
-      <c r="S778" s="14"/>
+      <c r="AC778" s="12"/>
+      <c r="AE778" s="12"/>
     </row>
     <row r="779">
-      <c r="Q779" s="14"/>
-      <c r="S779" s="14"/>
+      <c r="AC779" s="12"/>
+      <c r="AE779" s="12"/>
     </row>
     <row r="780">
-      <c r="Q780" s="14"/>
-      <c r="S780" s="14"/>
+      <c r="AC780" s="12"/>
+      <c r="AE780" s="12"/>
     </row>
     <row r="781">
-      <c r="Q781" s="14"/>
-      <c r="S781" s="14"/>
+      <c r="AC781" s="12"/>
+      <c r="AE781" s="12"/>
     </row>
     <row r="782">
-      <c r="Q782" s="14"/>
-      <c r="S782" s="14"/>
+      <c r="AC782" s="12"/>
+      <c r="AE782" s="12"/>
     </row>
     <row r="783">
-      <c r="Q783" s="14"/>
-      <c r="S783" s="14"/>
+      <c r="AC783" s="12"/>
+      <c r="AE783" s="12"/>
     </row>
     <row r="784">
-      <c r="Q784" s="14"/>
-      <c r="S784" s="14"/>
+      <c r="AC784" s="12"/>
+      <c r="AE784" s="12"/>
     </row>
     <row r="785">
-      <c r="Q785" s="14"/>
-      <c r="S785" s="14"/>
+      <c r="AC785" s="12"/>
+      <c r="AE785" s="12"/>
     </row>
     <row r="786">
-      <c r="Q786" s="14"/>
-      <c r="S786" s="14"/>
+      <c r="AC786" s="12"/>
+      <c r="AE786" s="12"/>
     </row>
     <row r="787">
-      <c r="Q787" s="14"/>
-      <c r="S787" s="14"/>
+      <c r="AC787" s="12"/>
+      <c r="AE787" s="12"/>
     </row>
     <row r="788">
-      <c r="Q788" s="14"/>
-      <c r="S788" s="14"/>
+      <c r="AC788" s="12"/>
+      <c r="AE788" s="12"/>
     </row>
     <row r="789">
-      <c r="Q789" s="14"/>
-      <c r="S789" s="14"/>
+      <c r="AC789" s="12"/>
+      <c r="AE789" s="12"/>
     </row>
     <row r="790">
-      <c r="Q790" s="14"/>
-      <c r="S790" s="14"/>
+      <c r="AC790" s="12"/>
+      <c r="AE790" s="12"/>
     </row>
     <row r="791">
-      <c r="Q791" s="14"/>
-      <c r="S791" s="14"/>
+      <c r="AC791" s="12"/>
+      <c r="AE791" s="12"/>
     </row>
     <row r="792">
-      <c r="Q792" s="14"/>
-      <c r="S792" s="14"/>
+      <c r="AC792" s="12"/>
+      <c r="AE792" s="12"/>
     </row>
     <row r="793">
-      <c r="Q793" s="14"/>
-      <c r="S793" s="14"/>
+      <c r="AC793" s="12"/>
+      <c r="AE793" s="12"/>
     </row>
     <row r="794">
-      <c r="Q794" s="14"/>
-      <c r="S794" s="14"/>
+      <c r="AC794" s="12"/>
+      <c r="AE794" s="12"/>
     </row>
     <row r="795">
-      <c r="Q795" s="14"/>
-      <c r="S795" s="14"/>
+      <c r="AC795" s="12"/>
+      <c r="AE795" s="12"/>
     </row>
     <row r="796">
-      <c r="Q796" s="14"/>
-      <c r="S796" s="14"/>
+      <c r="AC796" s="12"/>
+      <c r="AE796" s="12"/>
     </row>
     <row r="797">
-      <c r="Q797" s="14"/>
-      <c r="S797" s="14"/>
+      <c r="AC797" s="12"/>
+      <c r="AE797" s="12"/>
     </row>
     <row r="798">
-      <c r="Q798" s="14"/>
-      <c r="S798" s="14"/>
+      <c r="AC798" s="12"/>
+      <c r="AE798" s="12"/>
     </row>
     <row r="799">
-      <c r="Q799" s="14"/>
-      <c r="S799" s="14"/>
+      <c r="AC799" s="12"/>
+      <c r="AE799" s="12"/>
     </row>
     <row r="800">
-      <c r="Q800" s="14"/>
-      <c r="S800" s="14"/>
+      <c r="AC800" s="12"/>
+      <c r="AE800" s="12"/>
     </row>
     <row r="801">
-      <c r="Q801" s="14"/>
-      <c r="S801" s="14"/>
+      <c r="AC801" s="12"/>
+      <c r="AE801" s="12"/>
     </row>
     <row r="802">
-      <c r="Q802" s="14"/>
-      <c r="S802" s="14"/>
+      <c r="AC802" s="12"/>
+      <c r="AE802" s="12"/>
     </row>
     <row r="803">
-      <c r="Q803" s="14"/>
-      <c r="S803" s="14"/>
+      <c r="AC803" s="12"/>
+      <c r="AE803" s="12"/>
     </row>
     <row r="804">
-      <c r="Q804" s="14"/>
-      <c r="S804" s="14"/>
+      <c r="AC804" s="12"/>
+      <c r="AE804" s="12"/>
     </row>
     <row r="805">
-      <c r="Q805" s="14"/>
-      <c r="S805" s="14"/>
+      <c r="AC805" s="12"/>
+      <c r="AE805" s="12"/>
     </row>
     <row r="806">
-      <c r="Q806" s="14"/>
-      <c r="S806" s="14"/>
+      <c r="AC806" s="12"/>
+      <c r="AE806" s="12"/>
     </row>
     <row r="807">
-      <c r="Q807" s="14"/>
-      <c r="S807" s="14"/>
+      <c r="AC807" s="12"/>
+      <c r="AE807" s="12"/>
     </row>
     <row r="808">
-      <c r="Q808" s="14"/>
-      <c r="S808" s="14"/>
+      <c r="AC808" s="12"/>
+      <c r="AE808" s="12"/>
     </row>
     <row r="809">
-      <c r="Q809" s="14"/>
-      <c r="S809" s="14"/>
+      <c r="AC809" s="12"/>
+      <c r="AE809" s="12"/>
     </row>
     <row r="810">
-      <c r="Q810" s="14"/>
-      <c r="S810" s="14"/>
+      <c r="AC810" s="12"/>
+      <c r="AE810" s="12"/>
     </row>
     <row r="811">
-      <c r="Q811" s="14"/>
-      <c r="S811" s="14"/>
+      <c r="AC811" s="12"/>
+      <c r="AE811" s="12"/>
     </row>
     <row r="812">
-      <c r="Q812" s="14"/>
-      <c r="S812" s="14"/>
+      <c r="AC812" s="12"/>
+      <c r="AE812" s="12"/>
     </row>
     <row r="813">
-      <c r="Q813" s="14"/>
-      <c r="S813" s="14"/>
+      <c r="AC813" s="12"/>
+      <c r="AE813" s="12"/>
     </row>
     <row r="814">
-      <c r="Q814" s="14"/>
-      <c r="S814" s="14"/>
+      <c r="AC814" s="12"/>
+      <c r="AE814" s="12"/>
     </row>
     <row r="815">
-      <c r="Q815" s="14"/>
-      <c r="S815" s="14"/>
+      <c r="AC815" s="12"/>
+      <c r="AE815" s="12"/>
     </row>
     <row r="816">
-      <c r="Q816" s="14"/>
-      <c r="S816" s="14"/>
+      <c r="AC816" s="12"/>
+      <c r="AE816" s="12"/>
     </row>
     <row r="817">
-      <c r="Q817" s="14"/>
-      <c r="S817" s="14"/>
+      <c r="AC817" s="12"/>
+      <c r="AE817" s="12"/>
     </row>
     <row r="818">
-      <c r="Q818" s="14"/>
-      <c r="S818" s="14"/>
+      <c r="AC818" s="12"/>
+      <c r="AE818" s="12"/>
     </row>
     <row r="819">
-      <c r="Q819" s="14"/>
-      <c r="S819" s="14"/>
+      <c r="AC819" s="12"/>
+      <c r="AE819" s="12"/>
     </row>
     <row r="820">
-      <c r="Q820" s="14"/>
-      <c r="S820" s="14"/>
+      <c r="AC820" s="12"/>
+      <c r="AE820" s="12"/>
     </row>
     <row r="821">
-      <c r="Q821" s="14"/>
-      <c r="S821" s="14"/>
+      <c r="AC821" s="12"/>
+      <c r="AE821" s="12"/>
     </row>
     <row r="822">
-      <c r="Q822" s="14"/>
-      <c r="S822" s="14"/>
+      <c r="AC822" s="12"/>
+      <c r="AE822" s="12"/>
     </row>
     <row r="823">
-      <c r="Q823" s="14"/>
-      <c r="S823" s="14"/>
+      <c r="AC823" s="12"/>
+      <c r="AE823" s="12"/>
     </row>
     <row r="824">
-      <c r="Q824" s="14"/>
-      <c r="S824" s="14"/>
+      <c r="AC824" s="12"/>
+      <c r="AE824" s="12"/>
     </row>
     <row r="825">
-      <c r="Q825" s="14"/>
-      <c r="S825" s="14"/>
+      <c r="AC825" s="12"/>
+      <c r="AE825" s="12"/>
     </row>
     <row r="826">
-      <c r="Q826" s="14"/>
-      <c r="S826" s="14"/>
+      <c r="AC826" s="12"/>
+      <c r="AE826" s="12"/>
     </row>
     <row r="827">
-      <c r="Q827" s="14"/>
-      <c r="S827" s="14"/>
+      <c r="AC827" s="12"/>
+      <c r="AE827" s="12"/>
     </row>
     <row r="828">
-      <c r="Q828" s="14"/>
-      <c r="S828" s="14"/>
+      <c r="AC828" s="12"/>
+      <c r="AE828" s="12"/>
     </row>
     <row r="829">
-      <c r="Q829" s="14"/>
-      <c r="S829" s="14"/>
+      <c r="AC829" s="12"/>
+      <c r="AE829" s="12"/>
     </row>
     <row r="830">
-      <c r="Q830" s="14"/>
-      <c r="S830" s="14"/>
+      <c r="AC830" s="12"/>
+      <c r="AE830" s="12"/>
     </row>
     <row r="831">
-      <c r="Q831" s="14"/>
-      <c r="S831" s="14"/>
+      <c r="AC831" s="12"/>
+      <c r="AE831" s="12"/>
     </row>
     <row r="832">
-      <c r="Q832" s="14"/>
-      <c r="S832" s="14"/>
+      <c r="AC832" s="12"/>
+      <c r="AE832" s="12"/>
     </row>
     <row r="833">
-      <c r="Q833" s="14"/>
-      <c r="S833" s="14"/>
+      <c r="AC833" s="12"/>
+      <c r="AE833" s="12"/>
     </row>
     <row r="834">
-      <c r="Q834" s="14"/>
-      <c r="S834" s="14"/>
+      <c r="AC834" s="12"/>
+      <c r="AE834" s="12"/>
     </row>
     <row r="835">
-      <c r="Q835" s="14"/>
-      <c r="S835" s="14"/>
+      <c r="AC835" s="12"/>
+      <c r="AE835" s="12"/>
     </row>
     <row r="836">
-      <c r="Q836" s="14"/>
-      <c r="S836" s="14"/>
+      <c r="AC836" s="12"/>
+      <c r="AE836" s="12"/>
     </row>
     <row r="837">
-      <c r="Q837" s="14"/>
-      <c r="S837" s="14"/>
+      <c r="AC837" s="12"/>
+      <c r="AE837" s="12"/>
     </row>
     <row r="838">
-      <c r="Q838" s="14"/>
-      <c r="S838" s="14"/>
+      <c r="AC838" s="12"/>
+      <c r="AE838" s="12"/>
     </row>
     <row r="839">
-      <c r="Q839" s="14"/>
-      <c r="S839" s="14"/>
+      <c r="AC839" s="12"/>
+      <c r="AE839" s="12"/>
     </row>
     <row r="840">
-      <c r="Q840" s="14"/>
-      <c r="S840" s="14"/>
+      <c r="AC840" s="12"/>
+      <c r="AE840" s="12"/>
     </row>
     <row r="841">
-      <c r="Q841" s="14"/>
-      <c r="S841" s="14"/>
+      <c r="AC841" s="12"/>
+      <c r="AE841" s="12"/>
     </row>
     <row r="842">
-      <c r="Q842" s="14"/>
-      <c r="S842" s="14"/>
+      <c r="AC842" s="12"/>
+      <c r="AE842" s="12"/>
     </row>
     <row r="843">
-      <c r="Q843" s="14"/>
-      <c r="S843" s="14"/>
+      <c r="AC843" s="12"/>
+      <c r="AE843" s="12"/>
     </row>
     <row r="844">
-      <c r="Q844" s="14"/>
-      <c r="S844" s="14"/>
+      <c r="AC844" s="12"/>
+      <c r="AE844" s="12"/>
     </row>
     <row r="845">
-      <c r="Q845" s="14"/>
-      <c r="S845" s="14"/>
+      <c r="AC845" s="12"/>
+      <c r="AE845" s="12"/>
     </row>
     <row r="846">
-      <c r="Q846" s="14"/>
-      <c r="S846" s="14"/>
+      <c r="AC846" s="12"/>
+      <c r="AE846" s="12"/>
     </row>
     <row r="847">
-      <c r="Q847" s="14"/>
-      <c r="S847" s="14"/>
+      <c r="AC847" s="12"/>
+      <c r="AE847" s="12"/>
     </row>
     <row r="848">
-      <c r="Q848" s="14"/>
-      <c r="S848" s="14"/>
+      <c r="AC848" s="12"/>
+      <c r="AE848" s="12"/>
     </row>
     <row r="849">
-      <c r="Q849" s="14"/>
-      <c r="S849" s="14"/>
+      <c r="AC849" s="12"/>
+      <c r="AE849" s="12"/>
     </row>
     <row r="850">
-      <c r="Q850" s="14"/>
-      <c r="S850" s="14"/>
+      <c r="AC850" s="12"/>
+      <c r="AE850" s="12"/>
     </row>
     <row r="851">
-      <c r="Q851" s="14"/>
-      <c r="S851" s="14"/>
+      <c r="AC851" s="12"/>
+      <c r="AE851" s="12"/>
     </row>
     <row r="852">
-      <c r="Q852" s="14"/>
-      <c r="S852" s="14"/>
+      <c r="AC852" s="12"/>
+      <c r="AE852" s="12"/>
     </row>
     <row r="853">
-      <c r="Q853" s="14"/>
-      <c r="S853" s="14"/>
+      <c r="AC853" s="12"/>
+      <c r="AE853" s="12"/>
     </row>
     <row r="854">
-      <c r="Q854" s="14"/>
-      <c r="S854" s="14"/>
+      <c r="AC854" s="12"/>
+      <c r="AE854" s="12"/>
     </row>
     <row r="855">
-      <c r="Q855" s="14"/>
-      <c r="S855" s="14"/>
+      <c r="AC855" s="12"/>
+      <c r="AE855" s="12"/>
     </row>
     <row r="856">
-      <c r="Q856" s="14"/>
-      <c r="S856" s="14"/>
+      <c r="AC856" s="12"/>
+      <c r="AE856" s="12"/>
     </row>
     <row r="857">
-      <c r="Q857" s="14"/>
-      <c r="S857" s="14"/>
+      <c r="AC857" s="12"/>
+      <c r="AE857" s="12"/>
     </row>
     <row r="858">
-      <c r="Q858" s="14"/>
-      <c r="S858" s="14"/>
+      <c r="AC858" s="12"/>
+      <c r="AE858" s="12"/>
     </row>
     <row r="859">
-      <c r="Q859" s="14"/>
-      <c r="S859" s="14"/>
+      <c r="AC859" s="12"/>
+      <c r="AE859" s="12"/>
     </row>
     <row r="860">
-      <c r="Q860" s="14"/>
-      <c r="S860" s="14"/>
+      <c r="AC860" s="12"/>
+      <c r="AE860" s="12"/>
     </row>
     <row r="861">
-      <c r="Q861" s="14"/>
-      <c r="S861" s="14"/>
+      <c r="AC861" s="12"/>
+      <c r="AE861" s="12"/>
     </row>
     <row r="862">
-      <c r="Q862" s="14"/>
-      <c r="S862" s="14"/>
+      <c r="AC862" s="12"/>
+      <c r="AE862" s="12"/>
     </row>
     <row r="863">
-      <c r="Q863" s="14"/>
-      <c r="S863" s="14"/>
+      <c r="AC863" s="12"/>
+      <c r="AE863" s="12"/>
     </row>
     <row r="864">
-      <c r="Q864" s="14"/>
-      <c r="S864" s="14"/>
+      <c r="AC864" s="12"/>
+      <c r="AE864" s="12"/>
     </row>
     <row r="865">
-      <c r="Q865" s="14"/>
-      <c r="S865" s="14"/>
+      <c r="AC865" s="12"/>
+      <c r="AE865" s="12"/>
     </row>
     <row r="866">
-      <c r="Q866" s="14"/>
-      <c r="S866" s="14"/>
+      <c r="AC866" s="12"/>
+      <c r="AE866" s="12"/>
     </row>
     <row r="867">
-      <c r="Q867" s="14"/>
-      <c r="S867" s="14"/>
+      <c r="AC867" s="12"/>
+      <c r="AE867" s="12"/>
     </row>
     <row r="868">
-      <c r="Q868" s="14"/>
-      <c r="S868" s="14"/>
+      <c r="AC868" s="12"/>
+      <c r="AE868" s="12"/>
     </row>
     <row r="869">
-      <c r="Q869" s="14"/>
-      <c r="S869" s="14"/>
+      <c r="AC869" s="12"/>
+      <c r="AE869" s="12"/>
     </row>
     <row r="870">
-      <c r="Q870" s="14"/>
-      <c r="S870" s="14"/>
+      <c r="AC870" s="12"/>
+      <c r="AE870" s="12"/>
     </row>
     <row r="871">
-      <c r="Q871" s="14"/>
-      <c r="S871" s="14"/>
+      <c r="AC871" s="12"/>
+      <c r="AE871" s="12"/>
     </row>
     <row r="872">
-      <c r="Q872" s="14"/>
-      <c r="S872" s="14"/>
+      <c r="AC872" s="12"/>
+      <c r="AE872" s="12"/>
     </row>
     <row r="873">
-      <c r="Q873" s="14"/>
-      <c r="S873" s="14"/>
+      <c r="AC873" s="12"/>
+      <c r="AE873" s="12"/>
     </row>
     <row r="874">
-      <c r="Q874" s="14"/>
-      <c r="S874" s="14"/>
+      <c r="AC874" s="12"/>
+      <c r="AE874" s="12"/>
     </row>
     <row r="875">
-      <c r="Q875" s="14"/>
-      <c r="S875" s="14"/>
+      <c r="AC875" s="12"/>
+      <c r="AE875" s="12"/>
     </row>
     <row r="876">
-      <c r="Q876" s="14"/>
-      <c r="S876" s="14"/>
+      <c r="AC876" s="12"/>
+      <c r="AE876" s="12"/>
     </row>
     <row r="877">
-      <c r="Q877" s="14"/>
-      <c r="S877" s="14"/>
+      <c r="AC877" s="12"/>
+      <c r="AE877" s="12"/>
     </row>
     <row r="878">
-      <c r="Q878" s="14"/>
-      <c r="S878" s="14"/>
+      <c r="AC878" s="12"/>
+      <c r="AE878" s="12"/>
     </row>
     <row r="879">
-      <c r="Q879" s="14"/>
-      <c r="S879" s="14"/>
+      <c r="AC879" s="12"/>
+      <c r="AE879" s="12"/>
     </row>
     <row r="880">
-      <c r="Q880" s="14"/>
-      <c r="S880" s="14"/>
+      <c r="AC880" s="12"/>
+      <c r="AE880" s="12"/>
     </row>
     <row r="881">
-      <c r="Q881" s="14"/>
-      <c r="S881" s="14"/>
+      <c r="AC881" s="12"/>
+      <c r="AE881" s="12"/>
     </row>
     <row r="882">
-      <c r="Q882" s="14"/>
-      <c r="S882" s="14"/>
+      <c r="AC882" s="12"/>
+      <c r="AE882" s="12"/>
     </row>
     <row r="883">
-      <c r="Q883" s="14"/>
-      <c r="S883" s="14"/>
+      <c r="AC883" s="12"/>
+      <c r="AE883" s="12"/>
     </row>
     <row r="884">
-      <c r="Q884" s="14"/>
-      <c r="S884" s="14"/>
+      <c r="AC884" s="12"/>
+      <c r="AE884" s="12"/>
     </row>
     <row r="885">
-      <c r="Q885" s="14"/>
-      <c r="S885" s="14"/>
+      <c r="AC885" s="12"/>
+      <c r="AE885" s="12"/>
     </row>
     <row r="886">
-      <c r="Q886" s="14"/>
-      <c r="S886" s="14"/>
+      <c r="AC886" s="12"/>
+      <c r="AE886" s="12"/>
     </row>
     <row r="887">
-      <c r="Q887" s="14"/>
-      <c r="S887" s="14"/>
+      <c r="AC887" s="12"/>
+      <c r="AE887" s="12"/>
     </row>
     <row r="888">
-      <c r="Q888" s="14"/>
-      <c r="S888" s="14"/>
+      <c r="AC888" s="12"/>
+      <c r="AE888" s="12"/>
     </row>
     <row r="889">
-      <c r="Q889" s="14"/>
-      <c r="S889" s="14"/>
+      <c r="AC889" s="12"/>
+      <c r="AE889" s="12"/>
     </row>
     <row r="890">
-      <c r="Q890" s="14"/>
-      <c r="S890" s="14"/>
+      <c r="AC890" s="12"/>
+      <c r="AE890" s="12"/>
     </row>
     <row r="891">
-      <c r="Q891" s="14"/>
-      <c r="S891" s="14"/>
+      <c r="AC891" s="12"/>
+      <c r="AE891" s="12"/>
     </row>
     <row r="892">
-      <c r="Q892" s="14"/>
-      <c r="S892" s="14"/>
+      <c r="AC892" s="12"/>
+      <c r="AE892" s="12"/>
     </row>
     <row r="893">
-      <c r="Q893" s="14"/>
-      <c r="S893" s="14"/>
+      <c r="AC893" s="12"/>
+      <c r="AE893" s="12"/>
     </row>
     <row r="894">
-      <c r="Q894" s="14"/>
-      <c r="S894" s="14"/>
+      <c r="AC894" s="12"/>
+      <c r="AE894" s="12"/>
     </row>
     <row r="895">
-      <c r="Q895" s="14"/>
-      <c r="S895" s="14"/>
+      <c r="AC895" s="12"/>
+      <c r="AE895" s="12"/>
     </row>
     <row r="896">
-      <c r="Q896" s="14"/>
-      <c r="S896" s="14"/>
+      <c r="AC896" s="12"/>
+      <c r="AE896" s="12"/>
     </row>
     <row r="897">
-      <c r="Q897" s="14"/>
-      <c r="S897" s="14"/>
+      <c r="AC897" s="12"/>
+      <c r="AE897" s="12"/>
     </row>
     <row r="898">
-      <c r="Q898" s="14"/>
-      <c r="S898" s="14"/>
+      <c r="AC898" s="12"/>
+      <c r="AE898" s="12"/>
     </row>
     <row r="899">
-      <c r="Q899" s="14"/>
-      <c r="S899" s="14"/>
+      <c r="AC899" s="12"/>
+      <c r="AE899" s="12"/>
     </row>
     <row r="900">
-      <c r="Q900" s="14"/>
-      <c r="S900" s="14"/>
+      <c r="AC900" s="12"/>
+      <c r="AE900" s="12"/>
     </row>
     <row r="901">
-      <c r="Q901" s="14"/>
-      <c r="S901" s="14"/>
+      <c r="AC901" s="12"/>
+      <c r="AE901" s="12"/>
     </row>
     <row r="902">
-      <c r="Q902" s="14"/>
-      <c r="S902" s="14"/>
+      <c r="AC902" s="12"/>
+      <c r="AE902" s="12"/>
     </row>
     <row r="903">
-      <c r="Q903" s="14"/>
-      <c r="S903" s="14"/>
+      <c r="AC903" s="12"/>
+      <c r="AE903" s="12"/>
     </row>
     <row r="904">
-      <c r="Q904" s="14"/>
-      <c r="S904" s="14"/>
+      <c r="AC904" s="12"/>
+      <c r="AE904" s="12"/>
     </row>
     <row r="905">
-      <c r="Q905" s="14"/>
-      <c r="S905" s="14"/>
+      <c r="AC905" s="12"/>
+      <c r="AE905" s="12"/>
     </row>
     <row r="906">
-      <c r="Q906" s="14"/>
-      <c r="S906" s="14"/>
+      <c r="AC906" s="12"/>
+      <c r="AE906" s="12"/>
     </row>
     <row r="907">
-      <c r="Q907" s="14"/>
-      <c r="S907" s="14"/>
+      <c r="AC907" s="12"/>
+      <c r="AE907" s="12"/>
     </row>
     <row r="908">
-      <c r="Q908" s="14"/>
-      <c r="S908" s="14"/>
+      <c r="AC908" s="12"/>
+      <c r="AE908" s="12"/>
     </row>
     <row r="909">
-      <c r="Q909" s="14"/>
-      <c r="S909" s="14"/>
+      <c r="AC909" s="12"/>
+      <c r="AE909" s="12"/>
     </row>
     <row r="910">
-      <c r="Q910" s="14"/>
-      <c r="S910" s="14"/>
+      <c r="AC910" s="12"/>
+      <c r="AE910" s="12"/>
     </row>
     <row r="911">
-      <c r="Q911" s="14"/>
-      <c r="S911" s="14"/>
+      <c r="AC911" s="12"/>
+      <c r="AE911" s="12"/>
     </row>
     <row r="912">
-      <c r="Q912" s="14"/>
-      <c r="S912" s="14"/>
+      <c r="AC912" s="12"/>
+      <c r="AE912" s="12"/>
     </row>
     <row r="913">
-      <c r="Q913" s="14"/>
-      <c r="S913" s="14"/>
+      <c r="AC913" s="12"/>
+      <c r="AE913" s="12"/>
     </row>
     <row r="914">
-      <c r="Q914" s="14"/>
-      <c r="S914" s="14"/>
+      <c r="AC914" s="12"/>
+      <c r="AE914" s="12"/>
     </row>
     <row r="915">
-      <c r="Q915" s="14"/>
-      <c r="S915" s="14"/>
+      <c r="AC915" s="12"/>
+      <c r="AE915" s="12"/>
     </row>
     <row r="916">
-      <c r="Q916" s="14"/>
-      <c r="S916" s="14"/>
+      <c r="AC916" s="12"/>
+      <c r="AE916" s="12"/>
     </row>
     <row r="917">
-      <c r="Q917" s="14"/>
-      <c r="S917" s="14"/>
+      <c r="AC917" s="12"/>
+      <c r="AE917" s="12"/>
     </row>
     <row r="918">
-      <c r="Q918" s="14"/>
-      <c r="S918" s="14"/>
+      <c r="AC918" s="12"/>
+      <c r="AE918" s="12"/>
     </row>
     <row r="919">
-      <c r="Q919" s="14"/>
-      <c r="S919" s="14"/>
+      <c r="AC919" s="12"/>
+      <c r="AE919" s="12"/>
     </row>
     <row r="920">
-      <c r="Q920" s="14"/>
-      <c r="S920" s="14"/>
+      <c r="AC920" s="12"/>
+      <c r="AE920" s="12"/>
     </row>
     <row r="921">
-      <c r="Q921" s="14"/>
-      <c r="S921" s="14"/>
+      <c r="AC921" s="12"/>
+      <c r="AE921" s="12"/>
     </row>
     <row r="922">
-      <c r="Q922" s="14"/>
-      <c r="S922" s="14"/>
+      <c r="AC922" s="12"/>
+      <c r="AE922" s="12"/>
     </row>
     <row r="923">
-      <c r="Q923" s="14"/>
-      <c r="S923" s="14"/>
+      <c r="AC923" s="12"/>
+      <c r="AE923" s="12"/>
     </row>
     <row r="924">
-      <c r="Q924" s="14"/>
-      <c r="S924" s="14"/>
+      <c r="AC924" s="12"/>
+      <c r="AE924" s="12"/>
     </row>
     <row r="925">
-      <c r="Q925" s="14"/>
-      <c r="S925" s="14"/>
+      <c r="AC925" s="12"/>
+      <c r="AE925" s="12"/>
     </row>
     <row r="926">
-      <c r="Q926" s="14"/>
-      <c r="S926" s="14"/>
+      <c r="AC926" s="12"/>
+      <c r="AE926" s="12"/>
     </row>
     <row r="927">
-      <c r="Q927" s="14"/>
-      <c r="S927" s="14"/>
+      <c r="AC927" s="12"/>
+      <c r="AE927" s="12"/>
     </row>
     <row r="928">
-      <c r="Q928" s="14"/>
-      <c r="S928" s="14"/>
+      <c r="AC928" s="12"/>
+      <c r="AE928" s="12"/>
     </row>
     <row r="929">
-      <c r="Q929" s="14"/>
-      <c r="S929" s="14"/>
+      <c r="AC929" s="12"/>
+      <c r="AE929" s="12"/>
     </row>
     <row r="930">
-      <c r="Q930" s="14"/>
-      <c r="S930" s="14"/>
+      <c r="AC930" s="12"/>
+      <c r="AE930" s="12"/>
     </row>
     <row r="931">
-      <c r="Q931" s="14"/>
-      <c r="S931" s="14"/>
+      <c r="AC931" s="12"/>
+      <c r="AE931" s="12"/>
     </row>
     <row r="932">
-      <c r="Q932" s="14"/>
-      <c r="S932" s="14"/>
+      <c r="AC932" s="12"/>
+      <c r="AE932" s="12"/>
     </row>
     <row r="933">
-      <c r="Q933" s="14"/>
-      <c r="S933" s="14"/>
+      <c r="AC933" s="12"/>
+      <c r="AE933" s="12"/>
     </row>
     <row r="934">
-      <c r="Q934" s="14"/>
-      <c r="S934" s="14"/>
+      <c r="AC934" s="12"/>
+      <c r="AE934" s="12"/>
     </row>
     <row r="935">
-      <c r="Q935" s="14"/>
-      <c r="S935" s="14"/>
+      <c r="AC935" s="12"/>
+      <c r="AE935" s="12"/>
     </row>
     <row r="936">
-      <c r="Q936" s="14"/>
-      <c r="S936" s="14"/>
+      <c r="AC936" s="12"/>
+      <c r="AE936" s="12"/>
     </row>
     <row r="937">
-      <c r="Q937" s="14"/>
-      <c r="S937" s="14"/>
+      <c r="AC937" s="12"/>
+      <c r="AE937" s="12"/>
     </row>
     <row r="938">
-      <c r="Q938" s="14"/>
-      <c r="S938" s="14"/>
+      <c r="AC938" s="12"/>
+      <c r="AE938" s="12"/>
     </row>
     <row r="939">
-      <c r="Q939" s="14"/>
-      <c r="S939" s="14"/>
+      <c r="AC939" s="12"/>
+      <c r="AE939" s="12"/>
     </row>
     <row r="940">
-      <c r="Q940" s="14"/>
-      <c r="S940" s="14"/>
+      <c r="AC940" s="12"/>
+      <c r="AE940" s="12"/>
     </row>
     <row r="941">
-      <c r="Q941" s="14"/>
-      <c r="S941" s="14"/>
+      <c r="AC941" s="12"/>
+      <c r="AE941" s="12"/>
     </row>
     <row r="942">
-      <c r="Q942" s="14"/>
-      <c r="S942" s="14"/>
+      <c r="AC942" s="12"/>
+      <c r="AE942" s="12"/>
     </row>
     <row r="943">
-      <c r="Q943" s="14"/>
-      <c r="S943" s="14"/>
+      <c r="AC943" s="12"/>
+      <c r="AE943" s="12"/>
     </row>
     <row r="944">
-      <c r="Q944" s="14"/>
-      <c r="S944" s="14"/>
+      <c r="AC944" s="12"/>
+      <c r="AE944" s="12"/>
     </row>
     <row r="945">
-      <c r="Q945" s="14"/>
-      <c r="S945" s="14"/>
+      <c r="AC945" s="12"/>
+      <c r="AE945" s="12"/>
     </row>
     <row r="946">
-      <c r="Q946" s="14"/>
-      <c r="S946" s="14"/>
+      <c r="AC946" s="12"/>
+      <c r="AE946" s="12"/>
     </row>
     <row r="947">
-      <c r="Q947" s="14"/>
-      <c r="S947" s="14"/>
+      <c r="AC947" s="12"/>
+      <c r="AE947" s="12"/>
     </row>
     <row r="948">
-      <c r="Q948" s="14"/>
-      <c r="S948" s="14"/>
+      <c r="AC948" s="12"/>
+      <c r="AE948" s="12"/>
     </row>
     <row r="949">
-      <c r="Q949" s="14"/>
-      <c r="S949" s="14"/>
+      <c r="AC949" s="12"/>
+      <c r="AE949" s="12"/>
     </row>
     <row r="950">
-      <c r="Q950" s="14"/>
-      <c r="S950" s="14"/>
+      <c r="AC950" s="12"/>
+      <c r="AE950" s="12"/>
     </row>
     <row r="951">
-      <c r="Q951" s="14"/>
-      <c r="S951" s="14"/>
+      <c r="AC951" s="12"/>
+      <c r="AE951" s="12"/>
     </row>
     <row r="952">
-      <c r="Q952" s="14"/>
-      <c r="S952" s="14"/>
+      <c r="AC952" s="12"/>
+      <c r="AE952" s="12"/>
     </row>
     <row r="953">
-      <c r="Q953" s="14"/>
-      <c r="S953" s="14"/>
+      <c r="AC953" s="12"/>
+      <c r="AE953" s="12"/>
     </row>
     <row r="954">
-      <c r="Q954" s="14"/>
-      <c r="S954" s="14"/>
+      <c r="AC954" s="12"/>
+      <c r="AE954" s="12"/>
     </row>
     <row r="955">
-      <c r="Q955" s="14"/>
-      <c r="S955" s="14"/>
+      <c r="AC955" s="12"/>
+      <c r="AE955" s="12"/>
     </row>
     <row r="956">
-      <c r="Q956" s="14"/>
-      <c r="S956" s="14"/>
+      <c r="AC956" s="12"/>
+      <c r="AE956" s="12"/>
     </row>
     <row r="957">
-      <c r="Q957" s="14"/>
-      <c r="S957" s="14"/>
+      <c r="AC957" s="12"/>
+      <c r="AE957" s="12"/>
     </row>
     <row r="958">
-      <c r="Q958" s="14"/>
-      <c r="S958" s="14"/>
+      <c r="AC958" s="12"/>
+      <c r="AE958" s="12"/>
     </row>
     <row r="959">
-      <c r="Q959" s="14"/>
-      <c r="S959" s="14"/>
+      <c r="AC959" s="12"/>
+      <c r="AE959" s="12"/>
     </row>
     <row r="960">
-      <c r="Q960" s="14"/>
-      <c r="S960" s="14"/>
+      <c r="AC960" s="12"/>
+      <c r="AE960" s="12"/>
     </row>
     <row r="961">
-      <c r="Q961" s="14"/>
-      <c r="S961" s="14"/>
+      <c r="AC961" s="12"/>
+      <c r="AE961" s="12"/>
     </row>
     <row r="962">
-      <c r="Q962" s="14"/>
-      <c r="S962" s="14"/>
+      <c r="AC962" s="12"/>
+      <c r="AE962" s="12"/>
     </row>
     <row r="963">
-      <c r="Q963" s="14"/>
-      <c r="S963" s="14"/>
+      <c r="AC963" s="12"/>
+      <c r="AE963" s="12"/>
     </row>
     <row r="964">
-      <c r="Q964" s="14"/>
-      <c r="S964" s="14"/>
+      <c r="AC964" s="12"/>
+      <c r="AE964" s="12"/>
     </row>
     <row r="965">
-      <c r="Q965" s="14"/>
-      <c r="S965" s="14"/>
+      <c r="AC965" s="12"/>
+      <c r="AE965" s="12"/>
     </row>
     <row r="966">
-      <c r="Q966" s="14"/>
-      <c r="S966" s="14"/>
+      <c r="AC966" s="12"/>
+      <c r="AE966" s="12"/>
     </row>
     <row r="967">
-      <c r="Q967" s="14"/>
-      <c r="S967" s="14"/>
+      <c r="AC967" s="12"/>
+      <c r="AE967" s="12"/>
     </row>
     <row r="968">
-      <c r="Q968" s="14"/>
-      <c r="S968" s="14"/>
+      <c r="AC968" s="12"/>
+      <c r="AE968" s="12"/>
     </row>
     <row r="969">
-      <c r="Q969" s="14"/>
-      <c r="S969" s="14"/>
+      <c r="AC969" s="12"/>
+      <c r="AE969" s="12"/>
     </row>
     <row r="970">
-      <c r="Q970" s="14"/>
-      <c r="S970" s="14"/>
+      <c r="AC970" s="12"/>
+      <c r="AE970" s="12"/>
     </row>
     <row r="971">
-      <c r="Q971" s="14"/>
-      <c r="S971" s="14"/>
+      <c r="AC971" s="12"/>
+      <c r="AE971" s="12"/>
     </row>
     <row r="972">
-      <c r="Q972" s="14"/>
-      <c r="S972" s="14"/>
+      <c r="AC972" s="12"/>
+      <c r="AE972" s="12"/>
     </row>
     <row r="973">
-      <c r="Q973" s="14"/>
-      <c r="S973" s="14"/>
+      <c r="AC973" s="12"/>
+      <c r="AE973" s="12"/>
     </row>
     <row r="974">
-      <c r="Q974" s="14"/>
-      <c r="S974" s="14"/>
+      <c r="AC974" s="12"/>
+      <c r="AE974" s="12"/>
     </row>
     <row r="975">
-      <c r="Q975" s="14"/>
-      <c r="S975" s="14"/>
+      <c r="AC975" s="12"/>
+      <c r="AE975" s="12"/>
     </row>
     <row r="976">
-      <c r="Q976" s="14"/>
-      <c r="S976" s="14"/>
+      <c r="AC976" s="12"/>
+      <c r="AE976" s="12"/>
     </row>
     <row r="977">
-      <c r="Q977" s="14"/>
-      <c r="S977" s="14"/>
+      <c r="AC977" s="12"/>
+      <c r="AE977" s="12"/>
     </row>
     <row r="978">
-      <c r="Q978" s="14"/>
-      <c r="S978" s="14"/>
+      <c r="AC978" s="12"/>
+      <c r="AE978" s="12"/>
     </row>
     <row r="979">
-      <c r="Q979" s="14"/>
-      <c r="S979" s="14"/>
+      <c r="AC979" s="12"/>
+      <c r="AE979" s="12"/>
     </row>
     <row r="980">
-      <c r="Q980" s="14"/>
-      <c r="S980" s="14"/>
+      <c r="AC980" s="12"/>
+      <c r="AE980" s="12"/>
     </row>
     <row r="981">
-      <c r="Q981" s="14"/>
-      <c r="S981" s="14"/>
+      <c r="AC981" s="12"/>
+      <c r="AE981" s="12"/>
     </row>
     <row r="982">
-      <c r="Q982" s="14"/>
-      <c r="S982" s="14"/>
+      <c r="AC982" s="12"/>
+      <c r="AE982" s="12"/>
     </row>
     <row r="983">
-      <c r="Q983" s="14"/>
-      <c r="S983" s="14"/>
+      <c r="AC983" s="12"/>
+      <c r="AE983" s="12"/>
     </row>
     <row r="984">
-      <c r="Q984" s="14"/>
-      <c r="S984" s="14"/>
+      <c r="AC984" s="12"/>
+      <c r="AE984" s="12"/>
     </row>
     <row r="985">
-      <c r="Q985" s="14"/>
-      <c r="S985" s="14"/>
+      <c r="AC985" s="12"/>
+      <c r="AE985" s="12"/>
     </row>
     <row r="986">
-      <c r="Q986" s="14"/>
-      <c r="S986" s="14"/>
+      <c r="AC986" s="12"/>
+      <c r="AE986" s="12"/>
     </row>
     <row r="987">
-      <c r="Q987" s="14"/>
-      <c r="S987" s="14"/>
+      <c r="AC987" s="12"/>
+      <c r="AE987" s="12"/>
     </row>
     <row r="988">
-      <c r="Q988" s="14"/>
-      <c r="S988" s="14"/>
+      <c r="AC988" s="12"/>
+      <c r="AE988" s="12"/>
     </row>
     <row r="989">
-      <c r="Q989" s="14"/>
-      <c r="S989" s="14"/>
+      <c r="AC989" s="12"/>
+      <c r="AE989" s="12"/>
     </row>
     <row r="990">
-      <c r="Q990" s="14"/>
-      <c r="S990" s="14"/>
+      <c r="AC990" s="12"/>
+      <c r="AE990" s="12"/>
     </row>
     <row r="991">
-      <c r="Q991" s="14"/>
-      <c r="S991" s="14"/>
+      <c r="AC991" s="12"/>
+      <c r="AE991" s="12"/>
     </row>
     <row r="992">
-      <c r="Q992" s="14"/>
-      <c r="S992" s="14"/>
+      <c r="AC992" s="12"/>
+      <c r="AE992" s="12"/>
     </row>
     <row r="993">
-      <c r="Q993" s="14"/>
-      <c r="S993" s="14"/>
+      <c r="AC993" s="12"/>
+      <c r="AE993" s="12"/>
     </row>
     <row r="994">
-      <c r="Q994" s="14"/>
-      <c r="S994" s="14"/>
+      <c r="AC994" s="12"/>
+      <c r="AE994" s="12"/>
     </row>
     <row r="995">
-      <c r="Q995" s="14"/>
-      <c r="S995" s="14"/>
+      <c r="AC995" s="12"/>
+      <c r="AE995" s="12"/>
     </row>
     <row r="996">
-      <c r="Q996" s="14"/>
-      <c r="S996" s="14"/>
+      <c r="AC996" s="12"/>
+      <c r="AE996" s="12"/>
     </row>
     <row r="997">
-      <c r="Q997" s="14"/>
-      <c r="S997" s="14"/>
+      <c r="AC997" s="12"/>
+      <c r="AE997" s="12"/>
     </row>
     <row r="998">
-      <c r="Q998" s="14"/>
-      <c r="S998" s="14"/>
+      <c r="AC998" s="12"/>
+      <c r="AE998" s="12"/>
     </row>
     <row r="999">
-      <c r="Q999" s="14"/>
-      <c r="S999" s="14"/>
+      <c r="AC999" s="12"/>
+      <c r="AE999" s="12"/>
     </row>
     <row r="1000">
-      <c r="Q1000" s="14"/>
-      <c r="S1000" s="14"/>
+      <c r="AC1000" s="12"/>
+      <c r="AE1000" s="12"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data/raw/Compiled Data.xlsx
+++ b/data/raw/Compiled Data.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -204,6 +204,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
@@ -698,6 +701,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B3" s="6">
         <v>0.7</v>
       </c>
@@ -820,6 +826,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B4" s="6">
         <v>1.0</v>
       </c>
@@ -942,6 +951,9 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B5" s="6">
         <v>1.5</v>
       </c>
@@ -1064,6 +1076,9 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B6" s="6">
         <v>2.0</v>
       </c>
@@ -1186,6 +1201,9 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B7" s="6">
         <v>3.0</v>
       </c>
@@ -1311,40 +1329,40 @@
       <c r="A8" s="6">
         <v>5.0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>73.99355924452814</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="11">
         <v>0.2019169515889416</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="11">
         <v>63.84502903896671</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="11">
         <v>1.534789151100213</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="11">
         <v>58.88002598277671</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="11">
         <v>1.458721097509793</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="11">
         <v>54.42699117129592</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="11">
         <v>1.40209177267346</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="11">
         <v>36.61485192537276</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="11">
         <v>1.185059863175494</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="11">
         <v>22.69466458079118</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="Q8" s="11">
         <v>0.9093739693106002</v>
       </c>
       <c r="R8" s="7">
@@ -1359,16 +1377,16 @@
       <c r="U8" s="7">
         <v>0.1492823005907599</v>
       </c>
-      <c r="V8" s="10">
+      <c r="V8" s="11">
         <v>51.13370272005709</v>
       </c>
-      <c r="W8" s="10">
+      <c r="W8" s="11">
         <v>1.236392889802275</v>
       </c>
-      <c r="X8" s="10">
+      <c r="X8" s="11">
         <v>67.30582937252298</v>
       </c>
-      <c r="Y8" s="10">
+      <c r="Y8" s="11">
         <v>0.1622273702403538</v>
       </c>
       <c r="Z8" s="7">
@@ -1430,43 +1448,46 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="10">
+        <v>5.0</v>
+      </c>
       <c r="C9" s="6">
         <v>0.7</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>79.92421293722248</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="11">
         <v>1.060739414862349</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="11">
         <v>71.16695716510256</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="11">
         <v>0.637433488948495</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="11">
         <v>66.1113443070845</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="11">
         <v>0.6931062667198676</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="11">
         <v>61.80656739110039</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="11">
         <v>0.6555559788753325</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="11">
         <v>44.58745972716397</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="11">
         <v>0.5390411507977482</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="11">
         <v>31.08458782866331</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="11">
         <v>0.5817211875057109</v>
       </c>
       <c r="R9" s="7">
@@ -1481,16 +1502,16 @@
       <c r="U9" s="7">
         <v>0.3699396952701384</v>
       </c>
-      <c r="V9" s="10">
+      <c r="V9" s="11">
         <v>82.81246062063757</v>
       </c>
-      <c r="W9" s="10">
+      <c r="W9" s="11">
         <v>4.037828309503719</v>
       </c>
-      <c r="X9" s="10">
+      <c r="X9" s="11">
         <v>62.21860357942923</v>
       </c>
-      <c r="Y9" s="10">
+      <c r="Y9" s="11">
         <v>1.567317736857665</v>
       </c>
       <c r="Z9" s="7">
@@ -1552,43 +1573,46 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="10">
+        <v>5.0</v>
+      </c>
       <c r="C10" s="6">
         <v>1.0</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <v>76.90387499485618</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="11">
         <v>1.187870053705751</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="11">
         <v>69.4709174227594</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="11">
         <v>1.789894463929565</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="11">
         <v>64.67219529003106</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="11">
         <v>1.614203341015746</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="11">
         <v>60.49107167180846</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="11">
         <v>1.526449247778018</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="11">
         <v>43.76657719891806</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="11">
         <v>1.175434272963217</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="11">
         <v>30.35502059653167</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="11">
         <v>1.198847225582804</v>
       </c>
       <c r="R10" s="7">
@@ -1603,16 +1627,16 @@
       <c r="U10" s="7">
         <v>0.261805359978352</v>
       </c>
-      <c r="V10" s="10">
+      <c r="V10" s="11">
         <v>77.13435359656211</v>
       </c>
-      <c r="W10" s="10">
+      <c r="W10" s="11">
         <v>1.777061441073681</v>
       </c>
-      <c r="X10" s="10">
+      <c r="X10" s="11">
         <v>66.76975615838113</v>
       </c>
-      <c r="Y10" s="10">
+      <c r="Y10" s="11">
         <v>0.5165008525294192</v>
       </c>
       <c r="Z10" s="7">
@@ -1674,43 +1698,46 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" s="10">
+        <v>5.0</v>
+      </c>
       <c r="C11" s="6">
         <v>2.0</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>77.79637766080326</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="11">
         <v>0.8747470232756213</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="11">
         <v>71.27647448658456</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="11">
         <v>0.9834641427533747</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="11">
         <v>66.99628823200119</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="11">
         <v>0.9099873534908839</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="11">
         <v>62.43433783532269</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="11">
         <v>0.9879723396750385</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="11">
         <v>44.18653624860868</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="11">
         <v>1.472876730519528</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="11">
         <v>30.00491915322759</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="11">
         <v>1.264635353404087</v>
       </c>
       <c r="R11" s="7">
@@ -1725,16 +1752,16 @@
       <c r="U11" s="7">
         <v>0.2336208538258209</v>
       </c>
-      <c r="V11" s="10">
+      <c r="V11" s="11">
         <v>76.40645992317215</v>
       </c>
-      <c r="W11" s="10">
+      <c r="W11" s="11">
         <v>2.33576366017232</v>
       </c>
-      <c r="X11" s="10">
+      <c r="X11" s="11">
         <v>68.83493440642118</v>
       </c>
-      <c r="Y11" s="10">
+      <c r="Y11" s="11">
         <v>0.3312629767268597</v>
       </c>
       <c r="Z11" s="7">
@@ -1796,43 +1823,46 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" s="10">
+        <v>5.0</v>
+      </c>
       <c r="C12" s="6">
         <v>3.0</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>74.14754443574773</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="11">
         <v>0.6913763566767633</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="11">
         <v>61.45754875090975</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="11">
         <v>1.461714730517133</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="11">
         <v>56.21463438750984</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="11">
         <v>1.260675235678731</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="11">
         <v>51.46090793541097</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="11">
         <v>1.193208375102689</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="11">
         <v>32.44600212701546</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="11">
         <v>0.9503504455416049</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="11">
         <v>17.47684828697292</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q12" s="11">
         <v>0.6574157761751536</v>
       </c>
       <c r="R12" s="7">
@@ -1847,16 +1877,16 @@
       <c r="U12" s="7">
         <v>0.07073680256538416</v>
       </c>
-      <c r="V12" s="10">
+      <c r="V12" s="11">
         <v>35.34997661060815</v>
       </c>
-      <c r="W12" s="10">
+      <c r="W12" s="11">
         <v>0.4679941073813578</v>
       </c>
-      <c r="X12" s="10">
+      <c r="X12" s="11">
         <v>73.18199863839158</v>
       </c>
-      <c r="Y12" s="10">
+      <c r="Y12" s="11">
         <v>2.079040093759844</v>
       </c>
       <c r="Z12" s="7">
@@ -1918,6 +1948,9 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B13" s="6">
         <v>1.0</v>
       </c>
@@ -2043,6 +2076,9 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="10">
+        <v>8.0</v>
+      </c>
       <c r="C14" s="6">
         <v>3.0</v>
       </c>
@@ -2168,6 +2204,9 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B15" s="6">
         <v>1.0</v>
       </c>
@@ -2293,6 +2332,9 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="10">
+        <v>8.0</v>
+      </c>
       <c r="C16" s="6">
         <v>3.0</v>
       </c>
@@ -2371,7 +2413,7 @@
       <c r="AC16" s="8">
         <v>0.1612333333333333</v>
       </c>
-      <c r="AD16" s="11">
+      <c r="AD16" s="12">
         <v>3.179797338056456E-4</v>
       </c>
       <c r="AE16" s="7">
@@ -2418,6 +2460,9 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B17" s="6">
         <v>1.0</v>
       </c>
@@ -2546,6 +2591,9 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" s="10">
+        <v>8.0</v>
+      </c>
       <c r="B18" s="6">
         <v>1.0</v>
       </c>
@@ -2674,43 +2722,46 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" s="10">
+        <v>8.0</v>
+      </c>
       <c r="D19" s="6">
         <v>0.7</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="11">
         <v>84.18601536311839</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="11">
         <v>0.9091840279411826</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="11">
         <v>68.45509097589972</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="11">
         <v>0.3598969647516739</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="11">
         <v>52.14960489232937</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="11">
         <v>1.185313900570214</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="11">
         <v>45.01676355204248</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="11">
         <v>1.330500135072292</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="11">
         <v>16.48539819089498</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="11">
         <v>1.9240272456203</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="11">
         <v>-1.464601584160882</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q19" s="11">
         <v>1.305516197334365</v>
       </c>
       <c r="R19" s="7">
@@ -2725,16 +2776,16 @@
       <c r="U19" s="7">
         <v>0.2886175748144108</v>
       </c>
-      <c r="V19" s="10">
+      <c r="V19" s="11">
         <v>29.00836015821067</v>
       </c>
-      <c r="W19" s="10">
+      <c r="W19" s="11">
         <v>0.3694448583843284</v>
       </c>
-      <c r="X19" s="10">
+      <c r="X19" s="11">
         <v>64.31160131613926</v>
       </c>
-      <c r="Y19" s="10">
+      <c r="Y19" s="11">
         <v>0.6415226993872251</v>
       </c>
       <c r="Z19" s="7">
@@ -2796,43 +2847,46 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" s="10">
+        <v>8.0</v>
+      </c>
       <c r="D20" s="6">
         <v>1.0</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="11">
         <v>81.2426020220643</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="11">
         <v>1.292547431931647</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="11">
         <v>64.06396712380118</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="11">
         <v>1.073899233258391</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="11">
         <v>46.65428644688735</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="11">
         <v>1.173277863282734</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="11">
         <v>38.83791036948328</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="11">
         <v>1.6619042723634</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="11">
         <v>7.572406059866998</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="11">
         <v>3.625971252381777</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="11">
         <v>-5.827536358239263</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="Q20" s="11">
         <v>1.025210659646665</v>
       </c>
       <c r="R20" s="7">
@@ -2847,16 +2901,16 @@
       <c r="U20" s="7">
         <v>0.2538071006812823</v>
       </c>
-      <c r="V20" s="10">
+      <c r="V20" s="11">
         <v>27.35995235026642</v>
       </c>
-      <c r="W20" s="10">
+      <c r="W20" s="11">
         <v>0.2903977663608577</v>
       </c>
-      <c r="X20" s="10">
+      <c r="X20" s="11">
         <v>63.35090212594795</v>
       </c>
-      <c r="Y20" s="10">
+      <c r="Y20" s="11">
         <v>0.3736357215980802</v>
       </c>
       <c r="Z20" s="7">
@@ -2918,43 +2972,46 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" s="10">
+        <v>8.0</v>
+      </c>
       <c r="D21" s="6">
         <v>2.0</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="11">
         <v>86.6940144786473</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="11">
         <v>0.7114936580565371</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="11">
         <v>64.9105623379963</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="11">
         <v>0.7718934035498882</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="11">
         <v>38.00580449625971</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="11">
         <v>1.319861812881732</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="11">
         <v>28.60627320686058</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="11">
         <v>1.073964193309294</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="11">
         <v>-0.99185195073595</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="11">
         <v>0.09076982424857508</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="11">
         <v>-10.13385366047071</v>
       </c>
-      <c r="Q21" s="10">
+      <c r="Q21" s="11">
         <v>0.2784644868687212</v>
       </c>
       <c r="R21" s="7">
@@ -2969,16 +3026,16 @@
       <c r="U21" s="7">
         <v>1.269214306624886</v>
       </c>
-      <c r="V21" s="10">
+      <c r="V21" s="11">
         <v>20.68191732117495</v>
       </c>
-      <c r="W21" s="10">
+      <c r="W21" s="11">
         <v>0.04663818994114876</v>
       </c>
-      <c r="X21" s="10">
+      <c r="X21" s="11">
         <v>66.32566586185372</v>
       </c>
-      <c r="Y21" s="10">
+      <c r="Y21" s="11">
         <v>3.327097647494963</v>
       </c>
       <c r="Z21" s="7">
@@ -3040,43 +3097,46 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" s="10">
+        <v>8.0</v>
+      </c>
       <c r="D22" s="6">
         <v>3.0</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="11">
         <v>86.57815055361479</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="11">
         <v>0.7989513576844337</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="11">
         <v>64.15458644690212</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="11">
         <v>0.71808930421684</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="11">
         <v>35.78785292872072</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="11">
         <v>2.012024404631783</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="11">
         <v>26.79474108383413</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="11">
         <v>1.643657644782541</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="11">
         <v>-1.17770629571225</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="11">
         <v>0.2509473820695613</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="11">
         <v>-11.78482783718485</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="11">
         <v>0.1444021369679515</v>
       </c>
       <c r="R22" s="7">
@@ -3091,16 +3151,16 @@
       <c r="U22" s="7">
         <v>0.1278441837045718</v>
       </c>
-      <c r="V22" s="10">
+      <c r="V22" s="11">
         <v>25.88702503377038</v>
       </c>
-      <c r="W22" s="10">
+      <c r="W22" s="11">
         <v>0.6750472904119466</v>
       </c>
-      <c r="X22" s="10">
+      <c r="X22" s="11">
         <v>66.37588979908838</v>
       </c>
-      <c r="Y22" s="10">
+      <c r="Y22" s="11">
         <v>0.7460293320340622</v>
       </c>
       <c r="Z22" s="7">
@@ -3162,43 +3222,46 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" s="10">
+        <v>8.0</v>
+      </c>
       <c r="E23" s="6">
         <v>0.7</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="11">
         <v>81.77790114931372</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="11">
         <v>0.3691331159436907</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="11">
         <v>65.43236709011298</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="11">
         <v>0.3955130409555167</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="11">
         <v>57.59146145032134</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="11">
         <v>0.4985572271949375</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="11">
         <v>52.98138102135169</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="11">
         <v>0.5283540464278488</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="11">
         <v>34.54105930547313</v>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="11">
         <v>0.6677593534746807</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="11">
         <v>21.76236995963651</v>
       </c>
-      <c r="Q23" s="10">
+      <c r="Q23" s="11">
         <v>0.4820305041701456</v>
       </c>
       <c r="R23" s="6">
@@ -3213,16 +3276,16 @@
       <c r="U23" s="6">
         <v>0.1815763206872865</v>
       </c>
-      <c r="V23" s="10">
+      <c r="V23" s="11">
         <v>28.97870735652493</v>
       </c>
-      <c r="W23" s="10">
+      <c r="W23" s="11">
         <v>1.016937112532046</v>
       </c>
-      <c r="X23" s="10">
+      <c r="X23" s="11">
         <v>67.95761378035826</v>
       </c>
-      <c r="Y23" s="10">
+      <c r="Y23" s="11">
         <v>1.048582259919522</v>
       </c>
       <c r="Z23" s="7">
@@ -3284,43 +3347,46 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" s="10">
+        <v>8.0</v>
+      </c>
       <c r="E24" s="6">
         <v>1.0</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="11">
         <v>79.28518883688204</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="11">
         <v>0.4342792604025347</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="11">
         <v>62.88819200284733</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="11">
         <v>0.2472251768427733</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="11">
         <v>53.8168715161362</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="11">
         <v>0.3650401921196924</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="11">
         <v>49.16109123093711</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="11">
         <v>0.3538628427661411</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="11">
         <v>30.53797009014078</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="11">
         <v>0.3334940408981691</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="11">
         <v>18.03367078727906</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q24" s="11">
         <v>0.2150558749298457</v>
       </c>
       <c r="R24" s="6">
@@ -3335,16 +3401,16 @@
       <c r="U24" s="6">
         <v>0.3128919174986041</v>
       </c>
-      <c r="V24" s="10">
+      <c r="V24" s="11">
         <v>25.60440652380082</v>
       </c>
-      <c r="W24" s="10">
+      <c r="W24" s="11">
         <v>0.633579669032225</v>
       </c>
-      <c r="X24" s="10">
+      <c r="X24" s="11">
         <v>66.85940228952235</v>
       </c>
-      <c r="Y24" s="10">
+      <c r="Y24" s="11">
         <v>0.4474666968200189</v>
       </c>
       <c r="Z24" s="7">
@@ -3406,6 +3472,9 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" s="10">
+        <v>8.0</v>
+      </c>
       <c r="E25" s="6">
         <v>2.0</v>
       </c>
@@ -3457,16 +3526,16 @@
       <c r="U25" s="6">
         <v>1.54167771885102</v>
       </c>
-      <c r="V25" s="10">
+      <c r="V25" s="11">
         <v>49.37446984808432</v>
       </c>
-      <c r="W25" s="10">
+      <c r="W25" s="11">
         <v>3.756724844909057</v>
       </c>
-      <c r="X25" s="10">
+      <c r="X25" s="11">
         <v>63.2545941277447</v>
       </c>
-      <c r="Y25" s="10">
+      <c r="Y25" s="11">
         <v>0.9731452218857441</v>
       </c>
       <c r="AC25" s="8">
@@ -3519,6 +3588,9 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" s="10">
+        <v>8.0</v>
+      </c>
       <c r="E26" s="6">
         <v>3.0</v>
       </c>
@@ -3570,16 +3642,16 @@
       <c r="U26" s="6">
         <v>0.1030087882187284</v>
       </c>
-      <c r="V26" s="10">
+      <c r="V26" s="11">
         <v>60.73168100916474</v>
       </c>
-      <c r="W26" s="10">
+      <c r="W26" s="11">
         <v>4.669153324683568</v>
       </c>
-      <c r="X26" s="10">
+      <c r="X26" s="11">
         <v>60.16621966134054</v>
       </c>
-      <c r="Y26" s="10">
+      <c r="Y26" s="11">
         <v>1.319433183635669</v>
       </c>
       <c r="AC26" s="8">
@@ -3642,3772 +3714,3772 @@
       <c r="Y27" s="6"/>
     </row>
     <row r="59">
-      <c r="AC59" s="12"/>
-      <c r="AE59" s="12"/>
+      <c r="AC59" s="13"/>
+      <c r="AE59" s="13"/>
     </row>
     <row r="60">
-      <c r="AC60" s="12"/>
-      <c r="AE60" s="12"/>
+      <c r="AC60" s="13"/>
+      <c r="AE60" s="13"/>
     </row>
     <row r="61">
-      <c r="AC61" s="12"/>
-      <c r="AE61" s="12"/>
+      <c r="AC61" s="13"/>
+      <c r="AE61" s="13"/>
     </row>
     <row r="62">
-      <c r="AC62" s="12"/>
-      <c r="AE62" s="12"/>
+      <c r="AC62" s="13"/>
+      <c r="AE62" s="13"/>
     </row>
     <row r="63">
-      <c r="AC63" s="12"/>
-      <c r="AE63" s="12"/>
+      <c r="AC63" s="13"/>
+      <c r="AE63" s="13"/>
     </row>
     <row r="64">
-      <c r="AC64" s="12"/>
-      <c r="AE64" s="12"/>
+      <c r="AC64" s="13"/>
+      <c r="AE64" s="13"/>
     </row>
     <row r="65">
-      <c r="AC65" s="12"/>
-      <c r="AE65" s="12"/>
+      <c r="AC65" s="13"/>
+      <c r="AE65" s="13"/>
     </row>
     <row r="66">
-      <c r="AC66" s="12"/>
-      <c r="AE66" s="12"/>
+      <c r="AC66" s="13"/>
+      <c r="AE66" s="13"/>
     </row>
     <row r="67">
-      <c r="AC67" s="12"/>
-      <c r="AE67" s="12"/>
+      <c r="AC67" s="13"/>
+      <c r="AE67" s="13"/>
     </row>
     <row r="68">
-      <c r="AC68" s="12"/>
-      <c r="AE68" s="12"/>
+      <c r="AC68" s="13"/>
+      <c r="AE68" s="13"/>
     </row>
     <row r="69">
-      <c r="AC69" s="12"/>
-      <c r="AE69" s="12"/>
+      <c r="AC69" s="13"/>
+      <c r="AE69" s="13"/>
     </row>
     <row r="70">
-      <c r="AC70" s="12"/>
-      <c r="AE70" s="12"/>
+      <c r="AC70" s="13"/>
+      <c r="AE70" s="13"/>
     </row>
     <row r="71">
-      <c r="AC71" s="12"/>
-      <c r="AE71" s="12"/>
+      <c r="AC71" s="13"/>
+      <c r="AE71" s="13"/>
     </row>
     <row r="72">
-      <c r="AC72" s="12"/>
-      <c r="AE72" s="12"/>
+      <c r="AC72" s="13"/>
+      <c r="AE72" s="13"/>
     </row>
     <row r="73">
-      <c r="AC73" s="12"/>
-      <c r="AE73" s="12"/>
+      <c r="AC73" s="13"/>
+      <c r="AE73" s="13"/>
     </row>
     <row r="74">
-      <c r="AC74" s="12"/>
-      <c r="AE74" s="12"/>
+      <c r="AC74" s="13"/>
+      <c r="AE74" s="13"/>
     </row>
     <row r="75">
-      <c r="AC75" s="12"/>
-      <c r="AE75" s="12"/>
+      <c r="AC75" s="13"/>
+      <c r="AE75" s="13"/>
     </row>
     <row r="76">
-      <c r="AC76" s="12"/>
-      <c r="AE76" s="12"/>
+      <c r="AC76" s="13"/>
+      <c r="AE76" s="13"/>
     </row>
     <row r="77">
-      <c r="AC77" s="12"/>
-      <c r="AE77" s="12"/>
+      <c r="AC77" s="13"/>
+      <c r="AE77" s="13"/>
     </row>
     <row r="78">
-      <c r="AC78" s="12"/>
-      <c r="AE78" s="12"/>
+      <c r="AC78" s="13"/>
+      <c r="AE78" s="13"/>
     </row>
     <row r="79">
-      <c r="AC79" s="12"/>
-      <c r="AE79" s="12"/>
+      <c r="AC79" s="13"/>
+      <c r="AE79" s="13"/>
     </row>
     <row r="80">
-      <c r="AC80" s="12"/>
-      <c r="AE80" s="12"/>
+      <c r="AC80" s="13"/>
+      <c r="AE80" s="13"/>
     </row>
     <row r="81">
-      <c r="AC81" s="12"/>
-      <c r="AE81" s="12"/>
+      <c r="AC81" s="13"/>
+      <c r="AE81" s="13"/>
     </row>
     <row r="82">
-      <c r="AC82" s="12"/>
-      <c r="AE82" s="12"/>
+      <c r="AC82" s="13"/>
+      <c r="AE82" s="13"/>
     </row>
     <row r="83">
-      <c r="AC83" s="12"/>
-      <c r="AE83" s="12"/>
+      <c r="AC83" s="13"/>
+      <c r="AE83" s="13"/>
     </row>
     <row r="84">
-      <c r="AC84" s="12"/>
-      <c r="AE84" s="12"/>
+      <c r="AC84" s="13"/>
+      <c r="AE84" s="13"/>
     </row>
     <row r="85">
-      <c r="AC85" s="12"/>
-      <c r="AE85" s="12"/>
+      <c r="AC85" s="13"/>
+      <c r="AE85" s="13"/>
     </row>
     <row r="86">
-      <c r="AC86" s="12"/>
-      <c r="AE86" s="12"/>
+      <c r="AC86" s="13"/>
+      <c r="AE86" s="13"/>
     </row>
     <row r="87">
-      <c r="AC87" s="12"/>
-      <c r="AE87" s="12"/>
+      <c r="AC87" s="13"/>
+      <c r="AE87" s="13"/>
     </row>
     <row r="88">
-      <c r="AC88" s="12"/>
-      <c r="AE88" s="12"/>
+      <c r="AC88" s="13"/>
+      <c r="AE88" s="13"/>
     </row>
     <row r="89">
-      <c r="AC89" s="12"/>
-      <c r="AE89" s="12"/>
+      <c r="AC89" s="13"/>
+      <c r="AE89" s="13"/>
     </row>
     <row r="90">
-      <c r="AC90" s="12"/>
-      <c r="AE90" s="12"/>
+      <c r="AC90" s="13"/>
+      <c r="AE90" s="13"/>
     </row>
     <row r="91">
-      <c r="AC91" s="12"/>
-      <c r="AE91" s="12"/>
+      <c r="AC91" s="13"/>
+      <c r="AE91" s="13"/>
     </row>
     <row r="92">
-      <c r="AC92" s="12"/>
-      <c r="AE92" s="12"/>
+      <c r="AC92" s="13"/>
+      <c r="AE92" s="13"/>
     </row>
     <row r="93">
-      <c r="AC93" s="12"/>
-      <c r="AE93" s="12"/>
+      <c r="AC93" s="13"/>
+      <c r="AE93" s="13"/>
     </row>
     <row r="94">
-      <c r="AC94" s="12"/>
-      <c r="AE94" s="12"/>
+      <c r="AC94" s="13"/>
+      <c r="AE94" s="13"/>
     </row>
     <row r="95">
-      <c r="AC95" s="12"/>
-      <c r="AE95" s="12"/>
+      <c r="AC95" s="13"/>
+      <c r="AE95" s="13"/>
     </row>
     <row r="96">
-      <c r="AC96" s="12"/>
-      <c r="AE96" s="12"/>
+      <c r="AC96" s="13"/>
+      <c r="AE96" s="13"/>
     </row>
     <row r="97">
-      <c r="AC97" s="12"/>
-      <c r="AE97" s="12"/>
+      <c r="AC97" s="13"/>
+      <c r="AE97" s="13"/>
     </row>
     <row r="98">
-      <c r="AC98" s="12"/>
-      <c r="AE98" s="12"/>
+      <c r="AC98" s="13"/>
+      <c r="AE98" s="13"/>
     </row>
     <row r="99">
-      <c r="AC99" s="12"/>
-      <c r="AE99" s="12"/>
+      <c r="AC99" s="13"/>
+      <c r="AE99" s="13"/>
     </row>
     <row r="100">
-      <c r="AC100" s="12"/>
-      <c r="AE100" s="12"/>
+      <c r="AC100" s="13"/>
+      <c r="AE100" s="13"/>
     </row>
     <row r="101">
-      <c r="AC101" s="12"/>
-      <c r="AE101" s="12"/>
+      <c r="AC101" s="13"/>
+      <c r="AE101" s="13"/>
     </row>
     <row r="102">
-      <c r="AC102" s="12"/>
-      <c r="AE102" s="12"/>
+      <c r="AC102" s="13"/>
+      <c r="AE102" s="13"/>
     </row>
     <row r="103">
-      <c r="AC103" s="12"/>
-      <c r="AE103" s="12"/>
+      <c r="AC103" s="13"/>
+      <c r="AE103" s="13"/>
     </row>
     <row r="104">
-      <c r="AC104" s="12"/>
-      <c r="AE104" s="12"/>
+      <c r="AC104" s="13"/>
+      <c r="AE104" s="13"/>
     </row>
     <row r="105">
-      <c r="AC105" s="12"/>
-      <c r="AE105" s="12"/>
+      <c r="AC105" s="13"/>
+      <c r="AE105" s="13"/>
     </row>
     <row r="106">
-      <c r="AC106" s="12"/>
-      <c r="AE106" s="12"/>
+      <c r="AC106" s="13"/>
+      <c r="AE106" s="13"/>
     </row>
     <row r="107">
-      <c r="AC107" s="12"/>
-      <c r="AE107" s="12"/>
+      <c r="AC107" s="13"/>
+      <c r="AE107" s="13"/>
     </row>
     <row r="108">
-      <c r="AC108" s="12"/>
-      <c r="AE108" s="12"/>
+      <c r="AC108" s="13"/>
+      <c r="AE108" s="13"/>
     </row>
     <row r="109">
-      <c r="AC109" s="12"/>
-      <c r="AE109" s="12"/>
+      <c r="AC109" s="13"/>
+      <c r="AE109" s="13"/>
     </row>
     <row r="110">
-      <c r="AC110" s="12"/>
-      <c r="AE110" s="12"/>
+      <c r="AC110" s="13"/>
+      <c r="AE110" s="13"/>
     </row>
     <row r="111">
-      <c r="AC111" s="12"/>
-      <c r="AE111" s="12"/>
+      <c r="AC111" s="13"/>
+      <c r="AE111" s="13"/>
     </row>
     <row r="112">
-      <c r="AC112" s="12"/>
-      <c r="AE112" s="12"/>
+      <c r="AC112" s="13"/>
+      <c r="AE112" s="13"/>
     </row>
     <row r="113">
-      <c r="AC113" s="12"/>
-      <c r="AE113" s="12"/>
+      <c r="AC113" s="13"/>
+      <c r="AE113" s="13"/>
     </row>
     <row r="114">
-      <c r="AC114" s="12"/>
-      <c r="AE114" s="12"/>
+      <c r="AC114" s="13"/>
+      <c r="AE114" s="13"/>
     </row>
     <row r="115">
-      <c r="AC115" s="12"/>
-      <c r="AE115" s="12"/>
+      <c r="AC115" s="13"/>
+      <c r="AE115" s="13"/>
     </row>
     <row r="116">
-      <c r="AC116" s="12"/>
-      <c r="AE116" s="12"/>
+      <c r="AC116" s="13"/>
+      <c r="AE116" s="13"/>
     </row>
     <row r="117">
-      <c r="AC117" s="12"/>
-      <c r="AE117" s="12"/>
+      <c r="AC117" s="13"/>
+      <c r="AE117" s="13"/>
     </row>
     <row r="118">
-      <c r="AC118" s="12"/>
-      <c r="AE118" s="12"/>
+      <c r="AC118" s="13"/>
+      <c r="AE118" s="13"/>
     </row>
     <row r="119">
-      <c r="AC119" s="12"/>
-      <c r="AE119" s="12"/>
+      <c r="AC119" s="13"/>
+      <c r="AE119" s="13"/>
     </row>
     <row r="120">
-      <c r="AC120" s="12"/>
-      <c r="AE120" s="12"/>
+      <c r="AC120" s="13"/>
+      <c r="AE120" s="13"/>
     </row>
     <row r="121">
-      <c r="AC121" s="12"/>
-      <c r="AE121" s="12"/>
+      <c r="AC121" s="13"/>
+      <c r="AE121" s="13"/>
     </row>
     <row r="122">
-      <c r="AC122" s="12"/>
-      <c r="AE122" s="12"/>
+      <c r="AC122" s="13"/>
+      <c r="AE122" s="13"/>
     </row>
     <row r="123">
-      <c r="AC123" s="12"/>
-      <c r="AE123" s="12"/>
+      <c r="AC123" s="13"/>
+      <c r="AE123" s="13"/>
     </row>
     <row r="124">
-      <c r="AC124" s="12"/>
-      <c r="AE124" s="12"/>
+      <c r="AC124" s="13"/>
+      <c r="AE124" s="13"/>
     </row>
     <row r="125">
-      <c r="AC125" s="12"/>
-      <c r="AE125" s="12"/>
+      <c r="AC125" s="13"/>
+      <c r="AE125" s="13"/>
     </row>
     <row r="126">
-      <c r="AC126" s="12"/>
-      <c r="AE126" s="12"/>
+      <c r="AC126" s="13"/>
+      <c r="AE126" s="13"/>
     </row>
     <row r="127">
-      <c r="AC127" s="12"/>
-      <c r="AE127" s="12"/>
+      <c r="AC127" s="13"/>
+      <c r="AE127" s="13"/>
     </row>
     <row r="128">
-      <c r="AC128" s="12"/>
-      <c r="AE128" s="12"/>
+      <c r="AC128" s="13"/>
+      <c r="AE128" s="13"/>
     </row>
     <row r="129">
-      <c r="AC129" s="12"/>
-      <c r="AE129" s="12"/>
+      <c r="AC129" s="13"/>
+      <c r="AE129" s="13"/>
     </row>
     <row r="130">
-      <c r="AC130" s="12"/>
-      <c r="AE130" s="12"/>
+      <c r="AC130" s="13"/>
+      <c r="AE130" s="13"/>
     </row>
     <row r="131">
-      <c r="AC131" s="12"/>
-      <c r="AE131" s="12"/>
+      <c r="AC131" s="13"/>
+      <c r="AE131" s="13"/>
     </row>
     <row r="132">
-      <c r="AC132" s="12"/>
-      <c r="AE132" s="12"/>
+      <c r="AC132" s="13"/>
+      <c r="AE132" s="13"/>
     </row>
     <row r="133">
-      <c r="AC133" s="12"/>
-      <c r="AE133" s="12"/>
+      <c r="AC133" s="13"/>
+      <c r="AE133" s="13"/>
     </row>
     <row r="134">
-      <c r="AC134" s="12"/>
-      <c r="AE134" s="12"/>
+      <c r="AC134" s="13"/>
+      <c r="AE134" s="13"/>
     </row>
     <row r="135">
-      <c r="AC135" s="12"/>
-      <c r="AE135" s="12"/>
+      <c r="AC135" s="13"/>
+      <c r="AE135" s="13"/>
     </row>
     <row r="136">
-      <c r="AC136" s="12"/>
-      <c r="AE136" s="12"/>
+      <c r="AC136" s="13"/>
+      <c r="AE136" s="13"/>
     </row>
     <row r="137">
-      <c r="AC137" s="12"/>
-      <c r="AE137" s="12"/>
+      <c r="AC137" s="13"/>
+      <c r="AE137" s="13"/>
     </row>
     <row r="138">
-      <c r="AC138" s="12"/>
-      <c r="AE138" s="12"/>
+      <c r="AC138" s="13"/>
+      <c r="AE138" s="13"/>
     </row>
     <row r="139">
-      <c r="AC139" s="12"/>
-      <c r="AE139" s="12"/>
+      <c r="AC139" s="13"/>
+      <c r="AE139" s="13"/>
     </row>
     <row r="140">
-      <c r="AC140" s="12"/>
-      <c r="AE140" s="12"/>
+      <c r="AC140" s="13"/>
+      <c r="AE140" s="13"/>
     </row>
     <row r="141">
-      <c r="AC141" s="12"/>
-      <c r="AE141" s="12"/>
+      <c r="AC141" s="13"/>
+      <c r="AE141" s="13"/>
     </row>
     <row r="142">
-      <c r="AC142" s="12"/>
-      <c r="AE142" s="12"/>
+      <c r="AC142" s="13"/>
+      <c r="AE142" s="13"/>
     </row>
     <row r="143">
-      <c r="AC143" s="12"/>
-      <c r="AE143" s="12"/>
+      <c r="AC143" s="13"/>
+      <c r="AE143" s="13"/>
     </row>
     <row r="144">
-      <c r="AC144" s="12"/>
-      <c r="AE144" s="12"/>
+      <c r="AC144" s="13"/>
+      <c r="AE144" s="13"/>
     </row>
     <row r="145">
-      <c r="AC145" s="12"/>
-      <c r="AE145" s="12"/>
+      <c r="AC145" s="13"/>
+      <c r="AE145" s="13"/>
     </row>
     <row r="146">
-      <c r="AC146" s="12"/>
-      <c r="AE146" s="12"/>
+      <c r="AC146" s="13"/>
+      <c r="AE146" s="13"/>
     </row>
     <row r="147">
-      <c r="AC147" s="12"/>
-      <c r="AE147" s="12"/>
+      <c r="AC147" s="13"/>
+      <c r="AE147" s="13"/>
     </row>
     <row r="148">
-      <c r="AC148" s="12"/>
-      <c r="AE148" s="12"/>
+      <c r="AC148" s="13"/>
+      <c r="AE148" s="13"/>
     </row>
     <row r="149">
-      <c r="AC149" s="12"/>
-      <c r="AE149" s="12"/>
+      <c r="AC149" s="13"/>
+      <c r="AE149" s="13"/>
     </row>
     <row r="150">
-      <c r="AC150" s="12"/>
-      <c r="AE150" s="12"/>
+      <c r="AC150" s="13"/>
+      <c r="AE150" s="13"/>
     </row>
     <row r="151">
-      <c r="AC151" s="12"/>
-      <c r="AE151" s="12"/>
+      <c r="AC151" s="13"/>
+      <c r="AE151" s="13"/>
     </row>
     <row r="152">
-      <c r="AC152" s="12"/>
-      <c r="AE152" s="12"/>
+      <c r="AC152" s="13"/>
+      <c r="AE152" s="13"/>
     </row>
     <row r="153">
-      <c r="AC153" s="12"/>
-      <c r="AE153" s="12"/>
+      <c r="AC153" s="13"/>
+      <c r="AE153" s="13"/>
     </row>
     <row r="154">
-      <c r="AC154" s="12"/>
-      <c r="AE154" s="12"/>
+      <c r="AC154" s="13"/>
+      <c r="AE154" s="13"/>
     </row>
     <row r="155">
-      <c r="AC155" s="12"/>
-      <c r="AE155" s="12"/>
+      <c r="AC155" s="13"/>
+      <c r="AE155" s="13"/>
     </row>
     <row r="156">
-      <c r="AC156" s="12"/>
-      <c r="AE156" s="12"/>
+      <c r="AC156" s="13"/>
+      <c r="AE156" s="13"/>
     </row>
     <row r="157">
-      <c r="AC157" s="12"/>
-      <c r="AE157" s="12"/>
+      <c r="AC157" s="13"/>
+      <c r="AE157" s="13"/>
     </row>
     <row r="158">
-      <c r="AC158" s="12"/>
-      <c r="AE158" s="12"/>
+      <c r="AC158" s="13"/>
+      <c r="AE158" s="13"/>
     </row>
     <row r="159">
-      <c r="AC159" s="12"/>
-      <c r="AE159" s="12"/>
+      <c r="AC159" s="13"/>
+      <c r="AE159" s="13"/>
     </row>
     <row r="160">
-      <c r="AC160" s="12"/>
-      <c r="AE160" s="12"/>
+      <c r="AC160" s="13"/>
+      <c r="AE160" s="13"/>
     </row>
     <row r="161">
-      <c r="AC161" s="12"/>
-      <c r="AE161" s="12"/>
+      <c r="AC161" s="13"/>
+      <c r="AE161" s="13"/>
     </row>
     <row r="162">
-      <c r="AC162" s="12"/>
-      <c r="AE162" s="12"/>
+      <c r="AC162" s="13"/>
+      <c r="AE162" s="13"/>
     </row>
     <row r="163">
-      <c r="AC163" s="12"/>
-      <c r="AE163" s="12"/>
+      <c r="AC163" s="13"/>
+      <c r="AE163" s="13"/>
     </row>
     <row r="164">
-      <c r="AC164" s="12"/>
-      <c r="AE164" s="12"/>
+      <c r="AC164" s="13"/>
+      <c r="AE164" s="13"/>
     </row>
     <row r="165">
-      <c r="AC165" s="12"/>
-      <c r="AE165" s="12"/>
+      <c r="AC165" s="13"/>
+      <c r="AE165" s="13"/>
     </row>
     <row r="166">
-      <c r="AC166" s="12"/>
-      <c r="AE166" s="12"/>
+      <c r="AC166" s="13"/>
+      <c r="AE166" s="13"/>
     </row>
     <row r="167">
-      <c r="AC167" s="12"/>
-      <c r="AE167" s="12"/>
+      <c r="AC167" s="13"/>
+      <c r="AE167" s="13"/>
     </row>
     <row r="168">
-      <c r="AC168" s="12"/>
-      <c r="AE168" s="12"/>
+      <c r="AC168" s="13"/>
+      <c r="AE168" s="13"/>
     </row>
     <row r="169">
-      <c r="AC169" s="12"/>
-      <c r="AE169" s="12"/>
+      <c r="AC169" s="13"/>
+      <c r="AE169" s="13"/>
     </row>
     <row r="170">
-      <c r="AC170" s="12"/>
-      <c r="AE170" s="12"/>
+      <c r="AC170" s="13"/>
+      <c r="AE170" s="13"/>
     </row>
     <row r="171">
-      <c r="AC171" s="12"/>
-      <c r="AE171" s="12"/>
+      <c r="AC171" s="13"/>
+      <c r="AE171" s="13"/>
     </row>
     <row r="172">
-      <c r="AC172" s="12"/>
-      <c r="AE172" s="12"/>
+      <c r="AC172" s="13"/>
+      <c r="AE172" s="13"/>
     </row>
     <row r="173">
-      <c r="AC173" s="12"/>
-      <c r="AE173" s="12"/>
+      <c r="AC173" s="13"/>
+      <c r="AE173" s="13"/>
     </row>
     <row r="174">
-      <c r="AC174" s="12"/>
-      <c r="AE174" s="12"/>
+      <c r="AC174" s="13"/>
+      <c r="AE174" s="13"/>
     </row>
     <row r="175">
-      <c r="AC175" s="12"/>
-      <c r="AE175" s="12"/>
+      <c r="AC175" s="13"/>
+      <c r="AE175" s="13"/>
     </row>
     <row r="176">
-      <c r="AC176" s="12"/>
-      <c r="AE176" s="12"/>
+      <c r="AC176" s="13"/>
+      <c r="AE176" s="13"/>
     </row>
     <row r="177">
-      <c r="AC177" s="12"/>
-      <c r="AE177" s="12"/>
+      <c r="AC177" s="13"/>
+      <c r="AE177" s="13"/>
     </row>
     <row r="178">
-      <c r="AC178" s="12"/>
-      <c r="AE178" s="12"/>
+      <c r="AC178" s="13"/>
+      <c r="AE178" s="13"/>
     </row>
     <row r="179">
-      <c r="AC179" s="12"/>
-      <c r="AE179" s="12"/>
+      <c r="AC179" s="13"/>
+      <c r="AE179" s="13"/>
     </row>
     <row r="180">
-      <c r="AC180" s="12"/>
-      <c r="AE180" s="12"/>
+      <c r="AC180" s="13"/>
+      <c r="AE180" s="13"/>
     </row>
     <row r="181">
-      <c r="AC181" s="12"/>
-      <c r="AE181" s="12"/>
+      <c r="AC181" s="13"/>
+      <c r="AE181" s="13"/>
     </row>
     <row r="182">
-      <c r="AC182" s="12"/>
-      <c r="AE182" s="12"/>
+      <c r="AC182" s="13"/>
+      <c r="AE182" s="13"/>
     </row>
     <row r="183">
-      <c r="AC183" s="12"/>
-      <c r="AE183" s="12"/>
+      <c r="AC183" s="13"/>
+      <c r="AE183" s="13"/>
     </row>
     <row r="184">
-      <c r="AC184" s="12"/>
-      <c r="AE184" s="12"/>
+      <c r="AC184" s="13"/>
+      <c r="AE184" s="13"/>
     </row>
     <row r="185">
-      <c r="AC185" s="12"/>
-      <c r="AE185" s="12"/>
+      <c r="AC185" s="13"/>
+      <c r="AE185" s="13"/>
     </row>
     <row r="186">
-      <c r="AC186" s="12"/>
-      <c r="AE186" s="12"/>
+      <c r="AC186" s="13"/>
+      <c r="AE186" s="13"/>
     </row>
     <row r="187">
-      <c r="AC187" s="12"/>
-      <c r="AE187" s="12"/>
+      <c r="AC187" s="13"/>
+      <c r="AE187" s="13"/>
     </row>
     <row r="188">
-      <c r="AC188" s="12"/>
-      <c r="AE188" s="12"/>
+      <c r="AC188" s="13"/>
+      <c r="AE188" s="13"/>
     </row>
     <row r="189">
-      <c r="AC189" s="12"/>
-      <c r="AE189" s="12"/>
+      <c r="AC189" s="13"/>
+      <c r="AE189" s="13"/>
     </row>
     <row r="190">
-      <c r="AC190" s="12"/>
-      <c r="AE190" s="12"/>
+      <c r="AC190" s="13"/>
+      <c r="AE190" s="13"/>
     </row>
     <row r="191">
-      <c r="AC191" s="12"/>
-      <c r="AE191" s="12"/>
+      <c r="AC191" s="13"/>
+      <c r="AE191" s="13"/>
     </row>
     <row r="192">
-      <c r="AC192" s="12"/>
-      <c r="AE192" s="12"/>
+      <c r="AC192" s="13"/>
+      <c r="AE192" s="13"/>
     </row>
     <row r="193">
-      <c r="AC193" s="12"/>
-      <c r="AE193" s="12"/>
+      <c r="AC193" s="13"/>
+      <c r="AE193" s="13"/>
     </row>
     <row r="194">
-      <c r="AC194" s="12"/>
-      <c r="AE194" s="12"/>
+      <c r="AC194" s="13"/>
+      <c r="AE194" s="13"/>
     </row>
     <row r="195">
-      <c r="AC195" s="12"/>
-      <c r="AE195" s="12"/>
+      <c r="AC195" s="13"/>
+      <c r="AE195" s="13"/>
     </row>
     <row r="196">
-      <c r="AC196" s="12"/>
-      <c r="AE196" s="12"/>
+      <c r="AC196" s="13"/>
+      <c r="AE196" s="13"/>
     </row>
     <row r="197">
-      <c r="AC197" s="12"/>
-      <c r="AE197" s="12"/>
+      <c r="AC197" s="13"/>
+      <c r="AE197" s="13"/>
     </row>
     <row r="198">
-      <c r="AC198" s="12"/>
-      <c r="AE198" s="12"/>
+      <c r="AC198" s="13"/>
+      <c r="AE198" s="13"/>
     </row>
     <row r="199">
-      <c r="AC199" s="12"/>
-      <c r="AE199" s="12"/>
+      <c r="AC199" s="13"/>
+      <c r="AE199" s="13"/>
     </row>
     <row r="200">
-      <c r="AC200" s="12"/>
-      <c r="AE200" s="12"/>
+      <c r="AC200" s="13"/>
+      <c r="AE200" s="13"/>
     </row>
     <row r="201">
-      <c r="AC201" s="12"/>
-      <c r="AE201" s="12"/>
+      <c r="AC201" s="13"/>
+      <c r="AE201" s="13"/>
     </row>
     <row r="202">
-      <c r="AC202" s="12"/>
-      <c r="AE202" s="12"/>
+      <c r="AC202" s="13"/>
+      <c r="AE202" s="13"/>
     </row>
     <row r="203">
-      <c r="AC203" s="12"/>
-      <c r="AE203" s="12"/>
+      <c r="AC203" s="13"/>
+      <c r="AE203" s="13"/>
     </row>
     <row r="204">
-      <c r="AC204" s="12"/>
-      <c r="AE204" s="12"/>
+      <c r="AC204" s="13"/>
+      <c r="AE204" s="13"/>
     </row>
     <row r="205">
-      <c r="AC205" s="12"/>
-      <c r="AE205" s="12"/>
+      <c r="AC205" s="13"/>
+      <c r="AE205" s="13"/>
     </row>
     <row r="206">
-      <c r="AC206" s="12"/>
-      <c r="AE206" s="12"/>
+      <c r="AC206" s="13"/>
+      <c r="AE206" s="13"/>
     </row>
     <row r="207">
-      <c r="AC207" s="12"/>
-      <c r="AE207" s="12"/>
+      <c r="AC207" s="13"/>
+      <c r="AE207" s="13"/>
     </row>
     <row r="208">
-      <c r="AC208" s="12"/>
-      <c r="AE208" s="12"/>
+      <c r="AC208" s="13"/>
+      <c r="AE208" s="13"/>
     </row>
     <row r="209">
-      <c r="AC209" s="12"/>
-      <c r="AE209" s="12"/>
+      <c r="AC209" s="13"/>
+      <c r="AE209" s="13"/>
     </row>
     <row r="210">
-      <c r="AC210" s="12"/>
-      <c r="AE210" s="12"/>
+      <c r="AC210" s="13"/>
+      <c r="AE210" s="13"/>
     </row>
     <row r="211">
-      <c r="AC211" s="12"/>
-      <c r="AE211" s="12"/>
+      <c r="AC211" s="13"/>
+      <c r="AE211" s="13"/>
     </row>
     <row r="212">
-      <c r="AC212" s="12"/>
-      <c r="AE212" s="12"/>
+      <c r="AC212" s="13"/>
+      <c r="AE212" s="13"/>
     </row>
     <row r="213">
-      <c r="AC213" s="12"/>
-      <c r="AE213" s="12"/>
+      <c r="AC213" s="13"/>
+      <c r="AE213" s="13"/>
     </row>
     <row r="214">
-      <c r="AC214" s="12"/>
-      <c r="AE214" s="12"/>
+      <c r="AC214" s="13"/>
+      <c r="AE214" s="13"/>
     </row>
     <row r="215">
-      <c r="AC215" s="12"/>
-      <c r="AE215" s="12"/>
+      <c r="AC215" s="13"/>
+      <c r="AE215" s="13"/>
     </row>
     <row r="216">
-      <c r="AC216" s="12"/>
-      <c r="AE216" s="12"/>
+      <c r="AC216" s="13"/>
+      <c r="AE216" s="13"/>
     </row>
     <row r="217">
-      <c r="AC217" s="12"/>
-      <c r="AE217" s="12"/>
+      <c r="AC217" s="13"/>
+      <c r="AE217" s="13"/>
     </row>
     <row r="218">
-      <c r="AC218" s="12"/>
-      <c r="AE218" s="12"/>
+      <c r="AC218" s="13"/>
+      <c r="AE218" s="13"/>
     </row>
     <row r="219">
-      <c r="AC219" s="12"/>
-      <c r="AE219" s="12"/>
+      <c r="AC219" s="13"/>
+      <c r="AE219" s="13"/>
     </row>
     <row r="220">
-      <c r="AC220" s="12"/>
-      <c r="AE220" s="12"/>
+      <c r="AC220" s="13"/>
+      <c r="AE220" s="13"/>
     </row>
     <row r="221">
-      <c r="AC221" s="12"/>
-      <c r="AE221" s="12"/>
+      <c r="AC221" s="13"/>
+      <c r="AE221" s="13"/>
     </row>
     <row r="222">
-      <c r="AC222" s="12"/>
-      <c r="AE222" s="12"/>
+      <c r="AC222" s="13"/>
+      <c r="AE222" s="13"/>
     </row>
     <row r="223">
-      <c r="AC223" s="12"/>
-      <c r="AE223" s="12"/>
+      <c r="AC223" s="13"/>
+      <c r="AE223" s="13"/>
     </row>
     <row r="224">
-      <c r="AC224" s="12"/>
-      <c r="AE224" s="12"/>
+      <c r="AC224" s="13"/>
+      <c r="AE224" s="13"/>
     </row>
     <row r="225">
-      <c r="AC225" s="12"/>
-      <c r="AE225" s="12"/>
+      <c r="AC225" s="13"/>
+      <c r="AE225" s="13"/>
     </row>
     <row r="226">
-      <c r="AC226" s="12"/>
-      <c r="AE226" s="12"/>
+      <c r="AC226" s="13"/>
+      <c r="AE226" s="13"/>
     </row>
     <row r="227">
-      <c r="AC227" s="12"/>
-      <c r="AE227" s="12"/>
+      <c r="AC227" s="13"/>
+      <c r="AE227" s="13"/>
     </row>
     <row r="228">
-      <c r="AC228" s="12"/>
-      <c r="AE228" s="12"/>
+      <c r="AC228" s="13"/>
+      <c r="AE228" s="13"/>
     </row>
     <row r="229">
-      <c r="AC229" s="12"/>
-      <c r="AE229" s="12"/>
+      <c r="AC229" s="13"/>
+      <c r="AE229" s="13"/>
     </row>
     <row r="230">
-      <c r="AC230" s="12"/>
-      <c r="AE230" s="12"/>
+      <c r="AC230" s="13"/>
+      <c r="AE230" s="13"/>
     </row>
     <row r="231">
-      <c r="AC231" s="12"/>
-      <c r="AE231" s="12"/>
+      <c r="AC231" s="13"/>
+      <c r="AE231" s="13"/>
     </row>
     <row r="232">
-      <c r="AC232" s="12"/>
-      <c r="AE232" s="12"/>
+      <c r="AC232" s="13"/>
+      <c r="AE232" s="13"/>
     </row>
     <row r="233">
-      <c r="AC233" s="12"/>
-      <c r="AE233" s="12"/>
+      <c r="AC233" s="13"/>
+      <c r="AE233" s="13"/>
     </row>
     <row r="234">
-      <c r="AC234" s="12"/>
-      <c r="AE234" s="12"/>
+      <c r="AC234" s="13"/>
+      <c r="AE234" s="13"/>
     </row>
     <row r="235">
-      <c r="AC235" s="12"/>
-      <c r="AE235" s="12"/>
+      <c r="AC235" s="13"/>
+      <c r="AE235" s="13"/>
     </row>
     <row r="236">
-      <c r="AC236" s="12"/>
-      <c r="AE236" s="12"/>
+      <c r="AC236" s="13"/>
+      <c r="AE236" s="13"/>
     </row>
     <row r="237">
-      <c r="AC237" s="12"/>
-      <c r="AE237" s="12"/>
+      <c r="AC237" s="13"/>
+      <c r="AE237" s="13"/>
     </row>
     <row r="238">
-      <c r="AC238" s="12"/>
-      <c r="AE238" s="12"/>
+      <c r="AC238" s="13"/>
+      <c r="AE238" s="13"/>
     </row>
     <row r="239">
-      <c r="AC239" s="12"/>
-      <c r="AE239" s="12"/>
+      <c r="AC239" s="13"/>
+      <c r="AE239" s="13"/>
     </row>
     <row r="240">
-      <c r="AC240" s="12"/>
-      <c r="AE240" s="12"/>
+      <c r="AC240" s="13"/>
+      <c r="AE240" s="13"/>
     </row>
     <row r="241">
-      <c r="AC241" s="12"/>
-      <c r="AE241" s="12"/>
+      <c r="AC241" s="13"/>
+      <c r="AE241" s="13"/>
     </row>
     <row r="242">
-      <c r="AC242" s="12"/>
-      <c r="AE242" s="12"/>
+      <c r="AC242" s="13"/>
+      <c r="AE242" s="13"/>
     </row>
     <row r="243">
-      <c r="AC243" s="12"/>
-      <c r="AE243" s="12"/>
+      <c r="AC243" s="13"/>
+      <c r="AE243" s="13"/>
     </row>
     <row r="244">
-      <c r="AC244" s="12"/>
-      <c r="AE244" s="12"/>
+      <c r="AC244" s="13"/>
+      <c r="AE244" s="13"/>
     </row>
     <row r="245">
-      <c r="AC245" s="12"/>
-      <c r="AE245" s="12"/>
+      <c r="AC245" s="13"/>
+      <c r="AE245" s="13"/>
     </row>
     <row r="246">
-      <c r="AC246" s="12"/>
-      <c r="AE246" s="12"/>
+      <c r="AC246" s="13"/>
+      <c r="AE246" s="13"/>
     </row>
     <row r="247">
-      <c r="AC247" s="12"/>
-      <c r="AE247" s="12"/>
+      <c r="AC247" s="13"/>
+      <c r="AE247" s="13"/>
     </row>
     <row r="248">
-      <c r="AC248" s="12"/>
-      <c r="AE248" s="12"/>
+      <c r="AC248" s="13"/>
+      <c r="AE248" s="13"/>
     </row>
     <row r="249">
-      <c r="AC249" s="12"/>
-      <c r="AE249" s="12"/>
+      <c r="AC249" s="13"/>
+      <c r="AE249" s="13"/>
     </row>
     <row r="250">
-      <c r="AC250" s="12"/>
-      <c r="AE250" s="12"/>
+      <c r="AC250" s="13"/>
+      <c r="AE250" s="13"/>
     </row>
     <row r="251">
-      <c r="AC251" s="12"/>
-      <c r="AE251" s="12"/>
+      <c r="AC251" s="13"/>
+      <c r="AE251" s="13"/>
     </row>
     <row r="252">
-      <c r="AC252" s="12"/>
-      <c r="AE252" s="12"/>
+      <c r="AC252" s="13"/>
+      <c r="AE252" s="13"/>
     </row>
     <row r="253">
-      <c r="AC253" s="12"/>
-      <c r="AE253" s="12"/>
+      <c r="AC253" s="13"/>
+      <c r="AE253" s="13"/>
     </row>
     <row r="254">
-      <c r="AC254" s="12"/>
-      <c r="AE254" s="12"/>
+      <c r="AC254" s="13"/>
+      <c r="AE254" s="13"/>
     </row>
     <row r="255">
-      <c r="AC255" s="12"/>
-      <c r="AE255" s="12"/>
+      <c r="AC255" s="13"/>
+      <c r="AE255" s="13"/>
     </row>
     <row r="256">
-      <c r="AC256" s="12"/>
-      <c r="AE256" s="12"/>
+      <c r="AC256" s="13"/>
+      <c r="AE256" s="13"/>
     </row>
     <row r="257">
-      <c r="AC257" s="12"/>
-      <c r="AE257" s="12"/>
+      <c r="AC257" s="13"/>
+      <c r="AE257" s="13"/>
     </row>
     <row r="258">
-      <c r="AC258" s="12"/>
-      <c r="AE258" s="12"/>
+      <c r="AC258" s="13"/>
+      <c r="AE258" s="13"/>
     </row>
     <row r="259">
-      <c r="AC259" s="12"/>
-      <c r="AE259" s="12"/>
+      <c r="AC259" s="13"/>
+      <c r="AE259" s="13"/>
     </row>
     <row r="260">
-      <c r="AC260" s="12"/>
-      <c r="AE260" s="12"/>
+      <c r="AC260" s="13"/>
+      <c r="AE260" s="13"/>
     </row>
     <row r="261">
-      <c r="AC261" s="12"/>
-      <c r="AE261" s="12"/>
+      <c r="AC261" s="13"/>
+      <c r="AE261" s="13"/>
     </row>
     <row r="262">
-      <c r="AC262" s="12"/>
-      <c r="AE262" s="12"/>
+      <c r="AC262" s="13"/>
+      <c r="AE262" s="13"/>
     </row>
     <row r="263">
-      <c r="AC263" s="12"/>
-      <c r="AE263" s="12"/>
+      <c r="AC263" s="13"/>
+      <c r="AE263" s="13"/>
     </row>
     <row r="264">
-      <c r="AC264" s="12"/>
-      <c r="AE264" s="12"/>
+      <c r="AC264" s="13"/>
+      <c r="AE264" s="13"/>
     </row>
     <row r="265">
-      <c r="AC265" s="12"/>
-      <c r="AE265" s="12"/>
+      <c r="AC265" s="13"/>
+      <c r="AE265" s="13"/>
     </row>
     <row r="266">
-      <c r="AC266" s="12"/>
-      <c r="AE266" s="12"/>
+      <c r="AC266" s="13"/>
+      <c r="AE266" s="13"/>
     </row>
     <row r="267">
-      <c r="AC267" s="12"/>
-      <c r="AE267" s="12"/>
+      <c r="AC267" s="13"/>
+      <c r="AE267" s="13"/>
     </row>
     <row r="268">
-      <c r="AC268" s="12"/>
-      <c r="AE268" s="12"/>
+      <c r="AC268" s="13"/>
+      <c r="AE268" s="13"/>
     </row>
     <row r="269">
-      <c r="AC269" s="12"/>
-      <c r="AE269" s="12"/>
+      <c r="AC269" s="13"/>
+      <c r="AE269" s="13"/>
     </row>
     <row r="270">
-      <c r="AC270" s="12"/>
-      <c r="AE270" s="12"/>
+      <c r="AC270" s="13"/>
+      <c r="AE270" s="13"/>
     </row>
     <row r="271">
-      <c r="AC271" s="12"/>
-      <c r="AE271" s="12"/>
+      <c r="AC271" s="13"/>
+      <c r="AE271" s="13"/>
     </row>
     <row r="272">
-      <c r="AC272" s="12"/>
-      <c r="AE272" s="12"/>
+      <c r="AC272" s="13"/>
+      <c r="AE272" s="13"/>
     </row>
     <row r="273">
-      <c r="AC273" s="12"/>
-      <c r="AE273" s="12"/>
+      <c r="AC273" s="13"/>
+      <c r="AE273" s="13"/>
     </row>
     <row r="274">
-      <c r="AC274" s="12"/>
-      <c r="AE274" s="12"/>
+      <c r="AC274" s="13"/>
+      <c r="AE274" s="13"/>
     </row>
     <row r="275">
-      <c r="AC275" s="12"/>
-      <c r="AE275" s="12"/>
+      <c r="AC275" s="13"/>
+      <c r="AE275" s="13"/>
     </row>
     <row r="276">
-      <c r="AC276" s="12"/>
-      <c r="AE276" s="12"/>
+      <c r="AC276" s="13"/>
+      <c r="AE276" s="13"/>
     </row>
     <row r="277">
-      <c r="AC277" s="12"/>
-      <c r="AE277" s="12"/>
+      <c r="AC277" s="13"/>
+      <c r="AE277" s="13"/>
     </row>
     <row r="278">
-      <c r="AC278" s="12"/>
-      <c r="AE278" s="12"/>
+      <c r="AC278" s="13"/>
+      <c r="AE278" s="13"/>
     </row>
     <row r="279">
-      <c r="AC279" s="12"/>
-      <c r="AE279" s="12"/>
+      <c r="AC279" s="13"/>
+      <c r="AE279" s="13"/>
     </row>
     <row r="280">
-      <c r="AC280" s="12"/>
-      <c r="AE280" s="12"/>
+      <c r="AC280" s="13"/>
+      <c r="AE280" s="13"/>
     </row>
     <row r="281">
-      <c r="AC281" s="12"/>
-      <c r="AE281" s="12"/>
+      <c r="AC281" s="13"/>
+      <c r="AE281" s="13"/>
     </row>
     <row r="282">
-      <c r="AC282" s="12"/>
-      <c r="AE282" s="12"/>
+      <c r="AC282" s="13"/>
+      <c r="AE282" s="13"/>
     </row>
     <row r="283">
-      <c r="AC283" s="12"/>
-      <c r="AE283" s="12"/>
+      <c r="AC283" s="13"/>
+      <c r="AE283" s="13"/>
     </row>
     <row r="284">
-      <c r="AC284" s="12"/>
-      <c r="AE284" s="12"/>
+      <c r="AC284" s="13"/>
+      <c r="AE284" s="13"/>
     </row>
     <row r="285">
-      <c r="AC285" s="12"/>
-      <c r="AE285" s="12"/>
+      <c r="AC285" s="13"/>
+      <c r="AE285" s="13"/>
     </row>
     <row r="286">
-      <c r="AC286" s="12"/>
-      <c r="AE286" s="12"/>
+      <c r="AC286" s="13"/>
+      <c r="AE286" s="13"/>
     </row>
     <row r="287">
-      <c r="AC287" s="12"/>
-      <c r="AE287" s="12"/>
+      <c r="AC287" s="13"/>
+      <c r="AE287" s="13"/>
     </row>
     <row r="288">
-      <c r="AC288" s="12"/>
-      <c r="AE288" s="12"/>
+      <c r="AC288" s="13"/>
+      <c r="AE288" s="13"/>
     </row>
     <row r="289">
-      <c r="AC289" s="12"/>
-      <c r="AE289" s="12"/>
+      <c r="AC289" s="13"/>
+      <c r="AE289" s="13"/>
     </row>
     <row r="290">
-      <c r="AC290" s="12"/>
-      <c r="AE290" s="12"/>
+      <c r="AC290" s="13"/>
+      <c r="AE290" s="13"/>
     </row>
     <row r="291">
-      <c r="AC291" s="12"/>
-      <c r="AE291" s="12"/>
+      <c r="AC291" s="13"/>
+      <c r="AE291" s="13"/>
     </row>
     <row r="292">
-      <c r="AC292" s="12"/>
-      <c r="AE292" s="12"/>
+      <c r="AC292" s="13"/>
+      <c r="AE292" s="13"/>
     </row>
     <row r="293">
-      <c r="AC293" s="12"/>
-      <c r="AE293" s="12"/>
+      <c r="AC293" s="13"/>
+      <c r="AE293" s="13"/>
     </row>
     <row r="294">
-      <c r="AC294" s="12"/>
-      <c r="AE294" s="12"/>
+      <c r="AC294" s="13"/>
+      <c r="AE294" s="13"/>
     </row>
     <row r="295">
-      <c r="AC295" s="12"/>
-      <c r="AE295" s="12"/>
+      <c r="AC295" s="13"/>
+      <c r="AE295" s="13"/>
     </row>
     <row r="296">
-      <c r="AC296" s="12"/>
-      <c r="AE296" s="12"/>
+      <c r="AC296" s="13"/>
+      <c r="AE296" s="13"/>
     </row>
     <row r="297">
-      <c r="AC297" s="12"/>
-      <c r="AE297" s="12"/>
+      <c r="AC297" s="13"/>
+      <c r="AE297" s="13"/>
     </row>
     <row r="298">
-      <c r="AC298" s="12"/>
-      <c r="AE298" s="12"/>
+      <c r="AC298" s="13"/>
+      <c r="AE298" s="13"/>
     </row>
     <row r="299">
-      <c r="AC299" s="12"/>
-      <c r="AE299" s="12"/>
+      <c r="AC299" s="13"/>
+      <c r="AE299" s="13"/>
     </row>
     <row r="300">
-      <c r="AC300" s="12"/>
-      <c r="AE300" s="12"/>
+      <c r="AC300" s="13"/>
+      <c r="AE300" s="13"/>
     </row>
     <row r="301">
-      <c r="AC301" s="12"/>
-      <c r="AE301" s="12"/>
+      <c r="AC301" s="13"/>
+      <c r="AE301" s="13"/>
     </row>
     <row r="302">
-      <c r="AC302" s="12"/>
-      <c r="AE302" s="12"/>
+      <c r="AC302" s="13"/>
+      <c r="AE302" s="13"/>
     </row>
     <row r="303">
-      <c r="AC303" s="12"/>
-      <c r="AE303" s="12"/>
+      <c r="AC303" s="13"/>
+      <c r="AE303" s="13"/>
     </row>
     <row r="304">
-      <c r="AC304" s="12"/>
-      <c r="AE304" s="12"/>
+      <c r="AC304" s="13"/>
+      <c r="AE304" s="13"/>
     </row>
     <row r="305">
-      <c r="AC305" s="12"/>
-      <c r="AE305" s="12"/>
+      <c r="AC305" s="13"/>
+      <c r="AE305" s="13"/>
     </row>
     <row r="306">
-      <c r="AC306" s="12"/>
-      <c r="AE306" s="12"/>
+      <c r="AC306" s="13"/>
+      <c r="AE306" s="13"/>
     </row>
     <row r="307">
-      <c r="AC307" s="12"/>
-      <c r="AE307" s="12"/>
+      <c r="AC307" s="13"/>
+      <c r="AE307" s="13"/>
     </row>
     <row r="308">
-      <c r="AC308" s="12"/>
-      <c r="AE308" s="12"/>
+      <c r="AC308" s="13"/>
+      <c r="AE308" s="13"/>
     </row>
     <row r="309">
-      <c r="AC309" s="12"/>
-      <c r="AE309" s="12"/>
+      <c r="AC309" s="13"/>
+      <c r="AE309" s="13"/>
     </row>
     <row r="310">
-      <c r="AC310" s="12"/>
-      <c r="AE310" s="12"/>
+      <c r="AC310" s="13"/>
+      <c r="AE310" s="13"/>
     </row>
     <row r="311">
-      <c r="AC311" s="12"/>
-      <c r="AE311" s="12"/>
+      <c r="AC311" s="13"/>
+      <c r="AE311" s="13"/>
     </row>
     <row r="312">
-      <c r="AC312" s="12"/>
-      <c r="AE312" s="12"/>
+      <c r="AC312" s="13"/>
+      <c r="AE312" s="13"/>
     </row>
     <row r="313">
-      <c r="AC313" s="12"/>
-      <c r="AE313" s="12"/>
+      <c r="AC313" s="13"/>
+      <c r="AE313" s="13"/>
     </row>
     <row r="314">
-      <c r="AC314" s="12"/>
-      <c r="AE314" s="12"/>
+      <c r="AC314" s="13"/>
+      <c r="AE314" s="13"/>
     </row>
     <row r="315">
-      <c r="AC315" s="12"/>
-      <c r="AE315" s="12"/>
+      <c r="AC315" s="13"/>
+      <c r="AE315" s="13"/>
     </row>
     <row r="316">
-      <c r="AC316" s="12"/>
-      <c r="AE316" s="12"/>
+      <c r="AC316" s="13"/>
+      <c r="AE316" s="13"/>
     </row>
     <row r="317">
-      <c r="AC317" s="12"/>
-      <c r="AE317" s="12"/>
+      <c r="AC317" s="13"/>
+      <c r="AE317" s="13"/>
     </row>
     <row r="318">
-      <c r="AC318" s="12"/>
-      <c r="AE318" s="12"/>
+      <c r="AC318" s="13"/>
+      <c r="AE318" s="13"/>
     </row>
     <row r="319">
-      <c r="AC319" s="12"/>
-      <c r="AE319" s="12"/>
+      <c r="AC319" s="13"/>
+      <c r="AE319" s="13"/>
     </row>
     <row r="320">
-      <c r="AC320" s="12"/>
-      <c r="AE320" s="12"/>
+      <c r="AC320" s="13"/>
+      <c r="AE320" s="13"/>
     </row>
     <row r="321">
-      <c r="AC321" s="12"/>
-      <c r="AE321" s="12"/>
+      <c r="AC321" s="13"/>
+      <c r="AE321" s="13"/>
     </row>
     <row r="322">
-      <c r="AC322" s="12"/>
-      <c r="AE322" s="12"/>
+      <c r="AC322" s="13"/>
+      <c r="AE322" s="13"/>
     </row>
     <row r="323">
-      <c r="AC323" s="12"/>
-      <c r="AE323" s="12"/>
+      <c r="AC323" s="13"/>
+      <c r="AE323" s="13"/>
     </row>
     <row r="324">
-      <c r="AC324" s="12"/>
-      <c r="AE324" s="12"/>
+      <c r="AC324" s="13"/>
+      <c r="AE324" s="13"/>
     </row>
     <row r="325">
-      <c r="AC325" s="12"/>
-      <c r="AE325" s="12"/>
+      <c r="AC325" s="13"/>
+      <c r="AE325" s="13"/>
     </row>
     <row r="326">
-      <c r="AC326" s="12"/>
-      <c r="AE326" s="12"/>
+      <c r="AC326" s="13"/>
+      <c r="AE326" s="13"/>
     </row>
     <row r="327">
-      <c r="AC327" s="12"/>
-      <c r="AE327" s="12"/>
+      <c r="AC327" s="13"/>
+      <c r="AE327" s="13"/>
     </row>
     <row r="328">
-      <c r="AC328" s="12"/>
-      <c r="AE328" s="12"/>
+      <c r="AC328" s="13"/>
+      <c r="AE328" s="13"/>
     </row>
     <row r="329">
-      <c r="AC329" s="12"/>
-      <c r="AE329" s="12"/>
+      <c r="AC329" s="13"/>
+      <c r="AE329" s="13"/>
     </row>
     <row r="330">
-      <c r="AC330" s="12"/>
-      <c r="AE330" s="12"/>
+      <c r="AC330" s="13"/>
+      <c r="AE330" s="13"/>
     </row>
     <row r="331">
-      <c r="AC331" s="12"/>
-      <c r="AE331" s="12"/>
+      <c r="AC331" s="13"/>
+      <c r="AE331" s="13"/>
     </row>
     <row r="332">
-      <c r="AC332" s="12"/>
-      <c r="AE332" s="12"/>
+      <c r="AC332" s="13"/>
+      <c r="AE332" s="13"/>
     </row>
     <row r="333">
-      <c r="AC333" s="12"/>
-      <c r="AE333" s="12"/>
+      <c r="AC333" s="13"/>
+      <c r="AE333" s="13"/>
     </row>
     <row r="334">
-      <c r="AC334" s="12"/>
-      <c r="AE334" s="12"/>
+      <c r="AC334" s="13"/>
+      <c r="AE334" s="13"/>
     </row>
     <row r="335">
-      <c r="AC335" s="12"/>
-      <c r="AE335" s="12"/>
+      <c r="AC335" s="13"/>
+      <c r="AE335" s="13"/>
     </row>
     <row r="336">
-      <c r="AC336" s="12"/>
-      <c r="AE336" s="12"/>
+      <c r="AC336" s="13"/>
+      <c r="AE336" s="13"/>
     </row>
     <row r="337">
-      <c r="AC337" s="12"/>
-      <c r="AE337" s="12"/>
+      <c r="AC337" s="13"/>
+      <c r="AE337" s="13"/>
     </row>
     <row r="338">
-      <c r="AC338" s="12"/>
-      <c r="AE338" s="12"/>
+      <c r="AC338" s="13"/>
+      <c r="AE338" s="13"/>
     </row>
     <row r="339">
-      <c r="AC339" s="12"/>
-      <c r="AE339" s="12"/>
+      <c r="AC339" s="13"/>
+      <c r="AE339" s="13"/>
     </row>
     <row r="340">
-      <c r="AC340" s="12"/>
-      <c r="AE340" s="12"/>
+      <c r="AC340" s="13"/>
+      <c r="AE340" s="13"/>
     </row>
     <row r="341">
-      <c r="AC341" s="12"/>
-      <c r="AE341" s="12"/>
+      <c r="AC341" s="13"/>
+      <c r="AE341" s="13"/>
     </row>
     <row r="342">
-      <c r="AC342" s="12"/>
-      <c r="AE342" s="12"/>
+      <c r="AC342" s="13"/>
+      <c r="AE342" s="13"/>
     </row>
     <row r="343">
-      <c r="AC343" s="12"/>
-      <c r="AE343" s="12"/>
+      <c r="AC343" s="13"/>
+      <c r="AE343" s="13"/>
     </row>
     <row r="344">
-      <c r="AC344" s="12"/>
-      <c r="AE344" s="12"/>
+      <c r="AC344" s="13"/>
+      <c r="AE344" s="13"/>
     </row>
     <row r="345">
-      <c r="AC345" s="12"/>
-      <c r="AE345" s="12"/>
+      <c r="AC345" s="13"/>
+      <c r="AE345" s="13"/>
     </row>
     <row r="346">
-      <c r="AC346" s="12"/>
-      <c r="AE346" s="12"/>
+      <c r="AC346" s="13"/>
+      <c r="AE346" s="13"/>
     </row>
     <row r="347">
-      <c r="AC347" s="12"/>
-      <c r="AE347" s="12"/>
+      <c r="AC347" s="13"/>
+      <c r="AE347" s="13"/>
     </row>
     <row r="348">
-      <c r="AC348" s="12"/>
-      <c r="AE348" s="12"/>
+      <c r="AC348" s="13"/>
+      <c r="AE348" s="13"/>
     </row>
     <row r="349">
-      <c r="AC349" s="12"/>
-      <c r="AE349" s="12"/>
+      <c r="AC349" s="13"/>
+      <c r="AE349" s="13"/>
     </row>
     <row r="350">
-      <c r="AC350" s="12"/>
-      <c r="AE350" s="12"/>
+      <c r="AC350" s="13"/>
+      <c r="AE350" s="13"/>
     </row>
     <row r="351">
-      <c r="AC351" s="12"/>
-      <c r="AE351" s="12"/>
+      <c r="AC351" s="13"/>
+      <c r="AE351" s="13"/>
     </row>
     <row r="352">
-      <c r="AC352" s="12"/>
-      <c r="AE352" s="12"/>
+      <c r="AC352" s="13"/>
+      <c r="AE352" s="13"/>
     </row>
     <row r="353">
-      <c r="AC353" s="12"/>
-      <c r="AE353" s="12"/>
+      <c r="AC353" s="13"/>
+      <c r="AE353" s="13"/>
     </row>
     <row r="354">
-      <c r="AC354" s="12"/>
-      <c r="AE354" s="12"/>
+      <c r="AC354" s="13"/>
+      <c r="AE354" s="13"/>
     </row>
     <row r="355">
-      <c r="AC355" s="12"/>
-      <c r="AE355" s="12"/>
+      <c r="AC355" s="13"/>
+      <c r="AE355" s="13"/>
     </row>
     <row r="356">
-      <c r="AC356" s="12"/>
-      <c r="AE356" s="12"/>
+      <c r="AC356" s="13"/>
+      <c r="AE356" s="13"/>
     </row>
     <row r="357">
-      <c r="AC357" s="12"/>
-      <c r="AE357" s="12"/>
+      <c r="AC357" s="13"/>
+      <c r="AE357" s="13"/>
     </row>
     <row r="358">
-      <c r="AC358" s="12"/>
-      <c r="AE358" s="12"/>
+      <c r="AC358" s="13"/>
+      <c r="AE358" s="13"/>
     </row>
     <row r="359">
-      <c r="AC359" s="12"/>
-      <c r="AE359" s="12"/>
+      <c r="AC359" s="13"/>
+      <c r="AE359" s="13"/>
     </row>
     <row r="360">
-      <c r="AC360" s="12"/>
-      <c r="AE360" s="12"/>
+      <c r="AC360" s="13"/>
+      <c r="AE360" s="13"/>
     </row>
     <row r="361">
-      <c r="AC361" s="12"/>
-      <c r="AE361" s="12"/>
+      <c r="AC361" s="13"/>
+      <c r="AE361" s="13"/>
     </row>
     <row r="362">
-      <c r="AC362" s="12"/>
-      <c r="AE362" s="12"/>
+      <c r="AC362" s="13"/>
+      <c r="AE362" s="13"/>
     </row>
     <row r="363">
-      <c r="AC363" s="12"/>
-      <c r="AE363" s="12"/>
+      <c r="AC363" s="13"/>
+      <c r="AE363" s="13"/>
     </row>
     <row r="364">
-      <c r="AC364" s="12"/>
-      <c r="AE364" s="12"/>
+      <c r="AC364" s="13"/>
+      <c r="AE364" s="13"/>
     </row>
     <row r="365">
-      <c r="AC365" s="12"/>
-      <c r="AE365" s="12"/>
+      <c r="AC365" s="13"/>
+      <c r="AE365" s="13"/>
     </row>
     <row r="366">
-      <c r="AC366" s="12"/>
-      <c r="AE366" s="12"/>
+      <c r="AC366" s="13"/>
+      <c r="AE366" s="13"/>
     </row>
     <row r="367">
-      <c r="AC367" s="12"/>
-      <c r="AE367" s="12"/>
+      <c r="AC367" s="13"/>
+      <c r="AE367" s="13"/>
     </row>
     <row r="368">
-      <c r="AC368" s="12"/>
-      <c r="AE368" s="12"/>
+      <c r="AC368" s="13"/>
+      <c r="AE368" s="13"/>
     </row>
     <row r="369">
-      <c r="AC369" s="12"/>
-      <c r="AE369" s="12"/>
+      <c r="AC369" s="13"/>
+      <c r="AE369" s="13"/>
     </row>
     <row r="370">
-      <c r="AC370" s="12"/>
-      <c r="AE370" s="12"/>
+      <c r="AC370" s="13"/>
+      <c r="AE370" s="13"/>
     </row>
     <row r="371">
-      <c r="AC371" s="12"/>
-      <c r="AE371" s="12"/>
+      <c r="AC371" s="13"/>
+      <c r="AE371" s="13"/>
     </row>
     <row r="372">
-      <c r="AC372" s="12"/>
-      <c r="AE372" s="12"/>
+      <c r="AC372" s="13"/>
+      <c r="AE372" s="13"/>
     </row>
     <row r="373">
-      <c r="AC373" s="12"/>
-      <c r="AE373" s="12"/>
+      <c r="AC373" s="13"/>
+      <c r="AE373" s="13"/>
     </row>
     <row r="374">
-      <c r="AC374" s="12"/>
-      <c r="AE374" s="12"/>
+      <c r="AC374" s="13"/>
+      <c r="AE374" s="13"/>
     </row>
     <row r="375">
-      <c r="AC375" s="12"/>
-      <c r="AE375" s="12"/>
+      <c r="AC375" s="13"/>
+      <c r="AE375" s="13"/>
     </row>
     <row r="376">
-      <c r="AC376" s="12"/>
-      <c r="AE376" s="12"/>
+      <c r="AC376" s="13"/>
+      <c r="AE376" s="13"/>
     </row>
     <row r="377">
-      <c r="AC377" s="12"/>
-      <c r="AE377" s="12"/>
+      <c r="AC377" s="13"/>
+      <c r="AE377" s="13"/>
     </row>
     <row r="378">
-      <c r="AC378" s="12"/>
-      <c r="AE378" s="12"/>
+      <c r="AC378" s="13"/>
+      <c r="AE378" s="13"/>
     </row>
     <row r="379">
-      <c r="AC379" s="12"/>
-      <c r="AE379" s="12"/>
+      <c r="AC379" s="13"/>
+      <c r="AE379" s="13"/>
     </row>
     <row r="380">
-      <c r="AC380" s="12"/>
-      <c r="AE380" s="12"/>
+      <c r="AC380" s="13"/>
+      <c r="AE380" s="13"/>
     </row>
     <row r="381">
-      <c r="AC381" s="12"/>
-      <c r="AE381" s="12"/>
+      <c r="AC381" s="13"/>
+      <c r="AE381" s="13"/>
     </row>
     <row r="382">
-      <c r="AC382" s="12"/>
-      <c r="AE382" s="12"/>
+      <c r="AC382" s="13"/>
+      <c r="AE382" s="13"/>
     </row>
     <row r="383">
-      <c r="AC383" s="12"/>
-      <c r="AE383" s="12"/>
+      <c r="AC383" s="13"/>
+      <c r="AE383" s="13"/>
     </row>
     <row r="384">
-      <c r="AC384" s="12"/>
-      <c r="AE384" s="12"/>
+      <c r="AC384" s="13"/>
+      <c r="AE384" s="13"/>
     </row>
     <row r="385">
-      <c r="AC385" s="12"/>
-      <c r="AE385" s="12"/>
+      <c r="AC385" s="13"/>
+      <c r="AE385" s="13"/>
     </row>
     <row r="386">
-      <c r="AC386" s="12"/>
-      <c r="AE386" s="12"/>
+      <c r="AC386" s="13"/>
+      <c r="AE386" s="13"/>
     </row>
     <row r="387">
-      <c r="AC387" s="12"/>
-      <c r="AE387" s="12"/>
+      <c r="AC387" s="13"/>
+      <c r="AE387" s="13"/>
     </row>
     <row r="388">
-      <c r="AC388" s="12"/>
-      <c r="AE388" s="12"/>
+      <c r="AC388" s="13"/>
+      <c r="AE388" s="13"/>
     </row>
     <row r="389">
-      <c r="AC389" s="12"/>
-      <c r="AE389" s="12"/>
+      <c r="AC389" s="13"/>
+      <c r="AE389" s="13"/>
     </row>
     <row r="390">
-      <c r="AC390" s="12"/>
-      <c r="AE390" s="12"/>
+      <c r="AC390" s="13"/>
+      <c r="AE390" s="13"/>
     </row>
     <row r="391">
-      <c r="AC391" s="12"/>
-      <c r="AE391" s="12"/>
+      <c r="AC391" s="13"/>
+      <c r="AE391" s="13"/>
     </row>
     <row r="392">
-      <c r="AC392" s="12"/>
-      <c r="AE392" s="12"/>
+      <c r="AC392" s="13"/>
+      <c r="AE392" s="13"/>
     </row>
     <row r="393">
-      <c r="AC393" s="12"/>
-      <c r="AE393" s="12"/>
+      <c r="AC393" s="13"/>
+      <c r="AE393" s="13"/>
     </row>
     <row r="394">
-      <c r="AC394" s="12"/>
-      <c r="AE394" s="12"/>
+      <c r="AC394" s="13"/>
+      <c r="AE394" s="13"/>
     </row>
     <row r="395">
-      <c r="AC395" s="12"/>
-      <c r="AE395" s="12"/>
+      <c r="AC395" s="13"/>
+      <c r="AE395" s="13"/>
     </row>
     <row r="396">
-      <c r="AC396" s="12"/>
-      <c r="AE396" s="12"/>
+      <c r="AC396" s="13"/>
+      <c r="AE396" s="13"/>
     </row>
     <row r="397">
-      <c r="AC397" s="12"/>
-      <c r="AE397" s="12"/>
+      <c r="AC397" s="13"/>
+      <c r="AE397" s="13"/>
     </row>
     <row r="398">
-      <c r="AC398" s="12"/>
-      <c r="AE398" s="12"/>
+      <c r="AC398" s="13"/>
+      <c r="AE398" s="13"/>
     </row>
     <row r="399">
-      <c r="AC399" s="12"/>
-      <c r="AE399" s="12"/>
+      <c r="AC399" s="13"/>
+      <c r="AE399" s="13"/>
     </row>
     <row r="400">
-      <c r="AC400" s="12"/>
-      <c r="AE400" s="12"/>
+      <c r="AC400" s="13"/>
+      <c r="AE400" s="13"/>
     </row>
     <row r="401">
-      <c r="AC401" s="12"/>
-      <c r="AE401" s="12"/>
+      <c r="AC401" s="13"/>
+      <c r="AE401" s="13"/>
     </row>
     <row r="402">
-      <c r="AC402" s="12"/>
-      <c r="AE402" s="12"/>
+      <c r="AC402" s="13"/>
+      <c r="AE402" s="13"/>
     </row>
     <row r="403">
-      <c r="AC403" s="12"/>
-      <c r="AE403" s="12"/>
+      <c r="AC403" s="13"/>
+      <c r="AE403" s="13"/>
     </row>
     <row r="404">
-      <c r="AC404" s="12"/>
-      <c r="AE404" s="12"/>
+      <c r="AC404" s="13"/>
+      <c r="AE404" s="13"/>
     </row>
     <row r="405">
-      <c r="AC405" s="12"/>
-      <c r="AE405" s="12"/>
+      <c r="AC405" s="13"/>
+      <c r="AE405" s="13"/>
     </row>
     <row r="406">
-      <c r="AC406" s="12"/>
-      <c r="AE406" s="12"/>
+      <c r="AC406" s="13"/>
+      <c r="AE406" s="13"/>
     </row>
     <row r="407">
-      <c r="AC407" s="12"/>
-      <c r="AE407" s="12"/>
+      <c r="AC407" s="13"/>
+      <c r="AE407" s="13"/>
     </row>
     <row r="408">
-      <c r="AC408" s="12"/>
-      <c r="AE408" s="12"/>
+      <c r="AC408" s="13"/>
+      <c r="AE408" s="13"/>
     </row>
     <row r="409">
-      <c r="AC409" s="12"/>
-      <c r="AE409" s="12"/>
+      <c r="AC409" s="13"/>
+      <c r="AE409" s="13"/>
     </row>
     <row r="410">
-      <c r="AC410" s="12"/>
-      <c r="AE410" s="12"/>
+      <c r="AC410" s="13"/>
+      <c r="AE410" s="13"/>
     </row>
     <row r="411">
-      <c r="AC411" s="12"/>
-      <c r="AE411" s="12"/>
+      <c r="AC411" s="13"/>
+      <c r="AE411" s="13"/>
     </row>
     <row r="412">
-      <c r="AC412" s="12"/>
-      <c r="AE412" s="12"/>
+      <c r="AC412" s="13"/>
+      <c r="AE412" s="13"/>
     </row>
     <row r="413">
-      <c r="AC413" s="12"/>
-      <c r="AE413" s="12"/>
+      <c r="AC413" s="13"/>
+      <c r="AE413" s="13"/>
     </row>
     <row r="414">
-      <c r="AC414" s="12"/>
-      <c r="AE414" s="12"/>
+      <c r="AC414" s="13"/>
+      <c r="AE414" s="13"/>
     </row>
     <row r="415">
-      <c r="AC415" s="12"/>
-      <c r="AE415" s="12"/>
+      <c r="AC415" s="13"/>
+      <c r="AE415" s="13"/>
     </row>
     <row r="416">
-      <c r="AC416" s="12"/>
-      <c r="AE416" s="12"/>
+      <c r="AC416" s="13"/>
+      <c r="AE416" s="13"/>
     </row>
     <row r="417">
-      <c r="AC417" s="12"/>
-      <c r="AE417" s="12"/>
+      <c r="AC417" s="13"/>
+      <c r="AE417" s="13"/>
     </row>
     <row r="418">
-      <c r="AC418" s="12"/>
-      <c r="AE418" s="12"/>
+      <c r="AC418" s="13"/>
+      <c r="AE418" s="13"/>
     </row>
     <row r="419">
-      <c r="AC419" s="12"/>
-      <c r="AE419" s="12"/>
+      <c r="AC419" s="13"/>
+      <c r="AE419" s="13"/>
     </row>
     <row r="420">
-      <c r="AC420" s="12"/>
-      <c r="AE420" s="12"/>
+      <c r="AC420" s="13"/>
+      <c r="AE420" s="13"/>
     </row>
     <row r="421">
-      <c r="AC421" s="12"/>
-      <c r="AE421" s="12"/>
+      <c r="AC421" s="13"/>
+      <c r="AE421" s="13"/>
     </row>
     <row r="422">
-      <c r="AC422" s="12"/>
-      <c r="AE422" s="12"/>
+      <c r="AC422" s="13"/>
+      <c r="AE422" s="13"/>
     </row>
     <row r="423">
-      <c r="AC423" s="12"/>
-      <c r="AE423" s="12"/>
+      <c r="AC423" s="13"/>
+      <c r="AE423" s="13"/>
     </row>
     <row r="424">
-      <c r="AC424" s="12"/>
-      <c r="AE424" s="12"/>
+      <c r="AC424" s="13"/>
+      <c r="AE424" s="13"/>
     </row>
     <row r="425">
-      <c r="AC425" s="12"/>
-      <c r="AE425" s="12"/>
+      <c r="AC425" s="13"/>
+      <c r="AE425" s="13"/>
     </row>
     <row r="426">
-      <c r="AC426" s="12"/>
-      <c r="AE426" s="12"/>
+      <c r="AC426" s="13"/>
+      <c r="AE426" s="13"/>
     </row>
     <row r="427">
-      <c r="AC427" s="12"/>
-      <c r="AE427" s="12"/>
+      <c r="AC427" s="13"/>
+      <c r="AE427" s="13"/>
     </row>
     <row r="428">
-      <c r="AC428" s="12"/>
-      <c r="AE428" s="12"/>
+      <c r="AC428" s="13"/>
+      <c r="AE428" s="13"/>
     </row>
     <row r="429">
-      <c r="AC429" s="12"/>
-      <c r="AE429" s="12"/>
+      <c r="AC429" s="13"/>
+      <c r="AE429" s="13"/>
     </row>
     <row r="430">
-      <c r="AC430" s="12"/>
-      <c r="AE430" s="12"/>
+      <c r="AC430" s="13"/>
+      <c r="AE430" s="13"/>
     </row>
     <row r="431">
-      <c r="AC431" s="12"/>
-      <c r="AE431" s="12"/>
+      <c r="AC431" s="13"/>
+      <c r="AE431" s="13"/>
     </row>
     <row r="432">
-      <c r="AC432" s="12"/>
-      <c r="AE432" s="12"/>
+      <c r="AC432" s="13"/>
+      <c r="AE432" s="13"/>
     </row>
     <row r="433">
-      <c r="AC433" s="12"/>
-      <c r="AE433" s="12"/>
+      <c r="AC433" s="13"/>
+      <c r="AE433" s="13"/>
     </row>
     <row r="434">
-      <c r="AC434" s="12"/>
-      <c r="AE434" s="12"/>
+      <c r="AC434" s="13"/>
+      <c r="AE434" s="13"/>
     </row>
     <row r="435">
-      <c r="AC435" s="12"/>
-      <c r="AE435" s="12"/>
+      <c r="AC435" s="13"/>
+      <c r="AE435" s="13"/>
     </row>
     <row r="436">
-      <c r="AC436" s="12"/>
-      <c r="AE436" s="12"/>
+      <c r="AC436" s="13"/>
+      <c r="AE436" s="13"/>
     </row>
     <row r="437">
-      <c r="AC437" s="12"/>
-      <c r="AE437" s="12"/>
+      <c r="AC437" s="13"/>
+      <c r="AE437" s="13"/>
     </row>
     <row r="438">
-      <c r="AC438" s="12"/>
-      <c r="AE438" s="12"/>
+      <c r="AC438" s="13"/>
+      <c r="AE438" s="13"/>
     </row>
     <row r="439">
-      <c r="AC439" s="12"/>
-      <c r="AE439" s="12"/>
+      <c r="AC439" s="13"/>
+      <c r="AE439" s="13"/>
     </row>
     <row r="440">
-      <c r="AC440" s="12"/>
-      <c r="AE440" s="12"/>
+      <c r="AC440" s="13"/>
+      <c r="AE440" s="13"/>
     </row>
     <row r="441">
-      <c r="AC441" s="12"/>
-      <c r="AE441" s="12"/>
+      <c r="AC441" s="13"/>
+      <c r="AE441" s="13"/>
     </row>
     <row r="442">
-      <c r="AC442" s="12"/>
-      <c r="AE442" s="12"/>
+      <c r="AC442" s="13"/>
+      <c r="AE442" s="13"/>
     </row>
     <row r="443">
-      <c r="AC443" s="12"/>
-      <c r="AE443" s="12"/>
+      <c r="AC443" s="13"/>
+      <c r="AE443" s="13"/>
     </row>
     <row r="444">
-      <c r="AC444" s="12"/>
-      <c r="AE444" s="12"/>
+      <c r="AC444" s="13"/>
+      <c r="AE444" s="13"/>
     </row>
     <row r="445">
-      <c r="AC445" s="12"/>
-      <c r="AE445" s="12"/>
+      <c r="AC445" s="13"/>
+      <c r="AE445" s="13"/>
     </row>
     <row r="446">
-      <c r="AC446" s="12"/>
-      <c r="AE446" s="12"/>
+      <c r="AC446" s="13"/>
+      <c r="AE446" s="13"/>
     </row>
     <row r="447">
-      <c r="AC447" s="12"/>
-      <c r="AE447" s="12"/>
+      <c r="AC447" s="13"/>
+      <c r="AE447" s="13"/>
     </row>
     <row r="448">
-      <c r="AC448" s="12"/>
-      <c r="AE448" s="12"/>
+      <c r="AC448" s="13"/>
+      <c r="AE448" s="13"/>
     </row>
     <row r="449">
-      <c r="AC449" s="12"/>
-      <c r="AE449" s="12"/>
+      <c r="AC449" s="13"/>
+      <c r="AE449" s="13"/>
     </row>
     <row r="450">
-      <c r="AC450" s="12"/>
-      <c r="AE450" s="12"/>
+      <c r="AC450" s="13"/>
+      <c r="AE450" s="13"/>
     </row>
     <row r="451">
-      <c r="AC451" s="12"/>
-      <c r="AE451" s="12"/>
+      <c r="AC451" s="13"/>
+      <c r="AE451" s="13"/>
     </row>
     <row r="452">
-      <c r="AC452" s="12"/>
-      <c r="AE452" s="12"/>
+      <c r="AC452" s="13"/>
+      <c r="AE452" s="13"/>
     </row>
     <row r="453">
-      <c r="AC453" s="12"/>
-      <c r="AE453" s="12"/>
+      <c r="AC453" s="13"/>
+      <c r="AE453" s="13"/>
     </row>
     <row r="454">
-      <c r="AC454" s="12"/>
-      <c r="AE454" s="12"/>
+      <c r="AC454" s="13"/>
+      <c r="AE454" s="13"/>
     </row>
     <row r="455">
-      <c r="AC455" s="12"/>
-      <c r="AE455" s="12"/>
+      <c r="AC455" s="13"/>
+      <c r="AE455" s="13"/>
     </row>
     <row r="456">
-      <c r="AC456" s="12"/>
-      <c r="AE456" s="12"/>
+      <c r="AC456" s="13"/>
+      <c r="AE456" s="13"/>
     </row>
     <row r="457">
-      <c r="AC457" s="12"/>
-      <c r="AE457" s="12"/>
+      <c r="AC457" s="13"/>
+      <c r="AE457" s="13"/>
     </row>
     <row r="458">
-      <c r="AC458" s="12"/>
-      <c r="AE458" s="12"/>
+      <c r="AC458" s="13"/>
+      <c r="AE458" s="13"/>
     </row>
     <row r="459">
-      <c r="AC459" s="12"/>
-      <c r="AE459" s="12"/>
+      <c r="AC459" s="13"/>
+      <c r="AE459" s="13"/>
     </row>
     <row r="460">
-      <c r="AC460" s="12"/>
-      <c r="AE460" s="12"/>
+      <c r="AC460" s="13"/>
+      <c r="AE460" s="13"/>
     </row>
     <row r="461">
-      <c r="AC461" s="12"/>
-      <c r="AE461" s="12"/>
+      <c r="AC461" s="13"/>
+      <c r="AE461" s="13"/>
     </row>
     <row r="462">
-      <c r="AC462" s="12"/>
-      <c r="AE462" s="12"/>
+      <c r="AC462" s="13"/>
+      <c r="AE462" s="13"/>
     </row>
     <row r="463">
-      <c r="AC463" s="12"/>
-      <c r="AE463" s="12"/>
+      <c r="AC463" s="13"/>
+      <c r="AE463" s="13"/>
     </row>
     <row r="464">
-      <c r="AC464" s="12"/>
-      <c r="AE464" s="12"/>
+      <c r="AC464" s="13"/>
+      <c r="AE464" s="13"/>
     </row>
     <row r="465">
-      <c r="AC465" s="12"/>
-      <c r="AE465" s="12"/>
+      <c r="AC465" s="13"/>
+      <c r="AE465" s="13"/>
     </row>
     <row r="466">
-      <c r="AC466" s="12"/>
-      <c r="AE466" s="12"/>
+      <c r="AC466" s="13"/>
+      <c r="AE466" s="13"/>
     </row>
     <row r="467">
-      <c r="AC467" s="12"/>
-      <c r="AE467" s="12"/>
+      <c r="AC467" s="13"/>
+      <c r="AE467" s="13"/>
     </row>
     <row r="468">
-      <c r="AC468" s="12"/>
-      <c r="AE468" s="12"/>
+      <c r="AC468" s="13"/>
+      <c r="AE468" s="13"/>
     </row>
     <row r="469">
-      <c r="AC469" s="12"/>
-      <c r="AE469" s="12"/>
+      <c r="AC469" s="13"/>
+      <c r="AE469" s="13"/>
     </row>
     <row r="470">
-      <c r="AC470" s="12"/>
-      <c r="AE470" s="12"/>
+      <c r="AC470" s="13"/>
+      <c r="AE470" s="13"/>
     </row>
     <row r="471">
-      <c r="AC471" s="12"/>
-      <c r="AE471" s="12"/>
+      <c r="AC471" s="13"/>
+      <c r="AE471" s="13"/>
     </row>
     <row r="472">
-      <c r="AC472" s="12"/>
-      <c r="AE472" s="12"/>
+      <c r="AC472" s="13"/>
+      <c r="AE472" s="13"/>
     </row>
     <row r="473">
-      <c r="AC473" s="12"/>
-      <c r="AE473" s="12"/>
+      <c r="AC473" s="13"/>
+      <c r="AE473" s="13"/>
     </row>
     <row r="474">
-      <c r="AC474" s="12"/>
-      <c r="AE474" s="12"/>
+      <c r="AC474" s="13"/>
+      <c r="AE474" s="13"/>
     </row>
     <row r="475">
-      <c r="AC475" s="12"/>
-      <c r="AE475" s="12"/>
+      <c r="AC475" s="13"/>
+      <c r="AE475" s="13"/>
     </row>
     <row r="476">
-      <c r="AC476" s="12"/>
-      <c r="AE476" s="12"/>
+      <c r="AC476" s="13"/>
+      <c r="AE476" s="13"/>
     </row>
     <row r="477">
-      <c r="AC477" s="12"/>
-      <c r="AE477" s="12"/>
+      <c r="AC477" s="13"/>
+      <c r="AE477" s="13"/>
     </row>
     <row r="478">
-      <c r="AC478" s="12"/>
-      <c r="AE478" s="12"/>
+      <c r="AC478" s="13"/>
+      <c r="AE478" s="13"/>
     </row>
     <row r="479">
-      <c r="AC479" s="12"/>
-      <c r="AE479" s="12"/>
+      <c r="AC479" s="13"/>
+      <c r="AE479" s="13"/>
     </row>
     <row r="480">
-      <c r="AC480" s="12"/>
-      <c r="AE480" s="12"/>
+      <c r="AC480" s="13"/>
+      <c r="AE480" s="13"/>
     </row>
     <row r="481">
-      <c r="AC481" s="12"/>
-      <c r="AE481" s="12"/>
+      <c r="AC481" s="13"/>
+      <c r="AE481" s="13"/>
     </row>
     <row r="482">
-      <c r="AC482" s="12"/>
-      <c r="AE482" s="12"/>
+      <c r="AC482" s="13"/>
+      <c r="AE482" s="13"/>
     </row>
     <row r="483">
-      <c r="AC483" s="12"/>
-      <c r="AE483" s="12"/>
+      <c r="AC483" s="13"/>
+      <c r="AE483" s="13"/>
     </row>
     <row r="484">
-      <c r="AC484" s="12"/>
-      <c r="AE484" s="12"/>
+      <c r="AC484" s="13"/>
+      <c r="AE484" s="13"/>
     </row>
     <row r="485">
-      <c r="AC485" s="12"/>
-      <c r="AE485" s="12"/>
+      <c r="AC485" s="13"/>
+      <c r="AE485" s="13"/>
     </row>
     <row r="486">
-      <c r="AC486" s="12"/>
-      <c r="AE486" s="12"/>
+      <c r="AC486" s="13"/>
+      <c r="AE486" s="13"/>
     </row>
     <row r="487">
-      <c r="AC487" s="12"/>
-      <c r="AE487" s="12"/>
+      <c r="AC487" s="13"/>
+      <c r="AE487" s="13"/>
     </row>
     <row r="488">
-      <c r="AC488" s="12"/>
-      <c r="AE488" s="12"/>
+      <c r="AC488" s="13"/>
+      <c r="AE488" s="13"/>
     </row>
     <row r="489">
-      <c r="AC489" s="12"/>
-      <c r="AE489" s="12"/>
+      <c r="AC489" s="13"/>
+      <c r="AE489" s="13"/>
     </row>
     <row r="490">
-      <c r="AC490" s="12"/>
-      <c r="AE490" s="12"/>
+      <c r="AC490" s="13"/>
+      <c r="AE490" s="13"/>
     </row>
     <row r="491">
-      <c r="AC491" s="12"/>
-      <c r="AE491" s="12"/>
+      <c r="AC491" s="13"/>
+      <c r="AE491" s="13"/>
     </row>
     <row r="492">
-      <c r="AC492" s="12"/>
-      <c r="AE492" s="12"/>
+      <c r="AC492" s="13"/>
+      <c r="AE492" s="13"/>
     </row>
     <row r="493">
-      <c r="AC493" s="12"/>
-      <c r="AE493" s="12"/>
+      <c r="AC493" s="13"/>
+      <c r="AE493" s="13"/>
     </row>
     <row r="494">
-      <c r="AC494" s="12"/>
-      <c r="AE494" s="12"/>
+      <c r="AC494" s="13"/>
+      <c r="AE494" s="13"/>
     </row>
     <row r="495">
-      <c r="AC495" s="12"/>
-      <c r="AE495" s="12"/>
+      <c r="AC495" s="13"/>
+      <c r="AE495" s="13"/>
     </row>
     <row r="496">
-      <c r="AC496" s="12"/>
-      <c r="AE496" s="12"/>
+      <c r="AC496" s="13"/>
+      <c r="AE496" s="13"/>
     </row>
     <row r="497">
-      <c r="AC497" s="12"/>
-      <c r="AE497" s="12"/>
+      <c r="AC497" s="13"/>
+      <c r="AE497" s="13"/>
     </row>
     <row r="498">
-      <c r="AC498" s="12"/>
-      <c r="AE498" s="12"/>
+      <c r="AC498" s="13"/>
+      <c r="AE498" s="13"/>
     </row>
     <row r="499">
-      <c r="AC499" s="12"/>
-      <c r="AE499" s="12"/>
+      <c r="AC499" s="13"/>
+      <c r="AE499" s="13"/>
     </row>
     <row r="500">
-      <c r="AC500" s="12"/>
-      <c r="AE500" s="12"/>
+      <c r="AC500" s="13"/>
+      <c r="AE500" s="13"/>
     </row>
     <row r="501">
-      <c r="AC501" s="12"/>
-      <c r="AE501" s="12"/>
+      <c r="AC501" s="13"/>
+      <c r="AE501" s="13"/>
     </row>
     <row r="502">
-      <c r="AC502" s="12"/>
-      <c r="AE502" s="12"/>
+      <c r="AC502" s="13"/>
+      <c r="AE502" s="13"/>
     </row>
     <row r="503">
-      <c r="AC503" s="12"/>
-      <c r="AE503" s="12"/>
+      <c r="AC503" s="13"/>
+      <c r="AE503" s="13"/>
     </row>
     <row r="504">
-      <c r="AC504" s="12"/>
-      <c r="AE504" s="12"/>
+      <c r="AC504" s="13"/>
+      <c r="AE504" s="13"/>
     </row>
     <row r="505">
-      <c r="AC505" s="12"/>
-      <c r="AE505" s="12"/>
+      <c r="AC505" s="13"/>
+      <c r="AE505" s="13"/>
     </row>
     <row r="506">
-      <c r="AC506" s="12"/>
-      <c r="AE506" s="12"/>
+      <c r="AC506" s="13"/>
+      <c r="AE506" s="13"/>
     </row>
     <row r="507">
-      <c r="AC507" s="12"/>
-      <c r="AE507" s="12"/>
+      <c r="AC507" s="13"/>
+      <c r="AE507" s="13"/>
     </row>
     <row r="508">
-      <c r="AC508" s="12"/>
-      <c r="AE508" s="12"/>
+      <c r="AC508" s="13"/>
+      <c r="AE508" s="13"/>
     </row>
     <row r="509">
-      <c r="AC509" s="12"/>
-      <c r="AE509" s="12"/>
+      <c r="AC509" s="13"/>
+      <c r="AE509" s="13"/>
     </row>
     <row r="510">
-      <c r="AC510" s="12"/>
-      <c r="AE510" s="12"/>
+      <c r="AC510" s="13"/>
+      <c r="AE510" s="13"/>
     </row>
     <row r="511">
-      <c r="AC511" s="12"/>
-      <c r="AE511" s="12"/>
+      <c r="AC511" s="13"/>
+      <c r="AE511" s="13"/>
     </row>
     <row r="512">
-      <c r="AC512" s="12"/>
-      <c r="AE512" s="12"/>
+      <c r="AC512" s="13"/>
+      <c r="AE512" s="13"/>
     </row>
     <row r="513">
-      <c r="AC513" s="12"/>
-      <c r="AE513" s="12"/>
+      <c r="AC513" s="13"/>
+      <c r="AE513" s="13"/>
     </row>
     <row r="514">
-      <c r="AC514" s="12"/>
-      <c r="AE514" s="12"/>
+      <c r="AC514" s="13"/>
+      <c r="AE514" s="13"/>
     </row>
     <row r="515">
-      <c r="AC515" s="12"/>
-      <c r="AE515" s="12"/>
+      <c r="AC515" s="13"/>
+      <c r="AE515" s="13"/>
     </row>
     <row r="516">
-      <c r="AC516" s="12"/>
-      <c r="AE516" s="12"/>
+      <c r="AC516" s="13"/>
+      <c r="AE516" s="13"/>
     </row>
     <row r="517">
-      <c r="AC517" s="12"/>
-      <c r="AE517" s="12"/>
+      <c r="AC517" s="13"/>
+      <c r="AE517" s="13"/>
     </row>
     <row r="518">
-      <c r="AC518" s="12"/>
-      <c r="AE518" s="12"/>
+      <c r="AC518" s="13"/>
+      <c r="AE518" s="13"/>
     </row>
     <row r="519">
-      <c r="AC519" s="12"/>
-      <c r="AE519" s="12"/>
+      <c r="AC519" s="13"/>
+      <c r="AE519" s="13"/>
     </row>
     <row r="520">
-      <c r="AC520" s="12"/>
-      <c r="AE520" s="12"/>
+      <c r="AC520" s="13"/>
+      <c r="AE520" s="13"/>
     </row>
     <row r="521">
-      <c r="AC521" s="12"/>
-      <c r="AE521" s="12"/>
+      <c r="AC521" s="13"/>
+      <c r="AE521" s="13"/>
     </row>
     <row r="522">
-      <c r="AC522" s="12"/>
-      <c r="AE522" s="12"/>
+      <c r="AC522" s="13"/>
+      <c r="AE522" s="13"/>
     </row>
     <row r="523">
-      <c r="AC523" s="12"/>
-      <c r="AE523" s="12"/>
+      <c r="AC523" s="13"/>
+      <c r="AE523" s="13"/>
     </row>
     <row r="524">
-      <c r="AC524" s="12"/>
-      <c r="AE524" s="12"/>
+      <c r="AC524" s="13"/>
+      <c r="AE524" s="13"/>
     </row>
     <row r="525">
-      <c r="AC525" s="12"/>
-      <c r="AE525" s="12"/>
+      <c r="AC525" s="13"/>
+      <c r="AE525" s="13"/>
     </row>
     <row r="526">
-      <c r="AC526" s="12"/>
-      <c r="AE526" s="12"/>
+      <c r="AC526" s="13"/>
+      <c r="AE526" s="13"/>
     </row>
     <row r="527">
-      <c r="AC527" s="12"/>
-      <c r="AE527" s="12"/>
+      <c r="AC527" s="13"/>
+      <c r="AE527" s="13"/>
     </row>
     <row r="528">
-      <c r="AC528" s="12"/>
-      <c r="AE528" s="12"/>
+      <c r="AC528" s="13"/>
+      <c r="AE528" s="13"/>
     </row>
     <row r="529">
-      <c r="AC529" s="12"/>
-      <c r="AE529" s="12"/>
+      <c r="AC529" s="13"/>
+      <c r="AE529" s="13"/>
     </row>
     <row r="530">
-      <c r="AC530" s="12"/>
-      <c r="AE530" s="12"/>
+      <c r="AC530" s="13"/>
+      <c r="AE530" s="13"/>
     </row>
     <row r="531">
-      <c r="AC531" s="12"/>
-      <c r="AE531" s="12"/>
+      <c r="AC531" s="13"/>
+      <c r="AE531" s="13"/>
     </row>
     <row r="532">
-      <c r="AC532" s="12"/>
-      <c r="AE532" s="12"/>
+      <c r="AC532" s="13"/>
+      <c r="AE532" s="13"/>
     </row>
     <row r="533">
-      <c r="AC533" s="12"/>
-      <c r="AE533" s="12"/>
+      <c r="AC533" s="13"/>
+      <c r="AE533" s="13"/>
     </row>
     <row r="534">
-      <c r="AC534" s="12"/>
-      <c r="AE534" s="12"/>
+      <c r="AC534" s="13"/>
+      <c r="AE534" s="13"/>
     </row>
     <row r="535">
-      <c r="AC535" s="12"/>
-      <c r="AE535" s="12"/>
+      <c r="AC535" s="13"/>
+      <c r="AE535" s="13"/>
     </row>
     <row r="536">
-      <c r="AC536" s="12"/>
-      <c r="AE536" s="12"/>
+      <c r="AC536" s="13"/>
+      <c r="AE536" s="13"/>
     </row>
     <row r="537">
-      <c r="AC537" s="12"/>
-      <c r="AE537" s="12"/>
+      <c r="AC537" s="13"/>
+      <c r="AE537" s="13"/>
     </row>
     <row r="538">
-      <c r="AC538" s="12"/>
-      <c r="AE538" s="12"/>
+      <c r="AC538" s="13"/>
+      <c r="AE538" s="13"/>
     </row>
     <row r="539">
-      <c r="AC539" s="12"/>
-      <c r="AE539" s="12"/>
+      <c r="AC539" s="13"/>
+      <c r="AE539" s="13"/>
     </row>
     <row r="540">
-      <c r="AC540" s="12"/>
-      <c r="AE540" s="12"/>
+      <c r="AC540" s="13"/>
+      <c r="AE540" s="13"/>
     </row>
     <row r="541">
-      <c r="AC541" s="12"/>
-      <c r="AE541" s="12"/>
+      <c r="AC541" s="13"/>
+      <c r="AE541" s="13"/>
     </row>
     <row r="542">
-      <c r="AC542" s="12"/>
-      <c r="AE542" s="12"/>
+      <c r="AC542" s="13"/>
+      <c r="AE542" s="13"/>
     </row>
     <row r="543">
-      <c r="AC543" s="12"/>
-      <c r="AE543" s="12"/>
+      <c r="AC543" s="13"/>
+      <c r="AE543" s="13"/>
     </row>
     <row r="544">
-      <c r="AC544" s="12"/>
-      <c r="AE544" s="12"/>
+      <c r="AC544" s="13"/>
+      <c r="AE544" s="13"/>
     </row>
     <row r="545">
-      <c r="AC545" s="12"/>
-      <c r="AE545" s="12"/>
+      <c r="AC545" s="13"/>
+      <c r="AE545" s="13"/>
     </row>
     <row r="546">
-      <c r="AC546" s="12"/>
-      <c r="AE546" s="12"/>
+      <c r="AC546" s="13"/>
+      <c r="AE546" s="13"/>
     </row>
     <row r="547">
-      <c r="AC547" s="12"/>
-      <c r="AE547" s="12"/>
+      <c r="AC547" s="13"/>
+      <c r="AE547" s="13"/>
     </row>
     <row r="548">
-      <c r="AC548" s="12"/>
-      <c r="AE548" s="12"/>
+      <c r="AC548" s="13"/>
+      <c r="AE548" s="13"/>
     </row>
     <row r="549">
-      <c r="AC549" s="12"/>
-      <c r="AE549" s="12"/>
+      <c r="AC549" s="13"/>
+      <c r="AE549" s="13"/>
     </row>
     <row r="550">
-      <c r="AC550" s="12"/>
-      <c r="AE550" s="12"/>
+      <c r="AC550" s="13"/>
+      <c r="AE550" s="13"/>
     </row>
     <row r="551">
-      <c r="AC551" s="12"/>
-      <c r="AE551" s="12"/>
+      <c r="AC551" s="13"/>
+      <c r="AE551" s="13"/>
     </row>
     <row r="552">
-      <c r="AC552" s="12"/>
-      <c r="AE552" s="12"/>
+      <c r="AC552" s="13"/>
+      <c r="AE552" s="13"/>
     </row>
     <row r="553">
-      <c r="AC553" s="12"/>
-      <c r="AE553" s="12"/>
+      <c r="AC553" s="13"/>
+      <c r="AE553" s="13"/>
     </row>
     <row r="554">
-      <c r="AC554" s="12"/>
-      <c r="AE554" s="12"/>
+      <c r="AC554" s="13"/>
+      <c r="AE554" s="13"/>
     </row>
     <row r="555">
-      <c r="AC555" s="12"/>
-      <c r="AE555" s="12"/>
+      <c r="AC555" s="13"/>
+      <c r="AE555" s="13"/>
     </row>
     <row r="556">
-      <c r="AC556" s="12"/>
-      <c r="AE556" s="12"/>
+      <c r="AC556" s="13"/>
+      <c r="AE556" s="13"/>
     </row>
     <row r="557">
-      <c r="AC557" s="12"/>
-      <c r="AE557" s="12"/>
+      <c r="AC557" s="13"/>
+      <c r="AE557" s="13"/>
     </row>
     <row r="558">
-      <c r="AC558" s="12"/>
-      <c r="AE558" s="12"/>
+      <c r="AC558" s="13"/>
+      <c r="AE558" s="13"/>
     </row>
     <row r="559">
-      <c r="AC559" s="12"/>
-      <c r="AE559" s="12"/>
+      <c r="AC559" s="13"/>
+      <c r="AE559" s="13"/>
     </row>
     <row r="560">
-      <c r="AC560" s="12"/>
-      <c r="AE560" s="12"/>
+      <c r="AC560" s="13"/>
+      <c r="AE560" s="13"/>
     </row>
     <row r="561">
-      <c r="AC561" s="12"/>
-      <c r="AE561" s="12"/>
+      <c r="AC561" s="13"/>
+      <c r="AE561" s="13"/>
     </row>
     <row r="562">
-      <c r="AC562" s="12"/>
-      <c r="AE562" s="12"/>
+      <c r="AC562" s="13"/>
+      <c r="AE562" s="13"/>
     </row>
     <row r="563">
-      <c r="AC563" s="12"/>
-      <c r="AE563" s="12"/>
+      <c r="AC563" s="13"/>
+      <c r="AE563" s="13"/>
     </row>
     <row r="564">
-      <c r="AC564" s="12"/>
-      <c r="AE564" s="12"/>
+      <c r="AC564" s="13"/>
+      <c r="AE564" s="13"/>
     </row>
     <row r="565">
-      <c r="AC565" s="12"/>
-      <c r="AE565" s="12"/>
+      <c r="AC565" s="13"/>
+      <c r="AE565" s="13"/>
     </row>
     <row r="566">
-      <c r="AC566" s="12"/>
-      <c r="AE566" s="12"/>
+      <c r="AC566" s="13"/>
+      <c r="AE566" s="13"/>
     </row>
     <row r="567">
-      <c r="AC567" s="12"/>
-      <c r="AE567" s="12"/>
+      <c r="AC567" s="13"/>
+      <c r="AE567" s="13"/>
     </row>
     <row r="568">
-      <c r="AC568" s="12"/>
-      <c r="AE568" s="12"/>
+      <c r="AC568" s="13"/>
+      <c r="AE568" s="13"/>
     </row>
     <row r="569">
-      <c r="AC569" s="12"/>
-      <c r="AE569" s="12"/>
+      <c r="AC569" s="13"/>
+      <c r="AE569" s="13"/>
     </row>
     <row r="570">
-      <c r="AC570" s="12"/>
-      <c r="AE570" s="12"/>
+      <c r="AC570" s="13"/>
+      <c r="AE570" s="13"/>
     </row>
     <row r="571">
-      <c r="AC571" s="12"/>
-      <c r="AE571" s="12"/>
+      <c r="AC571" s="13"/>
+      <c r="AE571" s="13"/>
     </row>
     <row r="572">
-      <c r="AC572" s="12"/>
-      <c r="AE572" s="12"/>
+      <c r="AC572" s="13"/>
+      <c r="AE572" s="13"/>
     </row>
     <row r="573">
-      <c r="AC573" s="12"/>
-      <c r="AE573" s="12"/>
+      <c r="AC573" s="13"/>
+      <c r="AE573" s="13"/>
     </row>
     <row r="574">
-      <c r="AC574" s="12"/>
-      <c r="AE574" s="12"/>
+      <c r="AC574" s="13"/>
+      <c r="AE574" s="13"/>
     </row>
     <row r="575">
-      <c r="AC575" s="12"/>
-      <c r="AE575" s="12"/>
+      <c r="AC575" s="13"/>
+      <c r="AE575" s="13"/>
     </row>
     <row r="576">
-      <c r="AC576" s="12"/>
-      <c r="AE576" s="12"/>
+      <c r="AC576" s="13"/>
+      <c r="AE576" s="13"/>
     </row>
     <row r="577">
-      <c r="AC577" s="12"/>
-      <c r="AE577" s="12"/>
+      <c r="AC577" s="13"/>
+      <c r="AE577" s="13"/>
     </row>
     <row r="578">
-      <c r="AC578" s="12"/>
-      <c r="AE578" s="12"/>
+      <c r="AC578" s="13"/>
+      <c r="AE578" s="13"/>
     </row>
     <row r="579">
-      <c r="AC579" s="12"/>
-      <c r="AE579" s="12"/>
+      <c r="AC579" s="13"/>
+      <c r="AE579" s="13"/>
     </row>
     <row r="580">
-      <c r="AC580" s="12"/>
-      <c r="AE580" s="12"/>
+      <c r="AC580" s="13"/>
+      <c r="AE580" s="13"/>
     </row>
     <row r="581">
-      <c r="AC581" s="12"/>
-      <c r="AE581" s="12"/>
+      <c r="AC581" s="13"/>
+      <c r="AE581" s="13"/>
     </row>
     <row r="582">
-      <c r="AC582" s="12"/>
-      <c r="AE582" s="12"/>
+      <c r="AC582" s="13"/>
+      <c r="AE582" s="13"/>
     </row>
     <row r="583">
-      <c r="AC583" s="12"/>
-      <c r="AE583" s="12"/>
+      <c r="AC583" s="13"/>
+      <c r="AE583" s="13"/>
     </row>
     <row r="584">
-      <c r="AC584" s="12"/>
-      <c r="AE584" s="12"/>
+      <c r="AC584" s="13"/>
+      <c r="AE584" s="13"/>
     </row>
     <row r="585">
-      <c r="AC585" s="12"/>
-      <c r="AE585" s="12"/>
+      <c r="AC585" s="13"/>
+      <c r="AE585" s="13"/>
     </row>
     <row r="586">
-      <c r="AC586" s="12"/>
-      <c r="AE586" s="12"/>
+      <c r="AC586" s="13"/>
+      <c r="AE586" s="13"/>
     </row>
     <row r="587">
-      <c r="AC587" s="12"/>
-      <c r="AE587" s="12"/>
+      <c r="AC587" s="13"/>
+      <c r="AE587" s="13"/>
     </row>
     <row r="588">
-      <c r="AC588" s="12"/>
-      <c r="AE588" s="12"/>
+      <c r="AC588" s="13"/>
+      <c r="AE588" s="13"/>
     </row>
     <row r="589">
-      <c r="AC589" s="12"/>
-      <c r="AE589" s="12"/>
+      <c r="AC589" s="13"/>
+      <c r="AE589" s="13"/>
     </row>
     <row r="590">
-      <c r="AC590" s="12"/>
-      <c r="AE590" s="12"/>
+      <c r="AC590" s="13"/>
+      <c r="AE590" s="13"/>
     </row>
     <row r="591">
-      <c r="AC591" s="12"/>
-      <c r="AE591" s="12"/>
+      <c r="AC591" s="13"/>
+      <c r="AE591" s="13"/>
     </row>
     <row r="592">
-      <c r="AC592" s="12"/>
-      <c r="AE592" s="12"/>
+      <c r="AC592" s="13"/>
+      <c r="AE592" s="13"/>
     </row>
     <row r="593">
-      <c r="AC593" s="12"/>
-      <c r="AE593" s="12"/>
+      <c r="AC593" s="13"/>
+      <c r="AE593" s="13"/>
     </row>
     <row r="594">
-      <c r="AC594" s="12"/>
-      <c r="AE594" s="12"/>
+      <c r="AC594" s="13"/>
+      <c r="AE594" s="13"/>
     </row>
     <row r="595">
-      <c r="AC595" s="12"/>
-      <c r="AE595" s="12"/>
+      <c r="AC595" s="13"/>
+      <c r="AE595" s="13"/>
     </row>
     <row r="596">
-      <c r="AC596" s="12"/>
-      <c r="AE596" s="12"/>
+      <c r="AC596" s="13"/>
+      <c r="AE596" s="13"/>
     </row>
     <row r="597">
-      <c r="AC597" s="12"/>
-      <c r="AE597" s="12"/>
+      <c r="AC597" s="13"/>
+      <c r="AE597" s="13"/>
     </row>
     <row r="598">
-      <c r="AC598" s="12"/>
-      <c r="AE598" s="12"/>
+      <c r="AC598" s="13"/>
+      <c r="AE598" s="13"/>
     </row>
     <row r="599">
-      <c r="AC599" s="12"/>
-      <c r="AE599" s="12"/>
+      <c r="AC599" s="13"/>
+      <c r="AE599" s="13"/>
     </row>
     <row r="600">
-      <c r="AC600" s="12"/>
-      <c r="AE600" s="12"/>
+      <c r="AC600" s="13"/>
+      <c r="AE600" s="13"/>
     </row>
     <row r="601">
-      <c r="AC601" s="12"/>
-      <c r="AE601" s="12"/>
+      <c r="AC601" s="13"/>
+      <c r="AE601" s="13"/>
     </row>
     <row r="602">
-      <c r="AC602" s="12"/>
-      <c r="AE602" s="12"/>
+      <c r="AC602" s="13"/>
+      <c r="AE602" s="13"/>
     </row>
     <row r="603">
-      <c r="AC603" s="12"/>
-      <c r="AE603" s="12"/>
+      <c r="AC603" s="13"/>
+      <c r="AE603" s="13"/>
     </row>
     <row r="604">
-      <c r="AC604" s="12"/>
-      <c r="AE604" s="12"/>
+      <c r="AC604" s="13"/>
+      <c r="AE604" s="13"/>
     </row>
     <row r="605">
-      <c r="AC605" s="12"/>
-      <c r="AE605" s="12"/>
+      <c r="AC605" s="13"/>
+      <c r="AE605" s="13"/>
     </row>
     <row r="606">
-      <c r="AC606" s="12"/>
-      <c r="AE606" s="12"/>
+      <c r="AC606" s="13"/>
+      <c r="AE606" s="13"/>
     </row>
     <row r="607">
-      <c r="AC607" s="12"/>
-      <c r="AE607" s="12"/>
+      <c r="AC607" s="13"/>
+      <c r="AE607" s="13"/>
     </row>
     <row r="608">
-      <c r="AC608" s="12"/>
-      <c r="AE608" s="12"/>
+      <c r="AC608" s="13"/>
+      <c r="AE608" s="13"/>
     </row>
     <row r="609">
-      <c r="AC609" s="12"/>
-      <c r="AE609" s="12"/>
+      <c r="AC609" s="13"/>
+      <c r="AE609" s="13"/>
     </row>
     <row r="610">
-      <c r="AC610" s="12"/>
-      <c r="AE610" s="12"/>
+      <c r="AC610" s="13"/>
+      <c r="AE610" s="13"/>
     </row>
     <row r="611">
-      <c r="AC611" s="12"/>
-      <c r="AE611" s="12"/>
+      <c r="AC611" s="13"/>
+      <c r="AE611" s="13"/>
     </row>
     <row r="612">
-      <c r="AC612" s="12"/>
-      <c r="AE612" s="12"/>
+      <c r="AC612" s="13"/>
+      <c r="AE612" s="13"/>
     </row>
     <row r="613">
-      <c r="AC613" s="12"/>
-      <c r="AE613" s="12"/>
+      <c r="AC613" s="13"/>
+      <c r="AE613" s="13"/>
     </row>
     <row r="614">
-      <c r="AC614" s="12"/>
-      <c r="AE614" s="12"/>
+      <c r="AC614" s="13"/>
+      <c r="AE614" s="13"/>
     </row>
     <row r="615">
-      <c r="AC615" s="12"/>
-      <c r="AE615" s="12"/>
+      <c r="AC615" s="13"/>
+      <c r="AE615" s="13"/>
     </row>
     <row r="616">
-      <c r="AC616" s="12"/>
-      <c r="AE616" s="12"/>
+      <c r="AC616" s="13"/>
+      <c r="AE616" s="13"/>
     </row>
     <row r="617">
-      <c r="AC617" s="12"/>
-      <c r="AE617" s="12"/>
+      <c r="AC617" s="13"/>
+      <c r="AE617" s="13"/>
     </row>
     <row r="618">
-      <c r="AC618" s="12"/>
-      <c r="AE618" s="12"/>
+      <c r="AC618" s="13"/>
+      <c r="AE618" s="13"/>
     </row>
     <row r="619">
-      <c r="AC619" s="12"/>
-      <c r="AE619" s="12"/>
+      <c r="AC619" s="13"/>
+      <c r="AE619" s="13"/>
     </row>
     <row r="620">
-      <c r="AC620" s="12"/>
-      <c r="AE620" s="12"/>
+      <c r="AC620" s="13"/>
+      <c r="AE620" s="13"/>
     </row>
     <row r="621">
-      <c r="AC621" s="12"/>
-      <c r="AE621" s="12"/>
+      <c r="AC621" s="13"/>
+      <c r="AE621" s="13"/>
     </row>
     <row r="622">
-      <c r="AC622" s="12"/>
-      <c r="AE622" s="12"/>
+      <c r="AC622" s="13"/>
+      <c r="AE622" s="13"/>
     </row>
     <row r="623">
-      <c r="AC623" s="12"/>
-      <c r="AE623" s="12"/>
+      <c r="AC623" s="13"/>
+      <c r="AE623" s="13"/>
     </row>
     <row r="624">
-      <c r="AC624" s="12"/>
-      <c r="AE624" s="12"/>
+      <c r="AC624" s="13"/>
+      <c r="AE624" s="13"/>
     </row>
     <row r="625">
-      <c r="AC625" s="12"/>
-      <c r="AE625" s="12"/>
+      <c r="AC625" s="13"/>
+      <c r="AE625" s="13"/>
     </row>
     <row r="626">
-      <c r="AC626" s="12"/>
-      <c r="AE626" s="12"/>
+      <c r="AC626" s="13"/>
+      <c r="AE626" s="13"/>
     </row>
     <row r="627">
-      <c r="AC627" s="12"/>
-      <c r="AE627" s="12"/>
+      <c r="AC627" s="13"/>
+      <c r="AE627" s="13"/>
     </row>
     <row r="628">
-      <c r="AC628" s="12"/>
-      <c r="AE628" s="12"/>
+      <c r="AC628" s="13"/>
+      <c r="AE628" s="13"/>
     </row>
     <row r="629">
-      <c r="AC629" s="12"/>
-      <c r="AE629" s="12"/>
+      <c r="AC629" s="13"/>
+      <c r="AE629" s="13"/>
     </row>
     <row r="630">
-      <c r="AC630" s="12"/>
-      <c r="AE630" s="12"/>
+      <c r="AC630" s="13"/>
+      <c r="AE630" s="13"/>
     </row>
     <row r="631">
-      <c r="AC631" s="12"/>
-      <c r="AE631" s="12"/>
+      <c r="AC631" s="13"/>
+      <c r="AE631" s="13"/>
     </row>
     <row r="632">
-      <c r="AC632" s="12"/>
-      <c r="AE632" s="12"/>
+      <c r="AC632" s="13"/>
+      <c r="AE632" s="13"/>
     </row>
     <row r="633">
-      <c r="AC633" s="12"/>
-      <c r="AE633" s="12"/>
+      <c r="AC633" s="13"/>
+      <c r="AE633" s="13"/>
     </row>
     <row r="634">
-      <c r="AC634" s="12"/>
-      <c r="AE634" s="12"/>
+      <c r="AC634" s="13"/>
+      <c r="AE634" s="13"/>
     </row>
     <row r="635">
-      <c r="AC635" s="12"/>
-      <c r="AE635" s="12"/>
+      <c r="AC635" s="13"/>
+      <c r="AE635" s="13"/>
     </row>
     <row r="636">
-      <c r="AC636" s="12"/>
-      <c r="AE636" s="12"/>
+      <c r="AC636" s="13"/>
+      <c r="AE636" s="13"/>
     </row>
     <row r="637">
-      <c r="AC637" s="12"/>
-      <c r="AE637" s="12"/>
+      <c r="AC637" s="13"/>
+      <c r="AE637" s="13"/>
     </row>
     <row r="638">
-      <c r="AC638" s="12"/>
-      <c r="AE638" s="12"/>
+      <c r="AC638" s="13"/>
+      <c r="AE638" s="13"/>
     </row>
     <row r="639">
-      <c r="AC639" s="12"/>
-      <c r="AE639" s="12"/>
+      <c r="AC639" s="13"/>
+      <c r="AE639" s="13"/>
     </row>
     <row r="640">
-      <c r="AC640" s="12"/>
-      <c r="AE640" s="12"/>
+      <c r="AC640" s="13"/>
+      <c r="AE640" s="13"/>
     </row>
     <row r="641">
-      <c r="AC641" s="12"/>
-      <c r="AE641" s="12"/>
+      <c r="AC641" s="13"/>
+      <c r="AE641" s="13"/>
     </row>
     <row r="642">
-      <c r="AC642" s="12"/>
-      <c r="AE642" s="12"/>
+      <c r="AC642" s="13"/>
+      <c r="AE642" s="13"/>
     </row>
     <row r="643">
-      <c r="AC643" s="12"/>
-      <c r="AE643" s="12"/>
+      <c r="AC643" s="13"/>
+      <c r="AE643" s="13"/>
     </row>
     <row r="644">
-      <c r="AC644" s="12"/>
-      <c r="AE644" s="12"/>
+      <c r="AC644" s="13"/>
+      <c r="AE644" s="13"/>
     </row>
     <row r="645">
-      <c r="AC645" s="12"/>
-      <c r="AE645" s="12"/>
+      <c r="AC645" s="13"/>
+      <c r="AE645" s="13"/>
     </row>
     <row r="646">
-      <c r="AC646" s="12"/>
-      <c r="AE646" s="12"/>
+      <c r="AC646" s="13"/>
+      <c r="AE646" s="13"/>
     </row>
     <row r="647">
-      <c r="AC647" s="12"/>
-      <c r="AE647" s="12"/>
+      <c r="AC647" s="13"/>
+      <c r="AE647" s="13"/>
     </row>
     <row r="648">
-      <c r="AC648" s="12"/>
-      <c r="AE648" s="12"/>
+      <c r="AC648" s="13"/>
+      <c r="AE648" s="13"/>
     </row>
     <row r="649">
-      <c r="AC649" s="12"/>
-      <c r="AE649" s="12"/>
+      <c r="AC649" s="13"/>
+      <c r="AE649" s="13"/>
     </row>
     <row r="650">
-      <c r="AC650" s="12"/>
-      <c r="AE650" s="12"/>
+      <c r="AC650" s="13"/>
+      <c r="AE650" s="13"/>
     </row>
     <row r="651">
-      <c r="AC651" s="12"/>
-      <c r="AE651" s="12"/>
+      <c r="AC651" s="13"/>
+      <c r="AE651" s="13"/>
     </row>
     <row r="652">
-      <c r="AC652" s="12"/>
-      <c r="AE652" s="12"/>
+      <c r="AC652" s="13"/>
+      <c r="AE652" s="13"/>
     </row>
     <row r="653">
-      <c r="AC653" s="12"/>
-      <c r="AE653" s="12"/>
+      <c r="AC653" s="13"/>
+      <c r="AE653" s="13"/>
     </row>
     <row r="654">
-      <c r="AC654" s="12"/>
-      <c r="AE654" s="12"/>
+      <c r="AC654" s="13"/>
+      <c r="AE654" s="13"/>
     </row>
     <row r="655">
-      <c r="AC655" s="12"/>
-      <c r="AE655" s="12"/>
+      <c r="AC655" s="13"/>
+      <c r="AE655" s="13"/>
     </row>
     <row r="656">
-      <c r="AC656" s="12"/>
-      <c r="AE656" s="12"/>
+      <c r="AC656" s="13"/>
+      <c r="AE656" s="13"/>
     </row>
     <row r="657">
-      <c r="AC657" s="12"/>
-      <c r="AE657" s="12"/>
+      <c r="AC657" s="13"/>
+      <c r="AE657" s="13"/>
     </row>
     <row r="658">
-      <c r="AC658" s="12"/>
-      <c r="AE658" s="12"/>
+      <c r="AC658" s="13"/>
+      <c r="AE658" s="13"/>
     </row>
     <row r="659">
-      <c r="AC659" s="12"/>
-      <c r="AE659" s="12"/>
+      <c r="AC659" s="13"/>
+      <c r="AE659" s="13"/>
     </row>
     <row r="660">
-      <c r="AC660" s="12"/>
-      <c r="AE660" s="12"/>
+      <c r="AC660" s="13"/>
+      <c r="AE660" s="13"/>
     </row>
     <row r="661">
-      <c r="AC661" s="12"/>
-      <c r="AE661" s="12"/>
+      <c r="AC661" s="13"/>
+      <c r="AE661" s="13"/>
     </row>
     <row r="662">
-      <c r="AC662" s="12"/>
-      <c r="AE662" s="12"/>
+      <c r="AC662" s="13"/>
+      <c r="AE662" s="13"/>
     </row>
     <row r="663">
-      <c r="AC663" s="12"/>
-      <c r="AE663" s="12"/>
+      <c r="AC663" s="13"/>
+      <c r="AE663" s="13"/>
     </row>
     <row r="664">
-      <c r="AC664" s="12"/>
-      <c r="AE664" s="12"/>
+      <c r="AC664" s="13"/>
+      <c r="AE664" s="13"/>
     </row>
     <row r="665">
-      <c r="AC665" s="12"/>
-      <c r="AE665" s="12"/>
+      <c r="AC665" s="13"/>
+      <c r="AE665" s="13"/>
     </row>
     <row r="666">
-      <c r="AC666" s="12"/>
-      <c r="AE666" s="12"/>
+      <c r="AC666" s="13"/>
+      <c r="AE666" s="13"/>
     </row>
     <row r="667">
-      <c r="AC667" s="12"/>
-      <c r="AE667" s="12"/>
+      <c r="AC667" s="13"/>
+      <c r="AE667" s="13"/>
     </row>
     <row r="668">
-      <c r="AC668" s="12"/>
-      <c r="AE668" s="12"/>
+      <c r="AC668" s="13"/>
+      <c r="AE668" s="13"/>
     </row>
     <row r="669">
-      <c r="AC669" s="12"/>
-      <c r="AE669" s="12"/>
+      <c r="AC669" s="13"/>
+      <c r="AE669" s="13"/>
     </row>
     <row r="670">
-      <c r="AC670" s="12"/>
-      <c r="AE670" s="12"/>
+      <c r="AC670" s="13"/>
+      <c r="AE670" s="13"/>
     </row>
     <row r="671">
-      <c r="AC671" s="12"/>
-      <c r="AE671" s="12"/>
+      <c r="AC671" s="13"/>
+      <c r="AE671" s="13"/>
     </row>
     <row r="672">
-      <c r="AC672" s="12"/>
-      <c r="AE672" s="12"/>
+      <c r="AC672" s="13"/>
+      <c r="AE672" s="13"/>
     </row>
     <row r="673">
-      <c r="AC673" s="12"/>
-      <c r="AE673" s="12"/>
+      <c r="AC673" s="13"/>
+      <c r="AE673" s="13"/>
     </row>
     <row r="674">
-      <c r="AC674" s="12"/>
-      <c r="AE674" s="12"/>
+      <c r="AC674" s="13"/>
+      <c r="AE674" s="13"/>
     </row>
     <row r="675">
-      <c r="AC675" s="12"/>
-      <c r="AE675" s="12"/>
+      <c r="AC675" s="13"/>
+      <c r="AE675" s="13"/>
     </row>
     <row r="676">
-      <c r="AC676" s="12"/>
-      <c r="AE676" s="12"/>
+      <c r="AC676" s="13"/>
+      <c r="AE676" s="13"/>
     </row>
     <row r="677">
-      <c r="AC677" s="12"/>
-      <c r="AE677" s="12"/>
+      <c r="AC677" s="13"/>
+      <c r="AE677" s="13"/>
     </row>
     <row r="678">
-      <c r="AC678" s="12"/>
-      <c r="AE678" s="12"/>
+      <c r="AC678" s="13"/>
+      <c r="AE678" s="13"/>
     </row>
     <row r="679">
-      <c r="AC679" s="12"/>
-      <c r="AE679" s="12"/>
+      <c r="AC679" s="13"/>
+      <c r="AE679" s="13"/>
     </row>
     <row r="680">
-      <c r="AC680" s="12"/>
-      <c r="AE680" s="12"/>
+      <c r="AC680" s="13"/>
+      <c r="AE680" s="13"/>
     </row>
     <row r="681">
-      <c r="AC681" s="12"/>
-      <c r="AE681" s="12"/>
+      <c r="AC681" s="13"/>
+      <c r="AE681" s="13"/>
     </row>
     <row r="682">
-      <c r="AC682" s="12"/>
-      <c r="AE682" s="12"/>
+      <c r="AC682" s="13"/>
+      <c r="AE682" s="13"/>
     </row>
     <row r="683">
-      <c r="AC683" s="12"/>
-      <c r="AE683" s="12"/>
+      <c r="AC683" s="13"/>
+      <c r="AE683" s="13"/>
     </row>
     <row r="684">
-      <c r="AC684" s="12"/>
-      <c r="AE684" s="12"/>
+      <c r="AC684" s="13"/>
+      <c r="AE684" s="13"/>
     </row>
     <row r="685">
-      <c r="AC685" s="12"/>
-      <c r="AE685" s="12"/>
+      <c r="AC685" s="13"/>
+      <c r="AE685" s="13"/>
     </row>
     <row r="686">
-      <c r="AC686" s="12"/>
-      <c r="AE686" s="12"/>
+      <c r="AC686" s="13"/>
+      <c r="AE686" s="13"/>
     </row>
     <row r="687">
-      <c r="AC687" s="12"/>
-      <c r="AE687" s="12"/>
+      <c r="AC687" s="13"/>
+      <c r="AE687" s="13"/>
     </row>
     <row r="688">
-      <c r="AC688" s="12"/>
-      <c r="AE688" s="12"/>
+      <c r="AC688" s="13"/>
+      <c r="AE688" s="13"/>
     </row>
     <row r="689">
-      <c r="AC689" s="12"/>
-      <c r="AE689" s="12"/>
+      <c r="AC689" s="13"/>
+      <c r="AE689" s="13"/>
     </row>
     <row r="690">
-      <c r="AC690" s="12"/>
-      <c r="AE690" s="12"/>
+      <c r="AC690" s="13"/>
+      <c r="AE690" s="13"/>
     </row>
     <row r="691">
-      <c r="AC691" s="12"/>
-      <c r="AE691" s="12"/>
+      <c r="AC691" s="13"/>
+      <c r="AE691" s="13"/>
     </row>
     <row r="692">
-      <c r="AC692" s="12"/>
-      <c r="AE692" s="12"/>
+      <c r="AC692" s="13"/>
+      <c r="AE692" s="13"/>
     </row>
     <row r="693">
-      <c r="AC693" s="12"/>
-      <c r="AE693" s="12"/>
+      <c r="AC693" s="13"/>
+      <c r="AE693" s="13"/>
     </row>
     <row r="694">
-      <c r="AC694" s="12"/>
-      <c r="AE694" s="12"/>
+      <c r="AC694" s="13"/>
+      <c r="AE694" s="13"/>
     </row>
     <row r="695">
-      <c r="AC695" s="12"/>
-      <c r="AE695" s="12"/>
+      <c r="AC695" s="13"/>
+      <c r="AE695" s="13"/>
     </row>
     <row r="696">
-      <c r="AC696" s="12"/>
-      <c r="AE696" s="12"/>
+      <c r="AC696" s="13"/>
+      <c r="AE696" s="13"/>
     </row>
     <row r="697">
-      <c r="AC697" s="12"/>
-      <c r="AE697" s="12"/>
+      <c r="AC697" s="13"/>
+      <c r="AE697" s="13"/>
     </row>
     <row r="698">
-      <c r="AC698" s="12"/>
-      <c r="AE698" s="12"/>
+      <c r="AC698" s="13"/>
+      <c r="AE698" s="13"/>
     </row>
     <row r="699">
-      <c r="AC699" s="12"/>
-      <c r="AE699" s="12"/>
+      <c r="AC699" s="13"/>
+      <c r="AE699" s="13"/>
     </row>
     <row r="700">
-      <c r="AC700" s="12"/>
-      <c r="AE700" s="12"/>
+      <c r="AC700" s="13"/>
+      <c r="AE700" s="13"/>
     </row>
     <row r="701">
-      <c r="AC701" s="12"/>
-      <c r="AE701" s="12"/>
+      <c r="AC701" s="13"/>
+      <c r="AE701" s="13"/>
     </row>
     <row r="702">
-      <c r="AC702" s="12"/>
-      <c r="AE702" s="12"/>
+      <c r="AC702" s="13"/>
+      <c r="AE702" s="13"/>
     </row>
     <row r="703">
-      <c r="AC703" s="12"/>
-      <c r="AE703" s="12"/>
+      <c r="AC703" s="13"/>
+      <c r="AE703" s="13"/>
     </row>
     <row r="704">
-      <c r="AC704" s="12"/>
-      <c r="AE704" s="12"/>
+      <c r="AC704" s="13"/>
+      <c r="AE704" s="13"/>
     </row>
     <row r="705">
-      <c r="AC705" s="12"/>
-      <c r="AE705" s="12"/>
+      <c r="AC705" s="13"/>
+      <c r="AE705" s="13"/>
     </row>
     <row r="706">
-      <c r="AC706" s="12"/>
-      <c r="AE706" s="12"/>
+      <c r="AC706" s="13"/>
+      <c r="AE706" s="13"/>
     </row>
     <row r="707">
-      <c r="AC707" s="12"/>
-      <c r="AE707" s="12"/>
+      <c r="AC707" s="13"/>
+      <c r="AE707" s="13"/>
     </row>
     <row r="708">
-      <c r="AC708" s="12"/>
-      <c r="AE708" s="12"/>
+      <c r="AC708" s="13"/>
+      <c r="AE708" s="13"/>
     </row>
     <row r="709">
-      <c r="AC709" s="12"/>
-      <c r="AE709" s="12"/>
+      <c r="AC709" s="13"/>
+      <c r="AE709" s="13"/>
     </row>
     <row r="710">
-      <c r="AC710" s="12"/>
-      <c r="AE710" s="12"/>
+      <c r="AC710" s="13"/>
+      <c r="AE710" s="13"/>
     </row>
     <row r="711">
-      <c r="AC711" s="12"/>
-      <c r="AE711" s="12"/>
+      <c r="AC711" s="13"/>
+      <c r="AE711" s="13"/>
     </row>
     <row r="712">
-      <c r="AC712" s="12"/>
-      <c r="AE712" s="12"/>
+      <c r="AC712" s="13"/>
+      <c r="AE712" s="13"/>
     </row>
     <row r="713">
-      <c r="AC713" s="12"/>
-      <c r="AE713" s="12"/>
+      <c r="AC713" s="13"/>
+      <c r="AE713" s="13"/>
     </row>
     <row r="714">
-      <c r="AC714" s="12"/>
-      <c r="AE714" s="12"/>
+      <c r="AC714" s="13"/>
+      <c r="AE714" s="13"/>
     </row>
     <row r="715">
-      <c r="AC715" s="12"/>
-      <c r="AE715" s="12"/>
+      <c r="AC715" s="13"/>
+      <c r="AE715" s="13"/>
     </row>
     <row r="716">
-      <c r="AC716" s="12"/>
-      <c r="AE716" s="12"/>
+      <c r="AC716" s="13"/>
+      <c r="AE716" s="13"/>
     </row>
     <row r="717">
-      <c r="AC717" s="12"/>
-      <c r="AE717" s="12"/>
+      <c r="AC717" s="13"/>
+      <c r="AE717" s="13"/>
     </row>
     <row r="718">
-      <c r="AC718" s="12"/>
-      <c r="AE718" s="12"/>
+      <c r="AC718" s="13"/>
+      <c r="AE718" s="13"/>
     </row>
     <row r="719">
-      <c r="AC719" s="12"/>
-      <c r="AE719" s="12"/>
+      <c r="AC719" s="13"/>
+      <c r="AE719" s="13"/>
     </row>
     <row r="720">
-      <c r="AC720" s="12"/>
-      <c r="AE720" s="12"/>
+      <c r="AC720" s="13"/>
+      <c r="AE720" s="13"/>
     </row>
     <row r="721">
-      <c r="AC721" s="12"/>
-      <c r="AE721" s="12"/>
+      <c r="AC721" s="13"/>
+      <c r="AE721" s="13"/>
     </row>
     <row r="722">
-      <c r="AC722" s="12"/>
-      <c r="AE722" s="12"/>
+      <c r="AC722" s="13"/>
+      <c r="AE722" s="13"/>
     </row>
     <row r="723">
-      <c r="AC723" s="12"/>
-      <c r="AE723" s="12"/>
+      <c r="AC723" s="13"/>
+      <c r="AE723" s="13"/>
     </row>
     <row r="724">
-      <c r="AC724" s="12"/>
-      <c r="AE724" s="12"/>
+      <c r="AC724" s="13"/>
+      <c r="AE724" s="13"/>
     </row>
     <row r="725">
-      <c r="AC725" s="12"/>
-      <c r="AE725" s="12"/>
+      <c r="AC725" s="13"/>
+      <c r="AE725" s="13"/>
     </row>
     <row r="726">
-      <c r="AC726" s="12"/>
-      <c r="AE726" s="12"/>
+      <c r="AC726" s="13"/>
+      <c r="AE726" s="13"/>
     </row>
     <row r="727">
-      <c r="AC727" s="12"/>
-      <c r="AE727" s="12"/>
+      <c r="AC727" s="13"/>
+      <c r="AE727" s="13"/>
     </row>
     <row r="728">
-      <c r="AC728" s="12"/>
-      <c r="AE728" s="12"/>
+      <c r="AC728" s="13"/>
+      <c r="AE728" s="13"/>
     </row>
     <row r="729">
-      <c r="AC729" s="12"/>
-      <c r="AE729" s="12"/>
+      <c r="AC729" s="13"/>
+      <c r="AE729" s="13"/>
     </row>
     <row r="730">
-      <c r="AC730" s="12"/>
-      <c r="AE730" s="12"/>
+      <c r="AC730" s="13"/>
+      <c r="AE730" s="13"/>
     </row>
     <row r="731">
-      <c r="AC731" s="12"/>
-      <c r="AE731" s="12"/>
+      <c r="AC731" s="13"/>
+      <c r="AE731" s="13"/>
     </row>
     <row r="732">
-      <c r="AC732" s="12"/>
-      <c r="AE732" s="12"/>
+      <c r="AC732" s="13"/>
+      <c r="AE732" s="13"/>
     </row>
     <row r="733">
-      <c r="AC733" s="12"/>
-      <c r="AE733" s="12"/>
+      <c r="AC733" s="13"/>
+      <c r="AE733" s="13"/>
     </row>
     <row r="734">
-      <c r="AC734" s="12"/>
-      <c r="AE734" s="12"/>
+      <c r="AC734" s="13"/>
+      <c r="AE734" s="13"/>
     </row>
     <row r="735">
-      <c r="AC735" s="12"/>
-      <c r="AE735" s="12"/>
+      <c r="AC735" s="13"/>
+      <c r="AE735" s="13"/>
     </row>
     <row r="736">
-      <c r="AC736" s="12"/>
-      <c r="AE736" s="12"/>
+      <c r="AC736" s="13"/>
+      <c r="AE736" s="13"/>
     </row>
     <row r="737">
-      <c r="AC737" s="12"/>
-      <c r="AE737" s="12"/>
+      <c r="AC737" s="13"/>
+      <c r="AE737" s="13"/>
     </row>
     <row r="738">
-      <c r="AC738" s="12"/>
-      <c r="AE738" s="12"/>
+      <c r="AC738" s="13"/>
+      <c r="AE738" s="13"/>
     </row>
     <row r="739">
-      <c r="AC739" s="12"/>
-      <c r="AE739" s="12"/>
+      <c r="AC739" s="13"/>
+      <c r="AE739" s="13"/>
     </row>
     <row r="740">
-      <c r="AC740" s="12"/>
-      <c r="AE740" s="12"/>
+      <c r="AC740" s="13"/>
+      <c r="AE740" s="13"/>
     </row>
     <row r="741">
-      <c r="AC741" s="12"/>
-      <c r="AE741" s="12"/>
+      <c r="AC741" s="13"/>
+      <c r="AE741" s="13"/>
     </row>
     <row r="742">
-      <c r="AC742" s="12"/>
-      <c r="AE742" s="12"/>
+      <c r="AC742" s="13"/>
+      <c r="AE742" s="13"/>
     </row>
     <row r="743">
-      <c r="AC743" s="12"/>
-      <c r="AE743" s="12"/>
+      <c r="AC743" s="13"/>
+      <c r="AE743" s="13"/>
     </row>
     <row r="744">
-      <c r="AC744" s="12"/>
-      <c r="AE744" s="12"/>
+      <c r="AC744" s="13"/>
+      <c r="AE744" s="13"/>
     </row>
     <row r="745">
-      <c r="AC745" s="12"/>
-      <c r="AE745" s="12"/>
+      <c r="AC745" s="13"/>
+      <c r="AE745" s="13"/>
     </row>
     <row r="746">
-      <c r="AC746" s="12"/>
-      <c r="AE746" s="12"/>
+      <c r="AC746" s="13"/>
+      <c r="AE746" s="13"/>
     </row>
     <row r="747">
-      <c r="AC747" s="12"/>
-      <c r="AE747" s="12"/>
+      <c r="AC747" s="13"/>
+      <c r="AE747" s="13"/>
     </row>
     <row r="748">
-      <c r="AC748" s="12"/>
-      <c r="AE748" s="12"/>
+      <c r="AC748" s="13"/>
+      <c r="AE748" s="13"/>
     </row>
     <row r="749">
-      <c r="AC749" s="12"/>
-      <c r="AE749" s="12"/>
+      <c r="AC749" s="13"/>
+      <c r="AE749" s="13"/>
     </row>
     <row r="750">
-      <c r="AC750" s="12"/>
-      <c r="AE750" s="12"/>
+      <c r="AC750" s="13"/>
+      <c r="AE750" s="13"/>
     </row>
     <row r="751">
-      <c r="AC751" s="12"/>
-      <c r="AE751" s="12"/>
+      <c r="AC751" s="13"/>
+      <c r="AE751" s="13"/>
     </row>
     <row r="752">
-      <c r="AC752" s="12"/>
-      <c r="AE752" s="12"/>
+      <c r="AC752" s="13"/>
+      <c r="AE752" s="13"/>
     </row>
     <row r="753">
-      <c r="AC753" s="12"/>
-      <c r="AE753" s="12"/>
+      <c r="AC753" s="13"/>
+      <c r="AE753" s="13"/>
     </row>
     <row r="754">
-      <c r="AC754" s="12"/>
-      <c r="AE754" s="12"/>
+      <c r="AC754" s="13"/>
+      <c r="AE754" s="13"/>
     </row>
     <row r="755">
-      <c r="AC755" s="12"/>
-      <c r="AE755" s="12"/>
+      <c r="AC755" s="13"/>
+      <c r="AE755" s="13"/>
     </row>
     <row r="756">
-      <c r="AC756" s="12"/>
-      <c r="AE756" s="12"/>
+      <c r="AC756" s="13"/>
+      <c r="AE756" s="13"/>
     </row>
     <row r="757">
-      <c r="AC757" s="12"/>
-      <c r="AE757" s="12"/>
+      <c r="AC757" s="13"/>
+      <c r="AE757" s="13"/>
     </row>
     <row r="758">
-      <c r="AC758" s="12"/>
-      <c r="AE758" s="12"/>
+      <c r="AC758" s="13"/>
+      <c r="AE758" s="13"/>
     </row>
     <row r="759">
-      <c r="AC759" s="12"/>
-      <c r="AE759" s="12"/>
+      <c r="AC759" s="13"/>
+      <c r="AE759" s="13"/>
     </row>
     <row r="760">
-      <c r="AC760" s="12"/>
-      <c r="AE760" s="12"/>
+      <c r="AC760" s="13"/>
+      <c r="AE760" s="13"/>
     </row>
     <row r="761">
-      <c r="AC761" s="12"/>
-      <c r="AE761" s="12"/>
+      <c r="AC761" s="13"/>
+      <c r="AE761" s="13"/>
     </row>
     <row r="762">
-      <c r="AC762" s="12"/>
-      <c r="AE762" s="12"/>
+      <c r="AC762" s="13"/>
+      <c r="AE762" s="13"/>
     </row>
     <row r="763">
-      <c r="AC763" s="12"/>
-      <c r="AE763" s="12"/>
+      <c r="AC763" s="13"/>
+      <c r="AE763" s="13"/>
     </row>
     <row r="764">
-      <c r="AC764" s="12"/>
-      <c r="AE764" s="12"/>
+      <c r="AC764" s="13"/>
+      <c r="AE764" s="13"/>
     </row>
     <row r="765">
-      <c r="AC765" s="12"/>
-      <c r="AE765" s="12"/>
+      <c r="AC765" s="13"/>
+      <c r="AE765" s="13"/>
     </row>
     <row r="766">
-      <c r="AC766" s="12"/>
-      <c r="AE766" s="12"/>
+      <c r="AC766" s="13"/>
+      <c r="AE766" s="13"/>
     </row>
     <row r="767">
-      <c r="AC767" s="12"/>
-      <c r="AE767" s="12"/>
+      <c r="AC767" s="13"/>
+      <c r="AE767" s="13"/>
     </row>
     <row r="768">
-      <c r="AC768" s="12"/>
-      <c r="AE768" s="12"/>
+      <c r="AC768" s="13"/>
+      <c r="AE768" s="13"/>
     </row>
     <row r="769">
-      <c r="AC769" s="12"/>
-      <c r="AE769" s="12"/>
+      <c r="AC769" s="13"/>
+      <c r="AE769" s="13"/>
     </row>
     <row r="770">
-      <c r="AC770" s="12"/>
-      <c r="AE770" s="12"/>
+      <c r="AC770" s="13"/>
+      <c r="AE770" s="13"/>
     </row>
     <row r="771">
-      <c r="AC771" s="12"/>
-      <c r="AE771" s="12"/>
+      <c r="AC771" s="13"/>
+      <c r="AE771" s="13"/>
     </row>
     <row r="772">
-      <c r="AC772" s="12"/>
-      <c r="AE772" s="12"/>
+      <c r="AC772" s="13"/>
+      <c r="AE772" s="13"/>
     </row>
     <row r="773">
-      <c r="AC773" s="12"/>
-      <c r="AE773" s="12"/>
+      <c r="AC773" s="13"/>
+      <c r="AE773" s="13"/>
     </row>
     <row r="774">
-      <c r="AC774" s="12"/>
-      <c r="AE774" s="12"/>
+      <c r="AC774" s="13"/>
+      <c r="AE774" s="13"/>
     </row>
     <row r="775">
-      <c r="AC775" s="12"/>
-      <c r="AE775" s="12"/>
+      <c r="AC775" s="13"/>
+      <c r="AE775" s="13"/>
     </row>
     <row r="776">
-      <c r="AC776" s="12"/>
-      <c r="AE776" s="12"/>
+      <c r="AC776" s="13"/>
+      <c r="AE776" s="13"/>
     </row>
     <row r="777">
-      <c r="AC777" s="12"/>
-      <c r="AE777" s="12"/>
+      <c r="AC777" s="13"/>
+      <c r="AE777" s="13"/>
     </row>
     <row r="778">
-      <c r="AC778" s="12"/>
-      <c r="AE778" s="12"/>
+      <c r="AC778" s="13"/>
+      <c r="AE778" s="13"/>
     </row>
     <row r="779">
-      <c r="AC779" s="12"/>
-      <c r="AE779" s="12"/>
+      <c r="AC779" s="13"/>
+      <c r="AE779" s="13"/>
     </row>
     <row r="780">
-      <c r="AC780" s="12"/>
-      <c r="AE780" s="12"/>
+      <c r="AC780" s="13"/>
+      <c r="AE780" s="13"/>
     </row>
     <row r="781">
-      <c r="AC781" s="12"/>
-      <c r="AE781" s="12"/>
+      <c r="AC781" s="13"/>
+      <c r="AE781" s="13"/>
     </row>
     <row r="782">
-      <c r="AC782" s="12"/>
-      <c r="AE782" s="12"/>
+      <c r="AC782" s="13"/>
+      <c r="AE782" s="13"/>
     </row>
     <row r="783">
-      <c r="AC783" s="12"/>
-      <c r="AE783" s="12"/>
+      <c r="AC783" s="13"/>
+      <c r="AE783" s="13"/>
     </row>
     <row r="784">
-      <c r="AC784" s="12"/>
-      <c r="AE784" s="12"/>
+      <c r="AC784" s="13"/>
+      <c r="AE784" s="13"/>
     </row>
     <row r="785">
-      <c r="AC785" s="12"/>
-      <c r="AE785" s="12"/>
+      <c r="AC785" s="13"/>
+      <c r="AE785" s="13"/>
     </row>
     <row r="786">
-      <c r="AC786" s="12"/>
-      <c r="AE786" s="12"/>
+      <c r="AC786" s="13"/>
+      <c r="AE786" s="13"/>
     </row>
     <row r="787">
-      <c r="AC787" s="12"/>
-      <c r="AE787" s="12"/>
+      <c r="AC787" s="13"/>
+      <c r="AE787" s="13"/>
     </row>
     <row r="788">
-      <c r="AC788" s="12"/>
-      <c r="AE788" s="12"/>
+      <c r="AC788" s="13"/>
+      <c r="AE788" s="13"/>
     </row>
     <row r="789">
-      <c r="AC789" s="12"/>
-      <c r="AE789" s="12"/>
+      <c r="AC789" s="13"/>
+      <c r="AE789" s="13"/>
     </row>
     <row r="790">
-      <c r="AC790" s="12"/>
-      <c r="AE790" s="12"/>
+      <c r="AC790" s="13"/>
+      <c r="AE790" s="13"/>
     </row>
     <row r="791">
-      <c r="AC791" s="12"/>
-      <c r="AE791" s="12"/>
+      <c r="AC791" s="13"/>
+      <c r="AE791" s="13"/>
     </row>
     <row r="792">
-      <c r="AC792" s="12"/>
-      <c r="AE792" s="12"/>
+      <c r="AC792" s="13"/>
+      <c r="AE792" s="13"/>
     </row>
     <row r="793">
-      <c r="AC793" s="12"/>
-      <c r="AE793" s="12"/>
+      <c r="AC793" s="13"/>
+      <c r="AE793" s="13"/>
     </row>
     <row r="794">
-      <c r="AC794" s="12"/>
-      <c r="AE794" s="12"/>
+      <c r="AC794" s="13"/>
+      <c r="AE794" s="13"/>
     </row>
     <row r="795">
-      <c r="AC795" s="12"/>
-      <c r="AE795" s="12"/>
+      <c r="AC795" s="13"/>
+      <c r="AE795" s="13"/>
     </row>
     <row r="796">
-      <c r="AC796" s="12"/>
-      <c r="AE796" s="12"/>
+      <c r="AC796" s="13"/>
+      <c r="AE796" s="13"/>
     </row>
     <row r="797">
-      <c r="AC797" s="12"/>
-      <c r="AE797" s="12"/>
+      <c r="AC797" s="13"/>
+      <c r="AE797" s="13"/>
     </row>
     <row r="798">
-      <c r="AC798" s="12"/>
-      <c r="AE798" s="12"/>
+      <c r="AC798" s="13"/>
+      <c r="AE798" s="13"/>
     </row>
     <row r="799">
-      <c r="AC799" s="12"/>
-      <c r="AE799" s="12"/>
+      <c r="AC799" s="13"/>
+      <c r="AE799" s="13"/>
     </row>
     <row r="800">
-      <c r="AC800" s="12"/>
-      <c r="AE800" s="12"/>
+      <c r="AC800" s="13"/>
+      <c r="AE800" s="13"/>
     </row>
     <row r="801">
-      <c r="AC801" s="12"/>
-      <c r="AE801" s="12"/>
+      <c r="AC801" s="13"/>
+      <c r="AE801" s="13"/>
     </row>
     <row r="802">
-      <c r="AC802" s="12"/>
-      <c r="AE802" s="12"/>
+      <c r="AC802" s="13"/>
+      <c r="AE802" s="13"/>
     </row>
     <row r="803">
-      <c r="AC803" s="12"/>
-      <c r="AE803" s="12"/>
+      <c r="AC803" s="13"/>
+      <c r="AE803" s="13"/>
     </row>
     <row r="804">
-      <c r="AC804" s="12"/>
-      <c r="AE804" s="12"/>
+      <c r="AC804" s="13"/>
+      <c r="AE804" s="13"/>
     </row>
     <row r="805">
-      <c r="AC805" s="12"/>
-      <c r="AE805" s="12"/>
+      <c r="AC805" s="13"/>
+      <c r="AE805" s="13"/>
     </row>
     <row r="806">
-      <c r="AC806" s="12"/>
-      <c r="AE806" s="12"/>
+      <c r="AC806" s="13"/>
+      <c r="AE806" s="13"/>
     </row>
     <row r="807">
-      <c r="AC807" s="12"/>
-      <c r="AE807" s="12"/>
+      <c r="AC807" s="13"/>
+      <c r="AE807" s="13"/>
     </row>
     <row r="808">
-      <c r="AC808" s="12"/>
-      <c r="AE808" s="12"/>
+      <c r="AC808" s="13"/>
+      <c r="AE808" s="13"/>
     </row>
     <row r="809">
-      <c r="AC809" s="12"/>
-      <c r="AE809" s="12"/>
+      <c r="AC809" s="13"/>
+      <c r="AE809" s="13"/>
     </row>
     <row r="810">
-      <c r="AC810" s="12"/>
-      <c r="AE810" s="12"/>
+      <c r="AC810" s="13"/>
+      <c r="AE810" s="13"/>
     </row>
     <row r="811">
-      <c r="AC811" s="12"/>
-      <c r="AE811" s="12"/>
+      <c r="AC811" s="13"/>
+      <c r="AE811" s="13"/>
     </row>
     <row r="812">
-      <c r="AC812" s="12"/>
-      <c r="AE812" s="12"/>
+      <c r="AC812" s="13"/>
+      <c r="AE812" s="13"/>
     </row>
     <row r="813">
-      <c r="AC813" s="12"/>
-      <c r="AE813" s="12"/>
+      <c r="AC813" s="13"/>
+      <c r="AE813" s="13"/>
     </row>
     <row r="814">
-      <c r="AC814" s="12"/>
-      <c r="AE814" s="12"/>
+      <c r="AC814" s="13"/>
+      <c r="AE814" s="13"/>
     </row>
     <row r="815">
-      <c r="AC815" s="12"/>
-      <c r="AE815" s="12"/>
+      <c r="AC815" s="13"/>
+      <c r="AE815" s="13"/>
     </row>
     <row r="816">
-      <c r="AC816" s="12"/>
-      <c r="AE816" s="12"/>
+      <c r="AC816" s="13"/>
+      <c r="AE816" s="13"/>
     </row>
     <row r="817">
-      <c r="AC817" s="12"/>
-      <c r="AE817" s="12"/>
+      <c r="AC817" s="13"/>
+      <c r="AE817" s="13"/>
     </row>
     <row r="818">
-      <c r="AC818" s="12"/>
-      <c r="AE818" s="12"/>
+      <c r="AC818" s="13"/>
+      <c r="AE818" s="13"/>
     </row>
     <row r="819">
-      <c r="AC819" s="12"/>
-      <c r="AE819" s="12"/>
+      <c r="AC819" s="13"/>
+      <c r="AE819" s="13"/>
     </row>
     <row r="820">
-      <c r="AC820" s="12"/>
-      <c r="AE820" s="12"/>
+      <c r="AC820" s="13"/>
+      <c r="AE820" s="13"/>
     </row>
     <row r="821">
-      <c r="AC821" s="12"/>
-      <c r="AE821" s="12"/>
+      <c r="AC821" s="13"/>
+      <c r="AE821" s="13"/>
     </row>
     <row r="822">
-      <c r="AC822" s="12"/>
-      <c r="AE822" s="12"/>
+      <c r="AC822" s="13"/>
+      <c r="AE822" s="13"/>
     </row>
     <row r="823">
-      <c r="AC823" s="12"/>
-      <c r="AE823" s="12"/>
+      <c r="AC823" s="13"/>
+      <c r="AE823" s="13"/>
     </row>
     <row r="824">
-      <c r="AC824" s="12"/>
-      <c r="AE824" s="12"/>
+      <c r="AC824" s="13"/>
+      <c r="AE824" s="13"/>
     </row>
     <row r="825">
-      <c r="AC825" s="12"/>
-      <c r="AE825" s="12"/>
+      <c r="AC825" s="13"/>
+      <c r="AE825" s="13"/>
     </row>
     <row r="826">
-      <c r="AC826" s="12"/>
-      <c r="AE826" s="12"/>
+      <c r="AC826" s="13"/>
+      <c r="AE826" s="13"/>
     </row>
     <row r="827">
-      <c r="AC827" s="12"/>
-      <c r="AE827" s="12"/>
+      <c r="AC827" s="13"/>
+      <c r="AE827" s="13"/>
     </row>
     <row r="828">
-      <c r="AC828" s="12"/>
-      <c r="AE828" s="12"/>
+      <c r="AC828" s="13"/>
+      <c r="AE828" s="13"/>
     </row>
     <row r="829">
-      <c r="AC829" s="12"/>
-      <c r="AE829" s="12"/>
+      <c r="AC829" s="13"/>
+      <c r="AE829" s="13"/>
     </row>
     <row r="830">
-      <c r="AC830" s="12"/>
-      <c r="AE830" s="12"/>
+      <c r="AC830" s="13"/>
+      <c r="AE830" s="13"/>
     </row>
     <row r="831">
-      <c r="AC831" s="12"/>
-      <c r="AE831" s="12"/>
+      <c r="AC831" s="13"/>
+      <c r="AE831" s="13"/>
     </row>
     <row r="832">
-      <c r="AC832" s="12"/>
-      <c r="AE832" s="12"/>
+      <c r="AC832" s="13"/>
+      <c r="AE832" s="13"/>
     </row>
     <row r="833">
-      <c r="AC833" s="12"/>
-      <c r="AE833" s="12"/>
+      <c r="AC833" s="13"/>
+      <c r="AE833" s="13"/>
     </row>
     <row r="834">
-      <c r="AC834" s="12"/>
-      <c r="AE834" s="12"/>
+      <c r="AC834" s="13"/>
+      <c r="AE834" s="13"/>
     </row>
     <row r="835">
-      <c r="AC835" s="12"/>
-      <c r="AE835" s="12"/>
+      <c r="AC835" s="13"/>
+      <c r="AE835" s="13"/>
     </row>
     <row r="836">
-      <c r="AC836" s="12"/>
-      <c r="AE836" s="12"/>
+      <c r="AC836" s="13"/>
+      <c r="AE836" s="13"/>
     </row>
     <row r="837">
-      <c r="AC837" s="12"/>
-      <c r="AE837" s="12"/>
+      <c r="AC837" s="13"/>
+      <c r="AE837" s="13"/>
     </row>
     <row r="838">
-      <c r="AC838" s="12"/>
-      <c r="AE838" s="12"/>
+      <c r="AC838" s="13"/>
+      <c r="AE838" s="13"/>
     </row>
     <row r="839">
-      <c r="AC839" s="12"/>
-      <c r="AE839" s="12"/>
+      <c r="AC839" s="13"/>
+      <c r="AE839" s="13"/>
     </row>
     <row r="840">
-      <c r="AC840" s="12"/>
-      <c r="AE840" s="12"/>
+      <c r="AC840" s="13"/>
+      <c r="AE840" s="13"/>
     </row>
     <row r="841">
-      <c r="AC841" s="12"/>
-      <c r="AE841" s="12"/>
+      <c r="AC841" s="13"/>
+      <c r="AE841" s="13"/>
     </row>
     <row r="842">
-      <c r="AC842" s="12"/>
-      <c r="AE842" s="12"/>
+      <c r="AC842" s="13"/>
+      <c r="AE842" s="13"/>
     </row>
     <row r="843">
-      <c r="AC843" s="12"/>
-      <c r="AE843" s="12"/>
+      <c r="AC843" s="13"/>
+      <c r="AE843" s="13"/>
     </row>
     <row r="844">
-      <c r="AC844" s="12"/>
-      <c r="AE844" s="12"/>
+      <c r="AC844" s="13"/>
+      <c r="AE844" s="13"/>
     </row>
     <row r="845">
-      <c r="AC845" s="12"/>
-      <c r="AE845" s="12"/>
+      <c r="AC845" s="13"/>
+      <c r="AE845" s="13"/>
     </row>
     <row r="846">
-      <c r="AC846" s="12"/>
-      <c r="AE846" s="12"/>
+      <c r="AC846" s="13"/>
+      <c r="AE846" s="13"/>
     </row>
     <row r="847">
-      <c r="AC847" s="12"/>
-      <c r="AE847" s="12"/>
+      <c r="AC847" s="13"/>
+      <c r="AE847" s="13"/>
     </row>
     <row r="848">
-      <c r="AC848" s="12"/>
-      <c r="AE848" s="12"/>
+      <c r="AC848" s="13"/>
+      <c r="AE848" s="13"/>
     </row>
     <row r="849">
-      <c r="AC849" s="12"/>
-      <c r="AE849" s="12"/>
+      <c r="AC849" s="13"/>
+      <c r="AE849" s="13"/>
     </row>
     <row r="850">
-      <c r="AC850" s="12"/>
-      <c r="AE850" s="12"/>
+      <c r="AC850" s="13"/>
+      <c r="AE850" s="13"/>
     </row>
     <row r="851">
-      <c r="AC851" s="12"/>
-      <c r="AE851" s="12"/>
+      <c r="AC851" s="13"/>
+      <c r="AE851" s="13"/>
     </row>
     <row r="852">
-      <c r="AC852" s="12"/>
-      <c r="AE852" s="12"/>
+      <c r="AC852" s="13"/>
+      <c r="AE852" s="13"/>
     </row>
     <row r="853">
-      <c r="AC853" s="12"/>
-      <c r="AE853" s="12"/>
+      <c r="AC853" s="13"/>
+      <c r="AE853" s="13"/>
     </row>
     <row r="854">
-      <c r="AC854" s="12"/>
-      <c r="AE854" s="12"/>
+      <c r="AC854" s="13"/>
+      <c r="AE854" s="13"/>
     </row>
     <row r="855">
-      <c r="AC855" s="12"/>
-      <c r="AE855" s="12"/>
+      <c r="AC855" s="13"/>
+      <c r="AE855" s="13"/>
     </row>
     <row r="856">
-      <c r="AC856" s="12"/>
-      <c r="AE856" s="12"/>
+      <c r="AC856" s="13"/>
+      <c r="AE856" s="13"/>
     </row>
     <row r="857">
-      <c r="AC857" s="12"/>
-      <c r="AE857" s="12"/>
+      <c r="AC857" s="13"/>
+      <c r="AE857" s="13"/>
     </row>
     <row r="858">
-      <c r="AC858" s="12"/>
-      <c r="AE858" s="12"/>
+      <c r="AC858" s="13"/>
+      <c r="AE858" s="13"/>
     </row>
     <row r="859">
-      <c r="AC859" s="12"/>
-      <c r="AE859" s="12"/>
+      <c r="AC859" s="13"/>
+      <c r="AE859" s="13"/>
     </row>
     <row r="860">
-      <c r="AC860" s="12"/>
-      <c r="AE860" s="12"/>
+      <c r="AC860" s="13"/>
+      <c r="AE860" s="13"/>
     </row>
     <row r="861">
-      <c r="AC861" s="12"/>
-      <c r="AE861" s="12"/>
+      <c r="AC861" s="13"/>
+      <c r="AE861" s="13"/>
     </row>
     <row r="862">
-      <c r="AC862" s="12"/>
-      <c r="AE862" s="12"/>
+      <c r="AC862" s="13"/>
+      <c r="AE862" s="13"/>
     </row>
     <row r="863">
-      <c r="AC863" s="12"/>
-      <c r="AE863" s="12"/>
+      <c r="AC863" s="13"/>
+      <c r="AE863" s="13"/>
     </row>
     <row r="864">
-      <c r="AC864" s="12"/>
-      <c r="AE864" s="12"/>
+      <c r="AC864" s="13"/>
+      <c r="AE864" s="13"/>
     </row>
     <row r="865">
-      <c r="AC865" s="12"/>
-      <c r="AE865" s="12"/>
+      <c r="AC865" s="13"/>
+      <c r="AE865" s="13"/>
     </row>
     <row r="866">
-      <c r="AC866" s="12"/>
-      <c r="AE866" s="12"/>
+      <c r="AC866" s="13"/>
+      <c r="AE866" s="13"/>
     </row>
     <row r="867">
-      <c r="AC867" s="12"/>
-      <c r="AE867" s="12"/>
+      <c r="AC867" s="13"/>
+      <c r="AE867" s="13"/>
     </row>
     <row r="868">
-      <c r="AC868" s="12"/>
-      <c r="AE868" s="12"/>
+      <c r="AC868" s="13"/>
+      <c r="AE868" s="13"/>
     </row>
     <row r="869">
-      <c r="AC869" s="12"/>
-      <c r="AE869" s="12"/>
+      <c r="AC869" s="13"/>
+      <c r="AE869" s="13"/>
     </row>
     <row r="870">
-      <c r="AC870" s="12"/>
-      <c r="AE870" s="12"/>
+      <c r="AC870" s="13"/>
+      <c r="AE870" s="13"/>
     </row>
     <row r="871">
-      <c r="AC871" s="12"/>
-      <c r="AE871" s="12"/>
+      <c r="AC871" s="13"/>
+      <c r="AE871" s="13"/>
     </row>
     <row r="872">
-      <c r="AC872" s="12"/>
-      <c r="AE872" s="12"/>
+      <c r="AC872" s="13"/>
+      <c r="AE872" s="13"/>
     </row>
     <row r="873">
-      <c r="AC873" s="12"/>
-      <c r="AE873" s="12"/>
+      <c r="AC873" s="13"/>
+      <c r="AE873" s="13"/>
     </row>
     <row r="874">
-      <c r="AC874" s="12"/>
-      <c r="AE874" s="12"/>
+      <c r="AC874" s="13"/>
+      <c r="AE874" s="13"/>
     </row>
     <row r="875">
-      <c r="AC875" s="12"/>
-      <c r="AE875" s="12"/>
+      <c r="AC875" s="13"/>
+      <c r="AE875" s="13"/>
     </row>
     <row r="876">
-      <c r="AC876" s="12"/>
-      <c r="AE876" s="12"/>
+      <c r="AC876" s="13"/>
+      <c r="AE876" s="13"/>
     </row>
     <row r="877">
-      <c r="AC877" s="12"/>
-      <c r="AE877" s="12"/>
+      <c r="AC877" s="13"/>
+      <c r="AE877" s="13"/>
     </row>
     <row r="878">
-      <c r="AC878" s="12"/>
-      <c r="AE878" s="12"/>
+      <c r="AC878" s="13"/>
+      <c r="AE878" s="13"/>
     </row>
     <row r="879">
-      <c r="AC879" s="12"/>
-      <c r="AE879" s="12"/>
+      <c r="AC879" s="13"/>
+      <c r="AE879" s="13"/>
     </row>
     <row r="880">
-      <c r="AC880" s="12"/>
-      <c r="AE880" s="12"/>
+      <c r="AC880" s="13"/>
+      <c r="AE880" s="13"/>
     </row>
     <row r="881">
-      <c r="AC881" s="12"/>
-      <c r="AE881" s="12"/>
+      <c r="AC881" s="13"/>
+      <c r="AE881" s="13"/>
     </row>
     <row r="882">
-      <c r="AC882" s="12"/>
-      <c r="AE882" s="12"/>
+      <c r="AC882" s="13"/>
+      <c r="AE882" s="13"/>
     </row>
     <row r="883">
-      <c r="AC883" s="12"/>
-      <c r="AE883" s="12"/>
+      <c r="AC883" s="13"/>
+      <c r="AE883" s="13"/>
     </row>
     <row r="884">
-      <c r="AC884" s="12"/>
-      <c r="AE884" s="12"/>
+      <c r="AC884" s="13"/>
+      <c r="AE884" s="13"/>
     </row>
     <row r="885">
-      <c r="AC885" s="12"/>
-      <c r="AE885" s="12"/>
+      <c r="AC885" s="13"/>
+      <c r="AE885" s="13"/>
     </row>
     <row r="886">
-      <c r="AC886" s="12"/>
-      <c r="AE886" s="12"/>
+      <c r="AC886" s="13"/>
+      <c r="AE886" s="13"/>
     </row>
     <row r="887">
-      <c r="AC887" s="12"/>
-      <c r="AE887" s="12"/>
+      <c r="AC887" s="13"/>
+      <c r="AE887" s="13"/>
     </row>
     <row r="888">
-      <c r="AC888" s="12"/>
-      <c r="AE888" s="12"/>
+      <c r="AC888" s="13"/>
+      <c r="AE888" s="13"/>
     </row>
     <row r="889">
-      <c r="AC889" s="12"/>
-      <c r="AE889" s="12"/>
+      <c r="AC889" s="13"/>
+      <c r="AE889" s="13"/>
     </row>
     <row r="890">
-      <c r="AC890" s="12"/>
-      <c r="AE890" s="12"/>
+      <c r="AC890" s="13"/>
+      <c r="AE890" s="13"/>
     </row>
     <row r="891">
-      <c r="AC891" s="12"/>
-      <c r="AE891" s="12"/>
+      <c r="AC891" s="13"/>
+      <c r="AE891" s="13"/>
     </row>
     <row r="892">
-      <c r="AC892" s="12"/>
-      <c r="AE892" s="12"/>
+      <c r="AC892" s="13"/>
+      <c r="AE892" s="13"/>
     </row>
     <row r="893">
-      <c r="AC893" s="12"/>
-      <c r="AE893" s="12"/>
+      <c r="AC893" s="13"/>
+      <c r="AE893" s="13"/>
     </row>
     <row r="894">
-      <c r="AC894" s="12"/>
-      <c r="AE894" s="12"/>
+      <c r="AC894" s="13"/>
+      <c r="AE894" s="13"/>
     </row>
     <row r="895">
-      <c r="AC895" s="12"/>
-      <c r="AE895" s="12"/>
+      <c r="AC895" s="13"/>
+      <c r="AE895" s="13"/>
     </row>
     <row r="896">
-      <c r="AC896" s="12"/>
-      <c r="AE896" s="12"/>
+      <c r="AC896" s="13"/>
+      <c r="AE896" s="13"/>
     </row>
     <row r="897">
-      <c r="AC897" s="12"/>
-      <c r="AE897" s="12"/>
+      <c r="AC897" s="13"/>
+      <c r="AE897" s="13"/>
     </row>
     <row r="898">
-      <c r="AC898" s="12"/>
-      <c r="AE898" s="12"/>
+      <c r="AC898" s="13"/>
+      <c r="AE898" s="13"/>
     </row>
     <row r="899">
-      <c r="AC899" s="12"/>
-      <c r="AE899" s="12"/>
+      <c r="AC899" s="13"/>
+      <c r="AE899" s="13"/>
     </row>
     <row r="900">
-      <c r="AC900" s="12"/>
-      <c r="AE900" s="12"/>
+      <c r="AC900" s="13"/>
+      <c r="AE900" s="13"/>
     </row>
     <row r="901">
-      <c r="AC901" s="12"/>
-      <c r="AE901" s="12"/>
+      <c r="AC901" s="13"/>
+      <c r="AE901" s="13"/>
     </row>
     <row r="902">
-      <c r="AC902" s="12"/>
-      <c r="AE902" s="12"/>
+      <c r="AC902" s="13"/>
+      <c r="AE902" s="13"/>
     </row>
     <row r="903">
-      <c r="AC903" s="12"/>
-      <c r="AE903" s="12"/>
+      <c r="AC903" s="13"/>
+      <c r="AE903" s="13"/>
     </row>
     <row r="904">
-      <c r="AC904" s="12"/>
-      <c r="AE904" s="12"/>
+      <c r="AC904" s="13"/>
+      <c r="AE904" s="13"/>
     </row>
     <row r="905">
-      <c r="AC905" s="12"/>
-      <c r="AE905" s="12"/>
+      <c r="AC905" s="13"/>
+      <c r="AE905" s="13"/>
     </row>
     <row r="906">
-      <c r="AC906" s="12"/>
-      <c r="AE906" s="12"/>
+      <c r="AC906" s="13"/>
+      <c r="AE906" s="13"/>
     </row>
     <row r="907">
-      <c r="AC907" s="12"/>
-      <c r="AE907" s="12"/>
+      <c r="AC907" s="13"/>
+      <c r="AE907" s="13"/>
     </row>
     <row r="908">
-      <c r="AC908" s="12"/>
-      <c r="AE908" s="12"/>
+      <c r="AC908" s="13"/>
+      <c r="AE908" s="13"/>
     </row>
     <row r="909">
-      <c r="AC909" s="12"/>
-      <c r="AE909" s="12"/>
+      <c r="AC909" s="13"/>
+      <c r="AE909" s="13"/>
     </row>
     <row r="910">
-      <c r="AC910" s="12"/>
-      <c r="AE910" s="12"/>
+      <c r="AC910" s="13"/>
+      <c r="AE910" s="13"/>
     </row>
     <row r="911">
-      <c r="AC911" s="12"/>
-      <c r="AE911" s="12"/>
+      <c r="AC911" s="13"/>
+      <c r="AE911" s="13"/>
     </row>
     <row r="912">
-      <c r="AC912" s="12"/>
-      <c r="AE912" s="12"/>
+      <c r="AC912" s="13"/>
+      <c r="AE912" s="13"/>
     </row>
     <row r="913">
-      <c r="AC913" s="12"/>
-      <c r="AE913" s="12"/>
+      <c r="AC913" s="13"/>
+      <c r="AE913" s="13"/>
     </row>
     <row r="914">
-      <c r="AC914" s="12"/>
-      <c r="AE914" s="12"/>
+      <c r="AC914" s="13"/>
+      <c r="AE914" s="13"/>
     </row>
     <row r="915">
-      <c r="AC915" s="12"/>
-      <c r="AE915" s="12"/>
+      <c r="AC915" s="13"/>
+      <c r="AE915" s="13"/>
     </row>
     <row r="916">
-      <c r="AC916" s="12"/>
-      <c r="AE916" s="12"/>
+      <c r="AC916" s="13"/>
+      <c r="AE916" s="13"/>
     </row>
     <row r="917">
-      <c r="AC917" s="12"/>
-      <c r="AE917" s="12"/>
+      <c r="AC917" s="13"/>
+      <c r="AE917" s="13"/>
     </row>
     <row r="918">
-      <c r="AC918" s="12"/>
-      <c r="AE918" s="12"/>
+      <c r="AC918" s="13"/>
+      <c r="AE918" s="13"/>
     </row>
     <row r="919">
-      <c r="AC919" s="12"/>
-      <c r="AE919" s="12"/>
+      <c r="AC919" s="13"/>
+      <c r="AE919" s="13"/>
     </row>
     <row r="920">
-      <c r="AC920" s="12"/>
-      <c r="AE920" s="12"/>
+      <c r="AC920" s="13"/>
+      <c r="AE920" s="13"/>
     </row>
     <row r="921">
-      <c r="AC921" s="12"/>
-      <c r="AE921" s="12"/>
+      <c r="AC921" s="13"/>
+      <c r="AE921" s="13"/>
     </row>
     <row r="922">
-      <c r="AC922" s="12"/>
-      <c r="AE922" s="12"/>
+      <c r="AC922" s="13"/>
+      <c r="AE922" s="13"/>
     </row>
     <row r="923">
-      <c r="AC923" s="12"/>
-      <c r="AE923" s="12"/>
+      <c r="AC923" s="13"/>
+      <c r="AE923" s="13"/>
     </row>
     <row r="924">
-      <c r="AC924" s="12"/>
-      <c r="AE924" s="12"/>
+      <c r="AC924" s="13"/>
+      <c r="AE924" s="13"/>
     </row>
     <row r="925">
-      <c r="AC925" s="12"/>
-      <c r="AE925" s="12"/>
+      <c r="AC925" s="13"/>
+      <c r="AE925" s="13"/>
     </row>
     <row r="926">
-      <c r="AC926" s="12"/>
-      <c r="AE926" s="12"/>
+      <c r="AC926" s="13"/>
+      <c r="AE926" s="13"/>
     </row>
     <row r="927">
-      <c r="AC927" s="12"/>
-      <c r="AE927" s="12"/>
+      <c r="AC927" s="13"/>
+      <c r="AE927" s="13"/>
     </row>
     <row r="928">
-      <c r="AC928" s="12"/>
-      <c r="AE928" s="12"/>
+      <c r="AC928" s="13"/>
+      <c r="AE928" s="13"/>
     </row>
     <row r="929">
-      <c r="AC929" s="12"/>
-      <c r="AE929" s="12"/>
+      <c r="AC929" s="13"/>
+      <c r="AE929" s="13"/>
     </row>
     <row r="930">
-      <c r="AC930" s="12"/>
-      <c r="AE930" s="12"/>
+      <c r="AC930" s="13"/>
+      <c r="AE930" s="13"/>
     </row>
     <row r="931">
-      <c r="AC931" s="12"/>
-      <c r="AE931" s="12"/>
+      <c r="AC931" s="13"/>
+      <c r="AE931" s="13"/>
     </row>
     <row r="932">
-      <c r="AC932" s="12"/>
-      <c r="AE932" s="12"/>
+      <c r="AC932" s="13"/>
+      <c r="AE932" s="13"/>
     </row>
     <row r="933">
-      <c r="AC933" s="12"/>
-      <c r="AE933" s="12"/>
+      <c r="AC933" s="13"/>
+      <c r="AE933" s="13"/>
     </row>
     <row r="934">
-      <c r="AC934" s="12"/>
-      <c r="AE934" s="12"/>
+      <c r="AC934" s="13"/>
+      <c r="AE934" s="13"/>
     </row>
     <row r="935">
-      <c r="AC935" s="12"/>
-      <c r="AE935" s="12"/>
+      <c r="AC935" s="13"/>
+      <c r="AE935" s="13"/>
     </row>
     <row r="936">
-      <c r="AC936" s="12"/>
-      <c r="AE936" s="12"/>
+      <c r="AC936" s="13"/>
+      <c r="AE936" s="13"/>
     </row>
     <row r="937">
-      <c r="AC937" s="12"/>
-      <c r="AE937" s="12"/>
+      <c r="AC937" s="13"/>
+      <c r="AE937" s="13"/>
     </row>
     <row r="938">
-      <c r="AC938" s="12"/>
-      <c r="AE938" s="12"/>
+      <c r="AC938" s="13"/>
+      <c r="AE938" s="13"/>
     </row>
     <row r="939">
-      <c r="AC939" s="12"/>
-      <c r="AE939" s="12"/>
+      <c r="AC939" s="13"/>
+      <c r="AE939" s="13"/>
     </row>
     <row r="940">
-      <c r="AC940" s="12"/>
-      <c r="AE940" s="12"/>
+      <c r="AC940" s="13"/>
+      <c r="AE940" s="13"/>
     </row>
     <row r="941">
-      <c r="AC941" s="12"/>
-      <c r="AE941" s="12"/>
+      <c r="AC941" s="13"/>
+      <c r="AE941" s="13"/>
     </row>
     <row r="942">
-      <c r="AC942" s="12"/>
-      <c r="AE942" s="12"/>
+      <c r="AC942" s="13"/>
+      <c r="AE942" s="13"/>
     </row>
     <row r="943">
-      <c r="AC943" s="12"/>
-      <c r="AE943" s="12"/>
+      <c r="AC943" s="13"/>
+      <c r="AE943" s="13"/>
     </row>
     <row r="944">
-      <c r="AC944" s="12"/>
-      <c r="AE944" s="12"/>
+      <c r="AC944" s="13"/>
+      <c r="AE944" s="13"/>
     </row>
     <row r="945">
-      <c r="AC945" s="12"/>
-      <c r="AE945" s="12"/>
+      <c r="AC945" s="13"/>
+      <c r="AE945" s="13"/>
     </row>
     <row r="946">
-      <c r="AC946" s="12"/>
-      <c r="AE946" s="12"/>
+      <c r="AC946" s="13"/>
+      <c r="AE946" s="13"/>
     </row>
     <row r="947">
-      <c r="AC947" s="12"/>
-      <c r="AE947" s="12"/>
+      <c r="AC947" s="13"/>
+      <c r="AE947" s="13"/>
     </row>
     <row r="948">
-      <c r="AC948" s="12"/>
-      <c r="AE948" s="12"/>
+      <c r="AC948" s="13"/>
+      <c r="AE948" s="13"/>
     </row>
     <row r="949">
-      <c r="AC949" s="12"/>
-      <c r="AE949" s="12"/>
+      <c r="AC949" s="13"/>
+      <c r="AE949" s="13"/>
     </row>
     <row r="950">
-      <c r="AC950" s="12"/>
-      <c r="AE950" s="12"/>
+      <c r="AC950" s="13"/>
+      <c r="AE950" s="13"/>
     </row>
     <row r="951">
-      <c r="AC951" s="12"/>
-      <c r="AE951" s="12"/>
+      <c r="AC951" s="13"/>
+      <c r="AE951" s="13"/>
     </row>
     <row r="952">
-      <c r="AC952" s="12"/>
-      <c r="AE952" s="12"/>
+      <c r="AC952" s="13"/>
+      <c r="AE952" s="13"/>
     </row>
     <row r="953">
-      <c r="AC953" s="12"/>
-      <c r="AE953" s="12"/>
+      <c r="AC953" s="13"/>
+      <c r="AE953" s="13"/>
     </row>
     <row r="954">
-      <c r="AC954" s="12"/>
-      <c r="AE954" s="12"/>
+      <c r="AC954" s="13"/>
+      <c r="AE954" s="13"/>
     </row>
     <row r="955">
-      <c r="AC955" s="12"/>
-      <c r="AE955" s="12"/>
+      <c r="AC955" s="13"/>
+      <c r="AE955" s="13"/>
     </row>
     <row r="956">
-      <c r="AC956" s="12"/>
-      <c r="AE956" s="12"/>
+      <c r="AC956" s="13"/>
+      <c r="AE956" s="13"/>
     </row>
     <row r="957">
-      <c r="AC957" s="12"/>
-      <c r="AE957" s="12"/>
+      <c r="AC957" s="13"/>
+      <c r="AE957" s="13"/>
     </row>
     <row r="958">
-      <c r="AC958" s="12"/>
-      <c r="AE958" s="12"/>
+      <c r="AC958" s="13"/>
+      <c r="AE958" s="13"/>
     </row>
     <row r="959">
-      <c r="AC959" s="12"/>
-      <c r="AE959" s="12"/>
+      <c r="AC959" s="13"/>
+      <c r="AE959" s="13"/>
     </row>
     <row r="960">
-      <c r="AC960" s="12"/>
-      <c r="AE960" s="12"/>
+      <c r="AC960" s="13"/>
+      <c r="AE960" s="13"/>
     </row>
     <row r="961">
-      <c r="AC961" s="12"/>
-      <c r="AE961" s="12"/>
+      <c r="AC961" s="13"/>
+      <c r="AE961" s="13"/>
     </row>
     <row r="962">
-      <c r="AC962" s="12"/>
-      <c r="AE962" s="12"/>
+      <c r="AC962" s="13"/>
+      <c r="AE962" s="13"/>
     </row>
     <row r="963">
-      <c r="AC963" s="12"/>
-      <c r="AE963" s="12"/>
+      <c r="AC963" s="13"/>
+      <c r="AE963" s="13"/>
     </row>
     <row r="964">
-      <c r="AC964" s="12"/>
-      <c r="AE964" s="12"/>
+      <c r="AC964" s="13"/>
+      <c r="AE964" s="13"/>
     </row>
     <row r="965">
-      <c r="AC965" s="12"/>
-      <c r="AE965" s="12"/>
+      <c r="AC965" s="13"/>
+      <c r="AE965" s="13"/>
     </row>
     <row r="966">
-      <c r="AC966" s="12"/>
-      <c r="AE966" s="12"/>
+      <c r="AC966" s="13"/>
+      <c r="AE966" s="13"/>
     </row>
     <row r="967">
-      <c r="AC967" s="12"/>
-      <c r="AE967" s="12"/>
+      <c r="AC967" s="13"/>
+      <c r="AE967" s="13"/>
     </row>
     <row r="968">
-      <c r="AC968" s="12"/>
-      <c r="AE968" s="12"/>
+      <c r="AC968" s="13"/>
+      <c r="AE968" s="13"/>
     </row>
     <row r="969">
-      <c r="AC969" s="12"/>
-      <c r="AE969" s="12"/>
+      <c r="AC969" s="13"/>
+      <c r="AE969" s="13"/>
     </row>
     <row r="970">
-      <c r="AC970" s="12"/>
-      <c r="AE970" s="12"/>
+      <c r="AC970" s="13"/>
+      <c r="AE970" s="13"/>
     </row>
     <row r="971">
-      <c r="AC971" s="12"/>
-      <c r="AE971" s="12"/>
+      <c r="AC971" s="13"/>
+      <c r="AE971" s="13"/>
     </row>
     <row r="972">
-      <c r="AC972" s="12"/>
-      <c r="AE972" s="12"/>
+      <c r="AC972" s="13"/>
+      <c r="AE972" s="13"/>
     </row>
     <row r="973">
-      <c r="AC973" s="12"/>
-      <c r="AE973" s="12"/>
+      <c r="AC973" s="13"/>
+      <c r="AE973" s="13"/>
     </row>
     <row r="974">
-      <c r="AC974" s="12"/>
-      <c r="AE974" s="12"/>
+      <c r="AC974" s="13"/>
+      <c r="AE974" s="13"/>
     </row>
     <row r="975">
-      <c r="AC975" s="12"/>
-      <c r="AE975" s="12"/>
+      <c r="AC975" s="13"/>
+      <c r="AE975" s="13"/>
     </row>
     <row r="976">
-      <c r="AC976" s="12"/>
-      <c r="AE976" s="12"/>
+      <c r="AC976" s="13"/>
+      <c r="AE976" s="13"/>
     </row>
     <row r="977">
-      <c r="AC977" s="12"/>
-      <c r="AE977" s="12"/>
+      <c r="AC977" s="13"/>
+      <c r="AE977" s="13"/>
     </row>
     <row r="978">
-      <c r="AC978" s="12"/>
-      <c r="AE978" s="12"/>
+      <c r="AC978" s="13"/>
+      <c r="AE978" s="13"/>
     </row>
     <row r="979">
-      <c r="AC979" s="12"/>
-      <c r="AE979" s="12"/>
+      <c r="AC979" s="13"/>
+      <c r="AE979" s="13"/>
     </row>
     <row r="980">
-      <c r="AC980" s="12"/>
-      <c r="AE980" s="12"/>
+      <c r="AC980" s="13"/>
+      <c r="AE980" s="13"/>
     </row>
     <row r="981">
-      <c r="AC981" s="12"/>
-      <c r="AE981" s="12"/>
+      <c r="AC981" s="13"/>
+      <c r="AE981" s="13"/>
     </row>
     <row r="982">
-      <c r="AC982" s="12"/>
-      <c r="AE982" s="12"/>
+      <c r="AC982" s="13"/>
+      <c r="AE982" s="13"/>
     </row>
     <row r="983">
-      <c r="AC983" s="12"/>
-      <c r="AE983" s="12"/>
+      <c r="AC983" s="13"/>
+      <c r="AE983" s="13"/>
     </row>
     <row r="984">
-      <c r="AC984" s="12"/>
-      <c r="AE984" s="12"/>
+      <c r="AC984" s="13"/>
+      <c r="AE984" s="13"/>
     </row>
     <row r="985">
-      <c r="AC985" s="12"/>
-      <c r="AE985" s="12"/>
+      <c r="AC985" s="13"/>
+      <c r="AE985" s="13"/>
     </row>
     <row r="986">
-      <c r="AC986" s="12"/>
-      <c r="AE986" s="12"/>
+      <c r="AC986" s="13"/>
+      <c r="AE986" s="13"/>
     </row>
     <row r="987">
-      <c r="AC987" s="12"/>
-      <c r="AE987" s="12"/>
+      <c r="AC987" s="13"/>
+      <c r="AE987" s="13"/>
     </row>
     <row r="988">
-      <c r="AC988" s="12"/>
-      <c r="AE988" s="12"/>
+      <c r="AC988" s="13"/>
+      <c r="AE988" s="13"/>
     </row>
     <row r="989">
-      <c r="AC989" s="12"/>
-      <c r="AE989" s="12"/>
+      <c r="AC989" s="13"/>
+      <c r="AE989" s="13"/>
     </row>
     <row r="990">
-      <c r="AC990" s="12"/>
-      <c r="AE990" s="12"/>
+      <c r="AC990" s="13"/>
+      <c r="AE990" s="13"/>
     </row>
     <row r="991">
-      <c r="AC991" s="12"/>
-      <c r="AE991" s="12"/>
+      <c r="AC991" s="13"/>
+      <c r="AE991" s="13"/>
     </row>
     <row r="992">
-      <c r="AC992" s="12"/>
-      <c r="AE992" s="12"/>
+      <c r="AC992" s="13"/>
+      <c r="AE992" s="13"/>
     </row>
     <row r="993">
-      <c r="AC993" s="12"/>
-      <c r="AE993" s="12"/>
+      <c r="AC993" s="13"/>
+      <c r="AE993" s="13"/>
     </row>
     <row r="994">
-      <c r="AC994" s="12"/>
-      <c r="AE994" s="12"/>
+      <c r="AC994" s="13"/>
+      <c r="AE994" s="13"/>
     </row>
     <row r="995">
-      <c r="AC995" s="12"/>
-      <c r="AE995" s="12"/>
+      <c r="AC995" s="13"/>
+      <c r="AE995" s="13"/>
     </row>
     <row r="996">
-      <c r="AC996" s="12"/>
-      <c r="AE996" s="12"/>
+      <c r="AC996" s="13"/>
+      <c r="AE996" s="13"/>
     </row>
     <row r="997">
-      <c r="AC997" s="12"/>
-      <c r="AE997" s="12"/>
+      <c r="AC997" s="13"/>
+      <c r="AE997" s="13"/>
     </row>
     <row r="998">
-      <c r="AC998" s="12"/>
-      <c r="AE998" s="12"/>
+      <c r="AC998" s="13"/>
+      <c r="AE998" s="13"/>
     </row>
     <row r="999">
-      <c r="AC999" s="12"/>
-      <c r="AE999" s="12"/>
+      <c r="AC999" s="13"/>
+      <c r="AE999" s="13"/>
     </row>
     <row r="1000">
-      <c r="AC1000" s="12"/>
-      <c r="AE1000" s="12"/>
+      <c r="AC1000" s="13"/>
+      <c r="AE1000" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
